--- a/Översikt FINSPÅNG.xlsx
+++ b/Översikt FINSPÅNG.xlsx
@@ -601,7 +601,7 @@
         <v>46244</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -727,7 +727,7 @@
         <v>45945</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -858,7 +858,7 @@
         <v>45134</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
         <v>44896</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1121,7 +1121,7 @@
         <v>44888</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>45210</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1369,7 +1369,7 @@
         <v>44777</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1488,7 +1488,7 @@
         <v>44897</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1607,7 +1607,7 @@
         <v>44910</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1734,7 +1734,7 @@
         <v>45322</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1855,7 +1855,7 @@
         <v>44624</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1971,7 +1971,7 @@
         <v>44599</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2082,7 +2082,7 @@
         <v>45238</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2197,7 +2197,7 @@
         <v>45421</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2317,7 +2317,7 @@
         <v>45891</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2433,7 +2433,7 @@
         <v>45898</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2548,7 +2548,7 @@
         <v>45267</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2663,7 +2663,7 @@
         <v>45679</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2782,7 +2782,7 @@
         <v>44791</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2896,7 +2896,7 @@
         <v>45947</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3010,7 +3010,7 @@
         <v>45812</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3124,7 +3124,7 @@
         <v>44665</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3237,7 +3237,7 @@
         <v>45681</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3354,7 +3354,7 @@
         <v>45082</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3466,7 +3466,7 @@
         <v>45819</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3582,7 +3582,7 @@
         <v>44774</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3694,7 +3694,7 @@
         <v>45602</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3806,7 +3806,7 @@
         <v>46196</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3918,7 +3918,7 @@
         <v>45800</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4030,7 +4030,7 @@
         <v>44690</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4141,7 +4141,7 @@
         <v>45441</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4252,7 +4252,7 @@
         <v>44816</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4358,7 +4358,7 @@
         <v>45477</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4473,7 +4473,7 @@
         <v>45894</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4588,7 +4588,7 @@
         <v>45905</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4699,7 +4699,7 @@
         <v>45644</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4805,7 +4805,7 @@
         <v>45950</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4916,7 +4916,7 @@
         <v>44981</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5027,7 +5027,7 @@
         <v>46174</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5138,7 +5138,7 @@
         <v>45425</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5244,7 +5244,7 @@
         <v>46181</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5355,7 +5355,7 @@
         <v>46181</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5466,7 +5466,7 @@
         <v>45235</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5577,7 +5577,7 @@
         <v>45121</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5692,7 +5692,7 @@
         <v>44903</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5802,7 +5802,7 @@
         <v>44480</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5913,7 +5913,7 @@
         <v>44683</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6023,7 +6023,7 @@
         <v>44776</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6128,7 +6128,7 @@
         <v>44504</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6238,7 +6238,7 @@
         <v>44529</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6343,7 +6343,7 @@
         <v>45567</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6457,7 +6457,7 @@
         <v>45082</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6567,7 +6567,7 @@
         <v>45149</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6676,7 +6676,7 @@
         <v>44501</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6786,7 +6786,7 @@
         <v>45229</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6896,7 +6896,7 @@
         <v>44897</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7010,7 +7010,7 @@
         <v>45744</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7124,7 +7124,7 @@
         <v>45636</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7229,7 +7229,7 @@
         <v>45328</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7338,7 +7338,7 @@
         <v>44599</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7448,7 +7448,7 @@
         <v>45447</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7558,7 +7558,7 @@
         <v>45555</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7672,7 +7672,7 @@
         <v>46043</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7786,7 +7786,7 @@
         <v>45905</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7896,7 +7896,7 @@
         <v>45446</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8001,7 +8001,7 @@
         <v>45883</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8111,7 +8111,7 @@
         <v>44965</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8225,7 +8225,7 @@
         <v>45566</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8339,7 +8339,7 @@
         <v>44930</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8449,7 +8449,7 @@
         <v>46155</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8563,7 +8563,7 @@
         <v>44915</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8673,7 +8673,7 @@
         <v>45302</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8782,7 +8782,7 @@
         <v>45232</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8892,7 +8892,7 @@
         <v>44622</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8997,7 +8997,7 @@
         <v>44817</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9107,7 +9107,7 @@
         <v>46058</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9221,7 +9221,7 @@
         <v>46189</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9326,7 +9326,7 @@
         <v>44915</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9436,7 +9436,7 @@
         <v>46129</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9550,7 +9550,7 @@
         <v>45070</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9660,7 +9660,7 @@
         <v>46258</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9774,7 +9774,7 @@
         <v>46258</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9884,7 +9884,7 @@
         <v>44992</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9994,7 +9994,7 @@
         <v>45615</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10108,7 +10108,7 @@
         <v>46181</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10218,7 +10218,7 @@
         <v>45817</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10328,7 +10328,7 @@
         <v>45845</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10438,7 +10438,7 @@
         <v>45846</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10548,7 +10548,7 @@
         <v>45880</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10658,7 +10658,7 @@
         <v>44711</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10768,7 +10768,7 @@
         <v>45428</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10873,7 +10873,7 @@
         <v>46107</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10983,7 +10983,7 @@
         <v>46188</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11097,7 +11097,7 @@
         <v>44755</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11175,7 +11175,7 @@
         <v>44675</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11248,7 +11248,7 @@
         <v>44676</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11326,7 +11326,7 @@
         <v>44536</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11404,7 +11404,7 @@
         <v>44864</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11477,7 +11477,7 @@
         <v>44600</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11550,7 +11550,7 @@
         <v>44824</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11623,7 +11623,7 @@
         <v>44799</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11696,7 +11696,7 @@
         <v>44795</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11769,7 +11769,7 @@
         <v>44856</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11842,7 +11842,7 @@
         <v>44578</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -11920,7 +11920,7 @@
         <v>44675</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -11993,7 +11993,7 @@
         <v>44601</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12071,7 +12071,7 @@
         <v>44601</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12144,7 +12144,7 @@
         <v>44852</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12222,7 +12222,7 @@
         <v>44551</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12295,7 +12295,7 @@
         <v>44525</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12368,7 +12368,7 @@
         <v>44574</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12446,7 +12446,7 @@
         <v>44462</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12519,7 +12519,7 @@
         <v>44588</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12597,7 +12597,7 @@
         <v>44574</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -12670,7 +12670,7 @@
         <v>44889</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -12743,7 +12743,7 @@
         <v>44627</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -12816,7 +12816,7 @@
         <v>44503</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -12894,7 +12894,7 @@
         <v>44525</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -12972,7 +12972,7 @@
         <v>44874</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13045,7 +13045,7 @@
         <v>44503</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -13118,7 +13118,7 @@
         <v>44502</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -13196,7 +13196,7 @@
         <v>44551</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -13269,7 +13269,7 @@
         <v>44712</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -13347,7 +13347,7 @@
         <v>44581</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -13420,7 +13420,7 @@
         <v>44833</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -13493,7 +13493,7 @@
         <v>44601</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -13566,7 +13566,7 @@
         <v>44859</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -13639,7 +13639,7 @@
         <v>44672</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -13712,7 +13712,7 @@
         <v>44735</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -13785,7 +13785,7 @@
         <v>44462</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -13863,7 +13863,7 @@
         <v>44460</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -13936,7 +13936,7 @@
         <v>44796</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -14009,7 +14009,7 @@
         <v>44782</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -14082,7 +14082,7 @@
         <v>44741</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -14155,7 +14155,7 @@
         <v>44859</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -14228,7 +14228,7 @@
         <v>44613</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -14306,7 +14306,7 @@
         <v>44678</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -14379,7 +14379,7 @@
         <v>44855</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -14457,7 +14457,7 @@
         <v>44887</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -14530,7 +14530,7 @@
         <v>44860</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -14603,7 +14603,7 @@
         <v>44753</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -14676,7 +14676,7 @@
         <v>44802</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -14749,7 +14749,7 @@
         <v>44844</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -14827,7 +14827,7 @@
         <v>44541</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -14900,7 +14900,7 @@
         <v>44564</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -14973,7 +14973,7 @@
         <v>44781</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -15046,7 +15046,7 @@
         <v>44462</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -15119,7 +15119,7 @@
         <v>44859</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -15192,7 +15192,7 @@
         <v>44469</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -15265,7 +15265,7 @@
         <v>44595</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -15338,7 +15338,7 @@
         <v>44582</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -15411,7 +15411,7 @@
         <v>44508</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -15484,7 +15484,7 @@
         <v>44656</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -15557,7 +15557,7 @@
         <v>44816</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -15630,7 +15630,7 @@
         <v>44627</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -15703,7 +15703,7 @@
         <v>44587</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -15776,7 +15776,7 @@
         <v>44820</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -15849,7 +15849,7 @@
         <v>44532</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -15922,7 +15922,7 @@
         <v>44552</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -15995,7 +15995,7 @@
         <v>44879</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -16068,7 +16068,7 @@
         <v>44588</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -16146,7 +16146,7 @@
         <v>44581</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -16219,7 +16219,7 @@
         <v>44875</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -16292,7 +16292,7 @@
         <v>44463</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -16370,7 +16370,7 @@
         <v>44743</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -16443,7 +16443,7 @@
         <v>44831</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -16521,7 +16521,7 @@
         <v>44819</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -16594,7 +16594,7 @@
         <v>44581</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -16672,7 +16672,7 @@
         <v>44630</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -16745,7 +16745,7 @@
         <v>44469</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -16818,7 +16818,7 @@
         <v>44476</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -16891,7 +16891,7 @@
         <v>44804</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -16969,7 +16969,7 @@
         <v>44601</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -17042,7 +17042,7 @@
         <v>44742</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -17120,7 +17120,7 @@
         <v>44462</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -17193,7 +17193,7 @@
         <v>44859</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -17266,7 +17266,7 @@
         <v>44476</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -17339,7 +17339,7 @@
         <v>44600</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -17412,7 +17412,7 @@
         <v>44481</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -17485,7 +17485,7 @@
         <v>44635</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -17558,7 +17558,7 @@
         <v>44776</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -17631,7 +17631,7 @@
         <v>44713</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -17709,7 +17709,7 @@
         <v>44697</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -17787,7 +17787,7 @@
         <v>44468</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -17865,7 +17865,7 @@
         <v>44481</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -17938,7 +17938,7 @@
         <v>44533</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -18011,7 +18011,7 @@
         <v>44601</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -18084,7 +18084,7 @@
         <v>44678</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -18157,7 +18157,7 @@
         <v>44564</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -18230,7 +18230,7 @@
         <v>44642</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -18303,7 +18303,7 @@
         <v>44704</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -18376,7 +18376,7 @@
         <v>44659</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -18454,7 +18454,7 @@
         <v>44656</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -18532,7 +18532,7 @@
         <v>44966</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -18605,7 +18605,7 @@
         <v>45033</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -18683,7 +18683,7 @@
         <v>44866</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -18756,7 +18756,7 @@
         <v>45009</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -18829,7 +18829,7 @@
         <v>45258</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -18902,7 +18902,7 @@
         <v>44677</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -18975,7 +18975,7 @@
         <v>44802</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -19048,7 +19048,7 @@
         <v>44898</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -19121,7 +19121,7 @@
         <v>44476</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -19194,7 +19194,7 @@
         <v>44897</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -19272,7 +19272,7 @@
         <v>44672</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -19345,7 +19345,7 @@
         <v>44918</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -19423,7 +19423,7 @@
         <v>45447</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -19501,7 +19501,7 @@
         <v>44595</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -19579,7 +19579,7 @@
         <v>45097</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -19652,7 +19652,7 @@
         <v>45063</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -19725,7 +19725,7 @@
         <v>45086</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -19798,7 +19798,7 @@
         <v>45260</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -19871,7 +19871,7 @@
         <v>45021</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -19944,7 +19944,7 @@
         <v>45330</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -20017,7 +20017,7 @@
         <v>44973</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -20095,7 +20095,7 @@
         <v>45107</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -20168,7 +20168,7 @@
         <v>44767</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -20241,7 +20241,7 @@
         <v>45293</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -20319,7 +20319,7 @@
         <v>45428</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -20397,7 +20397,7 @@
         <v>45555</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -20475,7 +20475,7 @@
         <v>45623</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -20548,7 +20548,7 @@
         <v>45705</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -20621,7 +20621,7 @@
         <v>45206</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -20694,7 +20694,7 @@
         <v>45103</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -20767,7 +20767,7 @@
         <v>45293</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -20840,7 +20840,7 @@
         <v>44467</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -20913,7 +20913,7 @@
         <v>45642</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -20991,7 +20991,7 @@
         <v>45749</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -21069,7 +21069,7 @@
         <v>45095</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -21147,7 +21147,7 @@
         <v>44993</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -21220,7 +21220,7 @@
         <v>44914</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -21293,7 +21293,7 @@
         <v>45728</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -21371,7 +21371,7 @@
         <v>44844</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -21444,7 +21444,7 @@
         <v>44844</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -21517,7 +21517,7 @@
         <v>45554</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -21590,7 +21590,7 @@
         <v>45357</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -21663,7 +21663,7 @@
         <v>45740</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -21741,7 +21741,7 @@
         <v>45688</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -21819,7 +21819,7 @@
         <v>44960</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -21897,7 +21897,7 @@
         <v>45441</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -21970,7 +21970,7 @@
         <v>44778</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -22043,7 +22043,7 @@
         <v>45084</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -22116,7 +22116,7 @@
         <v>45720</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -22194,7 +22194,7 @@
         <v>45253</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -22272,7 +22272,7 @@
         <v>45233</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -22345,7 +22345,7 @@
         <v>44861</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -22423,7 +22423,7 @@
         <v>45149</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -22496,7 +22496,7 @@
         <v>44900</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -22569,7 +22569,7 @@
         <v>45677</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -22647,7 +22647,7 @@
         <v>45095</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -22725,7 +22725,7 @@
         <v>45095</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -22798,7 +22798,7 @@
         <v>44942</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -22871,7 +22871,7 @@
         <v>45103</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -22944,7 +22944,7 @@
         <v>45259</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -23017,7 +23017,7 @@
         <v>44817</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -23095,7 +23095,7 @@
         <v>44880</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -23173,7 +23173,7 @@
         <v>45264</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -23251,7 +23251,7 @@
         <v>44974</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -23324,7 +23324,7 @@
         <v>45008</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -23397,7 +23397,7 @@
         <v>45720</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -23475,7 +23475,7 @@
         <v>44918</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -23553,7 +23553,7 @@
         <v>45623</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -23631,7 +23631,7 @@
         <v>45593</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -23709,7 +23709,7 @@
         <v>45040</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -23787,7 +23787,7 @@
         <v>45147</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -23860,7 +23860,7 @@
         <v>45710</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -23933,7 +23933,7 @@
         <v>45554</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -24006,7 +24006,7 @@
         <v>45337</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -24079,7 +24079,7 @@
         <v>44958</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -24152,7 +24152,7 @@
         <v>45274</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -24225,7 +24225,7 @@
         <v>44490</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -24298,7 +24298,7 @@
         <v>45415</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -24371,7 +24371,7 @@
         <v>45328</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -24444,7 +24444,7 @@
         <v>45095</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -24517,7 +24517,7 @@
         <v>44950</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -24595,7 +24595,7 @@
         <v>44860</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -24668,7 +24668,7 @@
         <v>45744</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -24746,7 +24746,7 @@
         <v>45257</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -24824,7 +24824,7 @@
         <v>45257</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -24902,7 +24902,7 @@
         <v>44949</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -24975,7 +24975,7 @@
         <v>45456</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -25053,7 +25053,7 @@
         <v>45740</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -25131,7 +25131,7 @@
         <v>45002</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -25209,7 +25209,7 @@
         <v>45103</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -25282,7 +25282,7 @@
         <v>45178</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -25355,7 +25355,7 @@
         <v>44503</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -25428,7 +25428,7 @@
         <v>45421</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -25506,7 +25506,7 @@
         <v>45125</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -25584,7 +25584,7 @@
         <v>45541</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -25662,7 +25662,7 @@
         <v>44840</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -25735,7 +25735,7 @@
         <v>45463</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -25808,7 +25808,7 @@
         <v>45257</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -25886,7 +25886,7 @@
         <v>45206</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -25959,7 +25959,7 @@
         <v>45041</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -26032,7 +26032,7 @@
         <v>44516</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -26105,7 +26105,7 @@
         <v>44964</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -26183,7 +26183,7 @@
         <v>44993</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -26256,7 +26256,7 @@
         <v>45020</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -26329,7 +26329,7 @@
         <v>44607</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -26402,7 +26402,7 @@
         <v>44930</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -26475,7 +26475,7 @@
         <v>44957</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -26548,7 +26548,7 @@
         <v>44662</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -26626,7 +26626,7 @@
         <v>45601</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -26699,7 +26699,7 @@
         <v>45167</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -26777,7 +26777,7 @@
         <v>44767</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -26850,7 +26850,7 @@
         <v>44914</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -26928,7 +26928,7 @@
         <v>45084</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -27001,7 +27001,7 @@
         <v>44732</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -27079,7 +27079,7 @@
         <v>45463</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -27152,7 +27152,7 @@
         <v>44536</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -27225,7 +27225,7 @@
         <v>44734</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -27298,7 +27298,7 @@
         <v>45615</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -27376,7 +27376,7 @@
         <v>45442</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -27449,7 +27449,7 @@
         <v>44887</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -27522,7 +27522,7 @@
         <v>44614</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -27595,7 +27595,7 @@
         <v>45468</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -27673,7 +27673,7 @@
         <v>44833</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -27751,7 +27751,7 @@
         <v>45719</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -27829,7 +27829,7 @@
         <v>45604</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -27907,7 +27907,7 @@
         <v>44817</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -27980,7 +27980,7 @@
         <v>45832</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -28053,7 +28053,7 @@
         <v>44508</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -28126,7 +28126,7 @@
         <v>44865</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -28204,7 +28204,7 @@
         <v>44980</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -28277,7 +28277,7 @@
         <v>45118</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -28350,7 +28350,7 @@
         <v>45516</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -28423,7 +28423,7 @@
         <v>45915</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -28501,7 +28501,7 @@
         <v>45166</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -28579,7 +28579,7 @@
         <v>45467</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -28652,7 +28652,7 @@
         <v>45700</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -28730,7 +28730,7 @@
         <v>44735</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -28803,7 +28803,7 @@
         <v>45621</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -28881,7 +28881,7 @@
         <v>44550</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -28954,7 +28954,7 @@
         <v>45888</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -29032,7 +29032,7 @@
         <v>45600</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -29105,7 +29105,7 @@
         <v>45229</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -29183,7 +29183,7 @@
         <v>45891</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -29261,7 +29261,7 @@
         <v>45707</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -29339,7 +29339,7 @@
         <v>44900</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -29412,7 +29412,7 @@
         <v>45103</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -29485,7 +29485,7 @@
         <v>45560</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -29563,7 +29563,7 @@
         <v>45343</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -29641,7 +29641,7 @@
         <v>45894</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -29719,7 +29719,7 @@
         <v>45082</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -29797,7 +29797,7 @@
         <v>45895</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -29870,7 +29870,7 @@
         <v>45299</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -29943,7 +29943,7 @@
         <v>45006</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -30016,7 +30016,7 @@
         <v>45379</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -30089,7 +30089,7 @@
         <v>44840</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -30167,7 +30167,7 @@
         <v>45040</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -30240,7 +30240,7 @@
         <v>45896</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -30318,7 +30318,7 @@
         <v>45692</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -30396,7 +30396,7 @@
         <v>45898</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -30469,7 +30469,7 @@
         <v>45075</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -30542,7 +30542,7 @@
         <v>45617</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -30620,7 +30620,7 @@
         <v>44725</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -30693,7 +30693,7 @@
         <v>45082</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -30771,7 +30771,7 @@
         <v>45055</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -30844,7 +30844,7 @@
         <v>45903</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -30922,7 +30922,7 @@
         <v>45903</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -31000,7 +31000,7 @@
         <v>45688</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -31078,7 +31078,7 @@
         <v>45903</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -31156,7 +31156,7 @@
         <v>45250</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -31234,7 +31234,7 @@
         <v>45250</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -31307,7 +31307,7 @@
         <v>45903</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -31385,7 +31385,7 @@
         <v>45903</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -31463,7 +31463,7 @@
         <v>45853</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -31536,7 +31536,7 @@
         <v>45905</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -31614,7 +31614,7 @@
         <v>45905</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -31692,7 +31692,7 @@
         <v>45904</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -31770,7 +31770,7 @@
         <v>45905</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -31848,7 +31848,7 @@
         <v>45905</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -31926,7 +31926,7 @@
         <v>46064</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -32004,7 +32004,7 @@
         <v>45904</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -32082,7 +32082,7 @@
         <v>45908</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -32155,7 +32155,7 @@
         <v>45133</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -32228,7 +32228,7 @@
         <v>44903</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -32306,7 +32306,7 @@
         <v>45548</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -32379,7 +32379,7 @@
         <v>45267</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -32457,7 +32457,7 @@
         <v>45008</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -32535,7 +32535,7 @@
         <v>46141</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -32608,7 +32608,7 @@
         <v>44473</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -32686,7 +32686,7 @@
         <v>45344</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -32759,7 +32759,7 @@
         <v>45362</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -32832,7 +32832,7 @@
         <v>44634</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -32910,7 +32910,7 @@
         <v>45252</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -32983,7 +32983,7 @@
         <v>45209</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -33056,7 +33056,7 @@
         <v>45209</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -33129,7 +33129,7 @@
         <v>45566</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -33207,7 +33207,7 @@
         <v>44664</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -33285,7 +33285,7 @@
         <v>45924</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -33358,7 +33358,7 @@
         <v>44946</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -33436,7 +33436,7 @@
         <v>44946</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -33514,7 +33514,7 @@
         <v>44944</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -33592,7 +33592,7 @@
         <v>45009</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -33670,7 +33670,7 @@
         <v>45247</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -33743,7 +33743,7 @@
         <v>45095</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -33816,7 +33816,7 @@
         <v>45931</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -33889,7 +33889,7 @@
         <v>46141</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -33962,7 +33962,7 @@
         <v>45523</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -34040,7 +34040,7 @@
         <v>44767</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -34113,7 +34113,7 @@
         <v>44964</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -34191,7 +34191,7 @@
         <v>44759</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -34264,7 +34264,7 @@
         <v>45846</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -34342,7 +34342,7 @@
         <v>45935</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -34420,7 +34420,7 @@
         <v>45258</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -34493,7 +34493,7 @@
         <v>44617</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -34566,7 +34566,7 @@
         <v>45042</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -34644,7 +34644,7 @@
         <v>44937</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -34717,7 +34717,7 @@
         <v>45709</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -34795,7 +34795,7 @@
         <v>45944</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -34868,7 +34868,7 @@
         <v>44993</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -34941,7 +34941,7 @@
         <v>45095</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -35014,7 +35014,7 @@
         <v>44564</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -35087,7 +35087,7 @@
         <v>45607</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -35160,7 +35160,7 @@
         <v>45607</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -35233,7 +35233,7 @@
         <v>45609</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -35311,7 +35311,7 @@
         <v>45665</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -35384,7 +35384,7 @@
         <v>45551</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -35457,7 +35457,7 @@
         <v>44774</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -35535,7 +35535,7 @@
         <v>45184</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -35608,7 +35608,7 @@
         <v>45744</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -35686,7 +35686,7 @@
         <v>45950</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -35764,7 +35764,7 @@
         <v>45980</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -35837,7 +35837,7 @@
         <v>45013</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -35915,7 +35915,7 @@
         <v>45955</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -35988,7 +35988,7 @@
         <v>45688</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -36066,7 +36066,7 @@
         <v>45428</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -36139,7 +36139,7 @@
         <v>45744</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -36217,7 +36217,7 @@
         <v>45077</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -36295,7 +36295,7 @@
         <v>45002</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -36373,7 +36373,7 @@
         <v>45068</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -36451,7 +36451,7 @@
         <v>44867</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -36524,7 +36524,7 @@
         <v>45960</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -36597,7 +36597,7 @@
         <v>44886</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -36670,7 +36670,7 @@
         <v>45636</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -36743,7 +36743,7 @@
         <v>45728</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -36821,7 +36821,7 @@
         <v>45280</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -36899,7 +36899,7 @@
         <v>45845</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -36977,7 +36977,7 @@
         <v>45225</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -37050,7 +37050,7 @@
         <v>45969</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -37123,7 +37123,7 @@
         <v>45971</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -37196,7 +37196,7 @@
         <v>44987</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -37269,7 +37269,7 @@
         <v>45082</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -37347,7 +37347,7 @@
         <v>45566</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -37425,7 +37425,7 @@
         <v>45177</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -37498,7 +37498,7 @@
         <v>44995</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -37576,7 +37576,7 @@
         <v>45147</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -37649,7 +37649,7 @@
         <v>44966</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -37722,7 +37722,7 @@
         <v>45979</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -37795,7 +37795,7 @@
         <v>45230</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -37868,7 +37868,7 @@
         <v>45040</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -37941,7 +37941,7 @@
         <v>45983</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -38014,7 +38014,7 @@
         <v>45983</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -38087,7 +38087,7 @@
         <v>45983</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -38160,7 +38160,7 @@
         <v>45985</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -38233,7 +38233,7 @@
         <v>44876</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -38306,7 +38306,7 @@
         <v>45179</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -38379,7 +38379,7 @@
         <v>45179</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -38452,7 +38452,7 @@
         <v>45709</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -38530,7 +38530,7 @@
         <v>45986</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -38603,7 +38603,7 @@
         <v>45309</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -38681,7 +38681,7 @@
         <v>45309</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -38754,7 +38754,7 @@
         <v>45309</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -38827,7 +38827,7 @@
         <v>45986</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -38900,7 +38900,7 @@
         <v>44949</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -38973,7 +38973,7 @@
         <v>45323</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -39051,7 +39051,7 @@
         <v>46077</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -39129,7 +39129,7 @@
         <v>45013</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -39207,7 +39207,7 @@
         <v>44981</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -39285,7 +39285,7 @@
         <v>44930</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -39363,7 +39363,7 @@
         <v>45086</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -39436,7 +39436,7 @@
         <v>45042</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -39509,7 +39509,7 @@
         <v>45042</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -39582,7 +39582,7 @@
         <v>44939</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -39655,7 +39655,7 @@
         <v>45607</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -39728,7 +39728,7 @@
         <v>46160</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -39801,7 +39801,7 @@
         <v>44732</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -39879,7 +39879,7 @@
         <v>45425</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -39952,7 +39952,7 @@
         <v>45177</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -40025,7 +40025,7 @@
         <v>45302</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -40103,7 +40103,7 @@
         <v>45678</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -40181,7 +40181,7 @@
         <v>45622</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -40254,7 +40254,7 @@
         <v>45237</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -40332,7 +40332,7 @@
         <v>44642</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -40405,7 +40405,7 @@
         <v>45770</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -40478,7 +40478,7 @@
         <v>46000</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -40556,7 +40556,7 @@
         <v>45456</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -40634,7 +40634,7 @@
         <v>44749</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -40707,7 +40707,7 @@
         <v>45082</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -40785,7 +40785,7 @@
         <v>45082</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -40863,7 +40863,7 @@
         <v>46002</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -40941,7 +40941,7 @@
         <v>45167</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -41014,7 +41014,7 @@
         <v>46003</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -41087,7 +41087,7 @@
         <v>44930</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -41160,7 +41160,7 @@
         <v>46002</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -41238,7 +41238,7 @@
         <v>44782</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -41311,7 +41311,7 @@
         <v>46002</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -41389,7 +41389,7 @@
         <v>46002</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -41467,7 +41467,7 @@
         <v>46006</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -41540,7 +41540,7 @@
         <v>46006</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -41618,7 +41618,7 @@
         <v>45646</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -41691,7 +41691,7 @@
         <v>46006</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -41769,7 +41769,7 @@
         <v>45181</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -41842,7 +41842,7 @@
         <v>45225</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -41915,7 +41915,7 @@
         <v>44754</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -41988,7 +41988,7 @@
         <v>45421</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -42066,7 +42066,7 @@
         <v>45551</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -42139,7 +42139,7 @@
         <v>45530</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -42212,7 +42212,7 @@
         <v>44986</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -42285,7 +42285,7 @@
         <v>44770</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -42358,7 +42358,7 @@
         <v>45566</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -42436,7 +42436,7 @@
         <v>45302</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -42514,7 +42514,7 @@
         <v>45601</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -42587,7 +42587,7 @@
         <v>45712</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -42665,7 +42665,7 @@
         <v>45853</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -42738,7 +42738,7 @@
         <v>46029</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -42811,7 +42811,7 @@
         <v>44678</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -42889,7 +42889,7 @@
         <v>44637</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -42962,7 +42962,7 @@
         <v>46030</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -43040,7 +43040,7 @@
         <v>46030</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -43118,7 +43118,7 @@
         <v>46031</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -43196,7 +43196,7 @@
         <v>46034</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -43274,7 +43274,7 @@
         <v>46174</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -43352,7 +43352,7 @@
         <v>46174</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -43430,7 +43430,7 @@
         <v>46034</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -43508,7 +43508,7 @@
         <v>46034</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -43586,7 +43586,7 @@
         <v>45279</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -43664,7 +43664,7 @@
         <v>45609</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -43742,7 +43742,7 @@
         <v>46036</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -43820,7 +43820,7 @@
         <v>46036</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -43898,7 +43898,7 @@
         <v>45070</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -43976,7 +43976,7 @@
         <v>46040</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -44049,7 +44049,7 @@
         <v>44973</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -44127,7 +44127,7 @@
         <v>44891</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -44200,7 +44200,7 @@
         <v>46040</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -44273,7 +44273,7 @@
         <v>45616</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -44346,7 +44346,7 @@
         <v>44949</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -44419,7 +44419,7 @@
         <v>44966</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -44492,7 +44492,7 @@
         <v>44953</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -44570,7 +44570,7 @@
         <v>46048</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -44648,7 +44648,7 @@
         <v>44823</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -44721,7 +44721,7 @@
         <v>46049</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -44794,7 +44794,7 @@
         <v>45202</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -44867,7 +44867,7 @@
         <v>46048</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -44945,7 +44945,7 @@
         <v>46048</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -45023,7 +45023,7 @@
         <v>46176</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -45096,7 +45096,7 @@
         <v>46050</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -45174,7 +45174,7 @@
         <v>46050</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -45252,7 +45252,7 @@
         <v>46176</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -45325,7 +45325,7 @@
         <v>46176</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -45398,7 +45398,7 @@
         <v>45379</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -45471,7 +45471,7 @@
         <v>46055</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -45549,7 +45549,7 @@
         <v>46052</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -45622,7 +45622,7 @@
         <v>45428</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -45700,7 +45700,7 @@
         <v>45174</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -45778,7 +45778,7 @@
         <v>45770</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -45851,7 +45851,7 @@
         <v>46058</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -45929,7 +45929,7 @@
         <v>46058</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -46007,7 +46007,7 @@
         <v>45236</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -46085,7 +46085,7 @@
         <v>45236</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -46163,7 +46163,7 @@
         <v>46058</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -46241,7 +46241,7 @@
         <v>46058</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -46319,7 +46319,7 @@
         <v>46060</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -46392,7 +46392,7 @@
         <v>46178</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -46465,7 +46465,7 @@
         <v>46178</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -46538,7 +46538,7 @@
         <v>46063</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -46616,7 +46616,7 @@
         <v>46063</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -46694,7 +46694,7 @@
         <v>46177</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -46767,7 +46767,7 @@
         <v>46064</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -46845,7 +46845,7 @@
         <v>45357</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -46918,7 +46918,7 @@
         <v>46065</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -46996,7 +46996,7 @@
         <v>46065</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -47074,7 +47074,7 @@
         <v>46064</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -47152,7 +47152,7 @@
         <v>46064</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -47230,7 +47230,7 @@
         <v>46064</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -47308,7 +47308,7 @@
         <v>46064</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -47386,7 +47386,7 @@
         <v>46064</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -47464,7 +47464,7 @@
         <v>46178</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -47537,7 +47537,7 @@
         <v>45243</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -47615,7 +47615,7 @@
         <v>46069</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -47693,7 +47693,7 @@
         <v>45022</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -47771,7 +47771,7 @@
         <v>46070</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -47849,7 +47849,7 @@
         <v>46070</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -47927,7 +47927,7 @@
         <v>44816</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -48000,7 +48000,7 @@
         <v>46073</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -48078,7 +48078,7 @@
         <v>46181</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -48156,7 +48156,7 @@
         <v>45314</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -48229,7 +48229,7 @@
         <v>46076</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -48307,7 +48307,7 @@
         <v>46076</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -48385,7 +48385,7 @@
         <v>44820</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -48458,7 +48458,7 @@
         <v>45535</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -48536,7 +48536,7 @@
         <v>46078</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -48614,7 +48614,7 @@
         <v>46080</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -48692,7 +48692,7 @@
         <v>46080</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -48770,7 +48770,7 @@
         <v>46079</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -48848,7 +48848,7 @@
         <v>45250</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -48926,7 +48926,7 @@
         <v>46080</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -49004,7 +49004,7 @@
         <v>46080</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -49082,7 +49082,7 @@
         <v>45197</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -49155,7 +49155,7 @@
         <v>44966</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -49228,7 +49228,7 @@
         <v>44806</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -49306,7 +49306,7 @@
         <v>46085</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -49384,7 +49384,7 @@
         <v>46085</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -49462,7 +49462,7 @@
         <v>46085</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -49540,7 +49540,7 @@
         <v>46085</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -49618,7 +49618,7 @@
         <v>46185</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -49691,7 +49691,7 @@
         <v>46185</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -49764,7 +49764,7 @@
         <v>46188</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -49837,7 +49837,7 @@
         <v>45113</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -49910,7 +49910,7 @@
         <v>44964</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -49988,7 +49988,7 @@
         <v>46094</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -50066,7 +50066,7 @@
         <v>45420</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -50139,7 +50139,7 @@
         <v>44834</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -50217,7 +50217,7 @@
         <v>45616</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -50290,7 +50290,7 @@
         <v>46097</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -50363,7 +50363,7 @@
         <v>45258</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -50436,7 +50436,7 @@
         <v>44865</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -50509,7 +50509,7 @@
         <v>44953</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -50582,7 +50582,7 @@
         <v>45617</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -50660,7 +50660,7 @@
         <v>46099</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -50738,7 +50738,7 @@
         <v>46099</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -50811,7 +50811,7 @@
         <v>46099</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -50889,7 +50889,7 @@
         <v>44879</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -50962,7 +50962,7 @@
         <v>46099</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -51040,7 +51040,7 @@
         <v>46099</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -51113,7 +51113,7 @@
         <v>46196</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -51191,7 +51191,7 @@
         <v>45713</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -51269,7 +51269,7 @@
         <v>46106</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -51347,7 +51347,7 @@
         <v>45735</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -51425,7 +51425,7 @@
         <v>44862</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -51503,7 +51503,7 @@
         <v>44887</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -51576,7 +51576,7 @@
         <v>44887</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -51649,7 +51649,7 @@
         <v>45426</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -51722,7 +51722,7 @@
         <v>44616</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -51800,7 +51800,7 @@
         <v>44949</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -51873,7 +51873,7 @@
         <v>44995</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -51951,7 +51951,7 @@
         <v>46111</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -52029,7 +52029,7 @@
         <v>44813</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -52107,7 +52107,7 @@
         <v>46113</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -52180,7 +52180,7 @@
         <v>46114</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -52258,7 +52258,7 @@
         <v>46199</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -52331,7 +52331,7 @@
         <v>46114</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -52409,7 +52409,7 @@
         <v>46114</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -52487,7 +52487,7 @@
         <v>46113</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -52565,7 +52565,7 @@
         <v>46120</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -52643,7 +52643,7 @@
         <v>46121</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -52721,7 +52721,7 @@
         <v>46122</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -52794,7 +52794,7 @@
         <v>45142</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -52867,7 +52867,7 @@
         <v>45846</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -52945,7 +52945,7 @@
         <v>45715</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -53018,7 +53018,7 @@
         <v>46125</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -53091,7 +53091,7 @@
         <v>44653</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -53164,7 +53164,7 @@
         <v>46129</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -53242,7 +53242,7 @@
         <v>45645</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -53320,7 +53320,7 @@
         <v>45593</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -53398,7 +53398,7 @@
         <v>46128</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -53471,7 +53471,7 @@
         <v>44987</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -53544,7 +53544,7 @@
         <v>45555</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -53622,7 +53622,7 @@
         <v>45639</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -53700,7 +53700,7 @@
         <v>45314</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -53773,7 +53773,7 @@
         <v>45447</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -53851,7 +53851,7 @@
         <v>44729</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -53924,7 +53924,7 @@
         <v>44844</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -53997,7 +53997,7 @@
         <v>44973</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -54075,7 +54075,7 @@
         <v>45076</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -54153,7 +54153,7 @@
         <v>45095</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -54226,7 +54226,7 @@
         <v>45706</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -54299,7 +54299,7 @@
         <v>45639</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -54377,7 +54377,7 @@
         <v>44526</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -54450,7 +54450,7 @@
         <v>45706</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -54523,7 +54523,7 @@
         <v>46134</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -54596,7 +54596,7 @@
         <v>45086</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -54669,7 +54669,7 @@
         <v>44922</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -54747,7 +54747,7 @@
         <v>44795</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -54825,7 +54825,7 @@
         <v>45740</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -54898,7 +54898,7 @@
         <v>45783</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -54976,7 +54976,7 @@
         <v>45260</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -55049,7 +55049,7 @@
         <v>44491</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -55122,7 +55122,7 @@
         <v>45719</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -55200,7 +55200,7 @@
         <v>45041</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -55278,7 +55278,7 @@
         <v>45257</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -55351,7 +55351,7 @@
         <v>44871</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -55424,7 +55424,7 @@
         <v>45391</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -55497,7 +55497,7 @@
         <v>46204</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -55570,7 +55570,7 @@
         <v>45692</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -55648,7 +55648,7 @@
         <v>46203</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -55721,7 +55721,7 @@
         <v>45070</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -55799,7 +55799,7 @@
         <v>45202</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -55872,7 +55872,7 @@
         <v>44966</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -55950,7 +55950,7 @@
         <v>46209</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -56023,7 +56023,7 @@
         <v>45323</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -56101,7 +56101,7 @@
         <v>45341</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -56179,7 +56179,7 @@
         <v>44550</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -56252,7 +56252,7 @@
         <v>45566</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -56330,7 +56330,7 @@
         <v>45566</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -56408,7 +56408,7 @@
         <v>44476</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -56481,7 +56481,7 @@
         <v>45441</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -56554,7 +56554,7 @@
         <v>46209</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -56627,7 +56627,7 @@
         <v>45374</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -56705,7 +56705,7 @@
         <v>46209</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -56778,7 +56778,7 @@
         <v>45391</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -56851,7 +56851,7 @@
         <v>44981</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -56929,7 +56929,7 @@
         <v>44679</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -57007,7 +57007,7 @@
         <v>45293</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -57080,7 +57080,7 @@
         <v>45554</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -57153,7 +57153,7 @@
         <v>45214</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -57226,7 +57226,7 @@
         <v>45110</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -57299,7 +57299,7 @@
         <v>45660</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -57377,7 +57377,7 @@
         <v>45735</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -57455,7 +57455,7 @@
         <v>45516</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -57533,7 +57533,7 @@
         <v>44966</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -57611,7 +57611,7 @@
         <v>45078</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -57684,7 +57684,7 @@
         <v>45113</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -57757,7 +57757,7 @@
         <v>45191</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -57830,7 +57830,7 @@
         <v>46255</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -57908,7 +57908,7 @@
         <v>45763</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -57981,7 +57981,7 @@
         <v>44551</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -58054,7 +58054,7 @@
         <v>44833</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -58132,7 +58132,7 @@
         <v>46212</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -58205,7 +58205,7 @@
         <v>45103</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -58278,7 +58278,7 @@
         <v>46211</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -58351,7 +58351,7 @@
         <v>45618</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -58424,7 +58424,7 @@
         <v>45639</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -58502,7 +58502,7 @@
         <v>45299</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -58575,7 +58575,7 @@
         <v>45301</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -58653,7 +58653,7 @@
         <v>44714</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -58726,7 +58726,7 @@
         <v>46258</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -58804,7 +58804,7 @@
         <v>46258</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -58882,7 +58882,7 @@
         <v>44622</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -58955,7 +58955,7 @@
         <v>45232</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -59033,7 +59033,7 @@
         <v>44887</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -59106,7 +59106,7 @@
         <v>45422</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -59179,7 +59179,7 @@
         <v>44622</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -59252,7 +59252,7 @@
         <v>45191</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -59325,7 +59325,7 @@
         <v>44595</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -59398,7 +59398,7 @@
         <v>44589</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -59471,7 +59471,7 @@
         <v>46218</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -59549,7 +59549,7 @@
         <v>46218</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -59627,7 +59627,7 @@
         <v>45308</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -59700,7 +59700,7 @@
         <v>44922</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -59778,7 +59778,7 @@
         <v>45615</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -59856,7 +59856,7 @@
         <v>45149</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -59929,7 +59929,7 @@
         <v>45762</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -60002,7 +60002,7 @@
         <v>44817</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -60075,7 +60075,7 @@
         <v>45149</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -60148,7 +60148,7 @@
         <v>45622</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -60221,7 +60221,7 @@
         <v>46219</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -60294,7 +60294,7 @@
         <v>45554</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -60367,7 +60367,7 @@
         <v>45095</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -60440,7 +60440,7 @@
         <v>45593</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -60518,7 +60518,7 @@
         <v>45275</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -60591,7 +60591,7 @@
         <v>46269</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -60664,7 +60664,7 @@
         <v>44564</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -60737,7 +60737,7 @@
         <v>45744</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -60815,7 +60815,7 @@
         <v>46269</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -60888,7 +60888,7 @@
         <v>45407</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -60961,7 +60961,7 @@
         <v>45071</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -61039,7 +61039,7 @@
         <v>46268</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -61112,7 +61112,7 @@
         <v>45257</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -61190,7 +61190,7 @@
         <v>45257</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -61263,7 +61263,7 @@
         <v>46225</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -61336,7 +61336,7 @@
         <v>46269</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -61409,7 +61409,7 @@
         <v>46269</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -61482,7 +61482,7 @@
         <v>45566</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -61560,7 +61560,7 @@
         <v>46226</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -61633,7 +61633,7 @@
         <v>46226</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -61706,7 +61706,7 @@
         <v>46269</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -61779,7 +61779,7 @@
         <v>46225</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -61852,7 +61852,7 @@
         <v>45566</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -61930,7 +61930,7 @@
         <v>45566</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -62008,7 +62008,7 @@
         <v>45735</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -62086,7 +62086,7 @@
         <v>45736</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -62164,7 +62164,7 @@
         <v>45642</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -62237,7 +62237,7 @@
         <v>45530</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -62310,7 +62310,7 @@
         <v>46232</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -62383,7 +62383,7 @@
         <v>46279</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -62456,7 +62456,7 @@
         <v>45530</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -62529,7 +62529,7 @@
         <v>45371</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -62607,7 +62607,7 @@
         <v>46233</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -62680,7 +62680,7 @@
         <v>46279</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -62753,7 +62753,7 @@
         <v>46279</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -62826,7 +62826,7 @@
         <v>45727</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -62899,7 +62899,7 @@
         <v>45267</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -62977,7 +62977,7 @@
         <v>45797</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -63050,7 +63050,7 @@
         <v>45797</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -63128,7 +63128,7 @@
         <v>45796</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -63206,7 +63206,7 @@
         <v>46282</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -63284,7 +63284,7 @@
         <v>45797</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -63357,7 +63357,7 @@
         <v>45796</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -63435,7 +63435,7 @@
         <v>45702</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -63513,7 +63513,7 @@
         <v>46282</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -63591,7 +63591,7 @@
         <v>46282</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -63669,7 +63669,7 @@
         <v>46282</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -63747,7 +63747,7 @@
         <v>46282</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -63825,7 +63825,7 @@
         <v>45316</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -63903,7 +63903,7 @@
         <v>46281</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -63976,7 +63976,7 @@
         <v>46282</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -64054,7 +64054,7 @@
         <v>46282</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -64132,7 +64132,7 @@
         <v>45800</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -64210,7 +64210,7 @@
         <v>46282</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
@@ -64288,7 +64288,7 @@
         <v>46282</v>
       </c>
       <c r="E802" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -64366,7 +64366,7 @@
         <v>45800</v>
       </c>
       <c r="E803" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
@@ -64444,7 +64444,7 @@
         <v>45800</v>
       </c>
       <c r="E804" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
@@ -64522,7 +64522,7 @@
         <v>45800</v>
       </c>
       <c r="E805" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>
@@ -64600,7 +64600,7 @@
         <v>45812</v>
       </c>
       <c r="E806" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F806" t="inlineStr">
         <is>
@@ -64678,7 +64678,7 @@
         <v>45812</v>
       </c>
       <c r="E807" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F807" t="inlineStr">
         <is>
@@ -64756,7 +64756,7 @@
         <v>45812</v>
       </c>
       <c r="E808" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F808" t="inlineStr">
         <is>
@@ -64834,7 +64834,7 @@
         <v>45817</v>
       </c>
       <c r="E809" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F809" t="inlineStr">
         <is>
@@ -64912,7 +64912,7 @@
         <v>45817</v>
       </c>
       <c r="E810" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F810" t="inlineStr">
         <is>
@@ -64990,7 +64990,7 @@
         <v>45639</v>
       </c>
       <c r="E811" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F811" t="inlineStr">
         <is>
@@ -65068,7 +65068,7 @@
         <v>45819</v>
       </c>
       <c r="E812" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F812" t="inlineStr">
         <is>
@@ -65146,7 +65146,7 @@
         <v>45819</v>
       </c>
       <c r="E813" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F813" t="inlineStr">
         <is>
@@ -65224,7 +65224,7 @@
         <v>45819</v>
       </c>
       <c r="E814" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F814" t="inlineStr">
         <is>
@@ -65302,7 +65302,7 @@
         <v>45820</v>
       </c>
       <c r="E815" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F815" t="inlineStr">
         <is>
@@ -65380,7 +65380,7 @@
         <v>45824</v>
       </c>
       <c r="E816" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F816" t="inlineStr">
         <is>
@@ -65458,7 +65458,7 @@
         <v>45824</v>
       </c>
       <c r="E817" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F817" t="inlineStr">
         <is>
@@ -65536,7 +65536,7 @@
         <v>45824</v>
       </c>
       <c r="E818" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F818" t="inlineStr">
         <is>
@@ -65614,7 +65614,7 @@
         <v>45824</v>
       </c>
       <c r="E819" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F819" t="inlineStr">
         <is>
@@ -65692,7 +65692,7 @@
         <v>45835</v>
       </c>
       <c r="E820" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F820" t="inlineStr">
         <is>
@@ -65770,7 +65770,7 @@
         <v>45840</v>
       </c>
       <c r="E821" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F821" t="inlineStr">
         <is>
@@ -65848,7 +65848,7 @@
         <v>45845</v>
       </c>
       <c r="E822" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F822" t="inlineStr">
         <is>
@@ -65926,7 +65926,7 @@
         <v>45776</v>
       </c>
       <c r="E823" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F823" t="inlineStr">
         <is>
@@ -65999,7 +65999,7 @@
         <v>45854</v>
       </c>
       <c r="E824" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F824" t="inlineStr">
         <is>
@@ -66072,7 +66072,7 @@
         <v>45854</v>
       </c>
       <c r="E825" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F825" t="inlineStr">
         <is>
@@ -66145,7 +66145,7 @@
         <v>45853</v>
       </c>
       <c r="E826" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F826" t="inlineStr">
         <is>
@@ -66218,7 +66218,7 @@
         <v>45855</v>
       </c>
       <c r="E827" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F827" t="inlineStr">
         <is>
@@ -66291,7 +66291,7 @@
         <v>45523</v>
       </c>
       <c r="E828" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F828" t="inlineStr">
         <is>
@@ -66364,7 +66364,7 @@
         <v>45863</v>
       </c>
       <c r="E829" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F829" t="inlineStr">
         <is>
@@ -66437,7 +66437,7 @@
         <v>45831</v>
       </c>
       <c r="E830" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F830" t="inlineStr">
         <is>
@@ -66510,7 +66510,7 @@
         <v>45870</v>
       </c>
       <c r="E831" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F831" t="inlineStr">
         <is>
@@ -66583,7 +66583,7 @@
         <v>45820</v>
       </c>
       <c r="E832" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F832" t="inlineStr">
         <is>
@@ -66661,7 +66661,7 @@
         <v>45870</v>
       </c>
       <c r="E833" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F833" t="inlineStr">
         <is>
@@ -66734,7 +66734,7 @@
         <v>45709</v>
       </c>
       <c r="E834" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F834" t="inlineStr">
         <is>
@@ -66812,7 +66812,7 @@
         <v>45880</v>
       </c>
       <c r="E835" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F835" t="inlineStr">
         <is>
@@ -66890,7 +66890,7 @@
         <v>45880</v>
       </c>
       <c r="E836" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F836" t="inlineStr">
         <is>
@@ -66968,7 +66968,7 @@
         <v>45881</v>
       </c>
       <c r="E837" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F837" t="inlineStr">
         <is>
@@ -67046,7 +67046,7 @@
         <v>45883</v>
       </c>
       <c r="E838" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F838" t="inlineStr">
         <is>
@@ -67124,7 +67124,7 @@
         <v>45883</v>
       </c>
       <c r="E839" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F839" t="inlineStr">
         <is>
@@ -67202,7 +67202,7 @@
         <v>45644</v>
       </c>
       <c r="E840" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F840" t="inlineStr">
         <is>
@@ -67275,7 +67275,7 @@
         <v>45428</v>
       </c>
       <c r="E841" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F841" t="inlineStr">
         <is>
@@ -67348,7 +67348,7 @@
         <v>45429</v>
       </c>
       <c r="E842" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F842" t="inlineStr">
         <is>
@@ -67421,7 +67421,7 @@
         <v>45250</v>
       </c>
       <c r="E843" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F843" t="inlineStr">
         <is>
@@ -67499,7 +67499,7 @@
         <v>46188</v>
       </c>
       <c r="E844" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F844" t="inlineStr">
         <is>
@@ -67577,7 +67577,7 @@
         <v>46258</v>
       </c>
       <c r="E845" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F845" t="inlineStr">
         <is>

--- a/Översikt FINSPÅNG.xlsx
+++ b/Översikt FINSPÅNG.xlsx
@@ -601,7 +601,7 @@
         <v>46244</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -727,7 +727,7 @@
         <v>45945</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -858,7 +858,7 @@
         <v>45134</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
         <v>44896</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1121,7 +1121,7 @@
         <v>44888</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>45210</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1369,7 +1369,7 @@
         <v>44777</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1488,7 +1488,7 @@
         <v>44897</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1607,7 +1607,7 @@
         <v>44910</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1734,7 +1734,7 @@
         <v>45322</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1855,7 +1855,7 @@
         <v>44624</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1971,7 +1971,7 @@
         <v>44599</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2082,7 +2082,7 @@
         <v>45891</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2198,7 +2198,7 @@
         <v>45421</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2318,7 +2318,7 @@
         <v>45238</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2433,7 +2433,7 @@
         <v>45898</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2548,7 +2548,7 @@
         <v>45267</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2663,7 +2663,7 @@
         <v>45679</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2782,7 +2782,7 @@
         <v>45947</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2896,7 +2896,7 @@
         <v>45812</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3010,7 +3010,7 @@
         <v>44791</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3124,7 +3124,7 @@
         <v>44665</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3237,7 +3237,7 @@
         <v>45681</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3354,7 +3354,7 @@
         <v>45800</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3466,7 +3466,7 @@
         <v>45819</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3582,7 +3582,7 @@
         <v>45082</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3694,7 +3694,7 @@
         <v>45602</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3806,7 +3806,7 @@
         <v>44774</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3918,7 +3918,7 @@
         <v>46196</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4030,7 +4030,7 @@
         <v>44690</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4141,7 +4141,7 @@
         <v>44816</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4247,7 +4247,7 @@
         <v>45425</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4353,7 +4353,7 @@
         <v>45121</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4468,7 +4468,7 @@
         <v>45894</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4583,7 +4583,7 @@
         <v>45905</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4694,7 +4694,7 @@
         <v>45950</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4805,7 +4805,7 @@
         <v>45644</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4911,7 +4911,7 @@
         <v>44981</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5022,7 +5022,7 @@
         <v>46174</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5133,7 +5133,7 @@
         <v>46181</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5244,7 +5244,7 @@
         <v>46181</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5355,7 +5355,7 @@
         <v>45441</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5466,7 +5466,7 @@
         <v>45235</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5577,7 +5577,7 @@
         <v>44903</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5687,7 +5687,7 @@
         <v>45477</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5802,7 +5802,7 @@
         <v>44480</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5913,7 +5913,7 @@
         <v>44683</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6023,7 +6023,7 @@
         <v>44776</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6128,7 +6128,7 @@
         <v>44504</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6238,7 +6238,7 @@
         <v>44529</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6343,7 +6343,7 @@
         <v>45232</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6453,7 +6453,7 @@
         <v>44915</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6563,7 +6563,7 @@
         <v>44897</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6677,7 +6677,7 @@
         <v>44915</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6787,7 +6787,7 @@
         <v>45905</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6897,7 +6897,7 @@
         <v>45883</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7007,7 +7007,7 @@
         <v>46058</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7121,7 +7121,7 @@
         <v>45566</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7235,7 +7235,7 @@
         <v>44599</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7345,7 +7345,7 @@
         <v>45328</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7454,7 +7454,7 @@
         <v>46129</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7568,7 +7568,7 @@
         <v>45615</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7682,7 +7682,7 @@
         <v>46043</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7796,7 +7796,7 @@
         <v>45447</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7906,7 +7906,7 @@
         <v>44817</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8016,7 +8016,7 @@
         <v>44992</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8126,7 +8126,7 @@
         <v>45070</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8236,7 +8236,7 @@
         <v>44965</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8350,7 +8350,7 @@
         <v>46155</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8464,7 +8464,7 @@
         <v>45846</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8574,7 +8574,7 @@
         <v>45845</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8684,7 +8684,7 @@
         <v>46189</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8789,7 +8789,7 @@
         <v>45880</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8899,7 +8899,7 @@
         <v>45149</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9008,7 +9008,7 @@
         <v>46258</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9122,7 +9122,7 @@
         <v>46258</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9232,7 +9232,7 @@
         <v>46181</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9342,7 +9342,7 @@
         <v>45229</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9452,7 +9452,7 @@
         <v>45302</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9561,7 +9561,7 @@
         <v>45555</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9675,7 +9675,7 @@
         <v>44501</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9785,7 +9785,7 @@
         <v>44930</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9895,7 +9895,7 @@
         <v>45636</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10000,7 +10000,7 @@
         <v>44622</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10105,7 +10105,7 @@
         <v>45082</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10215,7 +10215,7 @@
         <v>45744</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10329,7 +10329,7 @@
         <v>45446</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10434,7 +10434,7 @@
         <v>45567</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10548,7 +10548,7 @@
         <v>44711</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10658,7 +10658,7 @@
         <v>45428</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10763,7 +10763,7 @@
         <v>46107</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10873,7 +10873,7 @@
         <v>46188</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10987,7 +10987,7 @@
         <v>44755</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11065,7 +11065,7 @@
         <v>44675</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11138,7 +11138,7 @@
         <v>44676</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11216,7 +11216,7 @@
         <v>44864</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11289,7 +11289,7 @@
         <v>44600</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11362,7 +11362,7 @@
         <v>44536</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11440,7 +11440,7 @@
         <v>44824</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11513,7 +11513,7 @@
         <v>44795</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11586,7 +11586,7 @@
         <v>44799</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11659,7 +11659,7 @@
         <v>44856</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11732,7 +11732,7 @@
         <v>44578</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11810,7 +11810,7 @@
         <v>44675</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -11883,7 +11883,7 @@
         <v>44852</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -11961,7 +11961,7 @@
         <v>44601</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12039,7 +12039,7 @@
         <v>44601</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12112,7 +12112,7 @@
         <v>44551</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12185,7 +12185,7 @@
         <v>44525</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12258,7 +12258,7 @@
         <v>44574</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12336,7 +12336,7 @@
         <v>44588</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12414,7 +12414,7 @@
         <v>44574</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12487,7 +12487,7 @@
         <v>44889</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12560,7 +12560,7 @@
         <v>44627</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -12633,7 +12633,7 @@
         <v>44503</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -12711,7 +12711,7 @@
         <v>44525</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -12789,7 +12789,7 @@
         <v>44503</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -12862,7 +12862,7 @@
         <v>44874</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -12935,7 +12935,7 @@
         <v>44502</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13013,7 +13013,7 @@
         <v>44551</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -13086,7 +13086,7 @@
         <v>44712</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -13164,7 +13164,7 @@
         <v>44581</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -13237,7 +13237,7 @@
         <v>44833</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -13310,7 +13310,7 @@
         <v>44601</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -13383,7 +13383,7 @@
         <v>44859</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -13456,7 +13456,7 @@
         <v>44735</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -13529,7 +13529,7 @@
         <v>44672</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -13602,7 +13602,7 @@
         <v>44796</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -13675,7 +13675,7 @@
         <v>44782</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -13748,7 +13748,7 @@
         <v>44741</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -13821,7 +13821,7 @@
         <v>44859</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -13894,7 +13894,7 @@
         <v>44613</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -13972,7 +13972,7 @@
         <v>44678</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -14045,7 +14045,7 @@
         <v>44855</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -14123,7 +14123,7 @@
         <v>44887</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -14196,7 +14196,7 @@
         <v>44860</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -14269,7 +14269,7 @@
         <v>44753</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -14342,7 +14342,7 @@
         <v>44802</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -14415,7 +14415,7 @@
         <v>44844</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -14493,7 +14493,7 @@
         <v>44781</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -14566,7 +14566,7 @@
         <v>44541</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -14639,7 +14639,7 @@
         <v>44564</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -14712,7 +14712,7 @@
         <v>44859</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -14785,7 +14785,7 @@
         <v>44469</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -14858,7 +14858,7 @@
         <v>44595</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -14931,7 +14931,7 @@
         <v>44582</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -15004,7 +15004,7 @@
         <v>44508</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -15077,7 +15077,7 @@
         <v>44816</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -15150,7 +15150,7 @@
         <v>44656</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -15223,7 +15223,7 @@
         <v>44627</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -15296,7 +15296,7 @@
         <v>44587</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -15369,7 +15369,7 @@
         <v>44820</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -15442,7 +15442,7 @@
         <v>44532</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -15515,7 +15515,7 @@
         <v>44552</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -15588,7 +15588,7 @@
         <v>44879</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -15661,7 +15661,7 @@
         <v>44581</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -15734,7 +15734,7 @@
         <v>44588</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -15812,7 +15812,7 @@
         <v>44875</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -15885,7 +15885,7 @@
         <v>44743</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -15958,7 +15958,7 @@
         <v>44831</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -16036,7 +16036,7 @@
         <v>44819</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -16109,7 +16109,7 @@
         <v>44581</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -16187,7 +16187,7 @@
         <v>44630</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -16260,7 +16260,7 @@
         <v>44469</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -16333,7 +16333,7 @@
         <v>44476</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -16406,7 +16406,7 @@
         <v>44804</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -16484,7 +16484,7 @@
         <v>44601</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -16557,7 +16557,7 @@
         <v>44742</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -16635,7 +16635,7 @@
         <v>44859</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -16708,7 +16708,7 @@
         <v>44476</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -16781,7 +16781,7 @@
         <v>44600</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -16854,7 +16854,7 @@
         <v>44481</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -16927,7 +16927,7 @@
         <v>44635</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -17000,7 +17000,7 @@
         <v>44776</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -17073,7 +17073,7 @@
         <v>44713</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -17151,7 +17151,7 @@
         <v>44697</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -17229,7 +17229,7 @@
         <v>44468</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -17307,7 +17307,7 @@
         <v>44481</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -17380,7 +17380,7 @@
         <v>44533</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -17453,7 +17453,7 @@
         <v>44601</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -17526,7 +17526,7 @@
         <v>44678</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -17599,7 +17599,7 @@
         <v>44704</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -17672,7 +17672,7 @@
         <v>44564</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -17745,7 +17745,7 @@
         <v>44642</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -17818,7 +17818,7 @@
         <v>44659</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -17896,7 +17896,7 @@
         <v>45617</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -17974,7 +17974,7 @@
         <v>44754</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -18047,7 +18047,7 @@
         <v>45042</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -18120,7 +18120,7 @@
         <v>45330</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -18193,7 +18193,7 @@
         <v>44778</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -18266,7 +18266,7 @@
         <v>44802</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -18339,7 +18339,7 @@
         <v>44833</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -18417,7 +18417,7 @@
         <v>45362</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -18490,7 +18490,7 @@
         <v>45535</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -18568,7 +18568,7 @@
         <v>44770</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -18641,7 +18641,7 @@
         <v>45374</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -18719,7 +18719,7 @@
         <v>45257</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -18797,7 +18797,7 @@
         <v>45257</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -18870,7 +18870,7 @@
         <v>45618</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -18943,7 +18943,7 @@
         <v>44930</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -19016,7 +19016,7 @@
         <v>44930</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -19089,7 +19089,7 @@
         <v>44844</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -19162,7 +19162,7 @@
         <v>45541</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -19240,7 +19240,7 @@
         <v>44806</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -19318,7 +19318,7 @@
         <v>45357</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -19391,7 +19391,7 @@
         <v>44817</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -19464,7 +19464,7 @@
         <v>45744</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -19542,7 +19542,7 @@
         <v>45744</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -19620,7 +19620,7 @@
         <v>44887</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -19693,7 +19693,7 @@
         <v>45252</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -19766,7 +19766,7 @@
         <v>44953</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -19839,7 +19839,7 @@
         <v>45447</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -19917,7 +19917,7 @@
         <v>44767</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -19990,7 +19990,7 @@
         <v>44986</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -20063,7 +20063,7 @@
         <v>45442</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -20136,7 +20136,7 @@
         <v>45258</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -20209,7 +20209,7 @@
         <v>45260</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -20282,7 +20282,7 @@
         <v>44957</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -20355,7 +20355,7 @@
         <v>44816</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -20428,7 +20428,7 @@
         <v>45258</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -20501,7 +20501,7 @@
         <v>45250</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -20574,7 +20574,7 @@
         <v>45323</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -20652,7 +20652,7 @@
         <v>44891</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -20725,7 +20725,7 @@
         <v>45551</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -20798,7 +20798,7 @@
         <v>45097</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -20871,7 +20871,7 @@
         <v>45095</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -20944,7 +20944,7 @@
         <v>45463</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -21017,7 +21017,7 @@
         <v>45796</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -21095,7 +21095,7 @@
         <v>45796</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -21173,7 +21173,7 @@
         <v>45853</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -21246,7 +21246,7 @@
         <v>46030</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -21324,7 +21324,7 @@
         <v>45293</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -21402,7 +21402,7 @@
         <v>44860</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -21475,7 +21475,7 @@
         <v>45328</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -21548,7 +21548,7 @@
         <v>46030</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -21626,7 +21626,7 @@
         <v>45467</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -21699,7 +21699,7 @@
         <v>44476</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -21772,7 +21772,7 @@
         <v>45316</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -21850,7 +21850,7 @@
         <v>45797</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -21923,7 +21923,7 @@
         <v>45797</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -21996,7 +21996,7 @@
         <v>45797</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -22074,7 +22074,7 @@
         <v>45702</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -22152,7 +22152,7 @@
         <v>46029</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -22225,7 +22225,7 @@
         <v>46031</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -22303,7 +22303,7 @@
         <v>45883</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -22381,7 +22381,7 @@
         <v>45888</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -22459,7 +22459,7 @@
         <v>46034</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -22537,7 +22537,7 @@
         <v>46034</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -22615,7 +22615,7 @@
         <v>46034</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -22693,7 +22693,7 @@
         <v>45621</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -22771,7 +22771,7 @@
         <v>45800</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -22849,7 +22849,7 @@
         <v>45337</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -22922,7 +22922,7 @@
         <v>46036</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -23000,7 +23000,7 @@
         <v>46036</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -23078,7 +23078,7 @@
         <v>45428</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -23156,7 +23156,7 @@
         <v>45428</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -23234,7 +23234,7 @@
         <v>45280</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -23312,7 +23312,7 @@
         <v>44844</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -23385,7 +23385,7 @@
         <v>44844</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -23458,7 +23458,7 @@
         <v>44866</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -23531,7 +23531,7 @@
         <v>44840</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -23609,7 +23609,7 @@
         <v>45891</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -23687,7 +23687,7 @@
         <v>45607</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -23760,7 +23760,7 @@
         <v>45707</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -23838,7 +23838,7 @@
         <v>44656</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -23916,7 +23916,7 @@
         <v>45894</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -23994,7 +23994,7 @@
         <v>45896</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -24072,7 +24072,7 @@
         <v>46040</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -24145,7 +24145,7 @@
         <v>45800</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -24223,7 +24223,7 @@
         <v>46040</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -24296,7 +24296,7 @@
         <v>45895</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -24369,7 +24369,7 @@
         <v>44865</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -24442,7 +24442,7 @@
         <v>45898</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -24515,7 +24515,7 @@
         <v>44887</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -24588,7 +24588,7 @@
         <v>44887</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -24661,7 +24661,7 @@
         <v>45740</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -24739,7 +24739,7 @@
         <v>44637</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -24812,7 +24812,7 @@
         <v>46048</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -24890,7 +24890,7 @@
         <v>46048</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -24968,7 +24968,7 @@
         <v>46048</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -25046,7 +25046,7 @@
         <v>45800</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -25124,7 +25124,7 @@
         <v>45642</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -25202,7 +25202,7 @@
         <v>45903</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -25280,7 +25280,7 @@
         <v>46050</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -25358,7 +25358,7 @@
         <v>45903</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -25436,7 +25436,7 @@
         <v>45904</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -25514,7 +25514,7 @@
         <v>45903</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -25592,7 +25592,7 @@
         <v>46050</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -25670,7 +25670,7 @@
         <v>45903</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -25748,7 +25748,7 @@
         <v>45904</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -25826,7 +25826,7 @@
         <v>45800</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -25904,7 +25904,7 @@
         <v>45903</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -25982,7 +25982,7 @@
         <v>46049</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -26055,7 +26055,7 @@
         <v>45908</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -26128,7 +26128,7 @@
         <v>45905</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -26206,7 +26206,7 @@
         <v>46052</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -26279,7 +26279,7 @@
         <v>45905</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -26357,7 +26357,7 @@
         <v>45622</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -26430,7 +26430,7 @@
         <v>44966</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -26503,7 +26503,7 @@
         <v>46055</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -26581,7 +26581,7 @@
         <v>46058</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -26659,7 +26659,7 @@
         <v>44964</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -26737,7 +26737,7 @@
         <v>46058</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -26815,7 +26815,7 @@
         <v>46058</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -26893,7 +26893,7 @@
         <v>44897</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -26971,7 +26971,7 @@
         <v>46060</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -27044,7 +27044,7 @@
         <v>46058</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -27122,7 +27122,7 @@
         <v>46064</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -27200,7 +27200,7 @@
         <v>44966</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -27273,7 +27273,7 @@
         <v>46064</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -27351,7 +27351,7 @@
         <v>46064</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -27429,7 +27429,7 @@
         <v>46063</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -27507,7 +27507,7 @@
         <v>46064</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -27585,7 +27585,7 @@
         <v>46063</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -27663,7 +27663,7 @@
         <v>46064</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -27741,7 +27741,7 @@
         <v>46064</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -27819,7 +27819,7 @@
         <v>46065</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -27897,7 +27897,7 @@
         <v>45554</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -27970,7 +27970,7 @@
         <v>46065</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -28048,7 +28048,7 @@
         <v>44491</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -28121,7 +28121,7 @@
         <v>46069</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -28199,7 +28199,7 @@
         <v>45924</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -28272,7 +28272,7 @@
         <v>46070</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -28350,7 +28350,7 @@
         <v>46070</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -28428,7 +28428,7 @@
         <v>44677</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -28501,7 +28501,7 @@
         <v>46073</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -28579,7 +28579,7 @@
         <v>45554</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -28652,7 +28652,7 @@
         <v>46076</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -28730,7 +28730,7 @@
         <v>46076</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -28808,7 +28808,7 @@
         <v>46078</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -28886,7 +28886,7 @@
         <v>46079</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -28964,7 +28964,7 @@
         <v>46080</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -29042,7 +29042,7 @@
         <v>45566</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -29120,7 +29120,7 @@
         <v>45555</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -29198,7 +29198,7 @@
         <v>45678</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -29276,7 +29276,7 @@
         <v>46080</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -29354,7 +29354,7 @@
         <v>45931</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -29427,7 +29427,7 @@
         <v>46080</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -29505,7 +29505,7 @@
         <v>46080</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -29583,7 +29583,7 @@
         <v>46085</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -29661,7 +29661,7 @@
         <v>45428</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -29734,7 +29734,7 @@
         <v>45229</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -29812,7 +29812,7 @@
         <v>46085</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -29890,7 +29890,7 @@
         <v>46085</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -29968,7 +29968,7 @@
         <v>46085</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -30046,7 +30046,7 @@
         <v>45935</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -30124,7 +30124,7 @@
         <v>45343</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -30202,7 +30202,7 @@
         <v>45441</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -30275,7 +30275,7 @@
         <v>45441</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -30348,7 +30348,7 @@
         <v>44964</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -30426,7 +30426,7 @@
         <v>45179</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -30499,7 +30499,7 @@
         <v>45179</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -30572,7 +30572,7 @@
         <v>45846</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -30650,7 +30650,7 @@
         <v>44734</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -30723,7 +30723,7 @@
         <v>44732</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -30801,7 +30801,7 @@
         <v>46094</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -30879,7 +30879,7 @@
         <v>46097</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -30952,7 +30952,7 @@
         <v>44918</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -31030,7 +31030,7 @@
         <v>46099</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -31103,7 +31103,7 @@
         <v>45705</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -31176,7 +31176,7 @@
         <v>46099</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -31249,7 +31249,7 @@
         <v>45944</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -31322,7 +31322,7 @@
         <v>46099</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -31400,7 +31400,7 @@
         <v>45006</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -31473,7 +31473,7 @@
         <v>46099</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -31551,7 +31551,7 @@
         <v>46099</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -31629,7 +31629,7 @@
         <v>44614</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -31702,7 +31702,7 @@
         <v>45426</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -31775,7 +31775,7 @@
         <v>44679</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -31853,7 +31853,7 @@
         <v>44725</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -31926,7 +31926,7 @@
         <v>44467</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -31999,7 +31999,7 @@
         <v>45950</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -32077,7 +32077,7 @@
         <v>44653</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -32150,7 +32150,7 @@
         <v>45107</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -32223,7 +32223,7 @@
         <v>45415</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -32296,7 +32296,7 @@
         <v>45070</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -32374,7 +32374,7 @@
         <v>46106</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -32452,7 +32452,7 @@
         <v>45600</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -32525,7 +32525,7 @@
         <v>45279</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -32603,7 +32603,7 @@
         <v>45421</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -32681,7 +32681,7 @@
         <v>46111</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -32759,7 +32759,7 @@
         <v>45344</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -32832,7 +32832,7 @@
         <v>45257</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -32910,7 +32910,7 @@
         <v>46113</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -32983,7 +32983,7 @@
         <v>45955</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -33056,7 +33056,7 @@
         <v>46113</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -33134,7 +33134,7 @@
         <v>46114</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -33212,7 +33212,7 @@
         <v>46114</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -33290,7 +33290,7 @@
         <v>46114</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -33368,7 +33368,7 @@
         <v>45812</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -33446,7 +33446,7 @@
         <v>45301</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -33524,7 +33524,7 @@
         <v>45095</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -33597,7 +33597,7 @@
         <v>46120</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -33675,7 +33675,7 @@
         <v>46121</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -33753,7 +33753,7 @@
         <v>45086</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -33826,7 +33826,7 @@
         <v>46125</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -33899,7 +33899,7 @@
         <v>46122</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -33972,7 +33972,7 @@
         <v>45812</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -34050,7 +34050,7 @@
         <v>45071</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -34128,7 +34128,7 @@
         <v>44903</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -34206,7 +34206,7 @@
         <v>45166</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -34284,7 +34284,7 @@
         <v>45075</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -34357,7 +34357,7 @@
         <v>45969</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -34430,7 +34430,7 @@
         <v>45971</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -34503,7 +34503,7 @@
         <v>45639</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -34581,7 +34581,7 @@
         <v>45639</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -34659,7 +34659,7 @@
         <v>46129</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -34737,7 +34737,7 @@
         <v>45665</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -34810,7 +34810,7 @@
         <v>45009</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -34888,7 +34888,7 @@
         <v>45979</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -34961,7 +34961,7 @@
         <v>46128</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -35034,7 +35034,7 @@
         <v>45516</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -35112,7 +35112,7 @@
         <v>45142</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -35185,7 +35185,7 @@
         <v>45616</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -35258,7 +35258,7 @@
         <v>45616</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -35331,7 +35331,7 @@
         <v>45983</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -35404,7 +35404,7 @@
         <v>45983</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -35477,7 +35477,7 @@
         <v>45593</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -35555,7 +35555,7 @@
         <v>45086</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -35628,7 +35628,7 @@
         <v>45706</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -35701,7 +35701,7 @@
         <v>45646</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -35774,7 +35774,7 @@
         <v>45986</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -35847,7 +35847,7 @@
         <v>45692</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -35925,7 +35925,7 @@
         <v>45983</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -35998,7 +35998,7 @@
         <v>45986</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -36071,7 +36071,7 @@
         <v>45985</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -36144,7 +36144,7 @@
         <v>45740</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -36217,7 +36217,7 @@
         <v>44774</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -36295,7 +36295,7 @@
         <v>45095</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -36373,7 +36373,7 @@
         <v>45095</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -36446,7 +36446,7 @@
         <v>45709</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -36524,7 +36524,7 @@
         <v>45728</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -36602,7 +36602,7 @@
         <v>45915</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -36680,7 +36680,7 @@
         <v>45706</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -36753,7 +36753,7 @@
         <v>45853</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -36826,7 +36826,7 @@
         <v>45783</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -36904,7 +36904,7 @@
         <v>45615</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -36982,7 +36982,7 @@
         <v>44973</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -37060,7 +37060,7 @@
         <v>46134</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -37133,7 +37133,7 @@
         <v>45002</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -37211,7 +37211,7 @@
         <v>45530</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -37284,7 +37284,7 @@
         <v>45713</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -37362,7 +37362,7 @@
         <v>45700</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -37440,7 +37440,7 @@
         <v>45744</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -37518,7 +37518,7 @@
         <v>46000</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -37596,7 +37596,7 @@
         <v>45147</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -37669,7 +37669,7 @@
         <v>44759</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -37742,7 +37742,7 @@
         <v>44840</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -37815,7 +37815,7 @@
         <v>45692</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -37893,7 +37893,7 @@
         <v>46002</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -37971,7 +37971,7 @@
         <v>46002</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -38049,7 +38049,7 @@
         <v>45688</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -38127,7 +38127,7 @@
         <v>46002</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -38205,7 +38205,7 @@
         <v>46002</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -38283,7 +38283,7 @@
         <v>46006</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -38361,7 +38361,7 @@
         <v>46006</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -38439,7 +38439,7 @@
         <v>44476</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -38512,7 +38512,7 @@
         <v>46003</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -38585,7 +38585,7 @@
         <v>46006</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -38658,7 +38658,7 @@
         <v>44473</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -38736,7 +38736,7 @@
         <v>45516</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -38809,7 +38809,7 @@
         <v>44820</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -38882,7 +38882,7 @@
         <v>45819</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -38960,7 +38960,7 @@
         <v>45819</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -39038,7 +39038,7 @@
         <v>45041</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -39116,7 +39116,7 @@
         <v>45082</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -39194,7 +39194,7 @@
         <v>45719</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -39272,7 +39272,7 @@
         <v>45688</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -39350,7 +39350,7 @@
         <v>45560</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -39428,7 +39428,7 @@
         <v>45719</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -39506,7 +39506,7 @@
         <v>44834</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -39584,7 +39584,7 @@
         <v>44862</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -39662,7 +39662,7 @@
         <v>44973</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -39740,7 +39740,7 @@
         <v>44880</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -39818,7 +39818,7 @@
         <v>45710</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -39891,7 +39891,7 @@
         <v>45191</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -39964,7 +39964,7 @@
         <v>45832</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -40037,7 +40037,7 @@
         <v>45824</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -40115,7 +40115,7 @@
         <v>45824</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -40193,7 +40193,7 @@
         <v>45824</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -40271,7 +40271,7 @@
         <v>45770</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -40344,7 +40344,7 @@
         <v>45824</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -40422,7 +40422,7 @@
         <v>45236</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -40500,7 +40500,7 @@
         <v>45236</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -40578,7 +40578,7 @@
         <v>44886</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -40651,7 +40651,7 @@
         <v>45070</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -40729,7 +40729,7 @@
         <v>45566</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -40807,7 +40807,7 @@
         <v>45042</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -40880,7 +40880,7 @@
         <v>45728</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -40958,7 +40958,7 @@
         <v>44876</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -41031,7 +41031,7 @@
         <v>46064</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -41109,7 +41109,7 @@
         <v>44642</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -41182,7 +41182,7 @@
         <v>44536</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -41255,7 +41255,7 @@
         <v>45735</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -41333,7 +41333,7 @@
         <v>45237</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -41411,7 +41411,7 @@
         <v>45076</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -41489,7 +41489,7 @@
         <v>45735</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -41567,7 +41567,7 @@
         <v>46141</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -41640,7 +41640,7 @@
         <v>44944</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -41718,7 +41718,7 @@
         <v>44595</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -41796,7 +41796,7 @@
         <v>45233</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -41869,7 +41869,7 @@
         <v>44564</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -41942,7 +41942,7 @@
         <v>45566</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -42020,7 +42020,7 @@
         <v>45095</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -42093,7 +42093,7 @@
         <v>45082</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -42171,7 +42171,7 @@
         <v>45082</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -42249,7 +42249,7 @@
         <v>45013</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -42327,7 +42327,7 @@
         <v>45086</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -42400,7 +42400,7 @@
         <v>44589</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -42473,7 +42473,7 @@
         <v>45980</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -42546,7 +42546,7 @@
         <v>45184</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -42619,7 +42619,7 @@
         <v>45407</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -42692,7 +42692,7 @@
         <v>45835</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -42770,7 +42770,7 @@
         <v>45845</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -42848,7 +42848,7 @@
         <v>44900</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -42921,7 +42921,7 @@
         <v>46160</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -42994,7 +42994,7 @@
         <v>45357</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -43067,7 +43067,7 @@
         <v>44887</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -43140,7 +43140,7 @@
         <v>45259</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -43213,7 +43213,7 @@
         <v>46077</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -43291,7 +43291,7 @@
         <v>45275</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -43364,7 +43364,7 @@
         <v>45463</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -43437,7 +43437,7 @@
         <v>44995</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -43515,7 +43515,7 @@
         <v>45677</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -43593,7 +43593,7 @@
         <v>45103</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -43666,7 +43666,7 @@
         <v>45840</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -43744,7 +43744,7 @@
         <v>45113</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -43817,7 +43817,7 @@
         <v>44993</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -43890,7 +43890,7 @@
         <v>44966</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -43968,7 +43968,7 @@
         <v>45845</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -44046,7 +44046,7 @@
         <v>45293</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -44119,7 +44119,7 @@
         <v>45391</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -44192,7 +44192,7 @@
         <v>45250</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -44270,7 +44270,7 @@
         <v>45776</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -44343,7 +44343,7 @@
         <v>44949</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -44416,7 +44416,7 @@
         <v>45853</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -44489,7 +44489,7 @@
         <v>44973</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -44567,7 +44567,7 @@
         <v>45854</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -44640,7 +44640,7 @@
         <v>44922</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -44718,7 +44718,7 @@
         <v>45103</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -44791,7 +44791,7 @@
         <v>45855</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -44864,7 +44864,7 @@
         <v>45854</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -44937,7 +44937,7 @@
         <v>45341</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -45015,7 +45015,7 @@
         <v>45523</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -45088,7 +45088,7 @@
         <v>45293</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -45161,7 +45161,7 @@
         <v>45391</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -45234,7 +45234,7 @@
         <v>44678</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -45312,7 +45312,7 @@
         <v>45002</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -45390,7 +45390,7 @@
         <v>45831</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -45463,7 +45463,7 @@
         <v>46176</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -45536,7 +45536,7 @@
         <v>46176</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -45609,7 +45609,7 @@
         <v>45078</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -45682,7 +45682,7 @@
         <v>44993</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -45755,7 +45755,7 @@
         <v>45133</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -45828,7 +45828,7 @@
         <v>44551</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -45901,7 +45901,7 @@
         <v>46176</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -45974,7 +45974,7 @@
         <v>46174</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -46052,7 +46052,7 @@
         <v>45447</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -46130,7 +46130,7 @@
         <v>45167</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -46208,7 +46208,7 @@
         <v>46174</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -46286,7 +46286,7 @@
         <v>46177</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -46359,7 +46359,7 @@
         <v>44937</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -46432,7 +46432,7 @@
         <v>45314</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -46505,7 +46505,7 @@
         <v>45870</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -46578,7 +46578,7 @@
         <v>44981</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -46656,7 +46656,7 @@
         <v>46181</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -46734,7 +46734,7 @@
         <v>45820</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -46812,7 +46812,7 @@
         <v>45870</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -46885,7 +46885,7 @@
         <v>46178</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -46958,7 +46958,7 @@
         <v>46178</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -47031,7 +47031,7 @@
         <v>45041</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -47104,7 +47104,7 @@
         <v>45063</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -47177,7 +47177,7 @@
         <v>46178</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -47250,7 +47250,7 @@
         <v>45113</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -47323,7 +47323,7 @@
         <v>45601</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -47396,7 +47396,7 @@
         <v>45040</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -47469,7 +47469,7 @@
         <v>45020</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -47542,7 +47542,7 @@
         <v>45593</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -47620,7 +47620,7 @@
         <v>45068</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -47698,7 +47698,7 @@
         <v>46185</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -47771,7 +47771,7 @@
         <v>45149</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -47844,7 +47844,7 @@
         <v>46185</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -47917,7 +47917,7 @@
         <v>45617</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -47995,7 +47995,7 @@
         <v>45302</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -48073,7 +48073,7 @@
         <v>44622</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -48146,7 +48146,7 @@
         <v>46188</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -48219,7 +48219,7 @@
         <v>44564</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -48292,7 +48292,7 @@
         <v>44958</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -48365,7 +48365,7 @@
         <v>45095</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -48438,7 +48438,7 @@
         <v>44516</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -48511,7 +48511,7 @@
         <v>45040</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -48589,7 +48589,7 @@
         <v>45615</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -48667,7 +48667,7 @@
         <v>45709</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -48745,7 +48745,7 @@
         <v>45609</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -48823,7 +48823,7 @@
         <v>45554</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -48896,7 +48896,7 @@
         <v>45880</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -48974,7 +48974,7 @@
         <v>46196</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -49052,7 +49052,7 @@
         <v>45880</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -49130,7 +49130,7 @@
         <v>45551</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -49203,7 +49203,7 @@
         <v>45846</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -49281,7 +49281,7 @@
         <v>46199</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -49354,7 +49354,7 @@
         <v>44622</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -49427,7 +49427,7 @@
         <v>46203</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -49500,7 +49500,7 @@
         <v>45077</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -49578,7 +49578,7 @@
         <v>45881</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -49656,7 +49656,7 @@
         <v>45206</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -49729,7 +49729,7 @@
         <v>45883</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -49807,7 +49807,7 @@
         <v>45084</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -49880,7 +49880,7 @@
         <v>45456</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -49958,7 +49958,7 @@
         <v>44550</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -50031,7 +50031,7 @@
         <v>45174</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -50109,7 +50109,7 @@
         <v>44508</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -50182,7 +50182,7 @@
         <v>46204</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -50255,7 +50255,7 @@
         <v>45645</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -50333,7 +50333,7 @@
         <v>44795</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -50411,7 +50411,7 @@
         <v>46209</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -50484,7 +50484,7 @@
         <v>45715</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -50557,7 +50557,7 @@
         <v>44634</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -50635,7 +50635,7 @@
         <v>46209</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -50708,7 +50708,7 @@
         <v>46209</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -50781,7 +50781,7 @@
         <v>46211</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -50854,7 +50854,7 @@
         <v>45762</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -50927,7 +50927,7 @@
         <v>46212</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -51000,7 +51000,7 @@
         <v>45147</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -51073,7 +51073,7 @@
         <v>46255</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -51151,7 +51151,7 @@
         <v>45209</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -51224,7 +51224,7 @@
         <v>45209</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -51297,7 +51297,7 @@
         <v>45243</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -51375,7 +51375,7 @@
         <v>46258</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -51453,7 +51453,7 @@
         <v>46258</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -51531,7 +51531,7 @@
         <v>45660</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -51609,7 +51609,7 @@
         <v>45103</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -51682,7 +51682,7 @@
         <v>45253</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -51760,7 +51760,7 @@
         <v>44664</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -51838,7 +51838,7 @@
         <v>45274</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -51911,7 +51911,7 @@
         <v>46218</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -51989,7 +51989,7 @@
         <v>44767</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -52062,7 +52062,7 @@
         <v>45720</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -52140,7 +52140,7 @@
         <v>44735</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -52213,7 +52213,7 @@
         <v>46218</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -52291,7 +52291,7 @@
         <v>46219</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -52364,7 +52364,7 @@
         <v>44729</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -52437,7 +52437,7 @@
         <v>45149</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -52510,7 +52510,7 @@
         <v>45257</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -52588,7 +52588,7 @@
         <v>45314</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -52661,7 +52661,7 @@
         <v>44672</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -52734,7 +52734,7 @@
         <v>45308</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -52807,7 +52807,7 @@
         <v>44823</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -52880,7 +52880,7 @@
         <v>45623</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -52953,7 +52953,7 @@
         <v>44813</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -53031,7 +53031,7 @@
         <v>44833</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -53109,7 +53109,7 @@
         <v>45468</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -53187,7 +53187,7 @@
         <v>45379</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -53260,7 +53260,7 @@
         <v>45309</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -53338,7 +53338,7 @@
         <v>45309</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -53411,7 +53411,7 @@
         <v>45309</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -53484,7 +53484,7 @@
         <v>45257</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -53557,7 +53557,7 @@
         <v>45302</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -53635,7 +53635,7 @@
         <v>44966</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -53708,7 +53708,7 @@
         <v>46268</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -53781,7 +53781,7 @@
         <v>46226</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -53854,7 +53854,7 @@
         <v>46269</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -53927,7 +53927,7 @@
         <v>44767</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -54000,7 +54000,7 @@
         <v>46269</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -54073,7 +54073,7 @@
         <v>46226</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -54146,7 +54146,7 @@
         <v>46225</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -54219,7 +54219,7 @@
         <v>46225</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -54292,7 +54292,7 @@
         <v>46269</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -54365,7 +54365,7 @@
         <v>46269</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -54438,7 +54438,7 @@
         <v>46269</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -54511,7 +54511,7 @@
         <v>44817</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -54589,7 +54589,7 @@
         <v>45040</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -54662,7 +54662,7 @@
         <v>44595</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -54735,7 +54735,7 @@
         <v>45009</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -54808,7 +54808,7 @@
         <v>46232</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -54881,7 +54881,7 @@
         <v>45084</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -54954,7 +54954,7 @@
         <v>44782</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -55027,7 +55027,7 @@
         <v>46233</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -55100,7 +55100,7 @@
         <v>44714</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -55173,7 +55173,7 @@
         <v>45299</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -55246,7 +55246,7 @@
         <v>46279</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -55319,7 +55319,7 @@
         <v>46279</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -55392,7 +55392,7 @@
         <v>44749</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -55465,7 +55465,7 @@
         <v>46279</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -55538,7 +55538,7 @@
         <v>44861</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -55616,7 +55616,7 @@
         <v>44987</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -55689,7 +55689,7 @@
         <v>44879</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -55762,7 +55762,7 @@
         <v>44871</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -55835,7 +55835,7 @@
         <v>44526</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -55908,7 +55908,7 @@
         <v>46282</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -55986,7 +55986,7 @@
         <v>46282</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -56064,7 +56064,7 @@
         <v>46282</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -56142,7 +56142,7 @@
         <v>46282</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -56220,7 +56220,7 @@
         <v>44914</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -56298,7 +56298,7 @@
         <v>46282</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -56376,7 +56376,7 @@
         <v>46282</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -56454,7 +56454,7 @@
         <v>46282</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -56532,7 +56532,7 @@
         <v>46282</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -56610,7 +56610,7 @@
         <v>45548</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -56683,7 +56683,7 @@
         <v>46282</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -56761,7 +56761,7 @@
         <v>45763</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -56834,7 +56834,7 @@
         <v>46281</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -56907,7 +56907,7 @@
         <v>44503</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -56980,7 +56980,7 @@
         <v>45636</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -57053,7 +57053,7 @@
         <v>44607</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -57126,7 +57126,7 @@
         <v>44953</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -57204,7 +57204,7 @@
         <v>44817</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -57277,7 +57277,7 @@
         <v>46286</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -57355,7 +57355,7 @@
         <v>45523</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -57433,7 +57433,7 @@
         <v>45863</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -57506,7 +57506,7 @@
         <v>44867</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -57579,7 +57579,7 @@
         <v>44732</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -57657,7 +57657,7 @@
         <v>44949</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -57730,7 +57730,7 @@
         <v>44949</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -57803,7 +57803,7 @@
         <v>44949</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -57876,7 +57876,7 @@
         <v>44960</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -57954,7 +57954,7 @@
         <v>44966</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -58027,7 +58027,7 @@
         <v>44662</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -58105,7 +58105,7 @@
         <v>45555</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -58183,7 +58183,7 @@
         <v>44918</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -58261,7 +58261,7 @@
         <v>45622</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -58334,7 +58334,7 @@
         <v>44930</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -58412,7 +58412,7 @@
         <v>45258</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -58485,7 +58485,7 @@
         <v>45379</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -58558,7 +58558,7 @@
         <v>45260</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -58631,7 +58631,7 @@
         <v>45021</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -58704,7 +58704,7 @@
         <v>45167</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -58777,7 +58777,7 @@
         <v>45008</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -58850,7 +58850,7 @@
         <v>44616</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -58928,7 +58928,7 @@
         <v>44550</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -59001,7 +59001,7 @@
         <v>45230</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -59074,7 +59074,7 @@
         <v>45013</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -59152,7 +59152,7 @@
         <v>45554</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -59225,7 +59225,7 @@
         <v>45095</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -59303,7 +59303,7 @@
         <v>45055</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -59376,7 +59376,7 @@
         <v>44995</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -59454,7 +59454,7 @@
         <v>45095</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -59527,7 +59527,7 @@
         <v>45425</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -59600,7 +59600,7 @@
         <v>44898</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -59673,7 +59673,7 @@
         <v>45177</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -59746,7 +59746,7 @@
         <v>45456</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -59824,7 +59824,7 @@
         <v>44865</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -59902,7 +59902,7 @@
         <v>44980</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -59975,7 +59975,7 @@
         <v>44966</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -60053,7 +60053,7 @@
         <v>44914</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -60126,7 +60126,7 @@
         <v>44974</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -60199,7 +60199,7 @@
         <v>44950</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -60277,7 +60277,7 @@
         <v>45601</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -60350,7 +60350,7 @@
         <v>45323</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -60428,7 +60428,7 @@
         <v>45181</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -60501,7 +60501,7 @@
         <v>45042</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -60579,7 +60579,7 @@
         <v>45257</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -60657,7 +60657,7 @@
         <v>45225</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -60730,7 +60730,7 @@
         <v>45082</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -60808,7 +60808,7 @@
         <v>45149</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -60881,7 +60881,7 @@
         <v>44993</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -60954,7 +60954,7 @@
         <v>44987</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -61027,7 +61027,7 @@
         <v>45247</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -61100,7 +61100,7 @@
         <v>45422</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -61173,7 +61173,7 @@
         <v>45214</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -61246,7 +61246,7 @@
         <v>45421</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -61324,7 +61324,7 @@
         <v>45420</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -61397,7 +61397,7 @@
         <v>45125</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -61475,7 +61475,7 @@
         <v>45033</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -61553,7 +61553,7 @@
         <v>45103</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -61626,7 +61626,7 @@
         <v>45688</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -61704,7 +61704,7 @@
         <v>45022</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -61782,7 +61782,7 @@
         <v>45744</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -61860,7 +61860,7 @@
         <v>45267</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -61938,7 +61938,7 @@
         <v>45202</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -62011,7 +62011,7 @@
         <v>45118</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -62084,7 +62084,7 @@
         <v>45225</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -62157,7 +62157,7 @@
         <v>44900</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -62230,7 +62230,7 @@
         <v>44981</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -62308,7 +62308,7 @@
         <v>44922</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -62386,7 +62386,7 @@
         <v>45191</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -62459,7 +62459,7 @@
         <v>45178</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -62532,7 +62532,7 @@
         <v>45177</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -62605,7 +62605,7 @@
         <v>45623</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -62683,7 +62683,7 @@
         <v>45639</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -62761,7 +62761,7 @@
         <v>45197</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -62834,7 +62834,7 @@
         <v>45264</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -62912,7 +62912,7 @@
         <v>45110</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -62985,7 +62985,7 @@
         <v>45008</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -63063,7 +63063,7 @@
         <v>45593</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -63141,7 +63141,7 @@
         <v>44942</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -63214,7 +63214,7 @@
         <v>44617</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -63287,7 +63287,7 @@
         <v>44939</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -63360,7 +63360,7 @@
         <v>45202</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -63433,7 +63433,7 @@
         <v>44946</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -63511,7 +63511,7 @@
         <v>44946</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -63589,7 +63589,7 @@
         <v>45082</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -63667,7 +63667,7 @@
         <v>45299</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -63740,7 +63740,7 @@
         <v>45720</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -63818,7 +63818,7 @@
         <v>45250</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -63896,7 +63896,7 @@
         <v>45206</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -63969,7 +63969,7 @@
         <v>44964</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -64047,7 +64047,7 @@
         <v>45607</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -64120,7 +64120,7 @@
         <v>45607</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -64193,7 +64193,7 @@
         <v>44490</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
@@ -64266,7 +64266,7 @@
         <v>45770</v>
       </c>
       <c r="E802" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -64339,7 +64339,7 @@
         <v>45749</v>
       </c>
       <c r="E803" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
@@ -64417,7 +64417,7 @@
         <v>45639</v>
       </c>
       <c r="E804" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
@@ -64495,7 +64495,7 @@
         <v>45709</v>
       </c>
       <c r="E805" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>
@@ -64573,7 +64573,7 @@
         <v>45566</v>
       </c>
       <c r="E806" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F806" t="inlineStr">
         <is>
@@ -64651,7 +64651,7 @@
         <v>45566</v>
       </c>
       <c r="E807" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F807" t="inlineStr">
         <is>
@@ -64729,7 +64729,7 @@
         <v>45740</v>
       </c>
       <c r="E808" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F808" t="inlineStr">
         <is>
@@ -64807,7 +64807,7 @@
         <v>45103</v>
       </c>
       <c r="E809" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F809" t="inlineStr">
         <is>
@@ -64880,7 +64880,7 @@
         <v>45232</v>
       </c>
       <c r="E810" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F810" t="inlineStr">
         <is>
@@ -64958,7 +64958,7 @@
         <v>45609</v>
       </c>
       <c r="E811" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F811" t="inlineStr">
         <is>
@@ -65036,7 +65036,7 @@
         <v>45566</v>
       </c>
       <c r="E812" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F812" t="inlineStr">
         <is>
@@ -65114,7 +65114,7 @@
         <v>45566</v>
       </c>
       <c r="E813" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F813" t="inlineStr">
         <is>
@@ -65192,7 +65192,7 @@
         <v>45566</v>
       </c>
       <c r="E814" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F814" t="inlineStr">
         <is>
@@ -65270,7 +65270,7 @@
         <v>45735</v>
       </c>
       <c r="E815" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F815" t="inlineStr">
         <is>
@@ -65348,7 +65348,7 @@
         <v>45736</v>
       </c>
       <c r="E816" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F816" t="inlineStr">
         <is>
@@ -65426,7 +65426,7 @@
         <v>45530</v>
       </c>
       <c r="E817" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F817" t="inlineStr">
         <is>
@@ -65499,7 +65499,7 @@
         <v>45642</v>
       </c>
       <c r="E818" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F818" t="inlineStr">
         <is>
@@ -65572,7 +65572,7 @@
         <v>45267</v>
       </c>
       <c r="E819" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F819" t="inlineStr">
         <is>
@@ -65650,7 +65650,7 @@
         <v>45530</v>
       </c>
       <c r="E820" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F820" t="inlineStr">
         <is>
@@ -65723,7 +65723,7 @@
         <v>45727</v>
       </c>
       <c r="E821" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F821" t="inlineStr">
         <is>
@@ -65796,7 +65796,7 @@
         <v>45371</v>
       </c>
       <c r="E822" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F822" t="inlineStr">
         <is>
@@ -65874,7 +65874,7 @@
         <v>45644</v>
       </c>
       <c r="E823" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F823" t="inlineStr">
         <is>
@@ -65947,7 +65947,7 @@
         <v>45428</v>
       </c>
       <c r="E824" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F824" t="inlineStr">
         <is>
@@ -66020,7 +66020,7 @@
         <v>45429</v>
       </c>
       <c r="E825" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F825" t="inlineStr">
         <is>
@@ -66093,7 +66093,7 @@
         <v>45250</v>
       </c>
       <c r="E826" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F826" t="inlineStr">
         <is>
@@ -66171,7 +66171,7 @@
         <v>46188</v>
       </c>
       <c r="E827" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F827" t="inlineStr">
         <is>
@@ -66249,7 +66249,7 @@
         <v>46258</v>
       </c>
       <c r="E828" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F828" t="inlineStr">
         <is>

--- a/Översikt FINSPÅNG.xlsx
+++ b/Översikt FINSPÅNG.xlsx
@@ -601,7 +601,7 @@
         <v>46244</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -727,7 +727,7 @@
         <v>45945</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -858,7 +858,7 @@
         <v>45134</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
         <v>44896</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1121,7 +1121,7 @@
         <v>44888</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>45210</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1369,7 +1369,7 @@
         <v>44777</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1488,7 +1488,7 @@
         <v>44897</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1607,7 +1607,7 @@
         <v>44910</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1734,7 +1734,7 @@
         <v>45322</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1855,7 +1855,7 @@
         <v>44624</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1971,7 +1971,7 @@
         <v>44599</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2082,7 +2082,7 @@
         <v>45891</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2198,7 +2198,7 @@
         <v>45421</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2318,7 +2318,7 @@
         <v>45238</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2433,7 +2433,7 @@
         <v>45898</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2548,7 +2548,7 @@
         <v>45267</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2663,7 +2663,7 @@
         <v>45679</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2782,7 +2782,7 @@
         <v>45947</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2896,7 +2896,7 @@
         <v>45812</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3010,7 +3010,7 @@
         <v>44791</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3124,7 +3124,7 @@
         <v>44665</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3237,7 +3237,7 @@
         <v>45681</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3354,7 +3354,7 @@
         <v>45800</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3466,7 +3466,7 @@
         <v>45819</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3582,7 +3582,7 @@
         <v>45082</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3694,7 +3694,7 @@
         <v>45602</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3806,7 +3806,7 @@
         <v>44774</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3918,7 +3918,7 @@
         <v>46196</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4030,7 +4030,7 @@
         <v>44690</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4141,7 +4141,7 @@
         <v>44816</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4247,7 +4247,7 @@
         <v>45425</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4353,7 +4353,7 @@
         <v>45121</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4468,7 +4468,7 @@
         <v>45894</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4583,7 +4583,7 @@
         <v>45905</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4694,7 +4694,7 @@
         <v>45950</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4805,7 +4805,7 @@
         <v>45644</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4911,7 +4911,7 @@
         <v>44981</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5022,7 +5022,7 @@
         <v>46174</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5133,7 +5133,7 @@
         <v>46181</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5244,7 +5244,7 @@
         <v>46181</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5355,7 +5355,7 @@
         <v>45441</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5466,7 +5466,7 @@
         <v>45235</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5577,7 +5577,7 @@
         <v>44903</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5687,7 +5687,7 @@
         <v>45477</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5802,7 +5802,7 @@
         <v>44480</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5913,7 +5913,7 @@
         <v>44683</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6023,7 +6023,7 @@
         <v>44776</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6128,7 +6128,7 @@
         <v>44504</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6238,7 +6238,7 @@
         <v>44529</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6343,7 +6343,7 @@
         <v>45232</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6453,7 +6453,7 @@
         <v>44915</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6563,7 +6563,7 @@
         <v>44897</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6677,7 +6677,7 @@
         <v>44915</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6787,7 +6787,7 @@
         <v>45905</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6897,7 +6897,7 @@
         <v>45883</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7007,7 +7007,7 @@
         <v>46058</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7121,7 +7121,7 @@
         <v>45566</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7235,7 +7235,7 @@
         <v>44599</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7345,7 +7345,7 @@
         <v>45328</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7454,7 +7454,7 @@
         <v>46129</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7568,7 +7568,7 @@
         <v>45615</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7682,7 +7682,7 @@
         <v>46043</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7796,7 +7796,7 @@
         <v>45447</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7906,7 +7906,7 @@
         <v>44817</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8016,7 +8016,7 @@
         <v>44992</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8126,7 +8126,7 @@
         <v>45070</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8236,7 +8236,7 @@
         <v>44965</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8350,7 +8350,7 @@
         <v>46155</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8464,7 +8464,7 @@
         <v>45846</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8574,7 +8574,7 @@
         <v>45845</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8684,7 +8684,7 @@
         <v>46189</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8789,7 +8789,7 @@
         <v>45880</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8899,7 +8899,7 @@
         <v>45149</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9008,7 +9008,7 @@
         <v>46258</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9122,7 +9122,7 @@
         <v>46258</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9232,7 +9232,7 @@
         <v>46181</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9342,7 +9342,7 @@
         <v>45229</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9452,7 +9452,7 @@
         <v>45302</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9561,7 +9561,7 @@
         <v>45555</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9675,7 +9675,7 @@
         <v>44501</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9785,7 +9785,7 @@
         <v>44930</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9895,7 +9895,7 @@
         <v>45636</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10000,7 +10000,7 @@
         <v>44622</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10105,7 +10105,7 @@
         <v>45082</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10215,7 +10215,7 @@
         <v>45744</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10329,7 +10329,7 @@
         <v>45446</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10434,7 +10434,7 @@
         <v>45567</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10548,7 +10548,7 @@
         <v>44711</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10658,7 +10658,7 @@
         <v>45428</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10763,7 +10763,7 @@
         <v>46107</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10873,7 +10873,7 @@
         <v>46188</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10987,7 +10987,7 @@
         <v>44755</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11065,7 +11065,7 @@
         <v>44675</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11138,7 +11138,7 @@
         <v>44676</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11216,7 +11216,7 @@
         <v>44864</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11289,7 +11289,7 @@
         <v>44600</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11362,7 +11362,7 @@
         <v>44536</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11440,7 +11440,7 @@
         <v>44824</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11513,7 +11513,7 @@
         <v>44795</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11586,7 +11586,7 @@
         <v>44799</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11659,7 +11659,7 @@
         <v>44856</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11732,7 +11732,7 @@
         <v>44578</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11810,7 +11810,7 @@
         <v>44675</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -11883,7 +11883,7 @@
         <v>44852</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -11961,7 +11961,7 @@
         <v>44601</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12039,7 +12039,7 @@
         <v>44601</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12112,7 +12112,7 @@
         <v>44551</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12185,7 +12185,7 @@
         <v>44525</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12258,7 +12258,7 @@
         <v>44574</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12336,7 +12336,7 @@
         <v>44588</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12414,7 +12414,7 @@
         <v>44574</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12487,7 +12487,7 @@
         <v>44889</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12560,7 +12560,7 @@
         <v>44627</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -12633,7 +12633,7 @@
         <v>44503</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -12711,7 +12711,7 @@
         <v>44525</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -12789,7 +12789,7 @@
         <v>44503</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -12862,7 +12862,7 @@
         <v>44874</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -12935,7 +12935,7 @@
         <v>44502</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13013,7 +13013,7 @@
         <v>44551</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -13086,7 +13086,7 @@
         <v>44712</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -13164,7 +13164,7 @@
         <v>44581</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -13237,7 +13237,7 @@
         <v>44833</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -13310,7 +13310,7 @@
         <v>44601</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -13383,7 +13383,7 @@
         <v>44859</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -13456,7 +13456,7 @@
         <v>44735</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -13529,7 +13529,7 @@
         <v>44672</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -13602,7 +13602,7 @@
         <v>44796</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -13675,7 +13675,7 @@
         <v>44782</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -13748,7 +13748,7 @@
         <v>44741</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -13821,7 +13821,7 @@
         <v>44859</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -13894,7 +13894,7 @@
         <v>44613</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -13972,7 +13972,7 @@
         <v>44678</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -14045,7 +14045,7 @@
         <v>44855</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -14123,7 +14123,7 @@
         <v>44887</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -14196,7 +14196,7 @@
         <v>44860</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -14269,7 +14269,7 @@
         <v>44753</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -14342,7 +14342,7 @@
         <v>44802</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -14415,7 +14415,7 @@
         <v>44844</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -14493,7 +14493,7 @@
         <v>44781</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -14566,7 +14566,7 @@
         <v>44541</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -14639,7 +14639,7 @@
         <v>44564</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -14712,7 +14712,7 @@
         <v>44859</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -14785,7 +14785,7 @@
         <v>44469</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -14858,7 +14858,7 @@
         <v>44595</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -14931,7 +14931,7 @@
         <v>44582</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -15004,7 +15004,7 @@
         <v>44508</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -15077,7 +15077,7 @@
         <v>44816</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -15150,7 +15150,7 @@
         <v>44656</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -15223,7 +15223,7 @@
         <v>44627</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -15296,7 +15296,7 @@
         <v>44587</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -15369,7 +15369,7 @@
         <v>44820</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -15442,7 +15442,7 @@
         <v>44532</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -15515,7 +15515,7 @@
         <v>44552</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -15588,7 +15588,7 @@
         <v>44879</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -15661,7 +15661,7 @@
         <v>44581</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -15734,7 +15734,7 @@
         <v>44588</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -15812,7 +15812,7 @@
         <v>44875</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -15885,7 +15885,7 @@
         <v>44743</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -15958,7 +15958,7 @@
         <v>44831</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -16036,7 +16036,7 @@
         <v>44819</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -16109,7 +16109,7 @@
         <v>44581</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -16187,7 +16187,7 @@
         <v>44630</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -16260,7 +16260,7 @@
         <v>44469</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -16333,7 +16333,7 @@
         <v>44476</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -16406,7 +16406,7 @@
         <v>44804</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -16484,7 +16484,7 @@
         <v>44601</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -16557,7 +16557,7 @@
         <v>44742</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -16635,7 +16635,7 @@
         <v>44859</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -16708,7 +16708,7 @@
         <v>44476</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -16781,7 +16781,7 @@
         <v>44600</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -16854,7 +16854,7 @@
         <v>44481</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -16927,7 +16927,7 @@
         <v>44635</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -17000,7 +17000,7 @@
         <v>44776</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -17073,7 +17073,7 @@
         <v>44713</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -17151,7 +17151,7 @@
         <v>44697</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -17229,7 +17229,7 @@
         <v>44468</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -17307,7 +17307,7 @@
         <v>44481</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -17380,7 +17380,7 @@
         <v>44533</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -17453,7 +17453,7 @@
         <v>44601</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -17526,7 +17526,7 @@
         <v>44678</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -17599,7 +17599,7 @@
         <v>44704</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -17672,7 +17672,7 @@
         <v>44564</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -17745,7 +17745,7 @@
         <v>44642</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -17818,7 +17818,7 @@
         <v>44659</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -17896,7 +17896,7 @@
         <v>45617</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -17974,7 +17974,7 @@
         <v>44754</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -18047,7 +18047,7 @@
         <v>45042</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -18120,7 +18120,7 @@
         <v>45330</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -18193,7 +18193,7 @@
         <v>44778</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -18266,7 +18266,7 @@
         <v>44802</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -18339,7 +18339,7 @@
         <v>44833</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -18417,7 +18417,7 @@
         <v>45362</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -18490,7 +18490,7 @@
         <v>45535</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -18568,7 +18568,7 @@
         <v>44770</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -18641,7 +18641,7 @@
         <v>45374</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -18719,7 +18719,7 @@
         <v>45257</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -18797,7 +18797,7 @@
         <v>45257</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -18870,7 +18870,7 @@
         <v>45618</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -18943,7 +18943,7 @@
         <v>44930</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -19016,7 +19016,7 @@
         <v>44930</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -19089,7 +19089,7 @@
         <v>44844</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -19162,7 +19162,7 @@
         <v>45541</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -19240,7 +19240,7 @@
         <v>44806</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -19318,7 +19318,7 @@
         <v>45357</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -19391,7 +19391,7 @@
         <v>44817</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -19464,7 +19464,7 @@
         <v>45744</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -19542,7 +19542,7 @@
         <v>45744</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -19620,7 +19620,7 @@
         <v>44887</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -19693,7 +19693,7 @@
         <v>45252</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -19766,7 +19766,7 @@
         <v>44953</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -19839,7 +19839,7 @@
         <v>45447</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -19917,7 +19917,7 @@
         <v>44767</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -19990,7 +19990,7 @@
         <v>44986</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -20063,7 +20063,7 @@
         <v>45442</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -20136,7 +20136,7 @@
         <v>45258</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -20209,7 +20209,7 @@
         <v>45260</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -20282,7 +20282,7 @@
         <v>44957</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -20355,7 +20355,7 @@
         <v>44816</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -20428,7 +20428,7 @@
         <v>45258</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -20501,7 +20501,7 @@
         <v>45250</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -20574,7 +20574,7 @@
         <v>45323</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -20652,7 +20652,7 @@
         <v>44891</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -20725,7 +20725,7 @@
         <v>45551</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -20798,7 +20798,7 @@
         <v>45097</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -20871,7 +20871,7 @@
         <v>45095</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -20944,7 +20944,7 @@
         <v>45463</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -21017,7 +21017,7 @@
         <v>45796</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -21095,7 +21095,7 @@
         <v>45796</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -21173,7 +21173,7 @@
         <v>45853</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -21246,7 +21246,7 @@
         <v>46030</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -21324,7 +21324,7 @@
         <v>45293</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -21402,7 +21402,7 @@
         <v>44860</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -21475,7 +21475,7 @@
         <v>45328</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -21548,7 +21548,7 @@
         <v>46030</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -21626,7 +21626,7 @@
         <v>45467</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -21699,7 +21699,7 @@
         <v>44476</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -21772,7 +21772,7 @@
         <v>45316</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -21850,7 +21850,7 @@
         <v>45797</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -21923,7 +21923,7 @@
         <v>45797</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -21996,7 +21996,7 @@
         <v>45797</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -22074,7 +22074,7 @@
         <v>45702</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -22152,7 +22152,7 @@
         <v>46029</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -22225,7 +22225,7 @@
         <v>46031</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -22303,7 +22303,7 @@
         <v>45883</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -22381,7 +22381,7 @@
         <v>45888</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -22459,7 +22459,7 @@
         <v>46034</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -22537,7 +22537,7 @@
         <v>46034</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -22615,7 +22615,7 @@
         <v>46034</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -22693,7 +22693,7 @@
         <v>45621</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -22771,7 +22771,7 @@
         <v>45800</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -22849,7 +22849,7 @@
         <v>45337</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -22922,7 +22922,7 @@
         <v>46036</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -23000,7 +23000,7 @@
         <v>46036</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -23078,7 +23078,7 @@
         <v>45428</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -23156,7 +23156,7 @@
         <v>45428</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -23234,7 +23234,7 @@
         <v>45280</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -23312,7 +23312,7 @@
         <v>44844</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -23385,7 +23385,7 @@
         <v>44844</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -23458,7 +23458,7 @@
         <v>44866</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -23531,7 +23531,7 @@
         <v>44840</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -23609,7 +23609,7 @@
         <v>45891</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -23687,7 +23687,7 @@
         <v>45607</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -23760,7 +23760,7 @@
         <v>45707</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -23838,7 +23838,7 @@
         <v>44656</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -23916,7 +23916,7 @@
         <v>45894</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -23994,7 +23994,7 @@
         <v>45896</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -24072,7 +24072,7 @@
         <v>46040</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -24145,7 +24145,7 @@
         <v>45800</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -24223,7 +24223,7 @@
         <v>46040</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -24296,7 +24296,7 @@
         <v>45895</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -24369,7 +24369,7 @@
         <v>44865</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -24442,7 +24442,7 @@
         <v>45898</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -24515,7 +24515,7 @@
         <v>44887</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -24588,7 +24588,7 @@
         <v>44887</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -24661,7 +24661,7 @@
         <v>45740</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -24739,7 +24739,7 @@
         <v>44637</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -24812,7 +24812,7 @@
         <v>46048</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -24890,7 +24890,7 @@
         <v>46048</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -24968,7 +24968,7 @@
         <v>46048</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -25046,7 +25046,7 @@
         <v>45800</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -25124,7 +25124,7 @@
         <v>45642</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -25202,7 +25202,7 @@
         <v>45903</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -25280,7 +25280,7 @@
         <v>46050</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -25358,7 +25358,7 @@
         <v>45903</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -25436,7 +25436,7 @@
         <v>45904</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -25514,7 +25514,7 @@
         <v>45903</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -25592,7 +25592,7 @@
         <v>46050</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -25670,7 +25670,7 @@
         <v>45903</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -25748,7 +25748,7 @@
         <v>45904</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -25826,7 +25826,7 @@
         <v>45800</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -25904,7 +25904,7 @@
         <v>45903</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -25982,7 +25982,7 @@
         <v>46049</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -26055,7 +26055,7 @@
         <v>45908</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -26128,7 +26128,7 @@
         <v>45905</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -26206,7 +26206,7 @@
         <v>46052</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -26279,7 +26279,7 @@
         <v>45905</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -26357,7 +26357,7 @@
         <v>45622</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -26430,7 +26430,7 @@
         <v>44966</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -26503,7 +26503,7 @@
         <v>46055</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -26581,7 +26581,7 @@
         <v>46058</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -26659,7 +26659,7 @@
         <v>44964</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -26737,7 +26737,7 @@
         <v>46058</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -26815,7 +26815,7 @@
         <v>46058</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -26893,7 +26893,7 @@
         <v>44897</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -26971,7 +26971,7 @@
         <v>46060</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -27044,7 +27044,7 @@
         <v>46058</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -27122,7 +27122,7 @@
         <v>46064</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -27200,7 +27200,7 @@
         <v>44966</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -27273,7 +27273,7 @@
         <v>46064</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -27351,7 +27351,7 @@
         <v>46064</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -27429,7 +27429,7 @@
         <v>46063</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -27507,7 +27507,7 @@
         <v>46064</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -27585,7 +27585,7 @@
         <v>46063</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -27663,7 +27663,7 @@
         <v>46064</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -27741,7 +27741,7 @@
         <v>46064</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -27819,7 +27819,7 @@
         <v>46065</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -27897,7 +27897,7 @@
         <v>45554</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -27970,7 +27970,7 @@
         <v>46065</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -28048,7 +28048,7 @@
         <v>44491</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -28121,7 +28121,7 @@
         <v>46069</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -28199,7 +28199,7 @@
         <v>45924</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -28272,7 +28272,7 @@
         <v>46070</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -28350,7 +28350,7 @@
         <v>46070</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -28428,7 +28428,7 @@
         <v>44677</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -28501,7 +28501,7 @@
         <v>46073</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -28579,7 +28579,7 @@
         <v>45554</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -28652,7 +28652,7 @@
         <v>46076</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -28730,7 +28730,7 @@
         <v>46076</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -28808,7 +28808,7 @@
         <v>46078</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -28886,7 +28886,7 @@
         <v>46079</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -28964,7 +28964,7 @@
         <v>46080</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -29042,7 +29042,7 @@
         <v>45566</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -29120,7 +29120,7 @@
         <v>45555</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -29198,7 +29198,7 @@
         <v>45678</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -29276,7 +29276,7 @@
         <v>46080</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -29354,7 +29354,7 @@
         <v>45931</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -29427,7 +29427,7 @@
         <v>46080</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -29505,7 +29505,7 @@
         <v>46080</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -29583,7 +29583,7 @@
         <v>46085</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -29661,7 +29661,7 @@
         <v>45428</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -29734,7 +29734,7 @@
         <v>45229</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -29812,7 +29812,7 @@
         <v>46085</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -29890,7 +29890,7 @@
         <v>46085</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -29968,7 +29968,7 @@
         <v>46085</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -30046,7 +30046,7 @@
         <v>45935</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -30124,7 +30124,7 @@
         <v>45343</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -30202,7 +30202,7 @@
         <v>45441</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -30275,7 +30275,7 @@
         <v>45441</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -30348,7 +30348,7 @@
         <v>44964</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -30426,7 +30426,7 @@
         <v>45179</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -30499,7 +30499,7 @@
         <v>45179</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -30572,7 +30572,7 @@
         <v>45846</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -30650,7 +30650,7 @@
         <v>44734</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -30723,7 +30723,7 @@
         <v>44732</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -30801,7 +30801,7 @@
         <v>46094</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -30879,7 +30879,7 @@
         <v>46097</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -30952,7 +30952,7 @@
         <v>44918</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -31030,7 +31030,7 @@
         <v>46099</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -31103,7 +31103,7 @@
         <v>45705</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -31176,7 +31176,7 @@
         <v>46099</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -31249,7 +31249,7 @@
         <v>45944</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -31322,7 +31322,7 @@
         <v>46099</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -31400,7 +31400,7 @@
         <v>45006</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -31473,7 +31473,7 @@
         <v>46099</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -31551,7 +31551,7 @@
         <v>46099</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -31629,7 +31629,7 @@
         <v>44614</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -31702,7 +31702,7 @@
         <v>45426</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -31775,7 +31775,7 @@
         <v>44679</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -31853,7 +31853,7 @@
         <v>44725</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -31926,7 +31926,7 @@
         <v>44467</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -31999,7 +31999,7 @@
         <v>45950</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -32077,7 +32077,7 @@
         <v>44653</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -32150,7 +32150,7 @@
         <v>45107</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -32223,7 +32223,7 @@
         <v>45415</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -32296,7 +32296,7 @@
         <v>45070</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -32374,7 +32374,7 @@
         <v>46106</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -32452,7 +32452,7 @@
         <v>45600</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -32525,7 +32525,7 @@
         <v>45279</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -32603,7 +32603,7 @@
         <v>45421</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -32681,7 +32681,7 @@
         <v>46111</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -32759,7 +32759,7 @@
         <v>45344</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -32832,7 +32832,7 @@
         <v>45257</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -32910,7 +32910,7 @@
         <v>46113</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -32983,7 +32983,7 @@
         <v>45955</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -33056,7 +33056,7 @@
         <v>46113</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -33134,7 +33134,7 @@
         <v>46114</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -33212,7 +33212,7 @@
         <v>46114</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -33290,7 +33290,7 @@
         <v>46114</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -33368,7 +33368,7 @@
         <v>45812</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -33446,7 +33446,7 @@
         <v>45301</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -33524,7 +33524,7 @@
         <v>45095</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -33597,7 +33597,7 @@
         <v>46120</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -33675,7 +33675,7 @@
         <v>46121</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -33753,7 +33753,7 @@
         <v>45086</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -33826,7 +33826,7 @@
         <v>46125</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -33899,7 +33899,7 @@
         <v>46122</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -33972,7 +33972,7 @@
         <v>45812</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -34050,7 +34050,7 @@
         <v>45071</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -34128,7 +34128,7 @@
         <v>44903</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -34206,7 +34206,7 @@
         <v>45166</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -34284,7 +34284,7 @@
         <v>45075</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -34357,7 +34357,7 @@
         <v>45969</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -34430,7 +34430,7 @@
         <v>45971</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -34503,7 +34503,7 @@
         <v>45639</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -34581,7 +34581,7 @@
         <v>45639</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -34659,7 +34659,7 @@
         <v>46129</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -34737,7 +34737,7 @@
         <v>45665</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -34810,7 +34810,7 @@
         <v>45009</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -34888,7 +34888,7 @@
         <v>45979</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -34961,7 +34961,7 @@
         <v>46128</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -35034,7 +35034,7 @@
         <v>45516</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -35112,7 +35112,7 @@
         <v>45142</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -35185,7 +35185,7 @@
         <v>45616</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -35258,7 +35258,7 @@
         <v>45616</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -35331,7 +35331,7 @@
         <v>45983</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -35404,7 +35404,7 @@
         <v>45983</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -35477,7 +35477,7 @@
         <v>45593</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -35555,7 +35555,7 @@
         <v>45086</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -35628,7 +35628,7 @@
         <v>45706</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -35701,7 +35701,7 @@
         <v>45646</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -35774,7 +35774,7 @@
         <v>45986</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -35847,7 +35847,7 @@
         <v>45692</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -35925,7 +35925,7 @@
         <v>45983</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -35998,7 +35998,7 @@
         <v>45986</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -36071,7 +36071,7 @@
         <v>45985</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -36144,7 +36144,7 @@
         <v>45740</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -36217,7 +36217,7 @@
         <v>44774</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -36295,7 +36295,7 @@
         <v>45095</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -36373,7 +36373,7 @@
         <v>45095</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -36446,7 +36446,7 @@
         <v>45709</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -36524,7 +36524,7 @@
         <v>45728</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -36602,7 +36602,7 @@
         <v>45915</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -36680,7 +36680,7 @@
         <v>45706</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -36753,7 +36753,7 @@
         <v>45853</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -36826,7 +36826,7 @@
         <v>45783</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -36904,7 +36904,7 @@
         <v>45615</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -36982,7 +36982,7 @@
         <v>44973</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -37060,7 +37060,7 @@
         <v>46134</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -37133,7 +37133,7 @@
         <v>45002</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -37211,7 +37211,7 @@
         <v>45530</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -37284,7 +37284,7 @@
         <v>45713</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -37362,7 +37362,7 @@
         <v>45700</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -37440,7 +37440,7 @@
         <v>45744</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -37518,7 +37518,7 @@
         <v>46000</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -37596,7 +37596,7 @@
         <v>45147</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -37669,7 +37669,7 @@
         <v>44759</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -37742,7 +37742,7 @@
         <v>44840</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -37815,7 +37815,7 @@
         <v>45692</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -37893,7 +37893,7 @@
         <v>46002</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -37971,7 +37971,7 @@
         <v>46002</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -38049,7 +38049,7 @@
         <v>45688</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -38127,7 +38127,7 @@
         <v>46002</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -38205,7 +38205,7 @@
         <v>46002</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -38283,7 +38283,7 @@
         <v>46006</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -38361,7 +38361,7 @@
         <v>46006</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -38439,7 +38439,7 @@
         <v>44476</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -38512,7 +38512,7 @@
         <v>46003</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -38585,7 +38585,7 @@
         <v>46006</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -38658,7 +38658,7 @@
         <v>44473</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -38736,7 +38736,7 @@
         <v>45516</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -38809,7 +38809,7 @@
         <v>44820</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -38882,7 +38882,7 @@
         <v>45819</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -38960,7 +38960,7 @@
         <v>45819</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -39038,7 +39038,7 @@
         <v>45041</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -39116,7 +39116,7 @@
         <v>45082</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -39194,7 +39194,7 @@
         <v>45719</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -39272,7 +39272,7 @@
         <v>45688</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -39350,7 +39350,7 @@
         <v>45560</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -39428,7 +39428,7 @@
         <v>45719</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -39506,7 +39506,7 @@
         <v>44834</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -39584,7 +39584,7 @@
         <v>44862</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -39662,7 +39662,7 @@
         <v>44973</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -39740,7 +39740,7 @@
         <v>44880</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -39818,7 +39818,7 @@
         <v>45710</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -39891,7 +39891,7 @@
         <v>45191</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -39964,7 +39964,7 @@
         <v>45832</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -40037,7 +40037,7 @@
         <v>45824</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -40115,7 +40115,7 @@
         <v>45824</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -40193,7 +40193,7 @@
         <v>45824</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -40271,7 +40271,7 @@
         <v>45770</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -40344,7 +40344,7 @@
         <v>45824</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -40422,7 +40422,7 @@
         <v>45236</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -40500,7 +40500,7 @@
         <v>45236</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -40578,7 +40578,7 @@
         <v>44886</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -40651,7 +40651,7 @@
         <v>45070</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -40729,7 +40729,7 @@
         <v>45566</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -40807,7 +40807,7 @@
         <v>45042</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -40880,7 +40880,7 @@
         <v>45728</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -40958,7 +40958,7 @@
         <v>44876</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -41031,7 +41031,7 @@
         <v>46064</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -41109,7 +41109,7 @@
         <v>44642</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -41182,7 +41182,7 @@
         <v>44536</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -41255,7 +41255,7 @@
         <v>45735</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -41333,7 +41333,7 @@
         <v>45237</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -41411,7 +41411,7 @@
         <v>45076</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -41489,7 +41489,7 @@
         <v>45735</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -41567,7 +41567,7 @@
         <v>46141</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -41640,7 +41640,7 @@
         <v>44944</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -41718,7 +41718,7 @@
         <v>44595</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -41796,7 +41796,7 @@
         <v>45233</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -41869,7 +41869,7 @@
         <v>44564</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -41942,7 +41942,7 @@
         <v>45566</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -42020,7 +42020,7 @@
         <v>45095</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -42093,7 +42093,7 @@
         <v>45082</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -42171,7 +42171,7 @@
         <v>45082</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -42249,7 +42249,7 @@
         <v>45013</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -42327,7 +42327,7 @@
         <v>45086</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -42400,7 +42400,7 @@
         <v>44589</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -42473,7 +42473,7 @@
         <v>45980</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -42546,7 +42546,7 @@
         <v>45184</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -42619,7 +42619,7 @@
         <v>45407</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -42692,7 +42692,7 @@
         <v>45835</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -42770,7 +42770,7 @@
         <v>45845</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -42848,7 +42848,7 @@
         <v>44900</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -42921,7 +42921,7 @@
         <v>46160</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -42994,7 +42994,7 @@
         <v>45357</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -43067,7 +43067,7 @@
         <v>44887</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -43140,7 +43140,7 @@
         <v>45259</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -43213,7 +43213,7 @@
         <v>46077</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -43291,7 +43291,7 @@
         <v>45275</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -43364,7 +43364,7 @@
         <v>45463</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -43437,7 +43437,7 @@
         <v>44995</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -43515,7 +43515,7 @@
         <v>45677</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -43593,7 +43593,7 @@
         <v>45103</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -43666,7 +43666,7 @@
         <v>45840</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -43744,7 +43744,7 @@
         <v>45113</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -43817,7 +43817,7 @@
         <v>44993</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -43890,7 +43890,7 @@
         <v>44966</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -43968,7 +43968,7 @@
         <v>45845</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -44046,7 +44046,7 @@
         <v>45293</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -44119,7 +44119,7 @@
         <v>45391</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -44192,7 +44192,7 @@
         <v>45250</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -44270,7 +44270,7 @@
         <v>45776</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -44343,7 +44343,7 @@
         <v>44949</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -44416,7 +44416,7 @@
         <v>45853</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -44489,7 +44489,7 @@
         <v>44973</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -44567,7 +44567,7 @@
         <v>45854</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -44640,7 +44640,7 @@
         <v>44922</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -44718,7 +44718,7 @@
         <v>45103</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -44791,7 +44791,7 @@
         <v>45855</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -44864,7 +44864,7 @@
         <v>45854</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -44937,7 +44937,7 @@
         <v>45341</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -45015,7 +45015,7 @@
         <v>45523</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -45088,7 +45088,7 @@
         <v>45293</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -45161,7 +45161,7 @@
         <v>45391</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -45234,7 +45234,7 @@
         <v>44678</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -45312,7 +45312,7 @@
         <v>45002</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -45390,7 +45390,7 @@
         <v>45831</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -45463,7 +45463,7 @@
         <v>46176</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -45536,7 +45536,7 @@
         <v>46176</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -45609,7 +45609,7 @@
         <v>45078</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -45682,7 +45682,7 @@
         <v>44993</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -45755,7 +45755,7 @@
         <v>45133</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -45828,7 +45828,7 @@
         <v>44551</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -45901,7 +45901,7 @@
         <v>46176</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -45974,7 +45974,7 @@
         <v>46174</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -46052,7 +46052,7 @@
         <v>45447</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -46130,7 +46130,7 @@
         <v>45167</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -46208,7 +46208,7 @@
         <v>46174</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -46286,7 +46286,7 @@
         <v>46177</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -46359,7 +46359,7 @@
         <v>44937</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -46432,7 +46432,7 @@
         <v>45314</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -46505,7 +46505,7 @@
         <v>45870</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -46578,7 +46578,7 @@
         <v>44981</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -46656,7 +46656,7 @@
         <v>46181</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -46734,7 +46734,7 @@
         <v>45820</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -46812,7 +46812,7 @@
         <v>45870</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -46885,7 +46885,7 @@
         <v>46178</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -46958,7 +46958,7 @@
         <v>46178</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -47031,7 +47031,7 @@
         <v>45041</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -47104,7 +47104,7 @@
         <v>45063</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -47177,7 +47177,7 @@
         <v>46178</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -47250,7 +47250,7 @@
         <v>45113</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -47323,7 +47323,7 @@
         <v>45601</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -47396,7 +47396,7 @@
         <v>45040</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -47469,7 +47469,7 @@
         <v>45020</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -47542,7 +47542,7 @@
         <v>45593</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -47620,7 +47620,7 @@
         <v>45068</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -47698,7 +47698,7 @@
         <v>46185</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -47771,7 +47771,7 @@
         <v>45149</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -47844,7 +47844,7 @@
         <v>46185</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -47917,7 +47917,7 @@
         <v>45617</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -47995,7 +47995,7 @@
         <v>45302</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -48073,7 +48073,7 @@
         <v>44622</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -48146,7 +48146,7 @@
         <v>46188</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -48219,7 +48219,7 @@
         <v>44564</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -48292,7 +48292,7 @@
         <v>44958</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -48365,7 +48365,7 @@
         <v>45095</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -48438,7 +48438,7 @@
         <v>44516</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -48511,7 +48511,7 @@
         <v>45040</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -48589,7 +48589,7 @@
         <v>45615</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -48667,7 +48667,7 @@
         <v>45709</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -48745,7 +48745,7 @@
         <v>45609</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -48823,7 +48823,7 @@
         <v>45554</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -48896,7 +48896,7 @@
         <v>45880</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -48974,7 +48974,7 @@
         <v>46196</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -49052,7 +49052,7 @@
         <v>45880</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -49130,7 +49130,7 @@
         <v>45551</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -49203,7 +49203,7 @@
         <v>45846</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -49281,7 +49281,7 @@
         <v>46199</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -49354,7 +49354,7 @@
         <v>44622</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -49427,7 +49427,7 @@
         <v>46203</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -49500,7 +49500,7 @@
         <v>45077</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -49578,7 +49578,7 @@
         <v>45881</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -49656,7 +49656,7 @@
         <v>45206</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -49729,7 +49729,7 @@
         <v>45883</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -49807,7 +49807,7 @@
         <v>45084</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -49880,7 +49880,7 @@
         <v>45456</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -49958,7 +49958,7 @@
         <v>44550</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -50031,7 +50031,7 @@
         <v>45174</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -50109,7 +50109,7 @@
         <v>44508</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -50182,7 +50182,7 @@
         <v>46204</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -50255,7 +50255,7 @@
         <v>45645</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -50333,7 +50333,7 @@
         <v>44795</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -50411,7 +50411,7 @@
         <v>46209</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -50484,7 +50484,7 @@
         <v>45715</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -50557,7 +50557,7 @@
         <v>44634</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -50635,7 +50635,7 @@
         <v>46209</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -50708,7 +50708,7 @@
         <v>46209</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -50781,7 +50781,7 @@
         <v>46211</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -50854,7 +50854,7 @@
         <v>45762</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -50927,7 +50927,7 @@
         <v>46212</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -51000,7 +51000,7 @@
         <v>45147</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -51073,7 +51073,7 @@
         <v>46255</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -51151,7 +51151,7 @@
         <v>45209</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -51224,7 +51224,7 @@
         <v>45209</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -51297,7 +51297,7 @@
         <v>45243</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -51375,7 +51375,7 @@
         <v>46258</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -51453,7 +51453,7 @@
         <v>46258</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -51531,7 +51531,7 @@
         <v>45660</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -51609,7 +51609,7 @@
         <v>45103</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -51682,7 +51682,7 @@
         <v>45253</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -51760,7 +51760,7 @@
         <v>44664</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -51838,7 +51838,7 @@
         <v>45274</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -51911,7 +51911,7 @@
         <v>46218</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -51989,7 +51989,7 @@
         <v>44767</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -52062,7 +52062,7 @@
         <v>45720</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -52140,7 +52140,7 @@
         <v>44735</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -52213,7 +52213,7 @@
         <v>46218</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -52291,7 +52291,7 @@
         <v>46219</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -52364,7 +52364,7 @@
         <v>44729</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -52437,7 +52437,7 @@
         <v>45149</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -52510,7 +52510,7 @@
         <v>45257</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -52588,7 +52588,7 @@
         <v>45314</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -52661,7 +52661,7 @@
         <v>44672</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -52734,7 +52734,7 @@
         <v>45308</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -52807,7 +52807,7 @@
         <v>44823</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -52880,7 +52880,7 @@
         <v>45623</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -52953,7 +52953,7 @@
         <v>44813</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -53031,7 +53031,7 @@
         <v>44833</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -53109,7 +53109,7 @@
         <v>45468</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -53187,7 +53187,7 @@
         <v>45379</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -53260,7 +53260,7 @@
         <v>45309</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -53338,7 +53338,7 @@
         <v>45309</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -53411,7 +53411,7 @@
         <v>45309</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -53484,7 +53484,7 @@
         <v>45257</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -53557,7 +53557,7 @@
         <v>45302</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -53635,7 +53635,7 @@
         <v>44966</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -53708,7 +53708,7 @@
         <v>46268</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -53781,7 +53781,7 @@
         <v>46226</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -53854,7 +53854,7 @@
         <v>46269</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -53927,7 +53927,7 @@
         <v>44767</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -54000,7 +54000,7 @@
         <v>46269</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -54073,7 +54073,7 @@
         <v>46226</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -54146,7 +54146,7 @@
         <v>46225</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -54219,7 +54219,7 @@
         <v>46225</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -54292,7 +54292,7 @@
         <v>46269</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -54365,7 +54365,7 @@
         <v>46269</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -54438,7 +54438,7 @@
         <v>46269</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -54511,7 +54511,7 @@
         <v>44817</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -54589,7 +54589,7 @@
         <v>45040</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -54662,7 +54662,7 @@
         <v>44595</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -54735,7 +54735,7 @@
         <v>45009</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -54808,7 +54808,7 @@
         <v>46232</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -54881,7 +54881,7 @@
         <v>45084</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -54954,7 +54954,7 @@
         <v>44782</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -55027,7 +55027,7 @@
         <v>46233</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -55100,7 +55100,7 @@
         <v>44714</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -55173,7 +55173,7 @@
         <v>45299</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -55246,7 +55246,7 @@
         <v>46279</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -55319,7 +55319,7 @@
         <v>46279</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -55392,7 +55392,7 @@
         <v>44749</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -55465,7 +55465,7 @@
         <v>46279</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -55538,7 +55538,7 @@
         <v>44861</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -55616,7 +55616,7 @@
         <v>44987</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -55689,7 +55689,7 @@
         <v>44879</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -55762,7 +55762,7 @@
         <v>44871</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -55835,7 +55835,7 @@
         <v>44526</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -55908,7 +55908,7 @@
         <v>46282</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -55986,7 +55986,7 @@
         <v>46282</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -56064,7 +56064,7 @@
         <v>46282</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -56142,7 +56142,7 @@
         <v>46282</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -56220,7 +56220,7 @@
         <v>44914</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -56298,7 +56298,7 @@
         <v>46282</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -56376,7 +56376,7 @@
         <v>46282</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -56454,7 +56454,7 @@
         <v>46282</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -56532,7 +56532,7 @@
         <v>46282</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -56610,7 +56610,7 @@
         <v>45548</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -56683,7 +56683,7 @@
         <v>46282</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -56761,7 +56761,7 @@
         <v>45763</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -56834,7 +56834,7 @@
         <v>46281</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -56907,7 +56907,7 @@
         <v>44503</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -56980,7 +56980,7 @@
         <v>45636</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -57053,7 +57053,7 @@
         <v>44607</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -57126,7 +57126,7 @@
         <v>44953</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -57204,7 +57204,7 @@
         <v>44817</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -57277,7 +57277,7 @@
         <v>46286</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -57355,7 +57355,7 @@
         <v>45523</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -57433,7 +57433,7 @@
         <v>45863</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -57506,7 +57506,7 @@
         <v>44867</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -57579,7 +57579,7 @@
         <v>44732</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -57657,7 +57657,7 @@
         <v>44949</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -57730,7 +57730,7 @@
         <v>44949</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -57803,7 +57803,7 @@
         <v>44949</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -57876,7 +57876,7 @@
         <v>44960</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -57954,7 +57954,7 @@
         <v>44966</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -58027,7 +58027,7 @@
         <v>44662</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -58105,7 +58105,7 @@
         <v>45555</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -58183,7 +58183,7 @@
         <v>44918</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -58261,7 +58261,7 @@
         <v>45622</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -58334,7 +58334,7 @@
         <v>44930</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -58412,7 +58412,7 @@
         <v>45258</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -58485,7 +58485,7 @@
         <v>45379</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -58558,7 +58558,7 @@
         <v>45260</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -58631,7 +58631,7 @@
         <v>45021</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -58704,7 +58704,7 @@
         <v>45167</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -58777,7 +58777,7 @@
         <v>45008</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -58850,7 +58850,7 @@
         <v>44616</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -58928,7 +58928,7 @@
         <v>44550</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -59001,7 +59001,7 @@
         <v>45230</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -59074,7 +59074,7 @@
         <v>45013</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -59152,7 +59152,7 @@
         <v>45554</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -59225,7 +59225,7 @@
         <v>45095</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -59303,7 +59303,7 @@
         <v>45055</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -59376,7 +59376,7 @@
         <v>44995</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -59454,7 +59454,7 @@
         <v>45095</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -59527,7 +59527,7 @@
         <v>45425</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -59600,7 +59600,7 @@
         <v>44898</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -59673,7 +59673,7 @@
         <v>45177</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -59746,7 +59746,7 @@
         <v>45456</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -59824,7 +59824,7 @@
         <v>44865</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -59902,7 +59902,7 @@
         <v>44980</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -59975,7 +59975,7 @@
         <v>44966</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -60053,7 +60053,7 @@
         <v>44914</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -60126,7 +60126,7 @@
         <v>44974</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -60199,7 +60199,7 @@
         <v>44950</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -60277,7 +60277,7 @@
         <v>45601</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -60350,7 +60350,7 @@
         <v>45323</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -60428,7 +60428,7 @@
         <v>45181</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -60501,7 +60501,7 @@
         <v>45042</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -60579,7 +60579,7 @@
         <v>45257</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -60657,7 +60657,7 @@
         <v>45225</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -60730,7 +60730,7 @@
         <v>45082</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -60808,7 +60808,7 @@
         <v>45149</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -60881,7 +60881,7 @@
         <v>44993</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -60954,7 +60954,7 @@
         <v>44987</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -61027,7 +61027,7 @@
         <v>45247</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -61100,7 +61100,7 @@
         <v>45422</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -61173,7 +61173,7 @@
         <v>45214</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -61246,7 +61246,7 @@
         <v>45421</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -61324,7 +61324,7 @@
         <v>45420</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -61397,7 +61397,7 @@
         <v>45125</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -61475,7 +61475,7 @@
         <v>45033</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -61553,7 +61553,7 @@
         <v>45103</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -61626,7 +61626,7 @@
         <v>45688</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -61704,7 +61704,7 @@
         <v>45022</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -61782,7 +61782,7 @@
         <v>45744</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -61860,7 +61860,7 @@
         <v>45267</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -61938,7 +61938,7 @@
         <v>45202</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -62011,7 +62011,7 @@
         <v>45118</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -62084,7 +62084,7 @@
         <v>45225</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -62157,7 +62157,7 @@
         <v>44900</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -62230,7 +62230,7 @@
         <v>44981</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -62308,7 +62308,7 @@
         <v>44922</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -62386,7 +62386,7 @@
         <v>45191</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -62459,7 +62459,7 @@
         <v>45178</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -62532,7 +62532,7 @@
         <v>45177</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -62605,7 +62605,7 @@
         <v>45623</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -62683,7 +62683,7 @@
         <v>45639</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -62761,7 +62761,7 @@
         <v>45197</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -62834,7 +62834,7 @@
         <v>45264</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -62912,7 +62912,7 @@
         <v>45110</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -62985,7 +62985,7 @@
         <v>45008</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -63063,7 +63063,7 @@
         <v>45593</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -63141,7 +63141,7 @@
         <v>44942</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -63214,7 +63214,7 @@
         <v>44617</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -63287,7 +63287,7 @@
         <v>44939</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -63360,7 +63360,7 @@
         <v>45202</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -63433,7 +63433,7 @@
         <v>44946</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -63511,7 +63511,7 @@
         <v>44946</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -63589,7 +63589,7 @@
         <v>45082</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -63667,7 +63667,7 @@
         <v>45299</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -63740,7 +63740,7 @@
         <v>45720</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -63818,7 +63818,7 @@
         <v>45250</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -63896,7 +63896,7 @@
         <v>45206</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -63969,7 +63969,7 @@
         <v>44964</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -64047,7 +64047,7 @@
         <v>45607</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -64120,7 +64120,7 @@
         <v>45607</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -64193,7 +64193,7 @@
         <v>44490</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
@@ -64266,7 +64266,7 @@
         <v>45770</v>
       </c>
       <c r="E802" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -64339,7 +64339,7 @@
         <v>45749</v>
       </c>
       <c r="E803" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
@@ -64417,7 +64417,7 @@
         <v>45639</v>
       </c>
       <c r="E804" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
@@ -64495,7 +64495,7 @@
         <v>45709</v>
       </c>
       <c r="E805" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>
@@ -64573,7 +64573,7 @@
         <v>45566</v>
       </c>
       <c r="E806" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F806" t="inlineStr">
         <is>
@@ -64651,7 +64651,7 @@
         <v>45566</v>
       </c>
       <c r="E807" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F807" t="inlineStr">
         <is>
@@ -64729,7 +64729,7 @@
         <v>45740</v>
       </c>
       <c r="E808" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F808" t="inlineStr">
         <is>
@@ -64807,7 +64807,7 @@
         <v>45103</v>
       </c>
       <c r="E809" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F809" t="inlineStr">
         <is>
@@ -64880,7 +64880,7 @@
         <v>45232</v>
       </c>
       <c r="E810" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F810" t="inlineStr">
         <is>
@@ -64958,7 +64958,7 @@
         <v>45609</v>
       </c>
       <c r="E811" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F811" t="inlineStr">
         <is>
@@ -65036,7 +65036,7 @@
         <v>45566</v>
       </c>
       <c r="E812" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F812" t="inlineStr">
         <is>
@@ -65114,7 +65114,7 @@
         <v>45566</v>
       </c>
       <c r="E813" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F813" t="inlineStr">
         <is>
@@ -65192,7 +65192,7 @@
         <v>45566</v>
       </c>
       <c r="E814" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F814" t="inlineStr">
         <is>
@@ -65270,7 +65270,7 @@
         <v>45735</v>
       </c>
       <c r="E815" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F815" t="inlineStr">
         <is>
@@ -65348,7 +65348,7 @@
         <v>45736</v>
       </c>
       <c r="E816" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F816" t="inlineStr">
         <is>
@@ -65426,7 +65426,7 @@
         <v>45530</v>
       </c>
       <c r="E817" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F817" t="inlineStr">
         <is>
@@ -65499,7 +65499,7 @@
         <v>45642</v>
       </c>
       <c r="E818" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F818" t="inlineStr">
         <is>
@@ -65572,7 +65572,7 @@
         <v>45267</v>
       </c>
       <c r="E819" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F819" t="inlineStr">
         <is>
@@ -65650,7 +65650,7 @@
         <v>45530</v>
       </c>
       <c r="E820" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F820" t="inlineStr">
         <is>
@@ -65723,7 +65723,7 @@
         <v>45727</v>
       </c>
       <c r="E821" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F821" t="inlineStr">
         <is>
@@ -65796,7 +65796,7 @@
         <v>45371</v>
       </c>
       <c r="E822" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F822" t="inlineStr">
         <is>
@@ -65874,7 +65874,7 @@
         <v>45644</v>
       </c>
       <c r="E823" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F823" t="inlineStr">
         <is>
@@ -65947,7 +65947,7 @@
         <v>45428</v>
       </c>
       <c r="E824" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F824" t="inlineStr">
         <is>
@@ -66020,7 +66020,7 @@
         <v>45429</v>
       </c>
       <c r="E825" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F825" t="inlineStr">
         <is>
@@ -66093,7 +66093,7 @@
         <v>45250</v>
       </c>
       <c r="E826" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F826" t="inlineStr">
         <is>
@@ -66171,7 +66171,7 @@
         <v>46188</v>
       </c>
       <c r="E827" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F827" t="inlineStr">
         <is>
@@ -66249,7 +66249,7 @@
         <v>46258</v>
       </c>
       <c r="E828" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F828" t="inlineStr">
         <is>

--- a/Översikt FINSPÅNG.xlsx
+++ b/Översikt FINSPÅNG.xlsx
@@ -601,7 +601,7 @@
         <v>46244</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -727,7 +727,7 @@
         <v>45945</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -858,7 +858,7 @@
         <v>45134</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
         <v>44896</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1121,7 +1121,7 @@
         <v>44888</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>45210</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1369,7 +1369,7 @@
         <v>44777</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1488,7 +1488,7 @@
         <v>44897</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1607,7 +1607,7 @@
         <v>44910</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1734,7 +1734,7 @@
         <v>45322</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1855,7 +1855,7 @@
         <v>44624</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1971,7 +1971,7 @@
         <v>44599</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2082,7 +2082,7 @@
         <v>45421</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2202,7 +2202,7 @@
         <v>45891</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2318,7 +2318,7 @@
         <v>45238</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2433,7 +2433,7 @@
         <v>45898</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2548,7 +2548,7 @@
         <v>45267</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2663,7 +2663,7 @@
         <v>45679</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2782,7 +2782,7 @@
         <v>45947</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2896,7 +2896,7 @@
         <v>44791</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3010,7 +3010,7 @@
         <v>45812</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3124,7 +3124,7 @@
         <v>44665</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3237,7 +3237,7 @@
         <v>45681</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3354,7 +3354,7 @@
         <v>45602</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3466,7 +3466,7 @@
         <v>45819</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3582,7 +3582,7 @@
         <v>45800</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3694,7 +3694,7 @@
         <v>45082</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3806,7 +3806,7 @@
         <v>44774</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3918,7 +3918,7 @@
         <v>46196</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4030,7 +4030,7 @@
         <v>44690</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4141,7 +4141,7 @@
         <v>45441</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4252,7 +4252,7 @@
         <v>45894</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4367,7 +4367,7 @@
         <v>45905</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4478,7 +4478,7 @@
         <v>44816</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4584,7 +4584,7 @@
         <v>45950</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4695,7 +4695,7 @@
         <v>45477</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4810,7 +4810,7 @@
         <v>45644</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4916,7 +4916,7 @@
         <v>44981</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5027,7 +5027,7 @@
         <v>46174</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5138,7 +5138,7 @@
         <v>46181</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5249,7 +5249,7 @@
         <v>46181</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5360,7 +5360,7 @@
         <v>45425</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5466,7 +5466,7 @@
         <v>45235</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5577,7 +5577,7 @@
         <v>45121</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5692,7 +5692,7 @@
         <v>44903</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5802,7 +5802,7 @@
         <v>44480</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5913,7 +5913,7 @@
         <v>44683</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6023,7 +6023,7 @@
         <v>44776</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6128,7 +6128,7 @@
         <v>44504</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6238,7 +6238,7 @@
         <v>44529</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6343,7 +6343,7 @@
         <v>45567</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6457,7 +6457,7 @@
         <v>45082</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6567,7 +6567,7 @@
         <v>45905</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6677,7 +6677,7 @@
         <v>45149</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6786,7 +6786,7 @@
         <v>45883</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6896,7 +6896,7 @@
         <v>46058</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7010,7 +7010,7 @@
         <v>45229</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7120,7 +7120,7 @@
         <v>44897</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7234,7 +7234,7 @@
         <v>44501</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7344,7 +7344,7 @@
         <v>45744</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7458,7 +7458,7 @@
         <v>45636</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7563,7 +7563,7 @@
         <v>45328</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7672,7 +7672,7 @@
         <v>44599</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7782,7 +7782,7 @@
         <v>46129</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7896,7 +7896,7 @@
         <v>45555</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8010,7 +8010,7 @@
         <v>45446</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8115,7 +8115,7 @@
         <v>45845</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8225,7 +8225,7 @@
         <v>45846</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8335,7 +8335,7 @@
         <v>45447</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8445,7 +8445,7 @@
         <v>46043</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8559,7 +8559,7 @@
         <v>44965</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8673,7 +8673,7 @@
         <v>45566</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8787,7 +8787,7 @@
         <v>46155</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8901,7 +8901,7 @@
         <v>44930</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9011,7 +9011,7 @@
         <v>45880</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9121,7 +9121,7 @@
         <v>44915</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9231,7 +9231,7 @@
         <v>45302</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9340,7 +9340,7 @@
         <v>45232</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9450,7 +9450,7 @@
         <v>46189</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9555,7 +9555,7 @@
         <v>44622</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9660,7 +9660,7 @@
         <v>46258</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9774,7 +9774,7 @@
         <v>46258</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9884,7 +9884,7 @@
         <v>44817</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9994,7 +9994,7 @@
         <v>46181</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10104,7 +10104,7 @@
         <v>44915</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10214,7 +10214,7 @@
         <v>45070</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10324,7 +10324,7 @@
         <v>44992</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10434,7 +10434,7 @@
         <v>45615</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10548,7 +10548,7 @@
         <v>44711</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10658,7 +10658,7 @@
         <v>45428</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10763,7 +10763,7 @@
         <v>46107</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10873,7 +10873,7 @@
         <v>46188</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10987,7 +10987,7 @@
         <v>44755</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11065,7 +11065,7 @@
         <v>44675</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11138,7 +11138,7 @@
         <v>44676</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11216,7 +11216,7 @@
         <v>44536</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11294,7 +11294,7 @@
         <v>44864</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11367,7 +11367,7 @@
         <v>44600</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11440,7 +11440,7 @@
         <v>44824</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11513,7 +11513,7 @@
         <v>44799</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11586,7 +11586,7 @@
         <v>44795</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11659,7 +11659,7 @@
         <v>44856</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11732,7 +11732,7 @@
         <v>44578</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11810,7 +11810,7 @@
         <v>44675</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -11883,7 +11883,7 @@
         <v>44852</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -11961,7 +11961,7 @@
         <v>44601</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12039,7 +12039,7 @@
         <v>44601</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12112,7 +12112,7 @@
         <v>44551</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12185,7 +12185,7 @@
         <v>44525</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12258,7 +12258,7 @@
         <v>44574</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12336,7 +12336,7 @@
         <v>44588</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12414,7 +12414,7 @@
         <v>44889</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12487,7 +12487,7 @@
         <v>44574</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12560,7 +12560,7 @@
         <v>44627</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -12633,7 +12633,7 @@
         <v>44525</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -12711,7 +12711,7 @@
         <v>44503</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -12789,7 +12789,7 @@
         <v>44874</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -12862,7 +12862,7 @@
         <v>44503</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -12935,7 +12935,7 @@
         <v>44502</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13013,7 +13013,7 @@
         <v>44551</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -13086,7 +13086,7 @@
         <v>44712</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -13164,7 +13164,7 @@
         <v>44581</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -13237,7 +13237,7 @@
         <v>44601</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -13310,7 +13310,7 @@
         <v>44833</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -13383,7 +13383,7 @@
         <v>44672</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -13456,7 +13456,7 @@
         <v>44859</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -13529,7 +13529,7 @@
         <v>44735</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -13602,7 +13602,7 @@
         <v>44796</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -13675,7 +13675,7 @@
         <v>44782</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -13748,7 +13748,7 @@
         <v>44741</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -13821,7 +13821,7 @@
         <v>44859</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -13894,7 +13894,7 @@
         <v>44678</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -13967,7 +13967,7 @@
         <v>44613</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -14045,7 +14045,7 @@
         <v>44855</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -14123,7 +14123,7 @@
         <v>44887</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -14196,7 +14196,7 @@
         <v>44860</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -14269,7 +14269,7 @@
         <v>44753</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -14342,7 +14342,7 @@
         <v>44802</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -14415,7 +14415,7 @@
         <v>44844</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -14493,7 +14493,7 @@
         <v>44781</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -14566,7 +14566,7 @@
         <v>44564</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -14639,7 +14639,7 @@
         <v>44541</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -14712,7 +14712,7 @@
         <v>44859</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -14785,7 +14785,7 @@
         <v>44595</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -14858,7 +14858,7 @@
         <v>44508</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -14931,7 +14931,7 @@
         <v>44582</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -15004,7 +15004,7 @@
         <v>44816</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -15077,7 +15077,7 @@
         <v>44656</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -15150,7 +15150,7 @@
         <v>44627</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -15223,7 +15223,7 @@
         <v>44587</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -15296,7 +15296,7 @@
         <v>44820</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -15369,7 +15369,7 @@
         <v>44532</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -15442,7 +15442,7 @@
         <v>44552</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -15515,7 +15515,7 @@
         <v>44581</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -15588,7 +15588,7 @@
         <v>44879</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -15661,7 +15661,7 @@
         <v>44588</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -15739,7 +15739,7 @@
         <v>44875</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -15812,7 +15812,7 @@
         <v>44743</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -15885,7 +15885,7 @@
         <v>44831</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -15963,7 +15963,7 @@
         <v>44819</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -16036,7 +16036,7 @@
         <v>44581</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -16114,7 +16114,7 @@
         <v>44630</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -16187,7 +16187,7 @@
         <v>44476</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -16260,7 +16260,7 @@
         <v>44804</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -16338,7 +16338,7 @@
         <v>44601</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -16411,7 +16411,7 @@
         <v>44742</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -16489,7 +16489,7 @@
         <v>44859</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -16562,7 +16562,7 @@
         <v>44476</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -16635,7 +16635,7 @@
         <v>44600</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -16708,7 +16708,7 @@
         <v>44481</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -16781,7 +16781,7 @@
         <v>44635</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -16854,7 +16854,7 @@
         <v>44776</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -16927,7 +16927,7 @@
         <v>44713</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -17005,7 +17005,7 @@
         <v>44697</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -17083,7 +17083,7 @@
         <v>44481</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -17156,7 +17156,7 @@
         <v>44533</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -17229,7 +17229,7 @@
         <v>44601</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -17302,7 +17302,7 @@
         <v>44678</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -17375,7 +17375,7 @@
         <v>44704</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -17448,7 +17448,7 @@
         <v>44564</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -17521,7 +17521,7 @@
         <v>44642</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -17594,7 +17594,7 @@
         <v>44659</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -17672,7 +17672,7 @@
         <v>44656</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -17750,7 +17750,7 @@
         <v>45258</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -17823,7 +17823,7 @@
         <v>45447</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -17901,7 +17901,7 @@
         <v>45103</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -17974,7 +17974,7 @@
         <v>44866</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -18047,7 +18047,7 @@
         <v>44898</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -18120,7 +18120,7 @@
         <v>44966</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -18193,7 +18193,7 @@
         <v>45293</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -18266,7 +18266,7 @@
         <v>45033</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -18344,7 +18344,7 @@
         <v>44802</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -18417,7 +18417,7 @@
         <v>44476</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -18490,7 +18490,7 @@
         <v>45009</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -18563,7 +18563,7 @@
         <v>44897</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -18641,7 +18641,7 @@
         <v>44672</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -18714,7 +18714,7 @@
         <v>44595</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -18792,7 +18792,7 @@
         <v>44918</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -18870,7 +18870,7 @@
         <v>45097</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -18943,7 +18943,7 @@
         <v>45063</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -19016,7 +19016,7 @@
         <v>45086</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -19089,7 +19089,7 @@
         <v>44677</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -19162,7 +19162,7 @@
         <v>45021</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -19235,7 +19235,7 @@
         <v>45330</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -19308,7 +19308,7 @@
         <v>45260</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -19381,7 +19381,7 @@
         <v>44973</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -19459,7 +19459,7 @@
         <v>45107</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -19532,7 +19532,7 @@
         <v>44767</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -19605,7 +19605,7 @@
         <v>45293</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -19683,7 +19683,7 @@
         <v>45428</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -19761,7 +19761,7 @@
         <v>45206</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -19834,7 +19834,7 @@
         <v>45705</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -19907,7 +19907,7 @@
         <v>45727</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -19980,7 +19980,7 @@
         <v>45555</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -20058,7 +20058,7 @@
         <v>45623</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -20131,7 +20131,7 @@
         <v>46002</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -20209,7 +20209,7 @@
         <v>45267</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -20287,7 +20287,7 @@
         <v>45642</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -20365,7 +20365,7 @@
         <v>45095</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -20443,7 +20443,7 @@
         <v>44993</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -20516,7 +20516,7 @@
         <v>46003</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -20589,7 +20589,7 @@
         <v>46002</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -20667,7 +20667,7 @@
         <v>46002</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -20745,7 +20745,7 @@
         <v>46002</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -20823,7 +20823,7 @@
         <v>44914</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -20896,7 +20896,7 @@
         <v>45728</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -20974,7 +20974,7 @@
         <v>45749</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -21052,7 +21052,7 @@
         <v>46006</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -21125,7 +21125,7 @@
         <v>46006</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -21203,7 +21203,7 @@
         <v>46006</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -21281,7 +21281,7 @@
         <v>44844</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -21354,7 +21354,7 @@
         <v>44844</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -21427,7 +21427,7 @@
         <v>45554</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -21500,7 +21500,7 @@
         <v>44960</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -21578,7 +21578,7 @@
         <v>45357</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -21651,7 +21651,7 @@
         <v>45740</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -21729,7 +21729,7 @@
         <v>45688</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -21807,7 +21807,7 @@
         <v>45441</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -21880,7 +21880,7 @@
         <v>44508</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -21953,7 +21953,7 @@
         <v>45084</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -22026,7 +22026,7 @@
         <v>45233</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -22099,7 +22099,7 @@
         <v>44778</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -22172,7 +22172,7 @@
         <v>45253</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -22250,7 +22250,7 @@
         <v>45621</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -22328,7 +22328,7 @@
         <v>45888</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -22406,7 +22406,7 @@
         <v>45149</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -22479,7 +22479,7 @@
         <v>45891</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -22557,7 +22557,7 @@
         <v>45707</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -22635,7 +22635,7 @@
         <v>44861</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -22713,7 +22713,7 @@
         <v>45894</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -22791,7 +22791,7 @@
         <v>45895</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -22864,7 +22864,7 @@
         <v>45853</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -22937,7 +22937,7 @@
         <v>46029</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -23010,7 +23010,7 @@
         <v>44900</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -23083,7 +23083,7 @@
         <v>46030</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -23161,7 +23161,7 @@
         <v>45896</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -23239,7 +23239,7 @@
         <v>45677</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -23317,7 +23317,7 @@
         <v>46030</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -23395,7 +23395,7 @@
         <v>46031</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -23473,7 +23473,7 @@
         <v>45898</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -23546,7 +23546,7 @@
         <v>44942</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -23619,7 +23619,7 @@
         <v>46034</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -23697,7 +23697,7 @@
         <v>45095</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -23775,7 +23775,7 @@
         <v>45095</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -23848,7 +23848,7 @@
         <v>45903</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -23926,7 +23926,7 @@
         <v>45903</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -24004,7 +24004,7 @@
         <v>46034</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -24082,7 +24082,7 @@
         <v>46034</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -24160,7 +24160,7 @@
         <v>45903</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -24238,7 +24238,7 @@
         <v>45903</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -24316,7 +24316,7 @@
         <v>45903</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -24394,7 +24394,7 @@
         <v>45103</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -24467,7 +24467,7 @@
         <v>45905</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -24545,7 +24545,7 @@
         <v>45904</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -24623,7 +24623,7 @@
         <v>46036</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -24701,7 +24701,7 @@
         <v>46036</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -24779,7 +24779,7 @@
         <v>45905</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -24857,7 +24857,7 @@
         <v>44817</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -24935,7 +24935,7 @@
         <v>46040</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -25008,7 +25008,7 @@
         <v>45904</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -25086,7 +25086,7 @@
         <v>45908</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -25159,7 +25159,7 @@
         <v>46040</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -25232,7 +25232,7 @@
         <v>45259</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -25305,7 +25305,7 @@
         <v>45797</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -25378,7 +25378,7 @@
         <v>45797</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -25456,7 +25456,7 @@
         <v>45796</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -25534,7 +25534,7 @@
         <v>45797</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -25607,7 +25607,7 @@
         <v>46048</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -25685,7 +25685,7 @@
         <v>45796</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -25763,7 +25763,7 @@
         <v>46049</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -25836,7 +25836,7 @@
         <v>45702</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -25914,7 +25914,7 @@
         <v>46048</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -25992,7 +25992,7 @@
         <v>46048</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -26070,7 +26070,7 @@
         <v>45316</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -26148,7 +26148,7 @@
         <v>45623</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -26226,7 +26226,7 @@
         <v>46050</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -26304,7 +26304,7 @@
         <v>45800</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -26382,7 +26382,7 @@
         <v>45800</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -26460,7 +26460,7 @@
         <v>45800</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -26538,7 +26538,7 @@
         <v>46050</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -26616,7 +26616,7 @@
         <v>45800</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -26694,7 +26694,7 @@
         <v>46055</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -26772,7 +26772,7 @@
         <v>44880</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -26850,7 +26850,7 @@
         <v>45264</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -26928,7 +26928,7 @@
         <v>46052</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -27001,7 +27001,7 @@
         <v>45924</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -27074,7 +27074,7 @@
         <v>44918</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -27152,7 +27152,7 @@
         <v>44974</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -27225,7 +27225,7 @@
         <v>45008</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -27298,7 +27298,7 @@
         <v>45720</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -27376,7 +27376,7 @@
         <v>46058</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -27454,7 +27454,7 @@
         <v>46058</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -27532,7 +27532,7 @@
         <v>45931</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -27605,7 +27605,7 @@
         <v>46058</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -27683,7 +27683,7 @@
         <v>46058</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -27761,7 +27761,7 @@
         <v>46060</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -27834,7 +27834,7 @@
         <v>45593</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -27912,7 +27912,7 @@
         <v>46063</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -27990,7 +27990,7 @@
         <v>46063</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -28068,7 +28068,7 @@
         <v>45147</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -28141,7 +28141,7 @@
         <v>46064</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -28219,7 +28219,7 @@
         <v>46065</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -28297,7 +28297,7 @@
         <v>46065</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -28375,7 +28375,7 @@
         <v>45040</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -28453,7 +28453,7 @@
         <v>46064</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -28531,7 +28531,7 @@
         <v>46064</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -28609,7 +28609,7 @@
         <v>46064</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -28687,7 +28687,7 @@
         <v>46064</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -28765,7 +28765,7 @@
         <v>46064</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -28843,7 +28843,7 @@
         <v>45710</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -28916,7 +28916,7 @@
         <v>46069</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -28994,7 +28994,7 @@
         <v>45554</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -29067,7 +29067,7 @@
         <v>45337</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -29140,7 +29140,7 @@
         <v>45846</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -29218,7 +29218,7 @@
         <v>45935</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -29296,7 +29296,7 @@
         <v>46070</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -29374,7 +29374,7 @@
         <v>46070</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -29452,7 +29452,7 @@
         <v>46073</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -29530,7 +29530,7 @@
         <v>44958</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -29603,7 +29603,7 @@
         <v>45274</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -29676,7 +29676,7 @@
         <v>45944</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -29749,7 +29749,7 @@
         <v>46076</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -29827,7 +29827,7 @@
         <v>46076</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -29905,7 +29905,7 @@
         <v>44490</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -29978,7 +29978,7 @@
         <v>45415</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -30051,7 +30051,7 @@
         <v>45328</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -30124,7 +30124,7 @@
         <v>46078</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -30202,7 +30202,7 @@
         <v>46080</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -30280,7 +30280,7 @@
         <v>46080</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -30358,7 +30358,7 @@
         <v>46079</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -30436,7 +30436,7 @@
         <v>45095</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -30509,7 +30509,7 @@
         <v>44950</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -30587,7 +30587,7 @@
         <v>45950</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -30665,7 +30665,7 @@
         <v>46080</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -30743,7 +30743,7 @@
         <v>46080</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -30821,7 +30821,7 @@
         <v>44949</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -30894,7 +30894,7 @@
         <v>44860</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -30967,7 +30967,7 @@
         <v>45456</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -31045,7 +31045,7 @@
         <v>45812</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -31123,7 +31123,7 @@
         <v>45744</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -31201,7 +31201,7 @@
         <v>45257</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -31279,7 +31279,7 @@
         <v>45257</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -31357,7 +31357,7 @@
         <v>45955</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -31430,7 +31430,7 @@
         <v>46085</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -31508,7 +31508,7 @@
         <v>46085</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -31586,7 +31586,7 @@
         <v>46085</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -31664,7 +31664,7 @@
         <v>46085</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -31742,7 +31742,7 @@
         <v>45103</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -31815,7 +31815,7 @@
         <v>45812</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -31893,7 +31893,7 @@
         <v>45740</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -31971,7 +31971,7 @@
         <v>45178</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -32044,7 +32044,7 @@
         <v>45002</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -32122,7 +32122,7 @@
         <v>44503</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -32195,7 +32195,7 @@
         <v>45125</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -32273,7 +32273,7 @@
         <v>45421</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -32351,7 +32351,7 @@
         <v>45541</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -32429,7 +32429,7 @@
         <v>45257</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -32507,7 +32507,7 @@
         <v>45206</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -32580,7 +32580,7 @@
         <v>46094</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -32658,7 +32658,7 @@
         <v>45020</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -32731,7 +32731,7 @@
         <v>44840</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -32804,7 +32804,7 @@
         <v>45041</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -32877,7 +32877,7 @@
         <v>44516</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -32950,7 +32950,7 @@
         <v>44964</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -33028,7 +33028,7 @@
         <v>46097</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -33101,7 +33101,7 @@
         <v>44607</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -33174,7 +33174,7 @@
         <v>45463</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -33247,7 +33247,7 @@
         <v>45969</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -33320,7 +33320,7 @@
         <v>44993</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -33393,7 +33393,7 @@
         <v>45971</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -33466,7 +33466,7 @@
         <v>46099</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -33544,7 +33544,7 @@
         <v>46099</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -33617,7 +33617,7 @@
         <v>46099</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -33695,7 +33695,7 @@
         <v>45167</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -33773,7 +33773,7 @@
         <v>44767</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -33846,7 +33846,7 @@
         <v>46099</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -33924,7 +33924,7 @@
         <v>46099</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -33997,7 +33997,7 @@
         <v>44930</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -34070,7 +34070,7 @@
         <v>44957</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -34143,7 +34143,7 @@
         <v>44662</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -34221,7 +34221,7 @@
         <v>45463</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -34294,7 +34294,7 @@
         <v>46106</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -34372,7 +34372,7 @@
         <v>45084</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -34445,7 +34445,7 @@
         <v>44732</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -34523,7 +34523,7 @@
         <v>45639</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -34601,7 +34601,7 @@
         <v>45601</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -34674,7 +34674,7 @@
         <v>44914</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -34752,7 +34752,7 @@
         <v>45979</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -34825,7 +34825,7 @@
         <v>45819</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -34903,7 +34903,7 @@
         <v>45819</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -34981,7 +34981,7 @@
         <v>44536</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -35054,7 +35054,7 @@
         <v>44734</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -35127,7 +35127,7 @@
         <v>45442</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -35200,7 +35200,7 @@
         <v>45983</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -35273,7 +35273,7 @@
         <v>45983</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -35346,7 +35346,7 @@
         <v>45983</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -35419,7 +35419,7 @@
         <v>46111</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -35497,7 +35497,7 @@
         <v>45985</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -35570,7 +35570,7 @@
         <v>44887</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -35643,7 +35643,7 @@
         <v>46113</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -35716,7 +35716,7 @@
         <v>45986</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -35789,7 +35789,7 @@
         <v>46114</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -35867,7 +35867,7 @@
         <v>45615</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -35945,7 +35945,7 @@
         <v>46114</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -36023,7 +36023,7 @@
         <v>45986</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -36096,7 +36096,7 @@
         <v>46114</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -36174,7 +36174,7 @@
         <v>46113</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -36252,7 +36252,7 @@
         <v>45824</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -36330,7 +36330,7 @@
         <v>44614</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -36403,7 +36403,7 @@
         <v>45824</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -36481,7 +36481,7 @@
         <v>45824</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -36559,7 +36559,7 @@
         <v>45468</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -36637,7 +36637,7 @@
         <v>46120</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -36715,7 +36715,7 @@
         <v>45824</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -36793,7 +36793,7 @@
         <v>46121</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -36871,7 +36871,7 @@
         <v>46122</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -36944,7 +36944,7 @@
         <v>44833</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -37022,7 +37022,7 @@
         <v>46125</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -37095,7 +37095,7 @@
         <v>44817</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -37168,7 +37168,7 @@
         <v>46129</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -37246,7 +37246,7 @@
         <v>44865</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -37324,7 +37324,7 @@
         <v>46128</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -37397,7 +37397,7 @@
         <v>44980</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -37470,7 +37470,7 @@
         <v>45118</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -37543,7 +37543,7 @@
         <v>46000</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -37621,7 +37621,7 @@
         <v>45166</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -37699,7 +37699,7 @@
         <v>45467</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -37772,7 +37772,7 @@
         <v>44735</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -37845,7 +37845,7 @@
         <v>45706</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -37918,7 +37918,7 @@
         <v>45600</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -37991,7 +37991,7 @@
         <v>45706</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -38064,7 +38064,7 @@
         <v>45229</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -38142,7 +38142,7 @@
         <v>46134</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -38215,7 +38215,7 @@
         <v>44900</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -38288,7 +38288,7 @@
         <v>45086</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -38361,7 +38361,7 @@
         <v>45103</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -38434,7 +38434,7 @@
         <v>45343</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -38512,7 +38512,7 @@
         <v>45835</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -38590,7 +38590,7 @@
         <v>45082</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -38668,7 +38668,7 @@
         <v>45299</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -38741,7 +38741,7 @@
         <v>45006</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -38814,7 +38814,7 @@
         <v>45740</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -38887,7 +38887,7 @@
         <v>45783</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -38965,7 +38965,7 @@
         <v>45719</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -39043,7 +39043,7 @@
         <v>45379</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -39116,7 +39116,7 @@
         <v>44840</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -39194,7 +39194,7 @@
         <v>45040</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -39267,7 +39267,7 @@
         <v>45840</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -39345,7 +39345,7 @@
         <v>45075</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -39418,7 +39418,7 @@
         <v>45617</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -39496,7 +39496,7 @@
         <v>44725</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -39569,7 +39569,7 @@
         <v>45082</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -39647,7 +39647,7 @@
         <v>45055</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -39720,7 +39720,7 @@
         <v>45688</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -39798,7 +39798,7 @@
         <v>45250</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -39876,7 +39876,7 @@
         <v>45250</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -39949,7 +39949,7 @@
         <v>45845</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -40027,7 +40027,7 @@
         <v>45832</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -40100,7 +40100,7 @@
         <v>45133</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -40173,7 +40173,7 @@
         <v>44903</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -40251,7 +40251,7 @@
         <v>45548</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -40324,7 +40324,7 @@
         <v>45267</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -40402,7 +40402,7 @@
         <v>45516</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -40475,7 +40475,7 @@
         <v>45915</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -40553,7 +40553,7 @@
         <v>45008</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -40631,7 +40631,7 @@
         <v>44473</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -40709,7 +40709,7 @@
         <v>45776</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -40782,7 +40782,7 @@
         <v>45344</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -40855,7 +40855,7 @@
         <v>45700</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -40933,7 +40933,7 @@
         <v>45362</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -41006,7 +41006,7 @@
         <v>44634</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -41084,7 +41084,7 @@
         <v>45252</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -41157,7 +41157,7 @@
         <v>45854</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -41230,7 +41230,7 @@
         <v>45209</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -41303,7 +41303,7 @@
         <v>45854</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -41376,7 +41376,7 @@
         <v>45209</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -41449,7 +41449,7 @@
         <v>45560</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -41527,7 +41527,7 @@
         <v>45853</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -41600,7 +41600,7 @@
         <v>45566</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -41678,7 +41678,7 @@
         <v>44664</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -41756,7 +41756,7 @@
         <v>45692</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -41834,7 +41834,7 @@
         <v>45855</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -41907,7 +41907,7 @@
         <v>44946</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -41985,7 +41985,7 @@
         <v>44946</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -42063,7 +42063,7 @@
         <v>44944</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -42141,7 +42141,7 @@
         <v>45009</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -42219,7 +42219,7 @@
         <v>45247</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -42292,7 +42292,7 @@
         <v>45095</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -42365,7 +42365,7 @@
         <v>45853</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -42438,7 +42438,7 @@
         <v>45523</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -42511,7 +42511,7 @@
         <v>46064</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -42589,7 +42589,7 @@
         <v>45523</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -42667,7 +42667,7 @@
         <v>44767</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -42740,7 +42740,7 @@
         <v>44964</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -42818,7 +42818,7 @@
         <v>44759</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -42891,7 +42891,7 @@
         <v>45258</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -42964,7 +42964,7 @@
         <v>45831</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -43037,7 +43037,7 @@
         <v>44617</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -43110,7 +43110,7 @@
         <v>45042</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -43188,7 +43188,7 @@
         <v>44937</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -43261,7 +43261,7 @@
         <v>45709</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -43339,7 +43339,7 @@
         <v>44993</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -43412,7 +43412,7 @@
         <v>45095</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -43485,7 +43485,7 @@
         <v>44564</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -43558,7 +43558,7 @@
         <v>45607</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -43631,7 +43631,7 @@
         <v>45607</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -43704,7 +43704,7 @@
         <v>45609</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -43782,7 +43782,7 @@
         <v>45665</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -43855,7 +43855,7 @@
         <v>45551</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -43928,7 +43928,7 @@
         <v>44774</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -44006,7 +44006,7 @@
         <v>45744</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -44084,7 +44084,7 @@
         <v>46141</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -44157,7 +44157,7 @@
         <v>45820</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -44235,7 +44235,7 @@
         <v>45013</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -44313,7 +44313,7 @@
         <v>45870</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -44386,7 +44386,7 @@
         <v>45688</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -44464,7 +44464,7 @@
         <v>45428</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -44537,7 +44537,7 @@
         <v>45744</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -44615,7 +44615,7 @@
         <v>45184</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -44688,7 +44688,7 @@
         <v>45980</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -44761,7 +44761,7 @@
         <v>45077</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -44839,7 +44839,7 @@
         <v>45002</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -44917,7 +44917,7 @@
         <v>45068</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -44995,7 +44995,7 @@
         <v>44867</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -45068,7 +45068,7 @@
         <v>45845</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -45146,7 +45146,7 @@
         <v>44886</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -45219,7 +45219,7 @@
         <v>45636</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -45292,7 +45292,7 @@
         <v>45728</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -45370,7 +45370,7 @@
         <v>45280</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -45448,7 +45448,7 @@
         <v>45225</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -45521,7 +45521,7 @@
         <v>46077</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -45599,7 +45599,7 @@
         <v>44987</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -45672,7 +45672,7 @@
         <v>45082</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -45750,7 +45750,7 @@
         <v>45566</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -45828,7 +45828,7 @@
         <v>45177</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -45901,7 +45901,7 @@
         <v>45709</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -45979,7 +45979,7 @@
         <v>46160</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -46052,7 +46052,7 @@
         <v>44995</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -46130,7 +46130,7 @@
         <v>45147</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -46203,7 +46203,7 @@
         <v>44966</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -46276,7 +46276,7 @@
         <v>45230</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -46349,7 +46349,7 @@
         <v>45040</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -46422,7 +46422,7 @@
         <v>45880</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -46500,7 +46500,7 @@
         <v>45880</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -46578,7 +46578,7 @@
         <v>44876</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -46651,7 +46651,7 @@
         <v>45179</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -46724,7 +46724,7 @@
         <v>45179</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -46797,7 +46797,7 @@
         <v>45709</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -46875,7 +46875,7 @@
         <v>45309</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -46953,7 +46953,7 @@
         <v>45309</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -47026,7 +47026,7 @@
         <v>45309</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -47099,7 +47099,7 @@
         <v>46174</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -47177,7 +47177,7 @@
         <v>46174</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -47255,7 +47255,7 @@
         <v>44949</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -47328,7 +47328,7 @@
         <v>45881</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -47406,7 +47406,7 @@
         <v>45323</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -47484,7 +47484,7 @@
         <v>45013</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -47562,7 +47562,7 @@
         <v>44981</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -47640,7 +47640,7 @@
         <v>44930</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -47718,7 +47718,7 @@
         <v>45883</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -47796,7 +47796,7 @@
         <v>45883</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -47874,7 +47874,7 @@
         <v>46176</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -47947,7 +47947,7 @@
         <v>46176</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -48020,7 +48020,7 @@
         <v>46176</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -48093,7 +48093,7 @@
         <v>44550</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -48166,7 +48166,7 @@
         <v>45086</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -48239,7 +48239,7 @@
         <v>45042</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -48312,7 +48312,7 @@
         <v>45042</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -48385,7 +48385,7 @@
         <v>44939</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -48458,7 +48458,7 @@
         <v>45607</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -48531,7 +48531,7 @@
         <v>44732</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -48609,7 +48609,7 @@
         <v>45425</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -48682,7 +48682,7 @@
         <v>45177</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -48755,7 +48755,7 @@
         <v>45302</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -48833,7 +48833,7 @@
         <v>46178</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -48906,7 +48906,7 @@
         <v>45678</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -48984,7 +48984,7 @@
         <v>46178</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -49057,7 +49057,7 @@
         <v>46177</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -49130,7 +49130,7 @@
         <v>46178</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -49203,7 +49203,7 @@
         <v>45622</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -49276,7 +49276,7 @@
         <v>46181</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -49354,7 +49354,7 @@
         <v>45237</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -49432,7 +49432,7 @@
         <v>44642</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -49505,7 +49505,7 @@
         <v>46185</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -49578,7 +49578,7 @@
         <v>46185</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -49651,7 +49651,7 @@
         <v>46188</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -49724,7 +49724,7 @@
         <v>45770</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -49797,7 +49797,7 @@
         <v>45456</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -49875,7 +49875,7 @@
         <v>44749</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -49948,7 +49948,7 @@
         <v>45082</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -50026,7 +50026,7 @@
         <v>45082</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -50104,7 +50104,7 @@
         <v>45167</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -50177,7 +50177,7 @@
         <v>44930</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -50250,7 +50250,7 @@
         <v>44782</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -50323,7 +50323,7 @@
         <v>45646</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -50396,7 +50396,7 @@
         <v>45181</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -50469,7 +50469,7 @@
         <v>45225</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -50542,7 +50542,7 @@
         <v>44754</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -50615,7 +50615,7 @@
         <v>45421</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -50693,7 +50693,7 @@
         <v>46196</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -50771,7 +50771,7 @@
         <v>45551</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -50844,7 +50844,7 @@
         <v>45530</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -50917,7 +50917,7 @@
         <v>44986</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -50990,7 +50990,7 @@
         <v>44770</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -51063,7 +51063,7 @@
         <v>45566</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -51141,7 +51141,7 @@
         <v>46199</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -51214,7 +51214,7 @@
         <v>45846</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -51292,7 +51292,7 @@
         <v>45302</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -51370,7 +51370,7 @@
         <v>45601</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -51443,7 +51443,7 @@
         <v>44678</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -51521,7 +51521,7 @@
         <v>44637</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -51594,7 +51594,7 @@
         <v>46204</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -51667,7 +51667,7 @@
         <v>46203</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -51740,7 +51740,7 @@
         <v>46209</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -51813,7 +51813,7 @@
         <v>46209</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -51886,7 +51886,7 @@
         <v>46209</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -51959,7 +51959,7 @@
         <v>45279</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -52037,7 +52037,7 @@
         <v>45609</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -52115,7 +52115,7 @@
         <v>45070</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -52193,7 +52193,7 @@
         <v>44973</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -52271,7 +52271,7 @@
         <v>44891</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -52344,7 +52344,7 @@
         <v>45616</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -52417,7 +52417,7 @@
         <v>46212</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -52490,7 +52490,7 @@
         <v>46211</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -52563,7 +52563,7 @@
         <v>44949</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -52636,7 +52636,7 @@
         <v>46258</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -52714,7 +52714,7 @@
         <v>46258</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -52792,7 +52792,7 @@
         <v>44966</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -52865,7 +52865,7 @@
         <v>44953</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -52943,7 +52943,7 @@
         <v>44823</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -53016,7 +53016,7 @@
         <v>45202</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -53089,7 +53089,7 @@
         <v>46218</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -53167,7 +53167,7 @@
         <v>45379</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -53240,7 +53240,7 @@
         <v>46218</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -53318,7 +53318,7 @@
         <v>45428</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -53396,7 +53396,7 @@
         <v>45174</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -53474,7 +53474,7 @@
         <v>45770</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -53547,7 +53547,7 @@
         <v>45236</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -53625,7 +53625,7 @@
         <v>45236</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -53703,7 +53703,7 @@
         <v>46219</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -53776,7 +53776,7 @@
         <v>45357</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -53849,7 +53849,7 @@
         <v>45243</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -53927,7 +53927,7 @@
         <v>45022</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -54005,7 +54005,7 @@
         <v>46269</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -54078,7 +54078,7 @@
         <v>44816</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -54151,7 +54151,7 @@
         <v>46269</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -54224,7 +54224,7 @@
         <v>46225</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -54297,7 +54297,7 @@
         <v>46269</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -54370,7 +54370,7 @@
         <v>46269</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -54443,7 +54443,7 @@
         <v>46226</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -54516,7 +54516,7 @@
         <v>46226</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -54589,7 +54589,7 @@
         <v>45314</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -54662,7 +54662,7 @@
         <v>46269</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -54735,7 +54735,7 @@
         <v>46225</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -54808,7 +54808,7 @@
         <v>44820</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -54881,7 +54881,7 @@
         <v>45535</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -54959,7 +54959,7 @@
         <v>45250</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -55037,7 +55037,7 @@
         <v>45197</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -55110,7 +55110,7 @@
         <v>44966</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -55183,7 +55183,7 @@
         <v>46232</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -55256,7 +55256,7 @@
         <v>46279</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -55329,7 +55329,7 @@
         <v>44806</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -55407,7 +55407,7 @@
         <v>46233</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -55480,7 +55480,7 @@
         <v>46279</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -55553,7 +55553,7 @@
         <v>46279</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -55626,7 +55626,7 @@
         <v>45113</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -55699,7 +55699,7 @@
         <v>44964</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -55777,7 +55777,7 @@
         <v>46282</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -55855,7 +55855,7 @@
         <v>45420</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -55928,7 +55928,7 @@
         <v>44834</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -56006,7 +56006,7 @@
         <v>45616</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -56079,7 +56079,7 @@
         <v>46282</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -56157,7 +56157,7 @@
         <v>45258</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -56230,7 +56230,7 @@
         <v>44865</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -56303,7 +56303,7 @@
         <v>46282</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -56381,7 +56381,7 @@
         <v>46282</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -56459,7 +56459,7 @@
         <v>44953</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -56532,7 +56532,7 @@
         <v>45617</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -56610,7 +56610,7 @@
         <v>46282</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -56688,7 +56688,7 @@
         <v>44879</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -56761,7 +56761,7 @@
         <v>46281</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -56834,7 +56834,7 @@
         <v>46282</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -56912,7 +56912,7 @@
         <v>46282</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -56990,7 +56990,7 @@
         <v>46282</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -57068,7 +57068,7 @@
         <v>46282</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -57146,7 +57146,7 @@
         <v>45713</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -57224,7 +57224,7 @@
         <v>45735</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -57302,7 +57302,7 @@
         <v>44862</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -57380,7 +57380,7 @@
         <v>44887</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -57453,7 +57453,7 @@
         <v>44887</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -57526,7 +57526,7 @@
         <v>45426</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -57599,7 +57599,7 @@
         <v>44616</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -57677,7 +57677,7 @@
         <v>44949</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -57750,7 +57750,7 @@
         <v>46286</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -57828,7 +57828,7 @@
         <v>44995</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -57906,7 +57906,7 @@
         <v>44813</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -57984,7 +57984,7 @@
         <v>45863</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -58057,7 +58057,7 @@
         <v>45142</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -58130,7 +58130,7 @@
         <v>45715</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -58203,7 +58203,7 @@
         <v>44653</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -58276,7 +58276,7 @@
         <v>45870</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -58349,7 +58349,7 @@
         <v>45645</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -58427,7 +58427,7 @@
         <v>45593</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -58505,7 +58505,7 @@
         <v>44987</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -58578,7 +58578,7 @@
         <v>45555</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -58656,7 +58656,7 @@
         <v>45639</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -58734,7 +58734,7 @@
         <v>45314</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -58807,7 +58807,7 @@
         <v>45447</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -58885,7 +58885,7 @@
         <v>44729</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -58958,7 +58958,7 @@
         <v>44844</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -59031,7 +59031,7 @@
         <v>44973</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -59109,7 +59109,7 @@
         <v>45076</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -59187,7 +59187,7 @@
         <v>45095</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -59260,7 +59260,7 @@
         <v>45639</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -59338,7 +59338,7 @@
         <v>44526</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -59411,7 +59411,7 @@
         <v>44922</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -59489,7 +59489,7 @@
         <v>46295</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -59567,7 +59567,7 @@
         <v>46295</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -59645,7 +59645,7 @@
         <v>44795</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -59723,7 +59723,7 @@
         <v>45260</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -59796,7 +59796,7 @@
         <v>44491</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -59869,7 +59869,7 @@
         <v>45041</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -59947,7 +59947,7 @@
         <v>45257</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -60020,7 +60020,7 @@
         <v>44871</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -60093,7 +60093,7 @@
         <v>45391</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -60166,7 +60166,7 @@
         <v>45692</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -60244,7 +60244,7 @@
         <v>45070</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -60322,7 +60322,7 @@
         <v>45202</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -60395,7 +60395,7 @@
         <v>44966</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -60473,7 +60473,7 @@
         <v>45323</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -60551,7 +60551,7 @@
         <v>45341</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -60629,7 +60629,7 @@
         <v>44550</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -60702,7 +60702,7 @@
         <v>45566</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -60780,7 +60780,7 @@
         <v>45566</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -60858,7 +60858,7 @@
         <v>44476</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -60931,7 +60931,7 @@
         <v>46255</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -61009,7 +61009,7 @@
         <v>45441</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -61082,7 +61082,7 @@
         <v>45374</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -61160,7 +61160,7 @@
         <v>45391</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -61233,7 +61233,7 @@
         <v>44981</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -61311,7 +61311,7 @@
         <v>44679</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -61389,7 +61389,7 @@
         <v>45293</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -61462,7 +61462,7 @@
         <v>45554</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -61535,7 +61535,7 @@
         <v>45214</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -61608,7 +61608,7 @@
         <v>45110</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -61681,7 +61681,7 @@
         <v>45660</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -61759,7 +61759,7 @@
         <v>45735</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -61837,7 +61837,7 @@
         <v>45516</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -61915,7 +61915,7 @@
         <v>44966</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -61993,7 +61993,7 @@
         <v>45078</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -62066,7 +62066,7 @@
         <v>45113</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -62139,7 +62139,7 @@
         <v>45191</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -62212,7 +62212,7 @@
         <v>45763</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -62285,7 +62285,7 @@
         <v>44551</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -62358,7 +62358,7 @@
         <v>44833</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -62436,7 +62436,7 @@
         <v>45103</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -62509,7 +62509,7 @@
         <v>45618</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -62582,7 +62582,7 @@
         <v>45639</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -62660,7 +62660,7 @@
         <v>45299</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -62733,7 +62733,7 @@
         <v>45301</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -62811,7 +62811,7 @@
         <v>44714</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -62884,7 +62884,7 @@
         <v>44622</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -62957,7 +62957,7 @@
         <v>45232</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -63035,7 +63035,7 @@
         <v>44887</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -63108,7 +63108,7 @@
         <v>45422</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -63181,7 +63181,7 @@
         <v>44622</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -63254,7 +63254,7 @@
         <v>45191</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -63327,7 +63327,7 @@
         <v>44595</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -63400,7 +63400,7 @@
         <v>44589</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -63473,7 +63473,7 @@
         <v>45308</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -63546,7 +63546,7 @@
         <v>44922</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -63624,7 +63624,7 @@
         <v>45615</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -63702,7 +63702,7 @@
         <v>45149</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -63775,7 +63775,7 @@
         <v>45762</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -63848,7 +63848,7 @@
         <v>44817</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -63921,7 +63921,7 @@
         <v>45149</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -63994,7 +63994,7 @@
         <v>45622</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -64067,7 +64067,7 @@
         <v>45554</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -64140,7 +64140,7 @@
         <v>45095</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -64213,7 +64213,7 @@
         <v>45593</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
@@ -64291,7 +64291,7 @@
         <v>45275</v>
       </c>
       <c r="E802" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -64364,7 +64364,7 @@
         <v>44564</v>
       </c>
       <c r="E803" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
@@ -64437,7 +64437,7 @@
         <v>45744</v>
       </c>
       <c r="E804" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
@@ -64515,7 +64515,7 @@
         <v>45407</v>
       </c>
       <c r="E805" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>
@@ -64588,7 +64588,7 @@
         <v>45071</v>
       </c>
       <c r="E806" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F806" t="inlineStr">
         <is>
@@ -64666,7 +64666,7 @@
         <v>45257</v>
       </c>
       <c r="E807" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F807" t="inlineStr">
         <is>
@@ -64744,7 +64744,7 @@
         <v>45257</v>
       </c>
       <c r="E808" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F808" t="inlineStr">
         <is>
@@ -64817,7 +64817,7 @@
         <v>45566</v>
       </c>
       <c r="E809" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F809" t="inlineStr">
         <is>
@@ -64895,7 +64895,7 @@
         <v>45566</v>
       </c>
       <c r="E810" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F810" t="inlineStr">
         <is>
@@ -64973,7 +64973,7 @@
         <v>45566</v>
       </c>
       <c r="E811" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F811" t="inlineStr">
         <is>
@@ -65051,7 +65051,7 @@
         <v>45735</v>
       </c>
       <c r="E812" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F812" t="inlineStr">
         <is>
@@ -65129,7 +65129,7 @@
         <v>45736</v>
       </c>
       <c r="E813" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F813" t="inlineStr">
         <is>
@@ -65207,7 +65207,7 @@
         <v>45642</v>
       </c>
       <c r="E814" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F814" t="inlineStr">
         <is>
@@ -65280,7 +65280,7 @@
         <v>45530</v>
       </c>
       <c r="E815" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F815" t="inlineStr">
         <is>
@@ -65353,7 +65353,7 @@
         <v>45530</v>
       </c>
       <c r="E816" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F816" t="inlineStr">
         <is>
@@ -65426,7 +65426,7 @@
         <v>45371</v>
       </c>
       <c r="E817" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F817" t="inlineStr">
         <is>
@@ -65504,7 +65504,7 @@
         <v>45644</v>
       </c>
       <c r="E818" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F818" t="inlineStr">
         <is>
@@ -65577,7 +65577,7 @@
         <v>45428</v>
       </c>
       <c r="E819" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F819" t="inlineStr">
         <is>
@@ -65650,7 +65650,7 @@
         <v>45429</v>
       </c>
       <c r="E820" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F820" t="inlineStr">
         <is>
@@ -65723,7 +65723,7 @@
         <v>45250</v>
       </c>
       <c r="E821" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F821" t="inlineStr">
         <is>
@@ -65801,7 +65801,7 @@
         <v>46188</v>
       </c>
       <c r="E822" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F822" t="inlineStr">
         <is>
@@ -65879,7 +65879,7 @@
         <v>46258</v>
       </c>
       <c r="E823" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F823" t="inlineStr">
         <is>

--- a/Översikt FINSPÅNG.xlsx
+++ b/Översikt FINSPÅNG.xlsx
@@ -601,7 +601,7 @@
         <v>46244</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -727,7 +727,7 @@
         <v>45945</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -858,7 +858,7 @@
         <v>45134</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
         <v>44896</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1121,7 +1121,7 @@
         <v>44888</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>45210</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1369,7 +1369,7 @@
         <v>44777</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1488,7 +1488,7 @@
         <v>44897</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1607,7 +1607,7 @@
         <v>44910</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1734,7 +1734,7 @@
         <v>45322</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1855,7 +1855,7 @@
         <v>44624</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1971,7 +1971,7 @@
         <v>44599</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2082,7 +2082,7 @@
         <v>45421</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2202,7 +2202,7 @@
         <v>45891</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2318,7 +2318,7 @@
         <v>45238</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2433,7 +2433,7 @@
         <v>45898</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2548,7 +2548,7 @@
         <v>45267</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2663,7 +2663,7 @@
         <v>45679</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2782,7 +2782,7 @@
         <v>45947</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2896,7 +2896,7 @@
         <v>44791</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3010,7 +3010,7 @@
         <v>45812</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3124,7 +3124,7 @@
         <v>44665</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3237,7 +3237,7 @@
         <v>45681</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3354,7 +3354,7 @@
         <v>45602</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3466,7 +3466,7 @@
         <v>45819</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3582,7 +3582,7 @@
         <v>45800</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3694,7 +3694,7 @@
         <v>45082</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3806,7 +3806,7 @@
         <v>44774</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3918,7 +3918,7 @@
         <v>46196</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4030,7 +4030,7 @@
         <v>44690</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4141,7 +4141,7 @@
         <v>45441</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4252,7 +4252,7 @@
         <v>45894</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4367,7 +4367,7 @@
         <v>45905</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4478,7 +4478,7 @@
         <v>44816</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4584,7 +4584,7 @@
         <v>45950</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4695,7 +4695,7 @@
         <v>45477</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4810,7 +4810,7 @@
         <v>45644</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4916,7 +4916,7 @@
         <v>44981</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5027,7 +5027,7 @@
         <v>46174</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5138,7 +5138,7 @@
         <v>46181</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5249,7 +5249,7 @@
         <v>46181</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5360,7 +5360,7 @@
         <v>45425</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5466,7 +5466,7 @@
         <v>45235</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5577,7 +5577,7 @@
         <v>45121</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5692,7 +5692,7 @@
         <v>44903</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5802,7 +5802,7 @@
         <v>44480</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5913,7 +5913,7 @@
         <v>44683</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6023,7 +6023,7 @@
         <v>44776</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6128,7 +6128,7 @@
         <v>44504</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6238,7 +6238,7 @@
         <v>44529</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6343,7 +6343,7 @@
         <v>45567</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6457,7 +6457,7 @@
         <v>45082</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6567,7 +6567,7 @@
         <v>45905</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6677,7 +6677,7 @@
         <v>45149</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6786,7 +6786,7 @@
         <v>45883</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6896,7 +6896,7 @@
         <v>46058</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7010,7 +7010,7 @@
         <v>45229</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7120,7 +7120,7 @@
         <v>44897</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7234,7 +7234,7 @@
         <v>44501</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7344,7 +7344,7 @@
         <v>45744</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7458,7 +7458,7 @@
         <v>45636</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7563,7 +7563,7 @@
         <v>45328</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7672,7 +7672,7 @@
         <v>44599</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7782,7 +7782,7 @@
         <v>46129</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7896,7 +7896,7 @@
         <v>45555</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8010,7 +8010,7 @@
         <v>45446</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8115,7 +8115,7 @@
         <v>45845</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8225,7 +8225,7 @@
         <v>45846</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8335,7 +8335,7 @@
         <v>45447</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8445,7 +8445,7 @@
         <v>46043</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8559,7 +8559,7 @@
         <v>44965</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8673,7 +8673,7 @@
         <v>45566</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8787,7 +8787,7 @@
         <v>46155</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8901,7 +8901,7 @@
         <v>44930</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9011,7 +9011,7 @@
         <v>45880</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9121,7 +9121,7 @@
         <v>44915</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9231,7 +9231,7 @@
         <v>45302</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9340,7 +9340,7 @@
         <v>45232</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9450,7 +9450,7 @@
         <v>46189</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9555,7 +9555,7 @@
         <v>44622</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9660,7 +9660,7 @@
         <v>46258</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9774,7 +9774,7 @@
         <v>46258</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9884,7 +9884,7 @@
         <v>44817</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9994,7 +9994,7 @@
         <v>46181</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10104,7 +10104,7 @@
         <v>44915</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10214,7 +10214,7 @@
         <v>45070</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10324,7 +10324,7 @@
         <v>44992</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10434,7 +10434,7 @@
         <v>45615</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10548,7 +10548,7 @@
         <v>44711</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10658,7 +10658,7 @@
         <v>45428</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10763,7 +10763,7 @@
         <v>46107</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10873,7 +10873,7 @@
         <v>46188</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10987,7 +10987,7 @@
         <v>44755</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11065,7 +11065,7 @@
         <v>44675</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11138,7 +11138,7 @@
         <v>44676</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11216,7 +11216,7 @@
         <v>44536</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11294,7 +11294,7 @@
         <v>44864</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11367,7 +11367,7 @@
         <v>44600</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11440,7 +11440,7 @@
         <v>44824</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11513,7 +11513,7 @@
         <v>44799</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11586,7 +11586,7 @@
         <v>44795</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11659,7 +11659,7 @@
         <v>44856</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11732,7 +11732,7 @@
         <v>44578</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11810,7 +11810,7 @@
         <v>44675</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -11883,7 +11883,7 @@
         <v>44852</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -11961,7 +11961,7 @@
         <v>44601</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12039,7 +12039,7 @@
         <v>44601</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12112,7 +12112,7 @@
         <v>44551</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12185,7 +12185,7 @@
         <v>44525</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12258,7 +12258,7 @@
         <v>44574</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12336,7 +12336,7 @@
         <v>44588</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12414,7 +12414,7 @@
         <v>44889</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12487,7 +12487,7 @@
         <v>44574</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12560,7 +12560,7 @@
         <v>44627</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -12633,7 +12633,7 @@
         <v>44525</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -12711,7 +12711,7 @@
         <v>44503</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -12789,7 +12789,7 @@
         <v>44874</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -12862,7 +12862,7 @@
         <v>44503</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -12935,7 +12935,7 @@
         <v>44502</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13013,7 +13013,7 @@
         <v>44551</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -13086,7 +13086,7 @@
         <v>44712</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -13164,7 +13164,7 @@
         <v>44581</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -13237,7 +13237,7 @@
         <v>44601</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -13310,7 +13310,7 @@
         <v>44833</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -13383,7 +13383,7 @@
         <v>44672</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -13456,7 +13456,7 @@
         <v>44859</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -13529,7 +13529,7 @@
         <v>44735</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -13602,7 +13602,7 @@
         <v>44796</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -13675,7 +13675,7 @@
         <v>44782</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -13748,7 +13748,7 @@
         <v>44741</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -13821,7 +13821,7 @@
         <v>44859</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -13894,7 +13894,7 @@
         <v>44678</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -13967,7 +13967,7 @@
         <v>44613</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -14045,7 +14045,7 @@
         <v>44855</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -14123,7 +14123,7 @@
         <v>44887</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -14196,7 +14196,7 @@
         <v>44860</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -14269,7 +14269,7 @@
         <v>44753</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -14342,7 +14342,7 @@
         <v>44802</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -14415,7 +14415,7 @@
         <v>44844</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -14493,7 +14493,7 @@
         <v>44781</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -14566,7 +14566,7 @@
         <v>44564</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -14639,7 +14639,7 @@
         <v>44541</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -14712,7 +14712,7 @@
         <v>44859</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -14785,7 +14785,7 @@
         <v>44595</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -14858,7 +14858,7 @@
         <v>44508</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -14931,7 +14931,7 @@
         <v>44582</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -15004,7 +15004,7 @@
         <v>44816</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -15077,7 +15077,7 @@
         <v>44656</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -15150,7 +15150,7 @@
         <v>44627</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -15223,7 +15223,7 @@
         <v>44587</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -15296,7 +15296,7 @@
         <v>44820</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -15369,7 +15369,7 @@
         <v>44532</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -15442,7 +15442,7 @@
         <v>44552</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -15515,7 +15515,7 @@
         <v>44581</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -15588,7 +15588,7 @@
         <v>44879</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -15661,7 +15661,7 @@
         <v>44588</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -15739,7 +15739,7 @@
         <v>44875</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -15812,7 +15812,7 @@
         <v>44743</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -15885,7 +15885,7 @@
         <v>44831</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -15963,7 +15963,7 @@
         <v>44819</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -16036,7 +16036,7 @@
         <v>44581</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -16114,7 +16114,7 @@
         <v>44630</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -16187,7 +16187,7 @@
         <v>44476</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -16260,7 +16260,7 @@
         <v>44804</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -16338,7 +16338,7 @@
         <v>44601</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -16411,7 +16411,7 @@
         <v>44742</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -16489,7 +16489,7 @@
         <v>44859</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -16562,7 +16562,7 @@
         <v>44476</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -16635,7 +16635,7 @@
         <v>44600</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -16708,7 +16708,7 @@
         <v>44481</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -16781,7 +16781,7 @@
         <v>44635</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -16854,7 +16854,7 @@
         <v>44776</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -16927,7 +16927,7 @@
         <v>44713</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -17005,7 +17005,7 @@
         <v>44697</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -17083,7 +17083,7 @@
         <v>44481</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -17156,7 +17156,7 @@
         <v>44533</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -17229,7 +17229,7 @@
         <v>44601</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -17302,7 +17302,7 @@
         <v>44678</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -17375,7 +17375,7 @@
         <v>44704</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -17448,7 +17448,7 @@
         <v>44564</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -17521,7 +17521,7 @@
         <v>44642</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -17594,7 +17594,7 @@
         <v>44659</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -17672,7 +17672,7 @@
         <v>44656</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -17750,7 +17750,7 @@
         <v>45258</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -17823,7 +17823,7 @@
         <v>45447</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -17901,7 +17901,7 @@
         <v>45103</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -17974,7 +17974,7 @@
         <v>44866</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -18047,7 +18047,7 @@
         <v>44898</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -18120,7 +18120,7 @@
         <v>44966</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -18193,7 +18193,7 @@
         <v>45293</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -18266,7 +18266,7 @@
         <v>45033</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -18344,7 +18344,7 @@
         <v>44802</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -18417,7 +18417,7 @@
         <v>44476</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -18490,7 +18490,7 @@
         <v>45009</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -18563,7 +18563,7 @@
         <v>44897</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -18641,7 +18641,7 @@
         <v>44672</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -18714,7 +18714,7 @@
         <v>44595</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -18792,7 +18792,7 @@
         <v>44918</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -18870,7 +18870,7 @@
         <v>45097</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -18943,7 +18943,7 @@
         <v>45063</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -19016,7 +19016,7 @@
         <v>45086</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -19089,7 +19089,7 @@
         <v>44677</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -19162,7 +19162,7 @@
         <v>45021</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -19235,7 +19235,7 @@
         <v>45330</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -19308,7 +19308,7 @@
         <v>45260</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -19381,7 +19381,7 @@
         <v>44973</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -19459,7 +19459,7 @@
         <v>45107</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -19532,7 +19532,7 @@
         <v>44767</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -19605,7 +19605,7 @@
         <v>45293</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -19683,7 +19683,7 @@
         <v>45428</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -19761,7 +19761,7 @@
         <v>45206</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -19834,7 +19834,7 @@
         <v>45705</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -19907,7 +19907,7 @@
         <v>45727</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -19980,7 +19980,7 @@
         <v>45555</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -20058,7 +20058,7 @@
         <v>45623</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -20131,7 +20131,7 @@
         <v>46002</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -20209,7 +20209,7 @@
         <v>45267</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -20287,7 +20287,7 @@
         <v>45642</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -20365,7 +20365,7 @@
         <v>45095</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -20443,7 +20443,7 @@
         <v>44993</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -20516,7 +20516,7 @@
         <v>46003</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -20589,7 +20589,7 @@
         <v>46002</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -20667,7 +20667,7 @@
         <v>46002</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -20745,7 +20745,7 @@
         <v>46002</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -20823,7 +20823,7 @@
         <v>44914</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -20896,7 +20896,7 @@
         <v>45728</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -20974,7 +20974,7 @@
         <v>45749</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -21052,7 +21052,7 @@
         <v>46006</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -21125,7 +21125,7 @@
         <v>46006</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -21203,7 +21203,7 @@
         <v>46006</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -21281,7 +21281,7 @@
         <v>44844</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -21354,7 +21354,7 @@
         <v>44844</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -21427,7 +21427,7 @@
         <v>45554</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -21500,7 +21500,7 @@
         <v>44960</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -21578,7 +21578,7 @@
         <v>45357</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -21651,7 +21651,7 @@
         <v>45740</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -21729,7 +21729,7 @@
         <v>45688</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -21807,7 +21807,7 @@
         <v>45441</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -21880,7 +21880,7 @@
         <v>44508</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -21953,7 +21953,7 @@
         <v>45084</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -22026,7 +22026,7 @@
         <v>45233</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -22099,7 +22099,7 @@
         <v>44778</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -22172,7 +22172,7 @@
         <v>45253</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -22250,7 +22250,7 @@
         <v>45621</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -22328,7 +22328,7 @@
         <v>45888</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -22406,7 +22406,7 @@
         <v>45149</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -22479,7 +22479,7 @@
         <v>45891</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -22557,7 +22557,7 @@
         <v>45707</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -22635,7 +22635,7 @@
         <v>44861</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -22713,7 +22713,7 @@
         <v>45894</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -22791,7 +22791,7 @@
         <v>45895</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -22864,7 +22864,7 @@
         <v>45853</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -22937,7 +22937,7 @@
         <v>46029</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -23010,7 +23010,7 @@
         <v>44900</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -23083,7 +23083,7 @@
         <v>46030</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -23161,7 +23161,7 @@
         <v>45896</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -23239,7 +23239,7 @@
         <v>45677</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -23317,7 +23317,7 @@
         <v>46030</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -23395,7 +23395,7 @@
         <v>46031</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -23473,7 +23473,7 @@
         <v>45898</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -23546,7 +23546,7 @@
         <v>44942</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -23619,7 +23619,7 @@
         <v>46034</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -23697,7 +23697,7 @@
         <v>45095</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -23775,7 +23775,7 @@
         <v>45095</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -23848,7 +23848,7 @@
         <v>45903</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -23926,7 +23926,7 @@
         <v>45903</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -24004,7 +24004,7 @@
         <v>46034</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -24082,7 +24082,7 @@
         <v>46034</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -24160,7 +24160,7 @@
         <v>45903</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -24238,7 +24238,7 @@
         <v>45903</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -24316,7 +24316,7 @@
         <v>45903</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -24394,7 +24394,7 @@
         <v>45103</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -24467,7 +24467,7 @@
         <v>45905</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -24545,7 +24545,7 @@
         <v>45904</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -24623,7 +24623,7 @@
         <v>46036</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -24701,7 +24701,7 @@
         <v>46036</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -24779,7 +24779,7 @@
         <v>45905</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -24857,7 +24857,7 @@
         <v>44817</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -24935,7 +24935,7 @@
         <v>46040</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -25008,7 +25008,7 @@
         <v>45904</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -25086,7 +25086,7 @@
         <v>45908</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -25159,7 +25159,7 @@
         <v>46040</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -25232,7 +25232,7 @@
         <v>45259</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -25305,7 +25305,7 @@
         <v>45797</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -25378,7 +25378,7 @@
         <v>45797</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -25456,7 +25456,7 @@
         <v>45796</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -25534,7 +25534,7 @@
         <v>45797</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -25607,7 +25607,7 @@
         <v>46048</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -25685,7 +25685,7 @@
         <v>45796</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -25763,7 +25763,7 @@
         <v>46049</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -25836,7 +25836,7 @@
         <v>45702</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -25914,7 +25914,7 @@
         <v>46048</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -25992,7 +25992,7 @@
         <v>46048</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -26070,7 +26070,7 @@
         <v>45316</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -26148,7 +26148,7 @@
         <v>45623</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -26226,7 +26226,7 @@
         <v>46050</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -26304,7 +26304,7 @@
         <v>45800</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -26382,7 +26382,7 @@
         <v>45800</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -26460,7 +26460,7 @@
         <v>45800</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -26538,7 +26538,7 @@
         <v>46050</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -26616,7 +26616,7 @@
         <v>45800</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -26694,7 +26694,7 @@
         <v>46055</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -26772,7 +26772,7 @@
         <v>44880</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -26850,7 +26850,7 @@
         <v>45264</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -26928,7 +26928,7 @@
         <v>46052</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -27001,7 +27001,7 @@
         <v>45924</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -27074,7 +27074,7 @@
         <v>44918</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -27152,7 +27152,7 @@
         <v>44974</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -27225,7 +27225,7 @@
         <v>45008</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -27298,7 +27298,7 @@
         <v>45720</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -27376,7 +27376,7 @@
         <v>46058</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -27454,7 +27454,7 @@
         <v>46058</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -27532,7 +27532,7 @@
         <v>45931</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -27605,7 +27605,7 @@
         <v>46058</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -27683,7 +27683,7 @@
         <v>46058</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -27761,7 +27761,7 @@
         <v>46060</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -27834,7 +27834,7 @@
         <v>45593</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -27912,7 +27912,7 @@
         <v>46063</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -27990,7 +27990,7 @@
         <v>46063</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -28068,7 +28068,7 @@
         <v>45147</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -28141,7 +28141,7 @@
         <v>46064</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -28219,7 +28219,7 @@
         <v>46065</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -28297,7 +28297,7 @@
         <v>46065</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -28375,7 +28375,7 @@
         <v>45040</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -28453,7 +28453,7 @@
         <v>46064</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -28531,7 +28531,7 @@
         <v>46064</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -28609,7 +28609,7 @@
         <v>46064</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -28687,7 +28687,7 @@
         <v>46064</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -28765,7 +28765,7 @@
         <v>46064</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -28843,7 +28843,7 @@
         <v>45710</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -28916,7 +28916,7 @@
         <v>46069</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -28994,7 +28994,7 @@
         <v>45554</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -29067,7 +29067,7 @@
         <v>45337</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -29140,7 +29140,7 @@
         <v>45846</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -29218,7 +29218,7 @@
         <v>45935</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -29296,7 +29296,7 @@
         <v>46070</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -29374,7 +29374,7 @@
         <v>46070</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -29452,7 +29452,7 @@
         <v>46073</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -29530,7 +29530,7 @@
         <v>44958</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -29603,7 +29603,7 @@
         <v>45274</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -29676,7 +29676,7 @@
         <v>45944</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -29749,7 +29749,7 @@
         <v>46076</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -29827,7 +29827,7 @@
         <v>46076</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -29905,7 +29905,7 @@
         <v>44490</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -29978,7 +29978,7 @@
         <v>45415</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -30051,7 +30051,7 @@
         <v>45328</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -30124,7 +30124,7 @@
         <v>46078</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -30202,7 +30202,7 @@
         <v>46080</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -30280,7 +30280,7 @@
         <v>46080</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -30358,7 +30358,7 @@
         <v>46079</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -30436,7 +30436,7 @@
         <v>45095</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -30509,7 +30509,7 @@
         <v>44950</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -30587,7 +30587,7 @@
         <v>45950</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -30665,7 +30665,7 @@
         <v>46080</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -30743,7 +30743,7 @@
         <v>46080</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -30821,7 +30821,7 @@
         <v>44949</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -30894,7 +30894,7 @@
         <v>44860</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -30967,7 +30967,7 @@
         <v>45456</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -31045,7 +31045,7 @@
         <v>45812</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -31123,7 +31123,7 @@
         <v>45744</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -31201,7 +31201,7 @@
         <v>45257</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -31279,7 +31279,7 @@
         <v>45257</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -31357,7 +31357,7 @@
         <v>45955</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -31430,7 +31430,7 @@
         <v>46085</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -31508,7 +31508,7 @@
         <v>46085</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -31586,7 +31586,7 @@
         <v>46085</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -31664,7 +31664,7 @@
         <v>46085</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -31742,7 +31742,7 @@
         <v>45103</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -31815,7 +31815,7 @@
         <v>45812</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -31893,7 +31893,7 @@
         <v>45740</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -31971,7 +31971,7 @@
         <v>45178</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -32044,7 +32044,7 @@
         <v>45002</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -32122,7 +32122,7 @@
         <v>44503</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -32195,7 +32195,7 @@
         <v>45125</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -32273,7 +32273,7 @@
         <v>45421</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -32351,7 +32351,7 @@
         <v>45541</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -32429,7 +32429,7 @@
         <v>45257</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -32507,7 +32507,7 @@
         <v>45206</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -32580,7 +32580,7 @@
         <v>46094</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -32658,7 +32658,7 @@
         <v>45020</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -32731,7 +32731,7 @@
         <v>44840</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -32804,7 +32804,7 @@
         <v>45041</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -32877,7 +32877,7 @@
         <v>44516</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -32950,7 +32950,7 @@
         <v>44964</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -33028,7 +33028,7 @@
         <v>46097</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -33101,7 +33101,7 @@
         <v>44607</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -33174,7 +33174,7 @@
         <v>45463</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -33247,7 +33247,7 @@
         <v>45969</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -33320,7 +33320,7 @@
         <v>44993</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -33393,7 +33393,7 @@
         <v>45971</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -33466,7 +33466,7 @@
         <v>46099</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -33544,7 +33544,7 @@
         <v>46099</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -33617,7 +33617,7 @@
         <v>46099</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -33695,7 +33695,7 @@
         <v>45167</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -33773,7 +33773,7 @@
         <v>44767</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -33846,7 +33846,7 @@
         <v>46099</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -33924,7 +33924,7 @@
         <v>46099</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -33997,7 +33997,7 @@
         <v>44930</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -34070,7 +34070,7 @@
         <v>44957</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -34143,7 +34143,7 @@
         <v>44662</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -34221,7 +34221,7 @@
         <v>45463</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -34294,7 +34294,7 @@
         <v>46106</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -34372,7 +34372,7 @@
         <v>45084</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -34445,7 +34445,7 @@
         <v>44732</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -34523,7 +34523,7 @@
         <v>45639</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -34601,7 +34601,7 @@
         <v>45601</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -34674,7 +34674,7 @@
         <v>44914</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -34752,7 +34752,7 @@
         <v>45979</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -34825,7 +34825,7 @@
         <v>45819</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -34903,7 +34903,7 @@
         <v>45819</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -34981,7 +34981,7 @@
         <v>44536</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -35054,7 +35054,7 @@
         <v>44734</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -35127,7 +35127,7 @@
         <v>45442</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -35200,7 +35200,7 @@
         <v>45983</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -35273,7 +35273,7 @@
         <v>45983</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -35346,7 +35346,7 @@
         <v>45983</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -35419,7 +35419,7 @@
         <v>46111</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -35497,7 +35497,7 @@
         <v>45985</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -35570,7 +35570,7 @@
         <v>44887</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -35643,7 +35643,7 @@
         <v>46113</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -35716,7 +35716,7 @@
         <v>45986</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -35789,7 +35789,7 @@
         <v>46114</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -35867,7 +35867,7 @@
         <v>45615</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -35945,7 +35945,7 @@
         <v>46114</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -36023,7 +36023,7 @@
         <v>45986</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -36096,7 +36096,7 @@
         <v>46114</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -36174,7 +36174,7 @@
         <v>46113</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -36252,7 +36252,7 @@
         <v>45824</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -36330,7 +36330,7 @@
         <v>44614</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -36403,7 +36403,7 @@
         <v>45824</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -36481,7 +36481,7 @@
         <v>45824</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -36559,7 +36559,7 @@
         <v>45468</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -36637,7 +36637,7 @@
         <v>46120</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -36715,7 +36715,7 @@
         <v>45824</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -36793,7 +36793,7 @@
         <v>46121</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -36871,7 +36871,7 @@
         <v>46122</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -36944,7 +36944,7 @@
         <v>44833</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -37022,7 +37022,7 @@
         <v>46125</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -37095,7 +37095,7 @@
         <v>44817</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -37168,7 +37168,7 @@
         <v>46129</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -37246,7 +37246,7 @@
         <v>44865</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -37324,7 +37324,7 @@
         <v>46128</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -37397,7 +37397,7 @@
         <v>44980</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -37470,7 +37470,7 @@
         <v>45118</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -37543,7 +37543,7 @@
         <v>46000</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -37621,7 +37621,7 @@
         <v>45166</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -37699,7 +37699,7 @@
         <v>45467</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -37772,7 +37772,7 @@
         <v>44735</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -37845,7 +37845,7 @@
         <v>45706</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -37918,7 +37918,7 @@
         <v>45600</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -37991,7 +37991,7 @@
         <v>45706</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -38064,7 +38064,7 @@
         <v>45229</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -38142,7 +38142,7 @@
         <v>46134</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -38215,7 +38215,7 @@
         <v>44900</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -38288,7 +38288,7 @@
         <v>45086</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -38361,7 +38361,7 @@
         <v>45103</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -38434,7 +38434,7 @@
         <v>45343</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -38512,7 +38512,7 @@
         <v>45835</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -38590,7 +38590,7 @@
         <v>45082</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -38668,7 +38668,7 @@
         <v>45299</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -38741,7 +38741,7 @@
         <v>45006</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -38814,7 +38814,7 @@
         <v>45740</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -38887,7 +38887,7 @@
         <v>45783</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -38965,7 +38965,7 @@
         <v>45719</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -39043,7 +39043,7 @@
         <v>45379</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -39116,7 +39116,7 @@
         <v>44840</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -39194,7 +39194,7 @@
         <v>45040</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -39267,7 +39267,7 @@
         <v>45840</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -39345,7 +39345,7 @@
         <v>45075</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -39418,7 +39418,7 @@
         <v>45617</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -39496,7 +39496,7 @@
         <v>44725</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -39569,7 +39569,7 @@
         <v>45082</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -39647,7 +39647,7 @@
         <v>45055</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -39720,7 +39720,7 @@
         <v>45688</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -39798,7 +39798,7 @@
         <v>45250</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -39876,7 +39876,7 @@
         <v>45250</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -39949,7 +39949,7 @@
         <v>45845</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -40027,7 +40027,7 @@
         <v>45832</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -40100,7 +40100,7 @@
         <v>45133</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -40173,7 +40173,7 @@
         <v>44903</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -40251,7 +40251,7 @@
         <v>45548</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -40324,7 +40324,7 @@
         <v>45267</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -40402,7 +40402,7 @@
         <v>45516</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -40475,7 +40475,7 @@
         <v>45915</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -40553,7 +40553,7 @@
         <v>45008</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -40631,7 +40631,7 @@
         <v>44473</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -40709,7 +40709,7 @@
         <v>45776</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -40782,7 +40782,7 @@
         <v>45344</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -40855,7 +40855,7 @@
         <v>45700</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -40933,7 +40933,7 @@
         <v>45362</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -41006,7 +41006,7 @@
         <v>44634</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -41084,7 +41084,7 @@
         <v>45252</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -41157,7 +41157,7 @@
         <v>45854</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -41230,7 +41230,7 @@
         <v>45209</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -41303,7 +41303,7 @@
         <v>45854</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -41376,7 +41376,7 @@
         <v>45209</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -41449,7 +41449,7 @@
         <v>45560</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -41527,7 +41527,7 @@
         <v>45853</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -41600,7 +41600,7 @@
         <v>45566</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -41678,7 +41678,7 @@
         <v>44664</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -41756,7 +41756,7 @@
         <v>45692</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -41834,7 +41834,7 @@
         <v>45855</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -41907,7 +41907,7 @@
         <v>44946</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -41985,7 +41985,7 @@
         <v>44946</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -42063,7 +42063,7 @@
         <v>44944</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -42141,7 +42141,7 @@
         <v>45009</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -42219,7 +42219,7 @@
         <v>45247</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -42292,7 +42292,7 @@
         <v>45095</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -42365,7 +42365,7 @@
         <v>45853</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -42438,7 +42438,7 @@
         <v>45523</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -42511,7 +42511,7 @@
         <v>46064</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -42589,7 +42589,7 @@
         <v>45523</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -42667,7 +42667,7 @@
         <v>44767</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -42740,7 +42740,7 @@
         <v>44964</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -42818,7 +42818,7 @@
         <v>44759</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -42891,7 +42891,7 @@
         <v>45258</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -42964,7 +42964,7 @@
         <v>45831</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -43037,7 +43037,7 @@
         <v>44617</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -43110,7 +43110,7 @@
         <v>45042</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -43188,7 +43188,7 @@
         <v>44937</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -43261,7 +43261,7 @@
         <v>45709</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -43339,7 +43339,7 @@
         <v>44993</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -43412,7 +43412,7 @@
         <v>45095</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -43485,7 +43485,7 @@
         <v>44564</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -43558,7 +43558,7 @@
         <v>45607</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -43631,7 +43631,7 @@
         <v>45607</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -43704,7 +43704,7 @@
         <v>45609</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -43782,7 +43782,7 @@
         <v>45665</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -43855,7 +43855,7 @@
         <v>45551</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -43928,7 +43928,7 @@
         <v>44774</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -44006,7 +44006,7 @@
         <v>45744</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -44084,7 +44084,7 @@
         <v>46141</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -44157,7 +44157,7 @@
         <v>45820</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -44235,7 +44235,7 @@
         <v>45013</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -44313,7 +44313,7 @@
         <v>45870</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -44386,7 +44386,7 @@
         <v>45688</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -44464,7 +44464,7 @@
         <v>45428</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -44537,7 +44537,7 @@
         <v>45744</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -44615,7 +44615,7 @@
         <v>45184</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -44688,7 +44688,7 @@
         <v>45980</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -44761,7 +44761,7 @@
         <v>45077</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -44839,7 +44839,7 @@
         <v>45002</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -44917,7 +44917,7 @@
         <v>45068</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -44995,7 +44995,7 @@
         <v>44867</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -45068,7 +45068,7 @@
         <v>45845</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -45146,7 +45146,7 @@
         <v>44886</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -45219,7 +45219,7 @@
         <v>45636</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -45292,7 +45292,7 @@
         <v>45728</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -45370,7 +45370,7 @@
         <v>45280</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -45448,7 +45448,7 @@
         <v>45225</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -45521,7 +45521,7 @@
         <v>46077</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -45599,7 +45599,7 @@
         <v>44987</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -45672,7 +45672,7 @@
         <v>45082</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -45750,7 +45750,7 @@
         <v>45566</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -45828,7 +45828,7 @@
         <v>45177</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -45901,7 +45901,7 @@
         <v>45709</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -45979,7 +45979,7 @@
         <v>46160</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -46052,7 +46052,7 @@
         <v>44995</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -46130,7 +46130,7 @@
         <v>45147</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -46203,7 +46203,7 @@
         <v>44966</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -46276,7 +46276,7 @@
         <v>45230</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -46349,7 +46349,7 @@
         <v>45040</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -46422,7 +46422,7 @@
         <v>45880</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -46500,7 +46500,7 @@
         <v>45880</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -46578,7 +46578,7 @@
         <v>44876</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -46651,7 +46651,7 @@
         <v>45179</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -46724,7 +46724,7 @@
         <v>45179</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -46797,7 +46797,7 @@
         <v>45709</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -46875,7 +46875,7 @@
         <v>45309</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -46953,7 +46953,7 @@
         <v>45309</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -47026,7 +47026,7 @@
         <v>45309</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -47099,7 +47099,7 @@
         <v>46174</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -47177,7 +47177,7 @@
         <v>46174</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -47255,7 +47255,7 @@
         <v>44949</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -47328,7 +47328,7 @@
         <v>45881</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -47406,7 +47406,7 @@
         <v>45323</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -47484,7 +47484,7 @@
         <v>45013</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -47562,7 +47562,7 @@
         <v>44981</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -47640,7 +47640,7 @@
         <v>44930</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -47718,7 +47718,7 @@
         <v>45883</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -47796,7 +47796,7 @@
         <v>45883</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -47874,7 +47874,7 @@
         <v>46176</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -47947,7 +47947,7 @@
         <v>46176</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -48020,7 +48020,7 @@
         <v>46176</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -48093,7 +48093,7 @@
         <v>44550</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -48166,7 +48166,7 @@
         <v>45086</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -48239,7 +48239,7 @@
         <v>45042</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -48312,7 +48312,7 @@
         <v>45042</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -48385,7 +48385,7 @@
         <v>44939</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -48458,7 +48458,7 @@
         <v>45607</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -48531,7 +48531,7 @@
         <v>44732</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -48609,7 +48609,7 @@
         <v>45425</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -48682,7 +48682,7 @@
         <v>45177</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -48755,7 +48755,7 @@
         <v>45302</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -48833,7 +48833,7 @@
         <v>46178</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -48906,7 +48906,7 @@
         <v>45678</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -48984,7 +48984,7 @@
         <v>46178</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -49057,7 +49057,7 @@
         <v>46177</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -49130,7 +49130,7 @@
         <v>46178</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -49203,7 +49203,7 @@
         <v>45622</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -49276,7 +49276,7 @@
         <v>46181</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -49354,7 +49354,7 @@
         <v>45237</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -49432,7 +49432,7 @@
         <v>44642</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -49505,7 +49505,7 @@
         <v>46185</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -49578,7 +49578,7 @@
         <v>46185</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -49651,7 +49651,7 @@
         <v>46188</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -49724,7 +49724,7 @@
         <v>45770</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -49797,7 +49797,7 @@
         <v>45456</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -49875,7 +49875,7 @@
         <v>44749</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -49948,7 +49948,7 @@
         <v>45082</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -50026,7 +50026,7 @@
         <v>45082</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -50104,7 +50104,7 @@
         <v>45167</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -50177,7 +50177,7 @@
         <v>44930</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -50250,7 +50250,7 @@
         <v>44782</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -50323,7 +50323,7 @@
         <v>45646</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -50396,7 +50396,7 @@
         <v>45181</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -50469,7 +50469,7 @@
         <v>45225</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -50542,7 +50542,7 @@
         <v>44754</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -50615,7 +50615,7 @@
         <v>45421</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -50693,7 +50693,7 @@
         <v>46196</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -50771,7 +50771,7 @@
         <v>45551</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -50844,7 +50844,7 @@
         <v>45530</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -50917,7 +50917,7 @@
         <v>44986</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -50990,7 +50990,7 @@
         <v>44770</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -51063,7 +51063,7 @@
         <v>45566</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -51141,7 +51141,7 @@
         <v>46199</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -51214,7 +51214,7 @@
         <v>45846</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -51292,7 +51292,7 @@
         <v>45302</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -51370,7 +51370,7 @@
         <v>45601</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -51443,7 +51443,7 @@
         <v>44678</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -51521,7 +51521,7 @@
         <v>44637</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -51594,7 +51594,7 @@
         <v>46204</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -51667,7 +51667,7 @@
         <v>46203</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -51740,7 +51740,7 @@
         <v>46209</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -51813,7 +51813,7 @@
         <v>46209</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -51886,7 +51886,7 @@
         <v>46209</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -51959,7 +51959,7 @@
         <v>45279</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -52037,7 +52037,7 @@
         <v>45609</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -52115,7 +52115,7 @@
         <v>45070</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -52193,7 +52193,7 @@
         <v>44973</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -52271,7 +52271,7 @@
         <v>44891</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -52344,7 +52344,7 @@
         <v>45616</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -52417,7 +52417,7 @@
         <v>46212</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -52490,7 +52490,7 @@
         <v>46211</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -52563,7 +52563,7 @@
         <v>44949</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -52636,7 +52636,7 @@
         <v>46258</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -52714,7 +52714,7 @@
         <v>46258</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -52792,7 +52792,7 @@
         <v>44966</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -52865,7 +52865,7 @@
         <v>44953</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -52943,7 +52943,7 @@
         <v>44823</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -53016,7 +53016,7 @@
         <v>45202</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -53089,7 +53089,7 @@
         <v>46218</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -53167,7 +53167,7 @@
         <v>45379</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -53240,7 +53240,7 @@
         <v>46218</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -53318,7 +53318,7 @@
         <v>45428</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -53396,7 +53396,7 @@
         <v>45174</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -53474,7 +53474,7 @@
         <v>45770</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -53547,7 +53547,7 @@
         <v>45236</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -53625,7 +53625,7 @@
         <v>45236</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -53703,7 +53703,7 @@
         <v>46219</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -53776,7 +53776,7 @@
         <v>45357</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -53849,7 +53849,7 @@
         <v>45243</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -53927,7 +53927,7 @@
         <v>45022</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -54005,7 +54005,7 @@
         <v>46269</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -54078,7 +54078,7 @@
         <v>44816</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -54151,7 +54151,7 @@
         <v>46269</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -54224,7 +54224,7 @@
         <v>46225</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -54297,7 +54297,7 @@
         <v>46269</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -54370,7 +54370,7 @@
         <v>46269</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -54443,7 +54443,7 @@
         <v>46226</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -54516,7 +54516,7 @@
         <v>46226</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -54589,7 +54589,7 @@
         <v>45314</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -54662,7 +54662,7 @@
         <v>46269</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -54735,7 +54735,7 @@
         <v>46225</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -54808,7 +54808,7 @@
         <v>44820</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -54881,7 +54881,7 @@
         <v>45535</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -54959,7 +54959,7 @@
         <v>45250</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -55037,7 +55037,7 @@
         <v>45197</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -55110,7 +55110,7 @@
         <v>44966</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -55183,7 +55183,7 @@
         <v>46232</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -55256,7 +55256,7 @@
         <v>46279</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -55329,7 +55329,7 @@
         <v>44806</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -55407,7 +55407,7 @@
         <v>46233</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -55480,7 +55480,7 @@
         <v>46279</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -55553,7 +55553,7 @@
         <v>46279</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -55626,7 +55626,7 @@
         <v>45113</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -55699,7 +55699,7 @@
         <v>44964</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -55777,7 +55777,7 @@
         <v>46282</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -55855,7 +55855,7 @@
         <v>45420</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -55928,7 +55928,7 @@
         <v>44834</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -56006,7 +56006,7 @@
         <v>45616</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -56079,7 +56079,7 @@
         <v>46282</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -56157,7 +56157,7 @@
         <v>45258</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -56230,7 +56230,7 @@
         <v>44865</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -56303,7 +56303,7 @@
         <v>46282</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -56381,7 +56381,7 @@
         <v>46282</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -56459,7 +56459,7 @@
         <v>44953</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -56532,7 +56532,7 @@
         <v>45617</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -56610,7 +56610,7 @@
         <v>46282</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -56688,7 +56688,7 @@
         <v>44879</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -56761,7 +56761,7 @@
         <v>46281</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -56834,7 +56834,7 @@
         <v>46282</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -56912,7 +56912,7 @@
         <v>46282</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -56990,7 +56990,7 @@
         <v>46282</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -57068,7 +57068,7 @@
         <v>46282</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -57146,7 +57146,7 @@
         <v>45713</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -57224,7 +57224,7 @@
         <v>45735</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -57302,7 +57302,7 @@
         <v>44862</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -57380,7 +57380,7 @@
         <v>44887</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -57453,7 +57453,7 @@
         <v>44887</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -57526,7 +57526,7 @@
         <v>45426</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -57599,7 +57599,7 @@
         <v>44616</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -57677,7 +57677,7 @@
         <v>44949</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -57750,7 +57750,7 @@
         <v>46286</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -57828,7 +57828,7 @@
         <v>44995</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -57906,7 +57906,7 @@
         <v>44813</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -57984,7 +57984,7 @@
         <v>45863</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -58057,7 +58057,7 @@
         <v>45142</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -58130,7 +58130,7 @@
         <v>45715</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -58203,7 +58203,7 @@
         <v>44653</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -58276,7 +58276,7 @@
         <v>45870</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -58349,7 +58349,7 @@
         <v>45645</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -58427,7 +58427,7 @@
         <v>45593</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -58505,7 +58505,7 @@
         <v>44987</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -58578,7 +58578,7 @@
         <v>45555</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -58656,7 +58656,7 @@
         <v>45639</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -58734,7 +58734,7 @@
         <v>45314</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -58807,7 +58807,7 @@
         <v>45447</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -58885,7 +58885,7 @@
         <v>44729</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -58958,7 +58958,7 @@
         <v>44844</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -59031,7 +59031,7 @@
         <v>44973</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -59109,7 +59109,7 @@
         <v>45076</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -59187,7 +59187,7 @@
         <v>45095</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -59260,7 +59260,7 @@
         <v>45639</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -59338,7 +59338,7 @@
         <v>44526</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -59411,7 +59411,7 @@
         <v>44922</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -59489,7 +59489,7 @@
         <v>46295</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -59567,7 +59567,7 @@
         <v>46295</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -59645,7 +59645,7 @@
         <v>44795</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -59723,7 +59723,7 @@
         <v>45260</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -59796,7 +59796,7 @@
         <v>44491</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -59869,7 +59869,7 @@
         <v>45041</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -59947,7 +59947,7 @@
         <v>45257</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -60020,7 +60020,7 @@
         <v>44871</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -60093,7 +60093,7 @@
         <v>45391</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -60166,7 +60166,7 @@
         <v>45692</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -60244,7 +60244,7 @@
         <v>45070</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -60322,7 +60322,7 @@
         <v>45202</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -60395,7 +60395,7 @@
         <v>44966</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -60473,7 +60473,7 @@
         <v>45323</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -60551,7 +60551,7 @@
         <v>45341</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -60629,7 +60629,7 @@
         <v>44550</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -60702,7 +60702,7 @@
         <v>45566</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -60780,7 +60780,7 @@
         <v>45566</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -60858,7 +60858,7 @@
         <v>44476</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -60931,7 +60931,7 @@
         <v>46255</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -61009,7 +61009,7 @@
         <v>45441</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -61082,7 +61082,7 @@
         <v>45374</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -61160,7 +61160,7 @@
         <v>45391</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -61233,7 +61233,7 @@
         <v>44981</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -61311,7 +61311,7 @@
         <v>44679</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -61389,7 +61389,7 @@
         <v>45293</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -61462,7 +61462,7 @@
         <v>45554</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -61535,7 +61535,7 @@
         <v>45214</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -61608,7 +61608,7 @@
         <v>45110</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -61681,7 +61681,7 @@
         <v>45660</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -61759,7 +61759,7 @@
         <v>45735</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -61837,7 +61837,7 @@
         <v>45516</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -61915,7 +61915,7 @@
         <v>44966</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -61993,7 +61993,7 @@
         <v>45078</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -62066,7 +62066,7 @@
         <v>45113</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -62139,7 +62139,7 @@
         <v>45191</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -62212,7 +62212,7 @@
         <v>45763</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -62285,7 +62285,7 @@
         <v>44551</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -62358,7 +62358,7 @@
         <v>44833</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -62436,7 +62436,7 @@
         <v>45103</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -62509,7 +62509,7 @@
         <v>45618</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -62582,7 +62582,7 @@
         <v>45639</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -62660,7 +62660,7 @@
         <v>45299</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -62733,7 +62733,7 @@
         <v>45301</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -62811,7 +62811,7 @@
         <v>44714</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -62884,7 +62884,7 @@
         <v>44622</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -62957,7 +62957,7 @@
         <v>45232</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -63035,7 +63035,7 @@
         <v>44887</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -63108,7 +63108,7 @@
         <v>45422</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -63181,7 +63181,7 @@
         <v>44622</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -63254,7 +63254,7 @@
         <v>45191</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -63327,7 +63327,7 @@
         <v>44595</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -63400,7 +63400,7 @@
         <v>44589</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -63473,7 +63473,7 @@
         <v>45308</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -63546,7 +63546,7 @@
         <v>44922</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -63624,7 +63624,7 @@
         <v>45615</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -63702,7 +63702,7 @@
         <v>45149</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -63775,7 +63775,7 @@
         <v>45762</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -63848,7 +63848,7 @@
         <v>44817</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -63921,7 +63921,7 @@
         <v>45149</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -63994,7 +63994,7 @@
         <v>45622</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -64067,7 +64067,7 @@
         <v>45554</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -64140,7 +64140,7 @@
         <v>45095</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -64213,7 +64213,7 @@
         <v>45593</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
@@ -64291,7 +64291,7 @@
         <v>45275</v>
       </c>
       <c r="E802" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -64364,7 +64364,7 @@
         <v>44564</v>
       </c>
       <c r="E803" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
@@ -64437,7 +64437,7 @@
         <v>45744</v>
       </c>
       <c r="E804" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
@@ -64515,7 +64515,7 @@
         <v>45407</v>
       </c>
       <c r="E805" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>
@@ -64588,7 +64588,7 @@
         <v>45071</v>
       </c>
       <c r="E806" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F806" t="inlineStr">
         <is>
@@ -64666,7 +64666,7 @@
         <v>45257</v>
       </c>
       <c r="E807" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F807" t="inlineStr">
         <is>
@@ -64744,7 +64744,7 @@
         <v>45257</v>
       </c>
       <c r="E808" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F808" t="inlineStr">
         <is>
@@ -64817,7 +64817,7 @@
         <v>45566</v>
       </c>
       <c r="E809" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F809" t="inlineStr">
         <is>
@@ -64895,7 +64895,7 @@
         <v>45566</v>
       </c>
       <c r="E810" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F810" t="inlineStr">
         <is>
@@ -64973,7 +64973,7 @@
         <v>45566</v>
       </c>
       <c r="E811" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F811" t="inlineStr">
         <is>
@@ -65051,7 +65051,7 @@
         <v>45735</v>
       </c>
       <c r="E812" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F812" t="inlineStr">
         <is>
@@ -65129,7 +65129,7 @@
         <v>45736</v>
       </c>
       <c r="E813" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F813" t="inlineStr">
         <is>
@@ -65207,7 +65207,7 @@
         <v>45642</v>
       </c>
       <c r="E814" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F814" t="inlineStr">
         <is>
@@ -65280,7 +65280,7 @@
         <v>45530</v>
       </c>
       <c r="E815" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F815" t="inlineStr">
         <is>
@@ -65353,7 +65353,7 @@
         <v>45530</v>
       </c>
       <c r="E816" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F816" t="inlineStr">
         <is>
@@ -65426,7 +65426,7 @@
         <v>45371</v>
       </c>
       <c r="E817" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F817" t="inlineStr">
         <is>
@@ -65504,7 +65504,7 @@
         <v>45644</v>
       </c>
       <c r="E818" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F818" t="inlineStr">
         <is>
@@ -65577,7 +65577,7 @@
         <v>45428</v>
       </c>
       <c r="E819" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F819" t="inlineStr">
         <is>
@@ -65650,7 +65650,7 @@
         <v>45429</v>
       </c>
       <c r="E820" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F820" t="inlineStr">
         <is>
@@ -65723,7 +65723,7 @@
         <v>45250</v>
       </c>
       <c r="E821" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F821" t="inlineStr">
         <is>
@@ -65801,7 +65801,7 @@
         <v>46188</v>
       </c>
       <c r="E822" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F822" t="inlineStr">
         <is>
@@ -65879,7 +65879,7 @@
         <v>46258</v>
       </c>
       <c r="E823" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F823" t="inlineStr">
         <is>

--- a/Översikt FINSPÅNG.xlsx
+++ b/Översikt FINSPÅNG.xlsx
@@ -601,7 +601,7 @@
         <v>46244</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -727,7 +727,7 @@
         <v>45945</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -858,7 +858,7 @@
         <v>45134</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
         <v>44896</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1121,7 +1121,7 @@
         <v>44888</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>45210</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1369,7 +1369,7 @@
         <v>44777</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1488,7 +1488,7 @@
         <v>44897</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1607,7 +1607,7 @@
         <v>44910</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1734,7 +1734,7 @@
         <v>45322</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1855,7 +1855,7 @@
         <v>44624</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1971,7 +1971,7 @@
         <v>44599</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2082,7 +2082,7 @@
         <v>45891</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2198,7 +2198,7 @@
         <v>45421</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2318,7 +2318,7 @@
         <v>45238</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2433,7 +2433,7 @@
         <v>45898</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2548,7 +2548,7 @@
         <v>45267</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2663,7 +2663,7 @@
         <v>45679</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2782,7 +2782,7 @@
         <v>45812</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2896,7 +2896,7 @@
         <v>44791</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3010,7 +3010,7 @@
         <v>44665</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3123,7 +3123,7 @@
         <v>45681</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3240,7 +3240,7 @@
         <v>45819</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3356,7 +3356,7 @@
         <v>45800</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3468,7 +3468,7 @@
         <v>45082</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3580,7 +3580,7 @@
         <v>44774</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3692,7 +3692,7 @@
         <v>45602</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3804,7 +3804,7 @@
         <v>46196</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3916,7 +3916,7 @@
         <v>44690</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4027,7 +4027,7 @@
         <v>44981</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4138,7 +4138,7 @@
         <v>44903</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4248,7 +4248,7 @@
         <v>45425</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4354,7 +4354,7 @@
         <v>45121</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4469,7 +4469,7 @@
         <v>44816</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4575,7 +4575,7 @@
         <v>45477</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4690,7 +4690,7 @@
         <v>45894</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4805,7 +4805,7 @@
         <v>45905</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4916,7 +4916,7 @@
         <v>45441</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5027,7 +5027,7 @@
         <v>45950</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5138,7 +5138,7 @@
         <v>45644</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5244,7 +5244,7 @@
         <v>45235</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5355,7 +5355,7 @@
         <v>46174</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5466,7 +5466,7 @@
         <v>46181</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5577,7 +5577,7 @@
         <v>46181</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5688,7 +5688,7 @@
         <v>44480</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5799,7 +5799,7 @@
         <v>44683</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5909,7 +5909,7 @@
         <v>44776</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6014,7 +6014,7 @@
         <v>44529</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6119,7 +6119,7 @@
         <v>44504</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6229,7 +6229,7 @@
         <v>45232</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6339,7 +6339,7 @@
         <v>45082</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6449,7 +6449,7 @@
         <v>45744</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6563,7 +6563,7 @@
         <v>45446</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6668,7 +6668,7 @@
         <v>44915</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6778,7 +6778,7 @@
         <v>44897</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6892,7 +6892,7 @@
         <v>45567</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7006,7 +7006,7 @@
         <v>45905</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7116,7 +7116,7 @@
         <v>44915</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7226,7 +7226,7 @@
         <v>45883</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7336,7 +7336,7 @@
         <v>45566</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7450,7 +7450,7 @@
         <v>44599</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7560,7 +7560,7 @@
         <v>45328</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7669,7 +7669,7 @@
         <v>45149</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7778,7 +7778,7 @@
         <v>45615</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7892,7 +7892,7 @@
         <v>45229</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8002,7 +8002,7 @@
         <v>45846</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8112,7 +8112,7 @@
         <v>45845</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8222,7 +8222,7 @@
         <v>45302</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8331,7 +8331,7 @@
         <v>44817</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8441,7 +8441,7 @@
         <v>44992</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8551,7 +8551,7 @@
         <v>45555</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8665,7 +8665,7 @@
         <v>45880</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8775,7 +8775,7 @@
         <v>45070</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8885,7 +8885,7 @@
         <v>44965</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8999,7 +8999,7 @@
         <v>44501</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9109,7 +9109,7 @@
         <v>46129</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9223,7 +9223,7 @@
         <v>44930</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9333,7 +9333,7 @@
         <v>46043</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9447,7 +9447,7 @@
         <v>45447</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9557,7 +9557,7 @@
         <v>45636</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9662,7 +9662,7 @@
         <v>44622</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9767,7 +9767,7 @@
         <v>46058</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9881,7 +9881,7 @@
         <v>46155</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9995,7 +9995,7 @@
         <v>46189</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10100,7 +10100,7 @@
         <v>46181</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10210,7 +10210,7 @@
         <v>46258</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10320,7 +10320,7 @@
         <v>46258</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10434,7 +10434,7 @@
         <v>44711</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10544,7 +10544,7 @@
         <v>45428</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10649,7 +10649,7 @@
         <v>46107</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10759,7 +10759,7 @@
         <v>46188</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10873,7 +10873,7 @@
         <v>44755</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10951,7 +10951,7 @@
         <v>44675</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11024,7 +11024,7 @@
         <v>44676</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11102,7 +11102,7 @@
         <v>44864</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11175,7 +11175,7 @@
         <v>44600</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11248,7 +11248,7 @@
         <v>44824</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11321,7 +11321,7 @@
         <v>44536</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11399,7 +11399,7 @@
         <v>44799</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11472,7 +11472,7 @@
         <v>44795</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11545,7 +11545,7 @@
         <v>44856</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11618,7 +11618,7 @@
         <v>44675</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11691,7 +11691,7 @@
         <v>44578</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11769,7 +11769,7 @@
         <v>44852</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -11847,7 +11847,7 @@
         <v>44601</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -11925,7 +11925,7 @@
         <v>44601</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -11998,7 +11998,7 @@
         <v>44551</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12071,7 +12071,7 @@
         <v>44525</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12144,7 +12144,7 @@
         <v>44574</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12222,7 +12222,7 @@
         <v>44588</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12300,7 +12300,7 @@
         <v>44889</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12373,7 +12373,7 @@
         <v>44574</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12446,7 +12446,7 @@
         <v>44627</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12519,7 +12519,7 @@
         <v>44503</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -12597,7 +12597,7 @@
         <v>44525</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -12675,7 +12675,7 @@
         <v>44503</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -12748,7 +12748,7 @@
         <v>44874</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -12821,7 +12821,7 @@
         <v>44502</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -12899,7 +12899,7 @@
         <v>44551</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -12972,7 +12972,7 @@
         <v>44712</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -13050,7 +13050,7 @@
         <v>44581</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -13123,7 +13123,7 @@
         <v>44601</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -13196,7 +13196,7 @@
         <v>44833</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -13269,7 +13269,7 @@
         <v>44859</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -13342,7 +13342,7 @@
         <v>44672</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -13415,7 +13415,7 @@
         <v>44735</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -13488,7 +13488,7 @@
         <v>44796</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -13561,7 +13561,7 @@
         <v>44782</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -13634,7 +13634,7 @@
         <v>44741</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -13707,7 +13707,7 @@
         <v>44859</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -13780,7 +13780,7 @@
         <v>44613</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -13858,7 +13858,7 @@
         <v>44678</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -13931,7 +13931,7 @@
         <v>44855</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -14009,7 +14009,7 @@
         <v>44887</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -14082,7 +14082,7 @@
         <v>44860</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -14155,7 +14155,7 @@
         <v>44753</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -14228,7 +14228,7 @@
         <v>44802</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -14301,7 +14301,7 @@
         <v>44844</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -14379,7 +14379,7 @@
         <v>44781</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -14452,7 +14452,7 @@
         <v>44541</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -14525,7 +14525,7 @@
         <v>44564</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -14598,7 +14598,7 @@
         <v>44859</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -14671,7 +14671,7 @@
         <v>44819</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -14744,7 +14744,7 @@
         <v>44742</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -14822,7 +14822,7 @@
         <v>44859</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -14895,7 +14895,7 @@
         <v>44595</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -14968,7 +14968,7 @@
         <v>44581</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -15046,7 +15046,7 @@
         <v>44630</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -15119,7 +15119,7 @@
         <v>44875</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -15192,7 +15192,7 @@
         <v>44582</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -15265,7 +15265,7 @@
         <v>44508</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -15338,7 +15338,7 @@
         <v>44600</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -15411,7 +15411,7 @@
         <v>44804</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -15489,7 +15489,7 @@
         <v>44816</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -15562,7 +15562,7 @@
         <v>44656</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -15635,7 +15635,7 @@
         <v>44481</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -15708,7 +15708,7 @@
         <v>44627</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -15781,7 +15781,7 @@
         <v>44635</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -15854,7 +15854,7 @@
         <v>44587</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -15927,7 +15927,7 @@
         <v>44820</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -16000,7 +16000,7 @@
         <v>44743</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -16073,7 +16073,7 @@
         <v>44776</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -16146,7 +16146,7 @@
         <v>44713</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -16224,7 +16224,7 @@
         <v>44697</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -16302,7 +16302,7 @@
         <v>44532</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -16375,7 +16375,7 @@
         <v>44831</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -16453,7 +16453,7 @@
         <v>44552</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -16526,7 +16526,7 @@
         <v>44879</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -16599,7 +16599,7 @@
         <v>44581</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -16672,7 +16672,7 @@
         <v>44588</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -16750,7 +16750,7 @@
         <v>44601</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -16823,7 +16823,7 @@
         <v>44481</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -16896,7 +16896,7 @@
         <v>45374</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -16974,7 +16974,7 @@
         <v>44533</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -17047,7 +17047,7 @@
         <v>44601</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -17120,7 +17120,7 @@
         <v>44678</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -17193,7 +17193,7 @@
         <v>44930</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -17266,7 +17266,7 @@
         <v>44930</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -17339,7 +17339,7 @@
         <v>44704</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -17412,7 +17412,7 @@
         <v>44564</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -17485,7 +17485,7 @@
         <v>44642</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -17558,7 +17558,7 @@
         <v>44659</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -17636,7 +17636,7 @@
         <v>44844</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -17709,7 +17709,7 @@
         <v>45181</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -17782,7 +17782,7 @@
         <v>45042</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -17860,7 +17860,7 @@
         <v>45257</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -17938,7 +17938,7 @@
         <v>45225</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -18011,7 +18011,7 @@
         <v>44564</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -18084,7 +18084,7 @@
         <v>44817</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -18157,7 +18157,7 @@
         <v>45082</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -18235,7 +18235,7 @@
         <v>45566</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -18313,7 +18313,7 @@
         <v>45095</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -18386,7 +18386,7 @@
         <v>44806</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -18464,7 +18464,7 @@
         <v>45149</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -18537,7 +18537,7 @@
         <v>45082</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -18615,7 +18615,7 @@
         <v>45082</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -18693,7 +18693,7 @@
         <v>45357</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -18766,7 +18766,7 @@
         <v>45617</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -18844,7 +18844,7 @@
         <v>45013</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -18922,7 +18922,7 @@
         <v>45086</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -18995,7 +18995,7 @@
         <v>44816</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -19068,7 +19068,7 @@
         <v>44589</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -19141,7 +19141,7 @@
         <v>45618</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -19214,7 +19214,7 @@
         <v>45744</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -19292,7 +19292,7 @@
         <v>45744</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -19370,7 +19370,7 @@
         <v>45252</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -19443,7 +19443,7 @@
         <v>44754</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -19516,7 +19516,7 @@
         <v>45407</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -19589,7 +19589,7 @@
         <v>44993</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -19662,7 +19662,7 @@
         <v>44802</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -19735,7 +19735,7 @@
         <v>44987</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -19808,7 +19808,7 @@
         <v>44900</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -19881,7 +19881,7 @@
         <v>45042</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -19954,7 +19954,7 @@
         <v>45330</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -20027,7 +20027,7 @@
         <v>45247</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -20100,7 +20100,7 @@
         <v>44778</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -20173,7 +20173,7 @@
         <v>45422</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -20246,7 +20246,7 @@
         <v>45357</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -20319,7 +20319,7 @@
         <v>45214</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -20392,7 +20392,7 @@
         <v>44887</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -20465,7 +20465,7 @@
         <v>45421</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -20543,7 +20543,7 @@
         <v>45420</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -20616,7 +20616,7 @@
         <v>45259</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -20689,7 +20689,7 @@
         <v>44887</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -20762,7 +20762,7 @@
         <v>45125</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -20840,7 +20840,7 @@
         <v>45033</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -20918,7 +20918,7 @@
         <v>44953</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -20991,7 +20991,7 @@
         <v>45275</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -21064,7 +21064,7 @@
         <v>45463</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -21137,7 +21137,7 @@
         <v>45447</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -21215,7 +21215,7 @@
         <v>45103</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -21288,7 +21288,7 @@
         <v>45688</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -21366,7 +21366,7 @@
         <v>44995</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -21444,7 +21444,7 @@
         <v>45677</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -21522,7 +21522,7 @@
         <v>45103</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -21595,7 +21595,7 @@
         <v>45022</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -21673,7 +21673,7 @@
         <v>45113</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -21746,7 +21746,7 @@
         <v>45744</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -21824,7 +21824,7 @@
         <v>45267</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -21902,7 +21902,7 @@
         <v>45202</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -21975,7 +21975,7 @@
         <v>45118</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -22048,7 +22048,7 @@
         <v>44993</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -22121,7 +22121,7 @@
         <v>44833</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -22199,7 +22199,7 @@
         <v>45442</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -22272,7 +22272,7 @@
         <v>44767</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -22345,7 +22345,7 @@
         <v>45225</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -22418,7 +22418,7 @@
         <v>44966</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -22496,7 +22496,7 @@
         <v>44900</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -22569,7 +22569,7 @@
         <v>45535</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -22647,7 +22647,7 @@
         <v>44770</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -22720,7 +22720,7 @@
         <v>44986</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -22793,7 +22793,7 @@
         <v>44957</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -22866,7 +22866,7 @@
         <v>45293</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -22939,7 +22939,7 @@
         <v>45257</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -23017,7 +23017,7 @@
         <v>44981</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -23095,7 +23095,7 @@
         <v>45257</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -23168,7 +23168,7 @@
         <v>44922</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -23246,7 +23246,7 @@
         <v>45191</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -23319,7 +23319,7 @@
         <v>45391</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -23392,7 +23392,7 @@
         <v>45541</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -23470,7 +23470,7 @@
         <v>45258</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -23543,7 +23543,7 @@
         <v>45178</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -23616,7 +23616,7 @@
         <v>45250</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -23694,7 +23694,7 @@
         <v>45258</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -23767,7 +23767,7 @@
         <v>45260</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -23840,7 +23840,7 @@
         <v>45362</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -23913,7 +23913,7 @@
         <v>45177</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -23986,7 +23986,7 @@
         <v>45623</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -24064,7 +24064,7 @@
         <v>45639</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -24142,7 +24142,7 @@
         <v>45197</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -24215,7 +24215,7 @@
         <v>45250</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -24288,7 +24288,7 @@
         <v>45264</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -24366,7 +24366,7 @@
         <v>44949</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -24439,7 +24439,7 @@
         <v>45883</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -24517,7 +24517,7 @@
         <v>45110</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -24590,7 +24590,7 @@
         <v>44973</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -24668,7 +24668,7 @@
         <v>44550</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -24741,7 +24741,7 @@
         <v>44508</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -24814,7 +24814,7 @@
         <v>45008</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -24892,7 +24892,7 @@
         <v>44922</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -24970,7 +24970,7 @@
         <v>45323</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -25048,7 +25048,7 @@
         <v>44891</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -25121,7 +25121,7 @@
         <v>45103</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -25194,7 +25194,7 @@
         <v>45593</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -25272,7 +25272,7 @@
         <v>45551</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -25345,7 +25345,7 @@
         <v>45097</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -25418,7 +25418,7 @@
         <v>45095</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -25491,7 +25491,7 @@
         <v>45463</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -25564,7 +25564,7 @@
         <v>44942</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -25637,7 +25637,7 @@
         <v>44617</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -25710,7 +25710,7 @@
         <v>45883</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -25788,7 +25788,7 @@
         <v>45888</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -25866,7 +25866,7 @@
         <v>45341</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -25944,7 +25944,7 @@
         <v>45293</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -26017,7 +26017,7 @@
         <v>45391</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -26090,7 +26090,7 @@
         <v>44678</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -26168,7 +26168,7 @@
         <v>44939</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -26241,7 +26241,7 @@
         <v>45293</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -26319,7 +26319,7 @@
         <v>45202</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -26392,7 +26392,7 @@
         <v>45621</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -26470,7 +26470,7 @@
         <v>44860</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -26543,7 +26543,7 @@
         <v>45328</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -26616,7 +26616,7 @@
         <v>45002</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -26694,7 +26694,7 @@
         <v>44946</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -26772,7 +26772,7 @@
         <v>44946</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -26850,7 +26850,7 @@
         <v>45467</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -26923,7 +26923,7 @@
         <v>45082</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -27001,7 +27001,7 @@
         <v>45299</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -27074,7 +27074,7 @@
         <v>45078</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -27147,7 +27147,7 @@
         <v>44993</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -27220,7 +27220,7 @@
         <v>45250</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -27298,7 +27298,7 @@
         <v>45206</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -27371,7 +27371,7 @@
         <v>45133</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -27444,7 +27444,7 @@
         <v>44551</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -27517,7 +27517,7 @@
         <v>45891</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -27595,7 +27595,7 @@
         <v>45707</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -27673,7 +27673,7 @@
         <v>45894</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -27751,7 +27751,7 @@
         <v>45896</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -27829,7 +27829,7 @@
         <v>45895</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -27902,7 +27902,7 @@
         <v>45898</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -27975,7 +27975,7 @@
         <v>45447</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -28053,7 +28053,7 @@
         <v>44964</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -28131,7 +28131,7 @@
         <v>45607</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -28204,7 +28204,7 @@
         <v>45607</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -28277,7 +28277,7 @@
         <v>45337</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -28350,7 +28350,7 @@
         <v>44490</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -28423,7 +28423,7 @@
         <v>45428</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -28501,7 +28501,7 @@
         <v>45428</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -28579,7 +28579,7 @@
         <v>45280</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -28657,7 +28657,7 @@
         <v>44844</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -28730,7 +28730,7 @@
         <v>44844</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -28803,7 +28803,7 @@
         <v>44866</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -28876,7 +28876,7 @@
         <v>44840</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -28954,7 +28954,7 @@
         <v>45167</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -29032,7 +29032,7 @@
         <v>45903</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -29110,7 +29110,7 @@
         <v>45770</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -29183,7 +29183,7 @@
         <v>45749</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -29261,7 +29261,7 @@
         <v>45639</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -29339,7 +29339,7 @@
         <v>45607</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -29412,7 +29412,7 @@
         <v>45709</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -29490,7 +29490,7 @@
         <v>45566</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -29568,7 +29568,7 @@
         <v>45566</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -29646,7 +29646,7 @@
         <v>45903</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -29724,7 +29724,7 @@
         <v>45904</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -29802,7 +29802,7 @@
         <v>44656</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -29880,7 +29880,7 @@
         <v>44937</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -29953,7 +29953,7 @@
         <v>45903</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -30031,7 +30031,7 @@
         <v>45314</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -30104,7 +30104,7 @@
         <v>45903</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -30182,7 +30182,7 @@
         <v>45740</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -30260,7 +30260,7 @@
         <v>45904</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -30338,7 +30338,7 @@
         <v>45903</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -30416,7 +30416,7 @@
         <v>45908</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -30489,7 +30489,7 @@
         <v>44865</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -30562,7 +30562,7 @@
         <v>45905</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -30640,7 +30640,7 @@
         <v>44887</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -30713,7 +30713,7 @@
         <v>44887</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -30786,7 +30786,7 @@
         <v>45103</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -30859,7 +30859,7 @@
         <v>45905</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -30937,7 +30937,7 @@
         <v>45232</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -31015,7 +31015,7 @@
         <v>44981</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -31093,7 +31093,7 @@
         <v>45740</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -31171,7 +31171,7 @@
         <v>45609</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -31249,7 +31249,7 @@
         <v>44637</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -31322,7 +31322,7 @@
         <v>45041</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -31395,7 +31395,7 @@
         <v>45642</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -31473,7 +31473,7 @@
         <v>45063</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -31546,7 +31546,7 @@
         <v>45113</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -31619,7 +31619,7 @@
         <v>45566</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -31697,7 +31697,7 @@
         <v>45566</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -31775,7 +31775,7 @@
         <v>45566</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -31853,7 +31853,7 @@
         <v>45735</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -31931,7 +31931,7 @@
         <v>45736</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -32009,7 +32009,7 @@
         <v>45601</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -32082,7 +32082,7 @@
         <v>45040</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -32155,7 +32155,7 @@
         <v>45020</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -32228,7 +32228,7 @@
         <v>45593</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -32306,7 +32306,7 @@
         <v>45530</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -32379,7 +32379,7 @@
         <v>45622</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -32452,7 +32452,7 @@
         <v>45068</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -32530,7 +32530,7 @@
         <v>44966</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -32603,7 +32603,7 @@
         <v>45149</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -32676,7 +32676,7 @@
         <v>44964</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -32754,7 +32754,7 @@
         <v>45617</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -32832,7 +32832,7 @@
         <v>45302</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -32910,7 +32910,7 @@
         <v>44897</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -32988,7 +32988,7 @@
         <v>45642</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -33061,7 +33061,7 @@
         <v>45267</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -33139,7 +33139,7 @@
         <v>44622</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -33212,7 +33212,7 @@
         <v>44966</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -33285,7 +33285,7 @@
         <v>45530</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -33358,7 +33358,7 @@
         <v>44564</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -33431,7 +33431,7 @@
         <v>44958</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -33504,7 +33504,7 @@
         <v>45095</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -33577,7 +33577,7 @@
         <v>45727</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -33650,7 +33650,7 @@
         <v>44516</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -33723,7 +33723,7 @@
         <v>45040</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -33801,7 +33801,7 @@
         <v>45554</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -33874,7 +33874,7 @@
         <v>45924</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -33947,7 +33947,7 @@
         <v>45371</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -34025,7 +34025,7 @@
         <v>44491</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -34098,7 +34098,7 @@
         <v>45615</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -34176,7 +34176,7 @@
         <v>44677</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -34249,7 +34249,7 @@
         <v>45609</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -34327,7 +34327,7 @@
         <v>45554</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -34400,7 +34400,7 @@
         <v>45554</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -34473,7 +34473,7 @@
         <v>45796</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -34551,7 +34551,7 @@
         <v>45566</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -34629,7 +34629,7 @@
         <v>45555</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -34707,7 +34707,7 @@
         <v>45678</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -34785,7 +34785,7 @@
         <v>45796</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -34863,7 +34863,7 @@
         <v>45551</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -34936,7 +34936,7 @@
         <v>45428</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -35009,7 +35009,7 @@
         <v>45931</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -35082,7 +35082,7 @@
         <v>45229</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -35160,7 +35160,7 @@
         <v>45316</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -35238,7 +35238,7 @@
         <v>45797</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -35311,7 +35311,7 @@
         <v>45797</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -35384,7 +35384,7 @@
         <v>45797</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -35462,7 +35462,7 @@
         <v>44622</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -35535,7 +35535,7 @@
         <v>45702</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -35613,7 +35613,7 @@
         <v>45343</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -35691,7 +35691,7 @@
         <v>45441</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -35764,7 +35764,7 @@
         <v>45441</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -35837,7 +35837,7 @@
         <v>44964</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -35915,7 +35915,7 @@
         <v>45800</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -35993,7 +35993,7 @@
         <v>45179</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -36066,7 +36066,7 @@
         <v>45179</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -36139,7 +36139,7 @@
         <v>45077</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -36217,7 +36217,7 @@
         <v>45800</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -36295,7 +36295,7 @@
         <v>45935</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -36373,7 +36373,7 @@
         <v>45800</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -36451,7 +36451,7 @@
         <v>45206</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -36524,7 +36524,7 @@
         <v>45800</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -36602,7 +36602,7 @@
         <v>44734</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -36675,7 +36675,7 @@
         <v>44732</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -36753,7 +36753,7 @@
         <v>45084</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -36826,7 +36826,7 @@
         <v>45456</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -36904,7 +36904,7 @@
         <v>45174</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -36982,7 +36982,7 @@
         <v>45645</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -37060,7 +37060,7 @@
         <v>44918</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -37138,7 +37138,7 @@
         <v>45705</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -37211,7 +37211,7 @@
         <v>44795</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -37289,7 +37289,7 @@
         <v>45006</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -37362,7 +37362,7 @@
         <v>44614</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -37435,7 +37435,7 @@
         <v>45426</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -37508,7 +37508,7 @@
         <v>44679</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -37586,7 +37586,7 @@
         <v>44725</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -37659,7 +37659,7 @@
         <v>45846</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -37737,7 +37737,7 @@
         <v>45715</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -37810,7 +37810,7 @@
         <v>44634</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -37888,7 +37888,7 @@
         <v>44653</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -37961,7 +37961,7 @@
         <v>45107</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -38034,7 +38034,7 @@
         <v>45415</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -38107,7 +38107,7 @@
         <v>45070</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -38185,7 +38185,7 @@
         <v>45762</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -38258,7 +38258,7 @@
         <v>45944</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -38331,7 +38331,7 @@
         <v>45812</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -38409,7 +38409,7 @@
         <v>45600</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -38482,7 +38482,7 @@
         <v>45812</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -38560,7 +38560,7 @@
         <v>45279</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -38638,7 +38638,7 @@
         <v>45421</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -38716,7 +38716,7 @@
         <v>45344</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -38789,7 +38789,7 @@
         <v>45639</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -38867,7 +38867,7 @@
         <v>45257</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -38945,7 +38945,7 @@
         <v>45819</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -39023,7 +39023,7 @@
         <v>45819</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -39101,7 +39101,7 @@
         <v>45301</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -39179,7 +39179,7 @@
         <v>45147</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -39252,7 +39252,7 @@
         <v>45950</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -39330,7 +39330,7 @@
         <v>45095</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -39403,7 +39403,7 @@
         <v>45824</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -39481,7 +39481,7 @@
         <v>45824</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -39559,7 +39559,7 @@
         <v>45824</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -39637,7 +39637,7 @@
         <v>45824</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -39715,7 +39715,7 @@
         <v>45209</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -39788,7 +39788,7 @@
         <v>45209</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -39861,7 +39861,7 @@
         <v>45086</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -39934,7 +39934,7 @@
         <v>45243</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -40012,7 +40012,7 @@
         <v>45071</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -40090,7 +40090,7 @@
         <v>45660</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -40168,7 +40168,7 @@
         <v>45103</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -40241,7 +40241,7 @@
         <v>44903</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -40319,7 +40319,7 @@
         <v>45166</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -40397,7 +40397,7 @@
         <v>45075</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -40470,7 +40470,7 @@
         <v>45253</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -40548,7 +40548,7 @@
         <v>45955</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -40621,7 +40621,7 @@
         <v>44664</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -40699,7 +40699,7 @@
         <v>45639</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -40777,7 +40777,7 @@
         <v>45274</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -40850,7 +40850,7 @@
         <v>45665</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -40923,7 +40923,7 @@
         <v>44767</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -40996,7 +40996,7 @@
         <v>45835</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -41074,7 +41074,7 @@
         <v>45009</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -41152,7 +41152,7 @@
         <v>45720</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -41230,7 +41230,7 @@
         <v>44735</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -41303,7 +41303,7 @@
         <v>45840</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -41381,7 +41381,7 @@
         <v>45516</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -41459,7 +41459,7 @@
         <v>45142</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -41532,7 +41532,7 @@
         <v>45616</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -41605,7 +41605,7 @@
         <v>45616</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -41678,7 +41678,7 @@
         <v>44729</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -41751,7 +41751,7 @@
         <v>45149</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -41824,7 +41824,7 @@
         <v>45593</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -41902,7 +41902,7 @@
         <v>45646</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -41975,7 +41975,7 @@
         <v>45257</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -42053,7 +42053,7 @@
         <v>45969</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -42126,7 +42126,7 @@
         <v>45971</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -42199,7 +42199,7 @@
         <v>45314</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -42272,7 +42272,7 @@
         <v>44774</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -42350,7 +42350,7 @@
         <v>45845</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -42428,7 +42428,7 @@
         <v>45095</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -42506,7 +42506,7 @@
         <v>45095</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -42579,7 +42579,7 @@
         <v>44672</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -42652,7 +42652,7 @@
         <v>45709</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -42730,7 +42730,7 @@
         <v>45728</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -42808,7 +42808,7 @@
         <v>45308</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -42881,7 +42881,7 @@
         <v>44823</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -42954,7 +42954,7 @@
         <v>45615</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -43032,7 +43032,7 @@
         <v>44973</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -43110,7 +43110,7 @@
         <v>45623</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -43183,7 +43183,7 @@
         <v>45776</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -43256,7 +43256,7 @@
         <v>44813</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -43334,7 +43334,7 @@
         <v>45002</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -43412,7 +43412,7 @@
         <v>44833</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -43490,7 +43490,7 @@
         <v>45468</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -43568,7 +43568,7 @@
         <v>45853</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -43641,7 +43641,7 @@
         <v>45530</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -43714,7 +43714,7 @@
         <v>45713</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -43792,7 +43792,7 @@
         <v>45854</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -43865,7 +43865,7 @@
         <v>45855</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -43938,7 +43938,7 @@
         <v>45854</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -44011,7 +44011,7 @@
         <v>45523</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -44084,7 +44084,7 @@
         <v>45744</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -44162,7 +44162,7 @@
         <v>45379</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -44235,7 +44235,7 @@
         <v>45309</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -44313,7 +44313,7 @@
         <v>45309</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -44386,7 +44386,7 @@
         <v>45309</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -44459,7 +44459,7 @@
         <v>45147</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -44532,7 +44532,7 @@
         <v>45831</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -44605,7 +44605,7 @@
         <v>45257</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -44678,7 +44678,7 @@
         <v>44759</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -44751,7 +44751,7 @@
         <v>45302</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -44829,7 +44829,7 @@
         <v>44840</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -44902,7 +44902,7 @@
         <v>44966</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -44975,7 +44975,7 @@
         <v>45692</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -45053,7 +45053,7 @@
         <v>45688</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -45131,7 +45131,7 @@
         <v>45870</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -45204,7 +45204,7 @@
         <v>45820</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -45282,7 +45282,7 @@
         <v>44767</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -45355,7 +45355,7 @@
         <v>45979</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -45428,7 +45428,7 @@
         <v>44820</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -45501,7 +45501,7 @@
         <v>44817</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -45579,7 +45579,7 @@
         <v>45041</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -45657,7 +45657,7 @@
         <v>45082</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -45735,7 +45735,7 @@
         <v>45688</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -45813,7 +45813,7 @@
         <v>45040</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -45886,7 +45886,7 @@
         <v>45709</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -45964,7 +45964,7 @@
         <v>44834</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -46042,7 +46042,7 @@
         <v>44862</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -46120,7 +46120,7 @@
         <v>44595</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -46193,7 +46193,7 @@
         <v>44973</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -46271,7 +46271,7 @@
         <v>44880</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -46349,7 +46349,7 @@
         <v>45880</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -46427,7 +46427,7 @@
         <v>45710</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -46500,7 +46500,7 @@
         <v>45191</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -46573,7 +46573,7 @@
         <v>45880</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -46651,7 +46651,7 @@
         <v>45009</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -46724,7 +46724,7 @@
         <v>45084</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -46797,7 +46797,7 @@
         <v>45881</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -46875,7 +46875,7 @@
         <v>44782</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -46948,7 +46948,7 @@
         <v>45770</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -47021,7 +47021,7 @@
         <v>46099</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -47094,7 +47094,7 @@
         <v>45236</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -47172,7 +47172,7 @@
         <v>45236</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -47250,7 +47250,7 @@
         <v>46099</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -47323,7 +47323,7 @@
         <v>44714</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -47396,7 +47396,7 @@
         <v>46099</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -47474,7 +47474,7 @@
         <v>44886</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -47547,7 +47547,7 @@
         <v>46099</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -47625,7 +47625,7 @@
         <v>45070</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -47703,7 +47703,7 @@
         <v>45299</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -47776,7 +47776,7 @@
         <v>46099</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -47854,7 +47854,7 @@
         <v>45983</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -47927,7 +47927,7 @@
         <v>45983</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -48000,7 +48000,7 @@
         <v>44749</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -48073,7 +48073,7 @@
         <v>45566</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -48151,7 +48151,7 @@
         <v>45986</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -48224,7 +48224,7 @@
         <v>45042</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -48297,7 +48297,7 @@
         <v>45728</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -48375,7 +48375,7 @@
         <v>44876</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -48448,7 +48448,7 @@
         <v>44861</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -48526,7 +48526,7 @@
         <v>45983</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -48599,7 +48599,7 @@
         <v>45986</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -48672,7 +48672,7 @@
         <v>44987</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -48745,7 +48745,7 @@
         <v>44879</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -48818,7 +48818,7 @@
         <v>45985</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -48891,7 +48891,7 @@
         <v>44871</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -48964,7 +48964,7 @@
         <v>44526</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -49037,7 +49037,7 @@
         <v>44642</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -49110,7 +49110,7 @@
         <v>44536</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -49183,7 +49183,7 @@
         <v>45735</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -49261,7 +49261,7 @@
         <v>46106</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -49339,7 +49339,7 @@
         <v>45237</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -49417,7 +49417,7 @@
         <v>44914</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -49495,7 +49495,7 @@
         <v>45076</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -49573,7 +49573,7 @@
         <v>45548</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -49646,7 +49646,7 @@
         <v>45735</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -49724,7 +49724,7 @@
         <v>46111</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -49802,7 +49802,7 @@
         <v>45763</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -49875,7 +49875,7 @@
         <v>44944</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -49953,7 +49953,7 @@
         <v>44503</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -50026,7 +50026,7 @@
         <v>46113</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -50104,7 +50104,7 @@
         <v>45636</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -50177,7 +50177,7 @@
         <v>44595</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -50255,7 +50255,7 @@
         <v>45233</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -50328,7 +50328,7 @@
         <v>46114</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -50406,7 +50406,7 @@
         <v>46114</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -50484,7 +50484,7 @@
         <v>46114</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -50562,7 +50562,7 @@
         <v>44607</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -50635,7 +50635,7 @@
         <v>46120</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -50713,7 +50713,7 @@
         <v>46121</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -50791,7 +50791,7 @@
         <v>44953</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -50869,7 +50869,7 @@
         <v>46125</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -50942,7 +50942,7 @@
         <v>44817</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -51015,7 +51015,7 @@
         <v>46122</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -51088,7 +51088,7 @@
         <v>45523</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -51166,7 +51166,7 @@
         <v>46000</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -51244,7 +51244,7 @@
         <v>46129</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -51322,7 +51322,7 @@
         <v>44867</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -51395,7 +51395,7 @@
         <v>46002</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -51473,7 +51473,7 @@
         <v>46002</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -51551,7 +51551,7 @@
         <v>44732</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -51629,7 +51629,7 @@
         <v>44949</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -51702,7 +51702,7 @@
         <v>44949</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -51775,7 +51775,7 @@
         <v>44949</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -51848,7 +51848,7 @@
         <v>46128</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -51921,7 +51921,7 @@
         <v>46002</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -51999,7 +51999,7 @@
         <v>46002</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -52077,7 +52077,7 @@
         <v>46006</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -52155,7 +52155,7 @@
         <v>46006</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -52233,7 +52233,7 @@
         <v>44960</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -52311,7 +52311,7 @@
         <v>44966</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -52384,7 +52384,7 @@
         <v>46003</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -52457,7 +52457,7 @@
         <v>46006</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -52530,7 +52530,7 @@
         <v>44662</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -52608,7 +52608,7 @@
         <v>45086</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -52681,7 +52681,7 @@
         <v>45706</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -52754,7 +52754,7 @@
         <v>45692</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -52832,7 +52832,7 @@
         <v>45555</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -52910,7 +52910,7 @@
         <v>44918</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -52988,7 +52988,7 @@
         <v>45740</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -53061,7 +53061,7 @@
         <v>45622</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -53134,7 +53134,7 @@
         <v>44930</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -53212,7 +53212,7 @@
         <v>45915</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -53290,7 +53290,7 @@
         <v>45258</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -53363,7 +53363,7 @@
         <v>45379</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -53436,7 +53436,7 @@
         <v>45706</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -53509,7 +53509,7 @@
         <v>45853</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -53582,7 +53582,7 @@
         <v>45783</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -53660,7 +53660,7 @@
         <v>45260</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -53733,7 +53733,7 @@
         <v>46134</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -53806,7 +53806,7 @@
         <v>45021</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -53879,7 +53879,7 @@
         <v>45167</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -53952,7 +53952,7 @@
         <v>45008</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -54025,7 +54025,7 @@
         <v>44616</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -54103,7 +54103,7 @@
         <v>45700</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -54181,7 +54181,7 @@
         <v>44550</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -54254,7 +54254,7 @@
         <v>45230</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -54327,7 +54327,7 @@
         <v>45013</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -54405,7 +54405,7 @@
         <v>45853</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -54478,7 +54478,7 @@
         <v>45554</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -54551,7 +54551,7 @@
         <v>46030</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -54629,7 +54629,7 @@
         <v>46030</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -54707,7 +54707,7 @@
         <v>45095</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -54785,7 +54785,7 @@
         <v>46029</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -54858,7 +54858,7 @@
         <v>46031</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -54936,7 +54936,7 @@
         <v>45516</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -55009,7 +55009,7 @@
         <v>46034</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -55087,7 +55087,7 @@
         <v>46034</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -55165,7 +55165,7 @@
         <v>45055</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -55238,7 +55238,7 @@
         <v>46034</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -55316,7 +55316,7 @@
         <v>44995</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -55394,7 +55394,7 @@
         <v>46036</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -55472,7 +55472,7 @@
         <v>46036</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -55550,7 +55550,7 @@
         <v>45095</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -55623,7 +55623,7 @@
         <v>45425</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -55696,7 +55696,7 @@
         <v>44898</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -55769,7 +55769,7 @@
         <v>45177</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -55842,7 +55842,7 @@
         <v>45560</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -55920,7 +55920,7 @@
         <v>45719</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -55998,7 +55998,7 @@
         <v>46040</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -56071,7 +56071,7 @@
         <v>46040</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -56144,7 +56144,7 @@
         <v>45456</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -56222,7 +56222,7 @@
         <v>44865</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -56300,7 +56300,7 @@
         <v>45832</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -56373,7 +56373,7 @@
         <v>44980</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -56446,7 +56446,7 @@
         <v>44966</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -56524,7 +56524,7 @@
         <v>46048</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -56602,7 +56602,7 @@
         <v>46048</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -56680,7 +56680,7 @@
         <v>44914</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -56753,7 +56753,7 @@
         <v>46048</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -56831,7 +56831,7 @@
         <v>46050</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -56909,7 +56909,7 @@
         <v>44974</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -56982,7 +56982,7 @@
         <v>44950</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -57060,7 +57060,7 @@
         <v>46050</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -57138,7 +57138,7 @@
         <v>45601</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -57211,7 +57211,7 @@
         <v>45323</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -57289,7 +57289,7 @@
         <v>46049</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -57362,7 +57362,7 @@
         <v>46064</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -57440,7 +57440,7 @@
         <v>46052</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -57513,7 +57513,7 @@
         <v>46055</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -57591,7 +57591,7 @@
         <v>46058</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -57669,7 +57669,7 @@
         <v>46058</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -57747,7 +57747,7 @@
         <v>46058</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -57825,7 +57825,7 @@
         <v>46060</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -57898,7 +57898,7 @@
         <v>46141</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -57971,7 +57971,7 @@
         <v>46058</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -58049,7 +58049,7 @@
         <v>46064</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -58127,7 +58127,7 @@
         <v>46064</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -58205,7 +58205,7 @@
         <v>46064</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -58283,7 +58283,7 @@
         <v>46063</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -58361,7 +58361,7 @@
         <v>46064</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -58439,7 +58439,7 @@
         <v>46063</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -58517,7 +58517,7 @@
         <v>46064</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -58595,7 +58595,7 @@
         <v>46064</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -58673,7 +58673,7 @@
         <v>46065</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -58751,7 +58751,7 @@
         <v>46065</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -58829,7 +58829,7 @@
         <v>46069</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -58907,7 +58907,7 @@
         <v>46070</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -58985,7 +58985,7 @@
         <v>46070</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -59063,7 +59063,7 @@
         <v>46073</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -59141,7 +59141,7 @@
         <v>46076</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -59219,7 +59219,7 @@
         <v>46076</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -59297,7 +59297,7 @@
         <v>46078</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -59375,7 +59375,7 @@
         <v>46079</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -59453,7 +59453,7 @@
         <v>45980</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -59526,7 +59526,7 @@
         <v>45184</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -59599,7 +59599,7 @@
         <v>46080</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -59677,7 +59677,7 @@
         <v>46080</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -59755,7 +59755,7 @@
         <v>46080</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -59833,7 +59833,7 @@
         <v>46080</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -59911,7 +59911,7 @@
         <v>46085</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -59989,7 +59989,7 @@
         <v>45845</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -60067,7 +60067,7 @@
         <v>46085</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -60145,7 +60145,7 @@
         <v>46085</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -60223,7 +60223,7 @@
         <v>46085</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -60301,7 +60301,7 @@
         <v>46077</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -60379,7 +60379,7 @@
         <v>46094</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -60457,7 +60457,7 @@
         <v>46097</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -60530,7 +60530,7 @@
         <v>46176</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -60603,7 +60603,7 @@
         <v>46176</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -60676,7 +60676,7 @@
         <v>46176</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -60749,7 +60749,7 @@
         <v>46174</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -60827,7 +60827,7 @@
         <v>46174</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -60905,7 +60905,7 @@
         <v>46177</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -60978,7 +60978,7 @@
         <v>46181</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -61056,7 +61056,7 @@
         <v>46178</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -61129,7 +61129,7 @@
         <v>46178</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -61202,7 +61202,7 @@
         <v>46178</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -61275,7 +61275,7 @@
         <v>46185</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -61348,7 +61348,7 @@
         <v>46185</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -61421,7 +61421,7 @@
         <v>46188</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -61494,7 +61494,7 @@
         <v>46196</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -61572,7 +61572,7 @@
         <v>45846</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -61650,7 +61650,7 @@
         <v>46199</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -61723,7 +61723,7 @@
         <v>46203</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -61796,7 +61796,7 @@
         <v>46204</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -61869,7 +61869,7 @@
         <v>46209</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -61942,7 +61942,7 @@
         <v>46211</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -62015,7 +62015,7 @@
         <v>46212</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -62088,7 +62088,7 @@
         <v>46218</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -62166,7 +62166,7 @@
         <v>46218</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -62244,7 +62244,7 @@
         <v>46219</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -62317,7 +62317,7 @@
         <v>46226</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -62390,7 +62390,7 @@
         <v>46269</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -62463,7 +62463,7 @@
         <v>46269</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -62536,7 +62536,7 @@
         <v>46226</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -62609,7 +62609,7 @@
         <v>46225</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -62682,7 +62682,7 @@
         <v>46225</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -62755,7 +62755,7 @@
         <v>46269</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -62828,7 +62828,7 @@
         <v>46269</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -62901,7 +62901,7 @@
         <v>46269</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -62974,7 +62974,7 @@
         <v>46232</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -63047,7 +63047,7 @@
         <v>46233</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -63120,7 +63120,7 @@
         <v>46279</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -63193,7 +63193,7 @@
         <v>46279</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -63266,7 +63266,7 @@
         <v>46279</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -63339,7 +63339,7 @@
         <v>46282</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -63417,7 +63417,7 @@
         <v>46282</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -63495,7 +63495,7 @@
         <v>46282</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -63573,7 +63573,7 @@
         <v>46282</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -63651,7 +63651,7 @@
         <v>46282</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -63729,7 +63729,7 @@
         <v>46282</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -63807,7 +63807,7 @@
         <v>46282</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -63885,7 +63885,7 @@
         <v>46282</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -63963,7 +63963,7 @@
         <v>46282</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -64041,7 +64041,7 @@
         <v>46281</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -64114,7 +64114,7 @@
         <v>46286</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -64192,7 +64192,7 @@
         <v>45863</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
@@ -64265,7 +64265,7 @@
         <v>45870</v>
       </c>
       <c r="E802" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -64338,7 +64338,7 @@
         <v>46295</v>
       </c>
       <c r="E803" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
@@ -64416,7 +64416,7 @@
         <v>46295</v>
       </c>
       <c r="E804" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
@@ -64494,7 +64494,7 @@
         <v>46255</v>
       </c>
       <c r="E805" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>
@@ -64572,7 +64572,7 @@
         <v>46302</v>
       </c>
       <c r="E806" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F806" t="inlineStr">
         <is>
@@ -64645,7 +64645,7 @@
         <v>46258</v>
       </c>
       <c r="E807" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F807" t="inlineStr">
         <is>
@@ -64723,7 +64723,7 @@
         <v>46258</v>
       </c>
       <c r="E808" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F808" t="inlineStr">
         <is>
@@ -64801,7 +64801,7 @@
         <v>46300</v>
       </c>
       <c r="E809" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F809" t="inlineStr">
         <is>
@@ -64874,7 +64874,7 @@
         <v>46304</v>
       </c>
       <c r="E810" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F810" t="inlineStr">
         <is>
@@ -64947,7 +64947,7 @@
         <v>46304</v>
       </c>
       <c r="E811" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F811" t="inlineStr">
         <is>
@@ -65020,7 +65020,7 @@
         <v>46304</v>
       </c>
       <c r="E812" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F812" t="inlineStr">
         <is>
@@ -65093,7 +65093,7 @@
         <v>46209</v>
       </c>
       <c r="E813" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F813" t="inlineStr">
         <is>
@@ -65166,7 +65166,7 @@
         <v>46304</v>
       </c>
       <c r="E814" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F814" t="inlineStr">
         <is>
@@ -65239,7 +65239,7 @@
         <v>46160</v>
       </c>
       <c r="E815" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F815" t="inlineStr">
         <is>
@@ -65312,7 +65312,7 @@
         <v>45644</v>
       </c>
       <c r="E816" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F816" t="inlineStr">
         <is>
@@ -65385,7 +65385,7 @@
         <v>45428</v>
       </c>
       <c r="E817" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F817" t="inlineStr">
         <is>
@@ -65458,7 +65458,7 @@
         <v>45429</v>
       </c>
       <c r="E818" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F818" t="inlineStr">
         <is>
@@ -65531,7 +65531,7 @@
         <v>45250</v>
       </c>
       <c r="E819" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F819" t="inlineStr">
         <is>
@@ -65609,7 +65609,7 @@
         <v>46188</v>
       </c>
       <c r="E820" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F820" t="inlineStr">
         <is>
@@ -65687,7 +65687,7 @@
         <v>46258</v>
       </c>
       <c r="E821" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F821" t="inlineStr">
         <is>

--- a/Översikt FINSPÅNG.xlsx
+++ b/Översikt FINSPÅNG.xlsx
@@ -601,7 +601,7 @@
         <v>46244</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -727,7 +727,7 @@
         <v>45945</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -858,7 +858,7 @@
         <v>45134</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
         <v>44896</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1121,7 +1121,7 @@
         <v>44888</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>45210</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1369,7 +1369,7 @@
         <v>44777</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1488,7 +1488,7 @@
         <v>44897</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1607,7 +1607,7 @@
         <v>44910</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1734,7 +1734,7 @@
         <v>45322</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1855,7 +1855,7 @@
         <v>44624</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1971,7 +1971,7 @@
         <v>44599</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2082,7 +2082,7 @@
         <v>45891</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2198,7 +2198,7 @@
         <v>45421</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2318,7 +2318,7 @@
         <v>45238</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2433,7 +2433,7 @@
         <v>45898</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2548,7 +2548,7 @@
         <v>45267</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2663,7 +2663,7 @@
         <v>45679</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2782,7 +2782,7 @@
         <v>45812</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2896,7 +2896,7 @@
         <v>44791</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3010,7 +3010,7 @@
         <v>44665</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3123,7 +3123,7 @@
         <v>45681</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3174,10 +3174,10 @@
         <v>4</v>
       </c>
       <c r="T23" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U23" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
@@ -3240,7 +3240,7 @@
         <v>45819</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3356,7 +3356,7 @@
         <v>45800</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3468,7 +3468,7 @@
         <v>45082</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3580,7 +3580,7 @@
         <v>44774</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3692,7 +3692,7 @@
         <v>45602</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3804,7 +3804,7 @@
         <v>46196</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3916,7 +3916,7 @@
         <v>44690</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4027,7 +4027,7 @@
         <v>44981</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4138,7 +4138,7 @@
         <v>44903</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4248,7 +4248,7 @@
         <v>45425</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4354,7 +4354,7 @@
         <v>45121</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4469,7 +4469,7 @@
         <v>44816</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4575,7 +4575,7 @@
         <v>45477</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4690,7 +4690,7 @@
         <v>45894</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4805,7 +4805,7 @@
         <v>45905</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4916,7 +4916,7 @@
         <v>45441</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5027,7 +5027,7 @@
         <v>45950</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5138,7 +5138,7 @@
         <v>45644</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5244,7 +5244,7 @@
         <v>45235</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5355,7 +5355,7 @@
         <v>46174</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5466,7 +5466,7 @@
         <v>46181</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5577,7 +5577,7 @@
         <v>46181</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5688,7 +5688,7 @@
         <v>44480</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5799,7 +5799,7 @@
         <v>44683</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5909,7 +5909,7 @@
         <v>44776</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6014,7 +6014,7 @@
         <v>44529</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6119,7 +6119,7 @@
         <v>44504</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6229,7 +6229,7 @@
         <v>45232</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6339,7 +6339,7 @@
         <v>45082</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6449,7 +6449,7 @@
         <v>45744</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6563,7 +6563,7 @@
         <v>45446</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6668,7 +6668,7 @@
         <v>44915</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6778,7 +6778,7 @@
         <v>44897</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6892,7 +6892,7 @@
         <v>45567</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7006,7 +7006,7 @@
         <v>45905</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7116,7 +7116,7 @@
         <v>44915</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7226,7 +7226,7 @@
         <v>45883</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7336,7 +7336,7 @@
         <v>45566</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7450,7 +7450,7 @@
         <v>44599</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7560,7 +7560,7 @@
         <v>45328</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7669,7 +7669,7 @@
         <v>45149</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7778,7 +7778,7 @@
         <v>45615</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7892,7 +7892,7 @@
         <v>45229</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8002,7 +8002,7 @@
         <v>45846</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8112,7 +8112,7 @@
         <v>45845</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8222,7 +8222,7 @@
         <v>45302</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8331,7 +8331,7 @@
         <v>44817</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8441,7 +8441,7 @@
         <v>44992</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8551,7 +8551,7 @@
         <v>45555</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8665,7 +8665,7 @@
         <v>45880</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8775,7 +8775,7 @@
         <v>45070</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8885,7 +8885,7 @@
         <v>44965</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8999,7 +8999,7 @@
         <v>44501</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9109,7 +9109,7 @@
         <v>46129</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9223,7 +9223,7 @@
         <v>44930</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9333,7 +9333,7 @@
         <v>46043</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9447,7 +9447,7 @@
         <v>45447</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9557,7 +9557,7 @@
         <v>45636</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9662,7 +9662,7 @@
         <v>44622</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9767,7 +9767,7 @@
         <v>46058</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9881,7 +9881,7 @@
         <v>46155</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9995,7 +9995,7 @@
         <v>46189</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10100,7 +10100,7 @@
         <v>46181</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10210,7 +10210,7 @@
         <v>46258</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10320,7 +10320,7 @@
         <v>46258</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10434,7 +10434,7 @@
         <v>44711</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10544,7 +10544,7 @@
         <v>45428</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10649,7 +10649,7 @@
         <v>46107</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10759,7 +10759,7 @@
         <v>46188</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10873,7 +10873,7 @@
         <v>44755</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10951,7 +10951,7 @@
         <v>44675</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11024,7 +11024,7 @@
         <v>44676</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11102,7 +11102,7 @@
         <v>44864</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11175,7 +11175,7 @@
         <v>44600</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11248,7 +11248,7 @@
         <v>44824</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11321,7 +11321,7 @@
         <v>44536</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11399,7 +11399,7 @@
         <v>44799</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11472,7 +11472,7 @@
         <v>44795</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11545,7 +11545,7 @@
         <v>44856</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11618,7 +11618,7 @@
         <v>44675</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11691,7 +11691,7 @@
         <v>44578</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11769,7 +11769,7 @@
         <v>44852</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -11847,7 +11847,7 @@
         <v>44601</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -11925,7 +11925,7 @@
         <v>44601</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -11998,7 +11998,7 @@
         <v>44551</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12071,7 +12071,7 @@
         <v>44525</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12144,7 +12144,7 @@
         <v>44574</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12222,7 +12222,7 @@
         <v>44588</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12300,7 +12300,7 @@
         <v>44889</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12373,7 +12373,7 @@
         <v>44574</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12446,7 +12446,7 @@
         <v>44627</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12519,7 +12519,7 @@
         <v>44503</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -12597,7 +12597,7 @@
         <v>44525</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -12675,7 +12675,7 @@
         <v>44503</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -12748,7 +12748,7 @@
         <v>44874</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -12821,7 +12821,7 @@
         <v>44502</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -12899,7 +12899,7 @@
         <v>44551</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -12972,7 +12972,7 @@
         <v>44712</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -13050,7 +13050,7 @@
         <v>44581</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -13123,7 +13123,7 @@
         <v>44601</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -13196,7 +13196,7 @@
         <v>44833</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -13269,7 +13269,7 @@
         <v>44859</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -13342,7 +13342,7 @@
         <v>44672</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -13415,7 +13415,7 @@
         <v>44735</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -13488,7 +13488,7 @@
         <v>44796</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -13561,7 +13561,7 @@
         <v>44782</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -13634,7 +13634,7 @@
         <v>44741</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -13707,7 +13707,7 @@
         <v>44859</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -13780,7 +13780,7 @@
         <v>44613</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -13858,7 +13858,7 @@
         <v>44678</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -13931,7 +13931,7 @@
         <v>44855</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -14009,7 +14009,7 @@
         <v>44887</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -14082,7 +14082,7 @@
         <v>44860</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -14155,7 +14155,7 @@
         <v>44753</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -14228,7 +14228,7 @@
         <v>44802</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -14301,7 +14301,7 @@
         <v>44844</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -14379,7 +14379,7 @@
         <v>44781</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -14452,7 +14452,7 @@
         <v>44541</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -14525,7 +14525,7 @@
         <v>44564</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -14598,7 +14598,7 @@
         <v>44859</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -14671,7 +14671,7 @@
         <v>44819</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -14744,7 +14744,7 @@
         <v>44742</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -14822,7 +14822,7 @@
         <v>44859</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -14895,7 +14895,7 @@
         <v>44595</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -14968,7 +14968,7 @@
         <v>44581</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -15046,7 +15046,7 @@
         <v>44630</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -15119,7 +15119,7 @@
         <v>44875</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -15192,7 +15192,7 @@
         <v>44582</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -15265,7 +15265,7 @@
         <v>44508</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -15338,7 +15338,7 @@
         <v>44600</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -15411,7 +15411,7 @@
         <v>44804</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -15489,7 +15489,7 @@
         <v>44816</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -15562,7 +15562,7 @@
         <v>44656</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -15635,7 +15635,7 @@
         <v>44481</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -15708,7 +15708,7 @@
         <v>44627</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -15781,7 +15781,7 @@
         <v>44635</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -15854,7 +15854,7 @@
         <v>44587</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -15927,7 +15927,7 @@
         <v>44820</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -16000,7 +16000,7 @@
         <v>44743</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -16073,7 +16073,7 @@
         <v>44776</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -16146,7 +16146,7 @@
         <v>44713</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -16224,7 +16224,7 @@
         <v>44697</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -16302,7 +16302,7 @@
         <v>44532</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -16375,7 +16375,7 @@
         <v>44831</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -16453,7 +16453,7 @@
         <v>44552</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -16526,7 +16526,7 @@
         <v>44879</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -16599,7 +16599,7 @@
         <v>44581</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -16672,7 +16672,7 @@
         <v>44588</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -16750,7 +16750,7 @@
         <v>44601</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -16823,7 +16823,7 @@
         <v>44481</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -16896,7 +16896,7 @@
         <v>45374</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -16974,7 +16974,7 @@
         <v>44533</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -17047,7 +17047,7 @@
         <v>44601</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -17120,7 +17120,7 @@
         <v>44678</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -17193,7 +17193,7 @@
         <v>44930</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -17266,7 +17266,7 @@
         <v>44930</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -17339,7 +17339,7 @@
         <v>44704</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -17412,7 +17412,7 @@
         <v>44564</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -17485,7 +17485,7 @@
         <v>44642</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -17558,7 +17558,7 @@
         <v>44659</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -17636,7 +17636,7 @@
         <v>44844</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -17709,7 +17709,7 @@
         <v>45181</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -17782,7 +17782,7 @@
         <v>45042</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -17860,7 +17860,7 @@
         <v>45257</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -17938,7 +17938,7 @@
         <v>45225</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -18011,7 +18011,7 @@
         <v>44564</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -18084,7 +18084,7 @@
         <v>44817</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -18157,7 +18157,7 @@
         <v>45082</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -18235,7 +18235,7 @@
         <v>45566</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -18313,7 +18313,7 @@
         <v>45095</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -18386,7 +18386,7 @@
         <v>44806</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -18464,7 +18464,7 @@
         <v>45149</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -18537,7 +18537,7 @@
         <v>45082</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -18615,7 +18615,7 @@
         <v>45082</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -18693,7 +18693,7 @@
         <v>45357</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -18766,7 +18766,7 @@
         <v>45617</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -18844,7 +18844,7 @@
         <v>45013</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -18922,7 +18922,7 @@
         <v>45086</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -18995,7 +18995,7 @@
         <v>44816</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -19068,7 +19068,7 @@
         <v>44589</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -19141,7 +19141,7 @@
         <v>45618</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -19214,7 +19214,7 @@
         <v>45744</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -19292,7 +19292,7 @@
         <v>45744</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -19370,7 +19370,7 @@
         <v>45252</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -19443,7 +19443,7 @@
         <v>44754</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -19516,7 +19516,7 @@
         <v>45407</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -19589,7 +19589,7 @@
         <v>44993</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -19662,7 +19662,7 @@
         <v>44802</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -19735,7 +19735,7 @@
         <v>44987</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -19808,7 +19808,7 @@
         <v>44900</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -19881,7 +19881,7 @@
         <v>45042</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -19954,7 +19954,7 @@
         <v>45330</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -20027,7 +20027,7 @@
         <v>45247</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -20100,7 +20100,7 @@
         <v>44778</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -20173,7 +20173,7 @@
         <v>45422</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -20246,7 +20246,7 @@
         <v>45357</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -20319,7 +20319,7 @@
         <v>45214</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -20392,7 +20392,7 @@
         <v>44887</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -20465,7 +20465,7 @@
         <v>45421</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -20543,7 +20543,7 @@
         <v>45420</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -20616,7 +20616,7 @@
         <v>45259</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -20689,7 +20689,7 @@
         <v>44887</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -20762,7 +20762,7 @@
         <v>45125</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -20840,7 +20840,7 @@
         <v>45033</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -20918,7 +20918,7 @@
         <v>44953</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -20991,7 +20991,7 @@
         <v>45275</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -21064,7 +21064,7 @@
         <v>45463</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -21137,7 +21137,7 @@
         <v>45447</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -21215,7 +21215,7 @@
         <v>45103</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -21288,7 +21288,7 @@
         <v>45688</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -21366,7 +21366,7 @@
         <v>44995</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -21444,7 +21444,7 @@
         <v>45677</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -21522,7 +21522,7 @@
         <v>45103</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -21595,7 +21595,7 @@
         <v>45022</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -21673,7 +21673,7 @@
         <v>45113</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -21746,7 +21746,7 @@
         <v>45744</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -21824,7 +21824,7 @@
         <v>45267</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -21902,7 +21902,7 @@
         <v>45202</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -21975,7 +21975,7 @@
         <v>45118</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -22048,7 +22048,7 @@
         <v>44993</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -22121,7 +22121,7 @@
         <v>44833</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -22199,7 +22199,7 @@
         <v>45442</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -22272,7 +22272,7 @@
         <v>44767</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -22345,7 +22345,7 @@
         <v>45225</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -22418,7 +22418,7 @@
         <v>44966</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -22496,7 +22496,7 @@
         <v>44900</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -22569,7 +22569,7 @@
         <v>45535</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -22647,7 +22647,7 @@
         <v>44770</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -22720,7 +22720,7 @@
         <v>44986</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -22793,7 +22793,7 @@
         <v>44957</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -22866,7 +22866,7 @@
         <v>45293</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -22939,7 +22939,7 @@
         <v>45257</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -23017,7 +23017,7 @@
         <v>44981</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -23095,7 +23095,7 @@
         <v>45257</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -23168,7 +23168,7 @@
         <v>44922</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -23246,7 +23246,7 @@
         <v>45191</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -23319,7 +23319,7 @@
         <v>45391</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -23392,7 +23392,7 @@
         <v>45541</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -23470,7 +23470,7 @@
         <v>45258</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -23543,7 +23543,7 @@
         <v>45178</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -23616,7 +23616,7 @@
         <v>45250</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -23694,7 +23694,7 @@
         <v>45258</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -23767,7 +23767,7 @@
         <v>45260</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -23840,7 +23840,7 @@
         <v>45362</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -23913,7 +23913,7 @@
         <v>45177</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -23986,7 +23986,7 @@
         <v>45623</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -24064,7 +24064,7 @@
         <v>45639</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -24142,7 +24142,7 @@
         <v>45197</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -24215,7 +24215,7 @@
         <v>45250</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -24288,7 +24288,7 @@
         <v>45264</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -24366,7 +24366,7 @@
         <v>44949</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -24439,7 +24439,7 @@
         <v>45883</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -24517,7 +24517,7 @@
         <v>45110</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -24590,7 +24590,7 @@
         <v>44973</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -24668,7 +24668,7 @@
         <v>44550</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -24741,7 +24741,7 @@
         <v>44508</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -24814,7 +24814,7 @@
         <v>45008</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -24892,7 +24892,7 @@
         <v>44922</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -24970,7 +24970,7 @@
         <v>45323</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -25048,7 +25048,7 @@
         <v>44891</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -25121,7 +25121,7 @@
         <v>45103</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -25194,7 +25194,7 @@
         <v>45593</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -25272,7 +25272,7 @@
         <v>45551</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -25345,7 +25345,7 @@
         <v>45097</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -25418,7 +25418,7 @@
         <v>45095</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -25491,7 +25491,7 @@
         <v>45463</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -25564,7 +25564,7 @@
         <v>44942</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -25637,7 +25637,7 @@
         <v>44617</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -25710,7 +25710,7 @@
         <v>45883</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -25788,7 +25788,7 @@
         <v>45888</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -25866,7 +25866,7 @@
         <v>45341</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -25944,7 +25944,7 @@
         <v>45293</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -26017,7 +26017,7 @@
         <v>45391</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -26090,7 +26090,7 @@
         <v>44678</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -26168,7 +26168,7 @@
         <v>44939</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -26241,7 +26241,7 @@
         <v>45293</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -26319,7 +26319,7 @@
         <v>45202</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -26392,7 +26392,7 @@
         <v>45621</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -26470,7 +26470,7 @@
         <v>44860</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -26543,7 +26543,7 @@
         <v>45328</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -26616,7 +26616,7 @@
         <v>45002</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -26694,7 +26694,7 @@
         <v>44946</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -26772,7 +26772,7 @@
         <v>44946</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -26850,7 +26850,7 @@
         <v>45467</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -26923,7 +26923,7 @@
         <v>45082</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -27001,7 +27001,7 @@
         <v>45299</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -27074,7 +27074,7 @@
         <v>45078</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -27147,7 +27147,7 @@
         <v>44993</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -27220,7 +27220,7 @@
         <v>45250</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -27298,7 +27298,7 @@
         <v>45206</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -27371,7 +27371,7 @@
         <v>45133</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -27444,7 +27444,7 @@
         <v>44551</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -27517,7 +27517,7 @@
         <v>45891</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -27595,7 +27595,7 @@
         <v>45707</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -27673,7 +27673,7 @@
         <v>45894</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -27751,7 +27751,7 @@
         <v>45896</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -27829,7 +27829,7 @@
         <v>45895</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -27902,7 +27902,7 @@
         <v>45898</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -27975,7 +27975,7 @@
         <v>45447</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -28053,7 +28053,7 @@
         <v>44964</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -28131,7 +28131,7 @@
         <v>45607</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -28204,7 +28204,7 @@
         <v>45607</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -28277,7 +28277,7 @@
         <v>45337</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -28350,7 +28350,7 @@
         <v>44490</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -28423,7 +28423,7 @@
         <v>45428</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -28501,7 +28501,7 @@
         <v>45428</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -28579,7 +28579,7 @@
         <v>45280</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -28657,7 +28657,7 @@
         <v>44844</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -28730,7 +28730,7 @@
         <v>44844</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -28803,7 +28803,7 @@
         <v>44866</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -28876,7 +28876,7 @@
         <v>44840</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -28954,7 +28954,7 @@
         <v>45167</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -29032,7 +29032,7 @@
         <v>45903</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -29110,7 +29110,7 @@
         <v>45770</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -29183,7 +29183,7 @@
         <v>45749</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -29261,7 +29261,7 @@
         <v>45639</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -29339,7 +29339,7 @@
         <v>45607</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -29412,7 +29412,7 @@
         <v>45709</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -29490,7 +29490,7 @@
         <v>45566</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -29568,7 +29568,7 @@
         <v>45566</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -29646,7 +29646,7 @@
         <v>45903</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -29724,7 +29724,7 @@
         <v>45904</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -29802,7 +29802,7 @@
         <v>44656</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -29880,7 +29880,7 @@
         <v>44937</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -29953,7 +29953,7 @@
         <v>45903</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -30031,7 +30031,7 @@
         <v>45314</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -30104,7 +30104,7 @@
         <v>45903</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -30182,7 +30182,7 @@
         <v>45740</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -30260,7 +30260,7 @@
         <v>45904</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -30338,7 +30338,7 @@
         <v>45903</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -30416,7 +30416,7 @@
         <v>45908</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -30489,7 +30489,7 @@
         <v>44865</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -30562,7 +30562,7 @@
         <v>45905</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -30640,7 +30640,7 @@
         <v>44887</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -30713,7 +30713,7 @@
         <v>44887</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -30786,7 +30786,7 @@
         <v>45103</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -30859,7 +30859,7 @@
         <v>45905</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -30937,7 +30937,7 @@
         <v>45232</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -31015,7 +31015,7 @@
         <v>44981</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -31093,7 +31093,7 @@
         <v>45740</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -31171,7 +31171,7 @@
         <v>45609</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -31249,7 +31249,7 @@
         <v>44637</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -31322,7 +31322,7 @@
         <v>45041</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -31395,7 +31395,7 @@
         <v>45642</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -31473,7 +31473,7 @@
         <v>45063</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -31546,7 +31546,7 @@
         <v>45113</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -31619,7 +31619,7 @@
         <v>45566</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -31697,7 +31697,7 @@
         <v>45566</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -31775,7 +31775,7 @@
         <v>45566</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -31853,7 +31853,7 @@
         <v>45735</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -31931,7 +31931,7 @@
         <v>45736</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -32009,7 +32009,7 @@
         <v>45601</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -32082,7 +32082,7 @@
         <v>45040</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -32155,7 +32155,7 @@
         <v>45020</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -32228,7 +32228,7 @@
         <v>45593</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -32306,7 +32306,7 @@
         <v>45530</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -32379,7 +32379,7 @@
         <v>45622</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -32452,7 +32452,7 @@
         <v>45068</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -32530,7 +32530,7 @@
         <v>44966</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -32603,7 +32603,7 @@
         <v>45149</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -32676,7 +32676,7 @@
         <v>44964</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -32754,7 +32754,7 @@
         <v>45617</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -32832,7 +32832,7 @@
         <v>45302</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -32910,7 +32910,7 @@
         <v>44897</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -32988,7 +32988,7 @@
         <v>45642</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -33061,7 +33061,7 @@
         <v>45267</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -33139,7 +33139,7 @@
         <v>44622</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -33212,7 +33212,7 @@
         <v>44966</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -33285,7 +33285,7 @@
         <v>45530</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -33358,7 +33358,7 @@
         <v>44564</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -33431,7 +33431,7 @@
         <v>44958</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -33504,7 +33504,7 @@
         <v>45095</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -33577,7 +33577,7 @@
         <v>45727</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -33650,7 +33650,7 @@
         <v>44516</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -33723,7 +33723,7 @@
         <v>45040</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -33801,7 +33801,7 @@
         <v>45554</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -33874,7 +33874,7 @@
         <v>45924</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -33947,7 +33947,7 @@
         <v>45371</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -34025,7 +34025,7 @@
         <v>44491</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -34098,7 +34098,7 @@
         <v>45615</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -34176,7 +34176,7 @@
         <v>44677</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -34249,7 +34249,7 @@
         <v>45609</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -34327,7 +34327,7 @@
         <v>45554</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -34400,7 +34400,7 @@
         <v>45554</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -34473,7 +34473,7 @@
         <v>45796</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -34551,7 +34551,7 @@
         <v>45566</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -34629,7 +34629,7 @@
         <v>45555</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -34707,7 +34707,7 @@
         <v>45678</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -34785,7 +34785,7 @@
         <v>45796</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -34863,7 +34863,7 @@
         <v>45551</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -34936,7 +34936,7 @@
         <v>45428</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -35009,7 +35009,7 @@
         <v>45931</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -35082,7 +35082,7 @@
         <v>45229</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -35160,7 +35160,7 @@
         <v>45316</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -35238,7 +35238,7 @@
         <v>45797</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -35311,7 +35311,7 @@
         <v>45797</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -35384,7 +35384,7 @@
         <v>45797</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -35462,7 +35462,7 @@
         <v>44622</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -35535,7 +35535,7 @@
         <v>45702</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -35613,7 +35613,7 @@
         <v>45343</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -35691,7 +35691,7 @@
         <v>45441</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -35764,7 +35764,7 @@
         <v>45441</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -35837,7 +35837,7 @@
         <v>44964</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -35915,7 +35915,7 @@
         <v>45800</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -35993,7 +35993,7 @@
         <v>45179</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -36066,7 +36066,7 @@
         <v>45179</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -36139,7 +36139,7 @@
         <v>45077</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -36217,7 +36217,7 @@
         <v>45800</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -36295,7 +36295,7 @@
         <v>45935</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -36373,7 +36373,7 @@
         <v>45800</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -36451,7 +36451,7 @@
         <v>45206</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -36524,7 +36524,7 @@
         <v>45800</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -36602,7 +36602,7 @@
         <v>44734</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -36675,7 +36675,7 @@
         <v>44732</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -36753,7 +36753,7 @@
         <v>45084</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -36826,7 +36826,7 @@
         <v>45456</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -36904,7 +36904,7 @@
         <v>45174</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -36982,7 +36982,7 @@
         <v>45645</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -37060,7 +37060,7 @@
         <v>44918</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -37138,7 +37138,7 @@
         <v>45705</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -37211,7 +37211,7 @@
         <v>44795</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -37289,7 +37289,7 @@
         <v>45006</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -37362,7 +37362,7 @@
         <v>44614</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -37435,7 +37435,7 @@
         <v>45426</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -37508,7 +37508,7 @@
         <v>44679</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -37586,7 +37586,7 @@
         <v>44725</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -37659,7 +37659,7 @@
         <v>45846</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -37737,7 +37737,7 @@
         <v>45715</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -37810,7 +37810,7 @@
         <v>44634</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -37888,7 +37888,7 @@
         <v>44653</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -37961,7 +37961,7 @@
         <v>45107</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -38034,7 +38034,7 @@
         <v>45415</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -38107,7 +38107,7 @@
         <v>45070</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -38185,7 +38185,7 @@
         <v>45762</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -38258,7 +38258,7 @@
         <v>45944</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -38331,7 +38331,7 @@
         <v>45812</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -38409,7 +38409,7 @@
         <v>45600</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -38482,7 +38482,7 @@
         <v>45812</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -38560,7 +38560,7 @@
         <v>45279</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -38638,7 +38638,7 @@
         <v>45421</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -38716,7 +38716,7 @@
         <v>45344</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -38789,7 +38789,7 @@
         <v>45639</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -38867,7 +38867,7 @@
         <v>45257</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -38945,7 +38945,7 @@
         <v>45819</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -39023,7 +39023,7 @@
         <v>45819</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -39101,7 +39101,7 @@
         <v>45301</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -39179,7 +39179,7 @@
         <v>45147</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -39252,7 +39252,7 @@
         <v>45950</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -39330,7 +39330,7 @@
         <v>45095</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -39403,7 +39403,7 @@
         <v>45824</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -39481,7 +39481,7 @@
         <v>45824</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -39559,7 +39559,7 @@
         <v>45824</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -39637,7 +39637,7 @@
         <v>45824</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -39715,7 +39715,7 @@
         <v>45209</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -39788,7 +39788,7 @@
         <v>45209</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -39861,7 +39861,7 @@
         <v>45086</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -39934,7 +39934,7 @@
         <v>45243</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -40012,7 +40012,7 @@
         <v>45071</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -40090,7 +40090,7 @@
         <v>45660</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -40168,7 +40168,7 @@
         <v>45103</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -40241,7 +40241,7 @@
         <v>44903</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -40319,7 +40319,7 @@
         <v>45166</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -40397,7 +40397,7 @@
         <v>45075</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -40470,7 +40470,7 @@
         <v>45253</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -40548,7 +40548,7 @@
         <v>45955</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -40621,7 +40621,7 @@
         <v>44664</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -40699,7 +40699,7 @@
         <v>45639</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -40777,7 +40777,7 @@
         <v>45274</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -40850,7 +40850,7 @@
         <v>45665</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -40923,7 +40923,7 @@
         <v>44767</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -40996,7 +40996,7 @@
         <v>45835</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -41074,7 +41074,7 @@
         <v>45009</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -41152,7 +41152,7 @@
         <v>45720</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -41230,7 +41230,7 @@
         <v>44735</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -41303,7 +41303,7 @@
         <v>45840</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -41381,7 +41381,7 @@
         <v>45516</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -41459,7 +41459,7 @@
         <v>45142</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -41532,7 +41532,7 @@
         <v>45616</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -41605,7 +41605,7 @@
         <v>45616</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -41678,7 +41678,7 @@
         <v>44729</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -41751,7 +41751,7 @@
         <v>45149</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -41824,7 +41824,7 @@
         <v>45593</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -41902,7 +41902,7 @@
         <v>45646</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -41975,7 +41975,7 @@
         <v>45257</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -42053,7 +42053,7 @@
         <v>45969</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -42126,7 +42126,7 @@
         <v>45971</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -42199,7 +42199,7 @@
         <v>45314</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -42272,7 +42272,7 @@
         <v>44774</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -42350,7 +42350,7 @@
         <v>45845</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -42428,7 +42428,7 @@
         <v>45095</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -42506,7 +42506,7 @@
         <v>45095</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -42579,7 +42579,7 @@
         <v>44672</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -42652,7 +42652,7 @@
         <v>45709</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -42730,7 +42730,7 @@
         <v>45728</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -42808,7 +42808,7 @@
         <v>45308</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -42881,7 +42881,7 @@
         <v>44823</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -42954,7 +42954,7 @@
         <v>45615</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -43032,7 +43032,7 @@
         <v>44973</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -43110,7 +43110,7 @@
         <v>45623</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -43183,7 +43183,7 @@
         <v>45776</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -43256,7 +43256,7 @@
         <v>44813</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -43334,7 +43334,7 @@
         <v>45002</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -43412,7 +43412,7 @@
         <v>44833</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -43490,7 +43490,7 @@
         <v>45468</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -43568,7 +43568,7 @@
         <v>45853</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -43641,7 +43641,7 @@
         <v>45530</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -43714,7 +43714,7 @@
         <v>45713</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -43792,7 +43792,7 @@
         <v>45854</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -43865,7 +43865,7 @@
         <v>45855</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -43938,7 +43938,7 @@
         <v>45854</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -44011,7 +44011,7 @@
         <v>45523</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -44084,7 +44084,7 @@
         <v>45744</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -44162,7 +44162,7 @@
         <v>45379</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -44235,7 +44235,7 @@
         <v>45309</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -44313,7 +44313,7 @@
         <v>45309</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -44386,7 +44386,7 @@
         <v>45309</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -44459,7 +44459,7 @@
         <v>45147</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -44532,7 +44532,7 @@
         <v>45831</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -44605,7 +44605,7 @@
         <v>45257</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -44678,7 +44678,7 @@
         <v>44759</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -44751,7 +44751,7 @@
         <v>45302</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -44829,7 +44829,7 @@
         <v>44840</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -44902,7 +44902,7 @@
         <v>44966</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -44975,7 +44975,7 @@
         <v>45692</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -45053,7 +45053,7 @@
         <v>45688</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -45131,7 +45131,7 @@
         <v>45870</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -45204,7 +45204,7 @@
         <v>45820</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -45282,7 +45282,7 @@
         <v>44767</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -45355,7 +45355,7 @@
         <v>45979</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -45428,7 +45428,7 @@
         <v>44820</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -45501,7 +45501,7 @@
         <v>44817</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -45579,7 +45579,7 @@
         <v>45041</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -45657,7 +45657,7 @@
         <v>45082</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -45735,7 +45735,7 @@
         <v>45688</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -45813,7 +45813,7 @@
         <v>45040</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -45886,7 +45886,7 @@
         <v>45709</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -45964,7 +45964,7 @@
         <v>44834</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -46042,7 +46042,7 @@
         <v>44862</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -46120,7 +46120,7 @@
         <v>44595</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -46193,7 +46193,7 @@
         <v>44973</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -46271,7 +46271,7 @@
         <v>44880</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -46349,7 +46349,7 @@
         <v>45880</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -46427,7 +46427,7 @@
         <v>45710</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -46500,7 +46500,7 @@
         <v>45191</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -46573,7 +46573,7 @@
         <v>45880</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -46651,7 +46651,7 @@
         <v>45009</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -46724,7 +46724,7 @@
         <v>45084</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -46797,7 +46797,7 @@
         <v>45881</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -46875,7 +46875,7 @@
         <v>44782</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -46948,7 +46948,7 @@
         <v>45770</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -47021,7 +47021,7 @@
         <v>46099</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -47094,7 +47094,7 @@
         <v>45236</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -47172,7 +47172,7 @@
         <v>45236</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -47250,7 +47250,7 @@
         <v>46099</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -47323,7 +47323,7 @@
         <v>44714</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -47396,7 +47396,7 @@
         <v>46099</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -47474,7 +47474,7 @@
         <v>44886</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -47547,7 +47547,7 @@
         <v>46099</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -47625,7 +47625,7 @@
         <v>45070</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -47703,7 +47703,7 @@
         <v>45299</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -47776,7 +47776,7 @@
         <v>46099</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -47854,7 +47854,7 @@
         <v>45983</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -47927,7 +47927,7 @@
         <v>45983</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -48000,7 +48000,7 @@
         <v>44749</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -48073,7 +48073,7 @@
         <v>45566</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -48151,7 +48151,7 @@
         <v>45986</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -48224,7 +48224,7 @@
         <v>45042</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -48297,7 +48297,7 @@
         <v>45728</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -48375,7 +48375,7 @@
         <v>44876</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -48448,7 +48448,7 @@
         <v>44861</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -48526,7 +48526,7 @@
         <v>45983</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -48599,7 +48599,7 @@
         <v>45986</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -48672,7 +48672,7 @@
         <v>44987</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -48745,7 +48745,7 @@
         <v>44879</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -48818,7 +48818,7 @@
         <v>45985</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -48891,7 +48891,7 @@
         <v>44871</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -48964,7 +48964,7 @@
         <v>44526</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -49037,7 +49037,7 @@
         <v>44642</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -49110,7 +49110,7 @@
         <v>44536</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -49183,7 +49183,7 @@
         <v>45735</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -49261,7 +49261,7 @@
         <v>46106</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -49339,7 +49339,7 @@
         <v>45237</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -49417,7 +49417,7 @@
         <v>44914</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -49495,7 +49495,7 @@
         <v>45076</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -49573,7 +49573,7 @@
         <v>45548</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -49646,7 +49646,7 @@
         <v>45735</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -49724,7 +49724,7 @@
         <v>46111</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -49802,7 +49802,7 @@
         <v>45763</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -49875,7 +49875,7 @@
         <v>44944</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -49953,7 +49953,7 @@
         <v>44503</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -50026,7 +50026,7 @@
         <v>46113</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -50104,7 +50104,7 @@
         <v>45636</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -50177,7 +50177,7 @@
         <v>44595</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -50255,7 +50255,7 @@
         <v>45233</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -50328,7 +50328,7 @@
         <v>46114</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -50406,7 +50406,7 @@
         <v>46114</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -50484,7 +50484,7 @@
         <v>46114</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -50562,7 +50562,7 @@
         <v>44607</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -50635,7 +50635,7 @@
         <v>46120</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -50713,7 +50713,7 @@
         <v>46121</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -50791,7 +50791,7 @@
         <v>44953</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -50869,7 +50869,7 @@
         <v>46125</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -50942,7 +50942,7 @@
         <v>44817</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -51015,7 +51015,7 @@
         <v>46122</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -51088,7 +51088,7 @@
         <v>45523</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -51166,7 +51166,7 @@
         <v>46000</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -51244,7 +51244,7 @@
         <v>46129</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -51322,7 +51322,7 @@
         <v>44867</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -51395,7 +51395,7 @@
         <v>46002</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -51473,7 +51473,7 @@
         <v>46002</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -51551,7 +51551,7 @@
         <v>44732</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -51629,7 +51629,7 @@
         <v>44949</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -51702,7 +51702,7 @@
         <v>44949</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -51775,7 +51775,7 @@
         <v>44949</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -51848,7 +51848,7 @@
         <v>46128</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -51921,7 +51921,7 @@
         <v>46002</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -51999,7 +51999,7 @@
         <v>46002</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -52077,7 +52077,7 @@
         <v>46006</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -52155,7 +52155,7 @@
         <v>46006</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -52233,7 +52233,7 @@
         <v>44960</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -52311,7 +52311,7 @@
         <v>44966</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -52384,7 +52384,7 @@
         <v>46003</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -52457,7 +52457,7 @@
         <v>46006</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -52530,7 +52530,7 @@
         <v>44662</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -52608,7 +52608,7 @@
         <v>45086</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -52681,7 +52681,7 @@
         <v>45706</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -52754,7 +52754,7 @@
         <v>45692</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -52832,7 +52832,7 @@
         <v>45555</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -52910,7 +52910,7 @@
         <v>44918</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -52988,7 +52988,7 @@
         <v>45740</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -53061,7 +53061,7 @@
         <v>45622</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -53134,7 +53134,7 @@
         <v>44930</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -53212,7 +53212,7 @@
         <v>45915</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -53290,7 +53290,7 @@
         <v>45258</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -53363,7 +53363,7 @@
         <v>45379</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -53436,7 +53436,7 @@
         <v>45706</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -53509,7 +53509,7 @@
         <v>45853</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -53582,7 +53582,7 @@
         <v>45783</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -53660,7 +53660,7 @@
         <v>45260</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -53733,7 +53733,7 @@
         <v>46134</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -53806,7 +53806,7 @@
         <v>45021</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -53879,7 +53879,7 @@
         <v>45167</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -53952,7 +53952,7 @@
         <v>45008</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -54025,7 +54025,7 @@
         <v>44616</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -54103,7 +54103,7 @@
         <v>45700</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -54181,7 +54181,7 @@
         <v>44550</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -54254,7 +54254,7 @@
         <v>45230</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -54327,7 +54327,7 @@
         <v>45013</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -54405,7 +54405,7 @@
         <v>45853</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -54478,7 +54478,7 @@
         <v>45554</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -54551,7 +54551,7 @@
         <v>46030</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -54629,7 +54629,7 @@
         <v>46030</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -54707,7 +54707,7 @@
         <v>45095</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -54785,7 +54785,7 @@
         <v>46029</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -54858,7 +54858,7 @@
         <v>46031</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -54936,7 +54936,7 @@
         <v>45516</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -55009,7 +55009,7 @@
         <v>46034</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -55087,7 +55087,7 @@
         <v>46034</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -55165,7 +55165,7 @@
         <v>45055</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -55238,7 +55238,7 @@
         <v>46034</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -55316,7 +55316,7 @@
         <v>44995</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -55394,7 +55394,7 @@
         <v>46036</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -55472,7 +55472,7 @@
         <v>46036</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -55550,7 +55550,7 @@
         <v>45095</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -55623,7 +55623,7 @@
         <v>45425</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -55696,7 +55696,7 @@
         <v>44898</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -55769,7 +55769,7 @@
         <v>45177</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -55842,7 +55842,7 @@
         <v>45560</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -55920,7 +55920,7 @@
         <v>45719</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -55998,7 +55998,7 @@
         <v>46040</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -56071,7 +56071,7 @@
         <v>46040</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -56144,7 +56144,7 @@
         <v>45456</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -56222,7 +56222,7 @@
         <v>44865</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -56300,7 +56300,7 @@
         <v>45832</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -56373,7 +56373,7 @@
         <v>44980</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -56446,7 +56446,7 @@
         <v>44966</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -56524,7 +56524,7 @@
         <v>46048</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -56602,7 +56602,7 @@
         <v>46048</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -56680,7 +56680,7 @@
         <v>44914</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -56753,7 +56753,7 @@
         <v>46048</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -56831,7 +56831,7 @@
         <v>46050</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -56909,7 +56909,7 @@
         <v>44974</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -56982,7 +56982,7 @@
         <v>44950</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -57060,7 +57060,7 @@
         <v>46050</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -57138,7 +57138,7 @@
         <v>45601</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -57211,7 +57211,7 @@
         <v>45323</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -57289,7 +57289,7 @@
         <v>46049</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -57362,7 +57362,7 @@
         <v>46064</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -57440,7 +57440,7 @@
         <v>46052</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -57513,7 +57513,7 @@
         <v>46055</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -57591,7 +57591,7 @@
         <v>46058</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -57669,7 +57669,7 @@
         <v>46058</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -57747,7 +57747,7 @@
         <v>46058</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -57825,7 +57825,7 @@
         <v>46060</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -57898,7 +57898,7 @@
         <v>46141</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -57971,7 +57971,7 @@
         <v>46058</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -58049,7 +58049,7 @@
         <v>46064</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -58127,7 +58127,7 @@
         <v>46064</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -58205,7 +58205,7 @@
         <v>46064</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -58283,7 +58283,7 @@
         <v>46063</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -58361,7 +58361,7 @@
         <v>46064</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -58439,7 +58439,7 @@
         <v>46063</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -58517,7 +58517,7 @@
         <v>46064</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -58595,7 +58595,7 @@
         <v>46064</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -58673,7 +58673,7 @@
         <v>46065</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -58751,7 +58751,7 @@
         <v>46065</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -58829,7 +58829,7 @@
         <v>46069</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -58907,7 +58907,7 @@
         <v>46070</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -58985,7 +58985,7 @@
         <v>46070</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -59063,7 +59063,7 @@
         <v>46073</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -59141,7 +59141,7 @@
         <v>46076</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -59219,7 +59219,7 @@
         <v>46076</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -59297,7 +59297,7 @@
         <v>46078</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -59375,7 +59375,7 @@
         <v>46079</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -59453,7 +59453,7 @@
         <v>45980</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -59526,7 +59526,7 @@
         <v>45184</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -59599,7 +59599,7 @@
         <v>46080</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -59677,7 +59677,7 @@
         <v>46080</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -59755,7 +59755,7 @@
         <v>46080</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -59833,7 +59833,7 @@
         <v>46080</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -59911,7 +59911,7 @@
         <v>46085</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -59989,7 +59989,7 @@
         <v>45845</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -60067,7 +60067,7 @@
         <v>46085</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -60145,7 +60145,7 @@
         <v>46085</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -60223,7 +60223,7 @@
         <v>46085</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -60301,7 +60301,7 @@
         <v>46077</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -60379,7 +60379,7 @@
         <v>46094</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -60457,7 +60457,7 @@
         <v>46097</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -60530,7 +60530,7 @@
         <v>46176</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -60603,7 +60603,7 @@
         <v>46176</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -60676,7 +60676,7 @@
         <v>46176</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -60749,7 +60749,7 @@
         <v>46174</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -60827,7 +60827,7 @@
         <v>46174</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -60905,7 +60905,7 @@
         <v>46177</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -60978,7 +60978,7 @@
         <v>46181</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -61056,7 +61056,7 @@
         <v>46178</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -61129,7 +61129,7 @@
         <v>46178</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -61202,7 +61202,7 @@
         <v>46178</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -61275,7 +61275,7 @@
         <v>46185</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -61348,7 +61348,7 @@
         <v>46185</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -61421,7 +61421,7 @@
         <v>46188</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -61494,7 +61494,7 @@
         <v>46196</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -61572,7 +61572,7 @@
         <v>45846</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -61650,7 +61650,7 @@
         <v>46199</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -61723,7 +61723,7 @@
         <v>46203</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -61796,7 +61796,7 @@
         <v>46204</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -61869,7 +61869,7 @@
         <v>46209</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -61942,7 +61942,7 @@
         <v>46211</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -62015,7 +62015,7 @@
         <v>46212</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -62088,7 +62088,7 @@
         <v>46218</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -62166,7 +62166,7 @@
         <v>46218</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -62244,7 +62244,7 @@
         <v>46219</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -62317,7 +62317,7 @@
         <v>46226</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -62390,7 +62390,7 @@
         <v>46269</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -62463,7 +62463,7 @@
         <v>46269</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -62536,7 +62536,7 @@
         <v>46226</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -62609,7 +62609,7 @@
         <v>46225</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -62682,7 +62682,7 @@
         <v>46225</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -62755,7 +62755,7 @@
         <v>46269</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -62828,7 +62828,7 @@
         <v>46269</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -62901,7 +62901,7 @@
         <v>46269</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -62974,7 +62974,7 @@
         <v>46232</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -63047,7 +63047,7 @@
         <v>46233</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -63120,7 +63120,7 @@
         <v>46279</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -63193,7 +63193,7 @@
         <v>46279</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -63266,7 +63266,7 @@
         <v>46279</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -63339,7 +63339,7 @@
         <v>46282</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -63417,7 +63417,7 @@
         <v>46282</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -63495,7 +63495,7 @@
         <v>46282</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -63573,7 +63573,7 @@
         <v>46282</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -63651,7 +63651,7 @@
         <v>46282</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -63729,7 +63729,7 @@
         <v>46282</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -63807,7 +63807,7 @@
         <v>46282</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -63885,7 +63885,7 @@
         <v>46282</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -63963,7 +63963,7 @@
         <v>46282</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -64041,7 +64041,7 @@
         <v>46281</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -64114,7 +64114,7 @@
         <v>46286</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -64192,7 +64192,7 @@
         <v>45863</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
@@ -64265,7 +64265,7 @@
         <v>45870</v>
       </c>
       <c r="E802" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -64338,7 +64338,7 @@
         <v>46295</v>
       </c>
       <c r="E803" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
@@ -64416,7 +64416,7 @@
         <v>46295</v>
       </c>
       <c r="E804" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
@@ -64494,7 +64494,7 @@
         <v>46255</v>
       </c>
       <c r="E805" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>
@@ -64572,7 +64572,7 @@
         <v>46302</v>
       </c>
       <c r="E806" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F806" t="inlineStr">
         <is>
@@ -64645,7 +64645,7 @@
         <v>46258</v>
       </c>
       <c r="E807" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F807" t="inlineStr">
         <is>
@@ -64723,7 +64723,7 @@
         <v>46258</v>
       </c>
       <c r="E808" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F808" t="inlineStr">
         <is>
@@ -64801,7 +64801,7 @@
         <v>46300</v>
       </c>
       <c r="E809" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F809" t="inlineStr">
         <is>
@@ -64874,7 +64874,7 @@
         <v>46304</v>
       </c>
       <c r="E810" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F810" t="inlineStr">
         <is>
@@ -64947,7 +64947,7 @@
         <v>46304</v>
       </c>
       <c r="E811" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F811" t="inlineStr">
         <is>
@@ -65020,7 +65020,7 @@
         <v>46304</v>
       </c>
       <c r="E812" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F812" t="inlineStr">
         <is>
@@ -65093,7 +65093,7 @@
         <v>46209</v>
       </c>
       <c r="E813" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F813" t="inlineStr">
         <is>
@@ -65166,7 +65166,7 @@
         <v>46304</v>
       </c>
       <c r="E814" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F814" t="inlineStr">
         <is>
@@ -65239,7 +65239,7 @@
         <v>46160</v>
       </c>
       <c r="E815" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F815" t="inlineStr">
         <is>
@@ -65312,7 +65312,7 @@
         <v>45644</v>
       </c>
       <c r="E816" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F816" t="inlineStr">
         <is>
@@ -65385,7 +65385,7 @@
         <v>45428</v>
       </c>
       <c r="E817" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F817" t="inlineStr">
         <is>
@@ -65458,7 +65458,7 @@
         <v>45429</v>
       </c>
       <c r="E818" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F818" t="inlineStr">
         <is>
@@ -65531,7 +65531,7 @@
         <v>45250</v>
       </c>
       <c r="E819" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F819" t="inlineStr">
         <is>
@@ -65609,7 +65609,7 @@
         <v>46188</v>
       </c>
       <c r="E820" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F820" t="inlineStr">
         <is>
@@ -65687,7 +65687,7 @@
         <v>46258</v>
       </c>
       <c r="E821" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F821" t="inlineStr">
         <is>

--- a/Översikt FINSPÅNG.xlsx
+++ b/Översikt FINSPÅNG.xlsx
@@ -601,7 +601,7 @@
         <v>46244</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -727,7 +727,7 @@
         <v>45945</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -858,7 +858,7 @@
         <v>45134</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
         <v>44896</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1121,7 +1121,7 @@
         <v>44888</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>45210</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1369,7 +1369,7 @@
         <v>44777</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1488,7 +1488,7 @@
         <v>44897</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1607,7 +1607,7 @@
         <v>44910</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1734,7 +1734,7 @@
         <v>45322</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1855,7 +1855,7 @@
         <v>44624</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1971,7 +1971,7 @@
         <v>44599</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2082,7 +2082,7 @@
         <v>45238</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2197,7 +2197,7 @@
         <v>45421</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2317,7 +2317,7 @@
         <v>45891</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2433,7 +2433,7 @@
         <v>45898</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2548,7 +2548,7 @@
         <v>45267</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2663,7 +2663,7 @@
         <v>45679</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2782,7 +2782,7 @@
         <v>44791</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2896,7 +2896,7 @@
         <v>45812</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3010,7 +3010,7 @@
         <v>44665</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3123,7 +3123,7 @@
         <v>45681</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3240,7 +3240,7 @@
         <v>46307</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3352,7 +3352,7 @@
         <v>45082</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3464,7 +3464,7 @@
         <v>45819</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3580,7 +3580,7 @@
         <v>44774</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3692,7 +3692,7 @@
         <v>45602</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3804,7 +3804,7 @@
         <v>46196</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3916,7 +3916,7 @@
         <v>45800</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4028,7 +4028,7 @@
         <v>44690</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4139,7 +4139,7 @@
         <v>45441</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4250,7 +4250,7 @@
         <v>44816</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4356,7 +4356,7 @@
         <v>45477</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4471,7 +4471,7 @@
         <v>45894</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4586,7 +4586,7 @@
         <v>45905</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4697,7 +4697,7 @@
         <v>45950</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4808,7 +4808,7 @@
         <v>45644</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4914,7 +4914,7 @@
         <v>44981</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5025,7 +5025,7 @@
         <v>46174</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5136,7 +5136,7 @@
         <v>46181</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5247,7 +5247,7 @@
         <v>46181</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5358,7 +5358,7 @@
         <v>45425</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5464,7 +5464,7 @@
         <v>45235</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5575,7 +5575,7 @@
         <v>45121</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5690,7 +5690,7 @@
         <v>44903</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5800,7 +5800,7 @@
         <v>44683</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5910,7 +5910,7 @@
         <v>44776</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6015,7 +6015,7 @@
         <v>44504</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6125,7 +6125,7 @@
         <v>44529</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6230,7 +6230,7 @@
         <v>45567</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6344,7 +6344,7 @@
         <v>45082</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6454,7 +6454,7 @@
         <v>45149</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6563,7 +6563,7 @@
         <v>44501</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6673,7 +6673,7 @@
         <v>44897</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6787,7 +6787,7 @@
         <v>45744</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6901,7 +6901,7 @@
         <v>45636</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7006,7 +7006,7 @@
         <v>45328</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7115,7 +7115,7 @@
         <v>45229</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7225,7 +7225,7 @@
         <v>44599</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7335,7 +7335,7 @@
         <v>45447</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7445,7 +7445,7 @@
         <v>45555</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7559,7 +7559,7 @@
         <v>46043</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7673,7 +7673,7 @@
         <v>45905</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7783,7 +7783,7 @@
         <v>45883</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7893,7 +7893,7 @@
         <v>45446</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7998,7 +7998,7 @@
         <v>44965</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8112,7 +8112,7 @@
         <v>46155</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8226,7 +8226,7 @@
         <v>45566</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8340,7 +8340,7 @@
         <v>44930</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8450,7 +8450,7 @@
         <v>44915</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8560,7 +8560,7 @@
         <v>45302</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8669,7 +8669,7 @@
         <v>45232</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8779,7 +8779,7 @@
         <v>44622</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8884,7 +8884,7 @@
         <v>46058</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8998,7 +8998,7 @@
         <v>46189</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9103,7 +9103,7 @@
         <v>44817</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9213,7 +9213,7 @@
         <v>46129</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9327,7 +9327,7 @@
         <v>44915</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9437,7 +9437,7 @@
         <v>46181</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9547,7 +9547,7 @@
         <v>45070</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9657,7 +9657,7 @@
         <v>44992</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9767,7 +9767,7 @@
         <v>45615</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9881,7 +9881,7 @@
         <v>46258</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9991,7 +9991,7 @@
         <v>46258</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10105,7 +10105,7 @@
         <v>45845</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10215,7 +10215,7 @@
         <v>45846</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10325,7 +10325,7 @@
         <v>45880</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10435,7 +10435,7 @@
         <v>44711</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10545,7 +10545,7 @@
         <v>45428</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10650,7 +10650,7 @@
         <v>46107</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10760,7 +10760,7 @@
         <v>46188</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10874,7 +10874,7 @@
         <v>44755</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10952,7 +10952,7 @@
         <v>44675</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11025,7 +11025,7 @@
         <v>44676</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11103,7 +11103,7 @@
         <v>44864</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11176,7 +11176,7 @@
         <v>44600</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11249,7 +11249,7 @@
         <v>44824</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11322,7 +11322,7 @@
         <v>44536</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11400,7 +11400,7 @@
         <v>44799</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11473,7 +11473,7 @@
         <v>44795</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11546,7 +11546,7 @@
         <v>44856</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11619,7 +11619,7 @@
         <v>44578</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11697,7 +11697,7 @@
         <v>44675</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11770,7 +11770,7 @@
         <v>44852</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -11848,7 +11848,7 @@
         <v>44601</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -11926,7 +11926,7 @@
         <v>44601</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -11999,7 +11999,7 @@
         <v>44551</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12072,7 +12072,7 @@
         <v>44525</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12145,7 +12145,7 @@
         <v>44574</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12223,7 +12223,7 @@
         <v>44574</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12296,7 +12296,7 @@
         <v>44588</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12374,7 +12374,7 @@
         <v>44889</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12447,7 +12447,7 @@
         <v>44627</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12520,7 +12520,7 @@
         <v>44503</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -12598,7 +12598,7 @@
         <v>44525</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -12676,7 +12676,7 @@
         <v>44503</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -12749,7 +12749,7 @@
         <v>44874</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -12822,7 +12822,7 @@
         <v>44502</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -12900,7 +12900,7 @@
         <v>44551</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -12973,7 +12973,7 @@
         <v>44712</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -13051,7 +13051,7 @@
         <v>44581</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -13124,7 +13124,7 @@
         <v>44833</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -13197,7 +13197,7 @@
         <v>44601</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -13270,7 +13270,7 @@
         <v>44672</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -13343,7 +13343,7 @@
         <v>44859</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -13416,7 +13416,7 @@
         <v>44735</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -13489,7 +13489,7 @@
         <v>44796</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -13562,7 +13562,7 @@
         <v>44782</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -13635,7 +13635,7 @@
         <v>44741</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -13708,7 +13708,7 @@
         <v>44613</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -13786,7 +13786,7 @@
         <v>44859</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -13859,7 +13859,7 @@
         <v>44678</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -13932,7 +13932,7 @@
         <v>44855</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -14010,7 +14010,7 @@
         <v>44887</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -14083,7 +14083,7 @@
         <v>44860</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -14156,7 +14156,7 @@
         <v>44753</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -14229,7 +14229,7 @@
         <v>44802</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -14302,7 +14302,7 @@
         <v>44844</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -14380,7 +14380,7 @@
         <v>44781</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -14453,7 +14453,7 @@
         <v>44541</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -14526,7 +14526,7 @@
         <v>44564</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -14599,7 +14599,7 @@
         <v>44859</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -14672,7 +14672,7 @@
         <v>44595</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -14745,7 +14745,7 @@
         <v>44582</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -14818,7 +14818,7 @@
         <v>44816</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -14891,7 +14891,7 @@
         <v>44508</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -14964,7 +14964,7 @@
         <v>44656</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -15037,7 +15037,7 @@
         <v>44587</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -15110,7 +15110,7 @@
         <v>44627</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -15183,7 +15183,7 @@
         <v>44820</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -15256,7 +15256,7 @@
         <v>44532</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -15329,7 +15329,7 @@
         <v>44552</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -15402,7 +15402,7 @@
         <v>44879</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -15475,7 +15475,7 @@
         <v>44588</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -15553,7 +15553,7 @@
         <v>44581</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -15626,7 +15626,7 @@
         <v>44875</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -15699,7 +15699,7 @@
         <v>44743</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -15772,7 +15772,7 @@
         <v>44831</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -15850,7 +15850,7 @@
         <v>44819</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -15923,7 +15923,7 @@
         <v>44581</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -16001,7 +16001,7 @@
         <v>44630</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -16074,7 +16074,7 @@
         <v>44804</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -16152,7 +16152,7 @@
         <v>44601</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -16225,7 +16225,7 @@
         <v>44742</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -16303,7 +16303,7 @@
         <v>44859</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -16376,7 +16376,7 @@
         <v>44600</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -16449,7 +16449,7 @@
         <v>44635</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -16522,7 +16522,7 @@
         <v>44776</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -16595,7 +16595,7 @@
         <v>44713</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -16673,7 +16673,7 @@
         <v>44697</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -16751,7 +16751,7 @@
         <v>44533</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -16824,7 +16824,7 @@
         <v>44601</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -16897,7 +16897,7 @@
         <v>44678</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -16970,7 +16970,7 @@
         <v>44564</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -17043,7 +17043,7 @@
         <v>44704</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -17116,7 +17116,7 @@
         <v>44642</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -17189,7 +17189,7 @@
         <v>44659</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -17267,7 +17267,7 @@
         <v>44656</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -17345,7 +17345,7 @@
         <v>45447</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -17423,7 +17423,7 @@
         <v>44966</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -17496,7 +17496,7 @@
         <v>45103</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -17569,7 +17569,7 @@
         <v>44866</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -17642,7 +17642,7 @@
         <v>45293</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -17715,7 +17715,7 @@
         <v>45033</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -17793,7 +17793,7 @@
         <v>45258</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -17866,7 +17866,7 @@
         <v>45009</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -17939,7 +17939,7 @@
         <v>44677</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -18012,7 +18012,7 @@
         <v>44802</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -18085,7 +18085,7 @@
         <v>44898</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -18158,7 +18158,7 @@
         <v>44897</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -18236,7 +18236,7 @@
         <v>44918</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -18314,7 +18314,7 @@
         <v>44595</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -18392,7 +18392,7 @@
         <v>45097</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -18465,7 +18465,7 @@
         <v>45086</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -18538,7 +18538,7 @@
         <v>45063</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -18611,7 +18611,7 @@
         <v>44672</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -18684,7 +18684,7 @@
         <v>45260</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -18757,7 +18757,7 @@
         <v>45021</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -18830,7 +18830,7 @@
         <v>45330</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -18903,7 +18903,7 @@
         <v>44973</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -18981,7 +18981,7 @@
         <v>45107</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -19054,7 +19054,7 @@
         <v>44767</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -19127,7 +19127,7 @@
         <v>45293</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -19205,7 +19205,7 @@
         <v>45428</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -19283,7 +19283,7 @@
         <v>45206</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -19356,7 +19356,7 @@
         <v>45705</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -19429,7 +19429,7 @@
         <v>45555</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -19507,7 +19507,7 @@
         <v>45623</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -19580,7 +19580,7 @@
         <v>45642</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -19658,7 +19658,7 @@
         <v>45095</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -19736,7 +19736,7 @@
         <v>44993</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -19809,7 +19809,7 @@
         <v>45749</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -19887,7 +19887,7 @@
         <v>44844</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -19960,7 +19960,7 @@
         <v>44844</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -20033,7 +20033,7 @@
         <v>45554</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -20106,7 +20106,7 @@
         <v>44960</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -20184,7 +20184,7 @@
         <v>44914</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -20257,7 +20257,7 @@
         <v>45728</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -20335,7 +20335,7 @@
         <v>45357</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -20408,7 +20408,7 @@
         <v>45740</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -20486,7 +20486,7 @@
         <v>45688</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -20564,7 +20564,7 @@
         <v>44778</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -20637,7 +20637,7 @@
         <v>45253</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -20715,7 +20715,7 @@
         <v>45149</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -20788,7 +20788,7 @@
         <v>45084</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -20861,7 +20861,7 @@
         <v>45441</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -20934,7 +20934,7 @@
         <v>45233</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -21007,7 +21007,7 @@
         <v>44861</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -21085,7 +21085,7 @@
         <v>45677</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -21163,7 +21163,7 @@
         <v>44942</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -21236,7 +21236,7 @@
         <v>44900</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -21309,7 +21309,7 @@
         <v>45095</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -21387,7 +21387,7 @@
         <v>45095</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -21460,7 +21460,7 @@
         <v>44817</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -21538,7 +21538,7 @@
         <v>45259</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -21611,7 +21611,7 @@
         <v>45103</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -21684,7 +21684,7 @@
         <v>45623</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -21762,7 +21762,7 @@
         <v>44880</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -21840,7 +21840,7 @@
         <v>45264</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -21918,7 +21918,7 @@
         <v>44974</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -21991,7 +21991,7 @@
         <v>45008</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -22064,7 +22064,7 @@
         <v>45720</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -22142,7 +22142,7 @@
         <v>44918</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -22220,7 +22220,7 @@
         <v>45040</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -22298,7 +22298,7 @@
         <v>45710</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -22371,7 +22371,7 @@
         <v>45554</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -22444,7 +22444,7 @@
         <v>45337</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -22517,7 +22517,7 @@
         <v>45593</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -22595,7 +22595,7 @@
         <v>44958</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -22668,7 +22668,7 @@
         <v>44490</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -22741,7 +22741,7 @@
         <v>45274</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -22814,7 +22814,7 @@
         <v>45415</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -22887,7 +22887,7 @@
         <v>45328</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -22960,7 +22960,7 @@
         <v>45095</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -23033,7 +23033,7 @@
         <v>44950</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -23111,7 +23111,7 @@
         <v>44860</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -23184,7 +23184,7 @@
         <v>45456</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -23262,7 +23262,7 @@
         <v>45744</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -23340,7 +23340,7 @@
         <v>45257</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -23418,7 +23418,7 @@
         <v>45257</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -23496,7 +23496,7 @@
         <v>44949</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -23569,7 +23569,7 @@
         <v>45740</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -23647,7 +23647,7 @@
         <v>45103</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -23720,7 +23720,7 @@
         <v>45178</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -23793,7 +23793,7 @@
         <v>45002</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -23871,7 +23871,7 @@
         <v>45421</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -23949,7 +23949,7 @@
         <v>44503</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -24022,7 +24022,7 @@
         <v>44840</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -24095,7 +24095,7 @@
         <v>45541</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -24173,7 +24173,7 @@
         <v>45041</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -24246,7 +24246,7 @@
         <v>45125</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -24324,7 +24324,7 @@
         <v>45257</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -24402,7 +24402,7 @@
         <v>45206</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -24475,7 +24475,7 @@
         <v>45463</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -24548,7 +24548,7 @@
         <v>44516</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -24621,7 +24621,7 @@
         <v>44964</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -24699,7 +24699,7 @@
         <v>44993</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -24772,7 +24772,7 @@
         <v>45020</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -24845,7 +24845,7 @@
         <v>44607</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -24918,7 +24918,7 @@
         <v>45167</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -24996,7 +24996,7 @@
         <v>44767</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -25069,7 +25069,7 @@
         <v>44930</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -25142,7 +25142,7 @@
         <v>44957</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -25215,7 +25215,7 @@
         <v>44662</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -25293,7 +25293,7 @@
         <v>45084</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -25366,7 +25366,7 @@
         <v>44732</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -25444,7 +25444,7 @@
         <v>45601</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -25517,7 +25517,7 @@
         <v>44914</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -25595,7 +25595,7 @@
         <v>44734</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -25668,7 +25668,7 @@
         <v>45463</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -25741,7 +25741,7 @@
         <v>45147</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -25814,7 +25814,7 @@
         <v>45442</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -25887,7 +25887,7 @@
         <v>44536</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -25960,7 +25960,7 @@
         <v>45883</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -26038,7 +26038,7 @@
         <v>45883</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -26116,7 +26116,7 @@
         <v>44887</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -26189,7 +26189,7 @@
         <v>45832</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -26262,7 +26262,7 @@
         <v>45615</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -26340,7 +26340,7 @@
         <v>44614</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -26413,7 +26413,7 @@
         <v>45468</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -26491,7 +26491,7 @@
         <v>45516</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -26564,7 +26564,7 @@
         <v>45915</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -26642,7 +26642,7 @@
         <v>44833</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -26720,7 +26720,7 @@
         <v>45700</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -26798,7 +26798,7 @@
         <v>44508</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -26871,7 +26871,7 @@
         <v>44817</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -26944,7 +26944,7 @@
         <v>44550</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -27017,7 +27017,7 @@
         <v>45621</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -27095,7 +27095,7 @@
         <v>45560</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -27173,7 +27173,7 @@
         <v>45888</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -27251,7 +27251,7 @@
         <v>45891</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -27329,7 +27329,7 @@
         <v>45707</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -27407,7 +27407,7 @@
         <v>44865</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -27485,7 +27485,7 @@
         <v>44980</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -27558,7 +27558,7 @@
         <v>45118</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -27631,7 +27631,7 @@
         <v>45894</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -27709,7 +27709,7 @@
         <v>45895</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -27782,7 +27782,7 @@
         <v>45692</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -27860,7 +27860,7 @@
         <v>45166</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -27938,7 +27938,7 @@
         <v>45467</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -28011,7 +28011,7 @@
         <v>45896</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -28089,7 +28089,7 @@
         <v>44735</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -28162,7 +28162,7 @@
         <v>45898</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -28235,7 +28235,7 @@
         <v>45853</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -28308,7 +28308,7 @@
         <v>45600</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -28381,7 +28381,7 @@
         <v>46064</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -28459,7 +28459,7 @@
         <v>45229</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -28537,7 +28537,7 @@
         <v>44900</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -28610,7 +28610,7 @@
         <v>45903</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -28688,7 +28688,7 @@
         <v>45903</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -28766,7 +28766,7 @@
         <v>45103</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -28839,7 +28839,7 @@
         <v>45903</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -28917,7 +28917,7 @@
         <v>45903</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -28995,7 +28995,7 @@
         <v>45903</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -29073,7 +29073,7 @@
         <v>45343</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -29151,7 +29151,7 @@
         <v>45905</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -29229,7 +29229,7 @@
         <v>45904</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -29307,7 +29307,7 @@
         <v>45082</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -29385,7 +29385,7 @@
         <v>45905</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -29463,7 +29463,7 @@
         <v>45299</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -29536,7 +29536,7 @@
         <v>45006</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -29609,7 +29609,7 @@
         <v>45904</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -29687,7 +29687,7 @@
         <v>45908</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -29760,7 +29760,7 @@
         <v>45379</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -29833,7 +29833,7 @@
         <v>44840</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -29911,7 +29911,7 @@
         <v>45040</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -29984,7 +29984,7 @@
         <v>46141</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -30057,7 +30057,7 @@
         <v>45075</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -30130,7 +30130,7 @@
         <v>45617</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -30208,7 +30208,7 @@
         <v>44725</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -30281,7 +30281,7 @@
         <v>45082</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -30359,7 +30359,7 @@
         <v>45055</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -30432,7 +30432,7 @@
         <v>45688</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -30510,7 +30510,7 @@
         <v>45250</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -30588,7 +30588,7 @@
         <v>45250</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -30661,7 +30661,7 @@
         <v>45133</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -30734,7 +30734,7 @@
         <v>44903</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -30812,7 +30812,7 @@
         <v>45548</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -30885,7 +30885,7 @@
         <v>45267</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -30963,7 +30963,7 @@
         <v>45924</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -31036,7 +31036,7 @@
         <v>45008</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -31114,7 +31114,7 @@
         <v>45344</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -31187,7 +31187,7 @@
         <v>45362</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -31260,7 +31260,7 @@
         <v>44634</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -31338,7 +31338,7 @@
         <v>45252</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -31411,7 +31411,7 @@
         <v>45209</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -31484,7 +31484,7 @@
         <v>45209</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -31557,7 +31557,7 @@
         <v>45931</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -31630,7 +31630,7 @@
         <v>45184</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -31703,7 +31703,7 @@
         <v>45980</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -31776,7 +31776,7 @@
         <v>45846</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -31854,7 +31854,7 @@
         <v>45935</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -31932,7 +31932,7 @@
         <v>45566</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -32010,7 +32010,7 @@
         <v>44664</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -32088,7 +32088,7 @@
         <v>44946</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -32166,7 +32166,7 @@
         <v>44946</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -32244,7 +32244,7 @@
         <v>44944</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -32322,7 +32322,7 @@
         <v>45944</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -32395,7 +32395,7 @@
         <v>45009</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -32473,7 +32473,7 @@
         <v>45247</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -32546,7 +32546,7 @@
         <v>45095</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -32619,7 +32619,7 @@
         <v>45845</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -32697,7 +32697,7 @@
         <v>45523</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -32775,7 +32775,7 @@
         <v>45950</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -32853,7 +32853,7 @@
         <v>44767</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -32926,7 +32926,7 @@
         <v>44964</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -33004,7 +33004,7 @@
         <v>44759</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -33077,7 +33077,7 @@
         <v>45258</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -33150,7 +33150,7 @@
         <v>44617</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -33223,7 +33223,7 @@
         <v>45955</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -33296,7 +33296,7 @@
         <v>45042</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -33374,7 +33374,7 @@
         <v>44937</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -33447,7 +33447,7 @@
         <v>45709</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -33525,7 +33525,7 @@
         <v>44993</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -33598,7 +33598,7 @@
         <v>45095</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -33671,7 +33671,7 @@
         <v>46077</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -33749,7 +33749,7 @@
         <v>44564</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -33822,7 +33822,7 @@
         <v>45607</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -33895,7 +33895,7 @@
         <v>45607</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -33968,7 +33968,7 @@
         <v>45609</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -34046,7 +34046,7 @@
         <v>45665</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -34119,7 +34119,7 @@
         <v>45551</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -34192,7 +34192,7 @@
         <v>44774</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -34270,7 +34270,7 @@
         <v>45969</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -34343,7 +34343,7 @@
         <v>45744</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -34421,7 +34421,7 @@
         <v>45971</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -34494,7 +34494,7 @@
         <v>45013</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -34572,7 +34572,7 @@
         <v>45688</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -34650,7 +34650,7 @@
         <v>45428</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -34723,7 +34723,7 @@
         <v>45744</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -34801,7 +34801,7 @@
         <v>45979</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -34874,7 +34874,7 @@
         <v>45077</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -34952,7 +34952,7 @@
         <v>45002</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -35030,7 +35030,7 @@
         <v>45068</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -35108,7 +35108,7 @@
         <v>44867</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -35181,7 +35181,7 @@
         <v>45983</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -35254,7 +35254,7 @@
         <v>45983</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -35327,7 +35327,7 @@
         <v>45983</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -35400,7 +35400,7 @@
         <v>45985</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -35473,7 +35473,7 @@
         <v>44886</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -35546,7 +35546,7 @@
         <v>45636</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -35619,7 +35619,7 @@
         <v>45986</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -35692,7 +35692,7 @@
         <v>45728</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -35770,7 +35770,7 @@
         <v>45280</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -35848,7 +35848,7 @@
         <v>45986</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -35921,7 +35921,7 @@
         <v>45225</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -35994,7 +35994,7 @@
         <v>44987</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -36067,7 +36067,7 @@
         <v>45082</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -36145,7 +36145,7 @@
         <v>45566</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -36223,7 +36223,7 @@
         <v>45177</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -36296,7 +36296,7 @@
         <v>44995</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -36374,7 +36374,7 @@
         <v>45147</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -36447,7 +36447,7 @@
         <v>44966</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -36520,7 +36520,7 @@
         <v>46000</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -36598,7 +36598,7 @@
         <v>45230</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -36671,7 +36671,7 @@
         <v>45040</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -36744,7 +36744,7 @@
         <v>46002</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -36822,7 +36822,7 @@
         <v>46003</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -36895,7 +36895,7 @@
         <v>46002</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -36973,7 +36973,7 @@
         <v>46174</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -37051,7 +37051,7 @@
         <v>46174</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -37129,7 +37129,7 @@
         <v>46002</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -37207,7 +37207,7 @@
         <v>44876</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -37280,7 +37280,7 @@
         <v>46002</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -37358,7 +37358,7 @@
         <v>45179</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -37431,7 +37431,7 @@
         <v>45179</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -37504,7 +37504,7 @@
         <v>45709</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -37582,7 +37582,7 @@
         <v>46006</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -37655,7 +37655,7 @@
         <v>46006</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -37733,7 +37733,7 @@
         <v>45309</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -37811,7 +37811,7 @@
         <v>45309</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -37884,7 +37884,7 @@
         <v>45309</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -37957,7 +37957,7 @@
         <v>46006</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -38035,7 +38035,7 @@
         <v>44949</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -38108,7 +38108,7 @@
         <v>45323</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -38186,7 +38186,7 @@
         <v>45013</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -38264,7 +38264,7 @@
         <v>44981</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -38342,7 +38342,7 @@
         <v>44930</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -38420,7 +38420,7 @@
         <v>45086</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -38493,7 +38493,7 @@
         <v>45042</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -38566,7 +38566,7 @@
         <v>45042</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -38639,7 +38639,7 @@
         <v>44939</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -38712,7 +38712,7 @@
         <v>45607</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -38785,7 +38785,7 @@
         <v>44732</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -38863,7 +38863,7 @@
         <v>45425</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -38936,7 +38936,7 @@
         <v>45177</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -39009,7 +39009,7 @@
         <v>45302</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -39087,7 +39087,7 @@
         <v>45678</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -39165,7 +39165,7 @@
         <v>45622</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -39238,7 +39238,7 @@
         <v>45853</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -39311,7 +39311,7 @@
         <v>46029</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -39384,7 +39384,7 @@
         <v>46030</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -39462,7 +39462,7 @@
         <v>45237</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -39540,7 +39540,7 @@
         <v>46030</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -39618,7 +39618,7 @@
         <v>46031</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -39696,7 +39696,7 @@
         <v>44642</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -39769,7 +39769,7 @@
         <v>46034</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -39847,7 +39847,7 @@
         <v>46176</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -39920,7 +39920,7 @@
         <v>45770</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -39993,7 +39993,7 @@
         <v>46176</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -40066,7 +40066,7 @@
         <v>46176</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -40139,7 +40139,7 @@
         <v>46034</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -40217,7 +40217,7 @@
         <v>46034</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -40295,7 +40295,7 @@
         <v>46036</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -40373,7 +40373,7 @@
         <v>46036</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -40451,7 +40451,7 @@
         <v>46040</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -40524,7 +40524,7 @@
         <v>46040</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -40597,7 +40597,7 @@
         <v>45456</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -40675,7 +40675,7 @@
         <v>44749</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -40748,7 +40748,7 @@
         <v>45082</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -40826,7 +40826,7 @@
         <v>45082</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -40904,7 +40904,7 @@
         <v>46178</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -40977,7 +40977,7 @@
         <v>46178</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -41050,7 +41050,7 @@
         <v>45167</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -41123,7 +41123,7 @@
         <v>46177</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -41196,7 +41196,7 @@
         <v>44930</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -41269,7 +41269,7 @@
         <v>46178</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -41342,7 +41342,7 @@
         <v>44782</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -41415,7 +41415,7 @@
         <v>46048</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -41493,7 +41493,7 @@
         <v>45646</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -41566,7 +41566,7 @@
         <v>46049</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -41639,7 +41639,7 @@
         <v>46048</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -41717,7 +41717,7 @@
         <v>46048</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -41795,7 +41795,7 @@
         <v>45181</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -41868,7 +41868,7 @@
         <v>45225</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -41941,7 +41941,7 @@
         <v>46050</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -42019,7 +42019,7 @@
         <v>44754</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -42092,7 +42092,7 @@
         <v>46050</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -42170,7 +42170,7 @@
         <v>45421</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -42248,7 +42248,7 @@
         <v>46055</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -42326,7 +42326,7 @@
         <v>46052</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -42399,7 +42399,7 @@
         <v>46181</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -42477,7 +42477,7 @@
         <v>45551</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -42550,7 +42550,7 @@
         <v>45530</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -42623,7 +42623,7 @@
         <v>46058</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -42701,7 +42701,7 @@
         <v>46058</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -42779,7 +42779,7 @@
         <v>46058</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -42857,7 +42857,7 @@
         <v>46058</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -42935,7 +42935,7 @@
         <v>46060</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -43008,7 +43008,7 @@
         <v>44986</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -43081,7 +43081,7 @@
         <v>46063</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -43159,7 +43159,7 @@
         <v>46063</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -43237,7 +43237,7 @@
         <v>44770</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -43310,7 +43310,7 @@
         <v>46064</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -43388,7 +43388,7 @@
         <v>45566</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -43466,7 +43466,7 @@
         <v>46065</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -43544,7 +43544,7 @@
         <v>46065</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -43622,7 +43622,7 @@
         <v>46064</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -43700,7 +43700,7 @@
         <v>46064</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -43778,7 +43778,7 @@
         <v>46064</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -43856,7 +43856,7 @@
         <v>46064</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -43934,7 +43934,7 @@
         <v>46064</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -44012,7 +44012,7 @@
         <v>46069</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -44090,7 +44090,7 @@
         <v>46185</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -44163,7 +44163,7 @@
         <v>46070</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -44241,7 +44241,7 @@
         <v>46070</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -44319,7 +44319,7 @@
         <v>46185</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -44392,7 +44392,7 @@
         <v>45302</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -44470,7 +44470,7 @@
         <v>45601</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -44543,7 +44543,7 @@
         <v>46073</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -44621,7 +44621,7 @@
         <v>46188</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -44694,7 +44694,7 @@
         <v>44678</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -44772,7 +44772,7 @@
         <v>46076</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -44850,7 +44850,7 @@
         <v>46076</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -44928,7 +44928,7 @@
         <v>44637</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -45001,7 +45001,7 @@
         <v>46078</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -45079,7 +45079,7 @@
         <v>46080</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -45157,7 +45157,7 @@
         <v>46080</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -45235,7 +45235,7 @@
         <v>46079</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -45313,7 +45313,7 @@
         <v>46080</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -45391,7 +45391,7 @@
         <v>46080</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -45469,7 +45469,7 @@
         <v>45279</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -45547,7 +45547,7 @@
         <v>45609</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -45625,7 +45625,7 @@
         <v>46085</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -45703,7 +45703,7 @@
         <v>46085</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -45781,7 +45781,7 @@
         <v>46085</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -45859,7 +45859,7 @@
         <v>46085</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -45937,7 +45937,7 @@
         <v>45070</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -46015,7 +46015,7 @@
         <v>44973</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -46093,7 +46093,7 @@
         <v>44891</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -46166,7 +46166,7 @@
         <v>45616</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -46239,7 +46239,7 @@
         <v>46094</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -46317,7 +46317,7 @@
         <v>44949</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -46390,7 +46390,7 @@
         <v>46097</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -46463,7 +46463,7 @@
         <v>44966</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -46536,7 +46536,7 @@
         <v>44953</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -46614,7 +46614,7 @@
         <v>46099</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -46692,7 +46692,7 @@
         <v>46099</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -46765,7 +46765,7 @@
         <v>46099</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -46843,7 +46843,7 @@
         <v>46099</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -46921,7 +46921,7 @@
         <v>44823</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -46994,7 +46994,7 @@
         <v>45202</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -47067,7 +47067,7 @@
         <v>46099</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -47140,7 +47140,7 @@
         <v>46196</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -47218,7 +47218,7 @@
         <v>45379</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -47291,7 +47291,7 @@
         <v>45428</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -47369,7 +47369,7 @@
         <v>46106</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -47447,7 +47447,7 @@
         <v>45174</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -47525,7 +47525,7 @@
         <v>45770</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -47598,7 +47598,7 @@
         <v>46111</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -47676,7 +47676,7 @@
         <v>45236</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -47754,7 +47754,7 @@
         <v>45236</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -47832,7 +47832,7 @@
         <v>46114</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -47910,7 +47910,7 @@
         <v>46114</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -47988,7 +47988,7 @@
         <v>46114</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -48066,7 +48066,7 @@
         <v>46113</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -48144,7 +48144,7 @@
         <v>45357</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -48217,7 +48217,7 @@
         <v>45243</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -48295,7 +48295,7 @@
         <v>46120</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -48373,7 +48373,7 @@
         <v>46121</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -48451,7 +48451,7 @@
         <v>46122</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -48524,7 +48524,7 @@
         <v>45022</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -48602,7 +48602,7 @@
         <v>46199</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -48675,7 +48675,7 @@
         <v>46125</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -48748,7 +48748,7 @@
         <v>45846</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -48826,7 +48826,7 @@
         <v>44816</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -48899,7 +48899,7 @@
         <v>45314</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -48972,7 +48972,7 @@
         <v>46129</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -49050,7 +49050,7 @@
         <v>46128</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -49123,7 +49123,7 @@
         <v>44820</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -49196,7 +49196,7 @@
         <v>45535</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -49274,7 +49274,7 @@
         <v>45706</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -49347,7 +49347,7 @@
         <v>45250</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -49425,7 +49425,7 @@
         <v>45706</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -49498,7 +49498,7 @@
         <v>45197</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -49571,7 +49571,7 @@
         <v>46134</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -49644,7 +49644,7 @@
         <v>45086</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -49717,7 +49717,7 @@
         <v>46204</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -49790,7 +49790,7 @@
         <v>46203</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -49863,7 +49863,7 @@
         <v>44966</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -49936,7 +49936,7 @@
         <v>44806</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -50014,7 +50014,7 @@
         <v>45740</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -50087,7 +50087,7 @@
         <v>45783</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -50165,7 +50165,7 @@
         <v>45113</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -50238,7 +50238,7 @@
         <v>45719</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -50316,7 +50316,7 @@
         <v>44964</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -50394,7 +50394,7 @@
         <v>46209</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -50467,7 +50467,7 @@
         <v>45420</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -50540,7 +50540,7 @@
         <v>44834</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -50618,7 +50618,7 @@
         <v>45616</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -50691,7 +50691,7 @@
         <v>45258</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -50764,7 +50764,7 @@
         <v>44865</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -50837,7 +50837,7 @@
         <v>44953</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -50910,7 +50910,7 @@
         <v>45617</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -50988,7 +50988,7 @@
         <v>44879</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -51061,7 +51061,7 @@
         <v>45713</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -51139,7 +51139,7 @@
         <v>46212</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -51212,7 +51212,7 @@
         <v>45735</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -51290,7 +51290,7 @@
         <v>46211</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -51363,7 +51363,7 @@
         <v>44862</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -51441,7 +51441,7 @@
         <v>44887</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -51514,7 +51514,7 @@
         <v>44887</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -51587,7 +51587,7 @@
         <v>45426</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -51660,7 +51660,7 @@
         <v>44616</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -51738,7 +51738,7 @@
         <v>46218</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -51816,7 +51816,7 @@
         <v>46218</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -51894,7 +51894,7 @@
         <v>44949</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -51967,7 +51967,7 @@
         <v>44995</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -52045,7 +52045,7 @@
         <v>44813</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -52123,7 +52123,7 @@
         <v>46219</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -52196,7 +52196,7 @@
         <v>46225</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -52269,7 +52269,7 @@
         <v>46226</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -52342,7 +52342,7 @@
         <v>46226</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -52415,7 +52415,7 @@
         <v>46225</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -52488,7 +52488,7 @@
         <v>45142</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -52561,7 +52561,7 @@
         <v>45715</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -52634,7 +52634,7 @@
         <v>44653</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -52707,7 +52707,7 @@
         <v>45645</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -52785,7 +52785,7 @@
         <v>45593</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -52863,7 +52863,7 @@
         <v>44987</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -52936,7 +52936,7 @@
         <v>45555</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -53014,7 +53014,7 @@
         <v>45639</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -53092,7 +53092,7 @@
         <v>45314</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -53165,7 +53165,7 @@
         <v>46232</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -53238,7 +53238,7 @@
         <v>45447</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -53316,7 +53316,7 @@
         <v>44729</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -53389,7 +53389,7 @@
         <v>44844</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -53462,7 +53462,7 @@
         <v>44973</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -53540,7 +53540,7 @@
         <v>45076</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -53618,7 +53618,7 @@
         <v>45095</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -53691,7 +53691,7 @@
         <v>46279</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -53764,7 +53764,7 @@
         <v>45639</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -53842,7 +53842,7 @@
         <v>44526</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -53915,7 +53915,7 @@
         <v>44922</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -53993,7 +53993,7 @@
         <v>46233</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -54066,7 +54066,7 @@
         <v>46279</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -54139,7 +54139,7 @@
         <v>46279</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -54212,7 +54212,7 @@
         <v>44795</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -54290,7 +54290,7 @@
         <v>45260</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -54363,7 +54363,7 @@
         <v>44491</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -54436,7 +54436,7 @@
         <v>45041</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -54514,7 +54514,7 @@
         <v>45257</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -54587,7 +54587,7 @@
         <v>44871</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -54660,7 +54660,7 @@
         <v>45391</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -54733,7 +54733,7 @@
         <v>45692</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -54811,7 +54811,7 @@
         <v>45070</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -54889,7 +54889,7 @@
         <v>45202</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -54962,7 +54962,7 @@
         <v>44966</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -55040,7 +55040,7 @@
         <v>46282</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -55118,7 +55118,7 @@
         <v>45323</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -55196,7 +55196,7 @@
         <v>46282</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -55274,7 +55274,7 @@
         <v>46282</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -55352,7 +55352,7 @@
         <v>46282</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -55430,7 +55430,7 @@
         <v>46282</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -55508,7 +55508,7 @@
         <v>45341</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -55586,7 +55586,7 @@
         <v>46281</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -55659,7 +55659,7 @@
         <v>46282</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -55737,7 +55737,7 @@
         <v>44550</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -55810,7 +55810,7 @@
         <v>45566</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -55888,7 +55888,7 @@
         <v>45566</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -55966,7 +55966,7 @@
         <v>46282</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -56044,7 +56044,7 @@
         <v>46282</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -56122,7 +56122,7 @@
         <v>46282</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -56200,7 +56200,7 @@
         <v>45441</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -56273,7 +56273,7 @@
         <v>45374</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -56351,7 +56351,7 @@
         <v>45391</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -56424,7 +56424,7 @@
         <v>44981</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -56502,7 +56502,7 @@
         <v>44679</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -56580,7 +56580,7 @@
         <v>45293</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -56653,7 +56653,7 @@
         <v>45554</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -56726,7 +56726,7 @@
         <v>45214</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -56799,7 +56799,7 @@
         <v>45110</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -56872,7 +56872,7 @@
         <v>45660</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -56950,7 +56950,7 @@
         <v>46286</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -57028,7 +57028,7 @@
         <v>45735</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -57106,7 +57106,7 @@
         <v>45516</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -57184,7 +57184,7 @@
         <v>44966</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -57262,7 +57262,7 @@
         <v>45078</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -57335,7 +57335,7 @@
         <v>45113</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -57408,7 +57408,7 @@
         <v>45191</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -57481,7 +57481,7 @@
         <v>45763</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -57554,7 +57554,7 @@
         <v>44551</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -57627,7 +57627,7 @@
         <v>44833</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -57705,7 +57705,7 @@
         <v>45103</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -57778,7 +57778,7 @@
         <v>45863</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -57851,7 +57851,7 @@
         <v>45618</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -57924,7 +57924,7 @@
         <v>45639</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -58002,7 +58002,7 @@
         <v>45299</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -58075,7 +58075,7 @@
         <v>45301</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -58153,7 +58153,7 @@
         <v>44714</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -58226,7 +58226,7 @@
         <v>45870</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -58299,7 +58299,7 @@
         <v>44622</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -58372,7 +58372,7 @@
         <v>45232</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -58450,7 +58450,7 @@
         <v>44887</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -58523,7 +58523,7 @@
         <v>45422</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -58596,7 +58596,7 @@
         <v>44622</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -58669,7 +58669,7 @@
         <v>45191</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -58742,7 +58742,7 @@
         <v>44595</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -58815,7 +58815,7 @@
         <v>44589</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -58888,7 +58888,7 @@
         <v>45308</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -58961,7 +58961,7 @@
         <v>44922</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -59039,7 +59039,7 @@
         <v>45615</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -59117,7 +59117,7 @@
         <v>46295</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -59195,7 +59195,7 @@
         <v>46295</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -59273,7 +59273,7 @@
         <v>45149</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -59346,7 +59346,7 @@
         <v>45762</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -59419,7 +59419,7 @@
         <v>44817</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -59492,7 +59492,7 @@
         <v>45149</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -59565,7 +59565,7 @@
         <v>45622</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -59638,7 +59638,7 @@
         <v>45554</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -59711,7 +59711,7 @@
         <v>45095</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -59784,7 +59784,7 @@
         <v>45593</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -59862,7 +59862,7 @@
         <v>45275</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -59935,7 +59935,7 @@
         <v>44564</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -60008,7 +60008,7 @@
         <v>45744</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -60086,7 +60086,7 @@
         <v>46255</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -60164,7 +60164,7 @@
         <v>45407</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -60237,7 +60237,7 @@
         <v>45071</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -60315,7 +60315,7 @@
         <v>45257</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -60393,7 +60393,7 @@
         <v>45257</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -60466,7 +60466,7 @@
         <v>45566</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -60544,7 +60544,7 @@
         <v>46300</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -60617,7 +60617,7 @@
         <v>45566</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -60695,7 +60695,7 @@
         <v>45566</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -60773,7 +60773,7 @@
         <v>45735</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -60851,7 +60851,7 @@
         <v>45736</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -60929,7 +60929,7 @@
         <v>45642</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -61002,7 +61002,7 @@
         <v>45530</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -61075,7 +61075,7 @@
         <v>46258</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -61153,7 +61153,7 @@
         <v>45530</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -61226,7 +61226,7 @@
         <v>45371</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -61304,7 +61304,7 @@
         <v>46258</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -61382,7 +61382,7 @@
         <v>46302</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -61455,7 +61455,7 @@
         <v>45727</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -61528,7 +61528,7 @@
         <v>45267</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -61606,7 +61606,7 @@
         <v>46307</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -61679,7 +61679,7 @@
         <v>45797</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -61752,7 +61752,7 @@
         <v>45797</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -61830,7 +61830,7 @@
         <v>45796</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -61908,7 +61908,7 @@
         <v>46304</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -61981,7 +61981,7 @@
         <v>46304</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -62054,7 +62054,7 @@
         <v>46307</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -62127,7 +62127,7 @@
         <v>46304</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -62200,7 +62200,7 @@
         <v>45797</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -62273,7 +62273,7 @@
         <v>45796</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -62351,7 +62351,7 @@
         <v>45702</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -62429,7 +62429,7 @@
         <v>46209</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -62502,7 +62502,7 @@
         <v>46304</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -62575,7 +62575,7 @@
         <v>45316</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -62653,7 +62653,7 @@
         <v>46160</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -62726,7 +62726,7 @@
         <v>46308</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -62799,7 +62799,7 @@
         <v>46308</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -62877,7 +62877,7 @@
         <v>46308</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -62955,7 +62955,7 @@
         <v>46308</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -63028,7 +63028,7 @@
         <v>45800</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -63106,7 +63106,7 @@
         <v>46308</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -63179,7 +63179,7 @@
         <v>45800</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -63257,7 +63257,7 @@
         <v>45800</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -63335,7 +63335,7 @@
         <v>45800</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -63413,7 +63413,7 @@
         <v>46308</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -63491,7 +63491,7 @@
         <v>46308</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -63564,7 +63564,7 @@
         <v>46308</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -63637,7 +63637,7 @@
         <v>46308</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -63710,7 +63710,7 @@
         <v>46308</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -63783,7 +63783,7 @@
         <v>46308</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -63856,7 +63856,7 @@
         <v>46269</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -63929,7 +63929,7 @@
         <v>45812</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -64007,7 +64007,7 @@
         <v>45812</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -64085,7 +64085,7 @@
         <v>46269</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -64158,7 +64158,7 @@
         <v>46269</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
@@ -64231,7 +64231,7 @@
         <v>45639</v>
       </c>
       <c r="E802" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -64309,7 +64309,7 @@
         <v>46269</v>
       </c>
       <c r="E803" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
@@ -64382,7 +64382,7 @@
         <v>45819</v>
       </c>
       <c r="E804" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
@@ -64460,7 +64460,7 @@
         <v>45819</v>
       </c>
       <c r="E805" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>
@@ -64538,7 +64538,7 @@
         <v>45824</v>
       </c>
       <c r="E806" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F806" t="inlineStr">
         <is>
@@ -64616,7 +64616,7 @@
         <v>45824</v>
       </c>
       <c r="E807" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F807" t="inlineStr">
         <is>
@@ -64694,7 +64694,7 @@
         <v>45824</v>
       </c>
       <c r="E808" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F808" t="inlineStr">
         <is>
@@ -64772,7 +64772,7 @@
         <v>46269</v>
       </c>
       <c r="E809" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F809" t="inlineStr">
         <is>
@@ -64845,7 +64845,7 @@
         <v>45824</v>
       </c>
       <c r="E810" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F810" t="inlineStr">
         <is>
@@ -64923,7 +64923,7 @@
         <v>45835</v>
       </c>
       <c r="E811" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F811" t="inlineStr">
         <is>
@@ -65001,7 +65001,7 @@
         <v>45840</v>
       </c>
       <c r="E812" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F812" t="inlineStr">
         <is>
@@ -65079,7 +65079,7 @@
         <v>45845</v>
       </c>
       <c r="E813" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F813" t="inlineStr">
         <is>
@@ -65157,7 +65157,7 @@
         <v>45776</v>
       </c>
       <c r="E814" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F814" t="inlineStr">
         <is>
@@ -65230,7 +65230,7 @@
         <v>45854</v>
       </c>
       <c r="E815" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F815" t="inlineStr">
         <is>
@@ -65303,7 +65303,7 @@
         <v>45854</v>
       </c>
       <c r="E816" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F816" t="inlineStr">
         <is>
@@ -65376,7 +65376,7 @@
         <v>45853</v>
       </c>
       <c r="E817" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F817" t="inlineStr">
         <is>
@@ -65449,7 +65449,7 @@
         <v>45855</v>
       </c>
       <c r="E818" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F818" t="inlineStr">
         <is>
@@ -65522,7 +65522,7 @@
         <v>45523</v>
       </c>
       <c r="E819" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F819" t="inlineStr">
         <is>
@@ -65595,7 +65595,7 @@
         <v>45831</v>
       </c>
       <c r="E820" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F820" t="inlineStr">
         <is>
@@ -65668,7 +65668,7 @@
         <v>45820</v>
       </c>
       <c r="E821" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F821" t="inlineStr">
         <is>
@@ -65746,7 +65746,7 @@
         <v>45870</v>
       </c>
       <c r="E822" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F822" t="inlineStr">
         <is>
@@ -65819,7 +65819,7 @@
         <v>45709</v>
       </c>
       <c r="E823" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F823" t="inlineStr">
         <is>
@@ -65897,7 +65897,7 @@
         <v>45880</v>
       </c>
       <c r="E824" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F824" t="inlineStr">
         <is>
@@ -65975,7 +65975,7 @@
         <v>45880</v>
       </c>
       <c r="E825" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F825" t="inlineStr">
         <is>
@@ -66053,7 +66053,7 @@
         <v>45881</v>
       </c>
       <c r="E826" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F826" t="inlineStr">
         <is>
@@ -66131,7 +66131,7 @@
         <v>45644</v>
       </c>
       <c r="E827" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F827" t="inlineStr">
         <is>
@@ -66204,7 +66204,7 @@
         <v>45428</v>
       </c>
       <c r="E828" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F828" t="inlineStr">
         <is>
@@ -66277,7 +66277,7 @@
         <v>45429</v>
       </c>
       <c r="E829" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F829" t="inlineStr">
         <is>
@@ -66350,7 +66350,7 @@
         <v>45250</v>
       </c>
       <c r="E830" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F830" t="inlineStr">
         <is>
@@ -66428,7 +66428,7 @@
         <v>46188</v>
       </c>
       <c r="E831" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F831" t="inlineStr">
         <is>
@@ -66506,7 +66506,7 @@
         <v>46258</v>
       </c>
       <c r="E832" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F832" t="inlineStr">
         <is>

--- a/Översikt FINSPÅNG.xlsx
+++ b/Översikt FINSPÅNG.xlsx
@@ -601,7 +601,7 @@
         <v>46244</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -727,7 +727,7 @@
         <v>45945</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -858,7 +858,7 @@
         <v>45134</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
         <v>44896</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1121,7 +1121,7 @@
         <v>44888</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>45210</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1369,7 +1369,7 @@
         <v>44777</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1488,7 +1488,7 @@
         <v>44897</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1607,7 +1607,7 @@
         <v>44910</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1734,7 +1734,7 @@
         <v>45322</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1855,7 +1855,7 @@
         <v>44624</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1971,7 +1971,7 @@
         <v>44599</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2082,7 +2082,7 @@
         <v>45238</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2197,7 +2197,7 @@
         <v>45421</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2317,7 +2317,7 @@
         <v>45891</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2433,7 +2433,7 @@
         <v>45898</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2548,7 +2548,7 @@
         <v>45267</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2663,7 +2663,7 @@
         <v>45679</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2782,7 +2782,7 @@
         <v>44791</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2896,7 +2896,7 @@
         <v>45812</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3010,7 +3010,7 @@
         <v>44665</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3123,7 +3123,7 @@
         <v>45681</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3240,7 +3240,7 @@
         <v>46307</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3352,7 +3352,7 @@
         <v>45082</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3464,7 +3464,7 @@
         <v>45819</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3580,7 +3580,7 @@
         <v>44774</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3692,7 +3692,7 @@
         <v>45602</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3804,7 +3804,7 @@
         <v>46196</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3916,7 +3916,7 @@
         <v>45800</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4028,7 +4028,7 @@
         <v>44690</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4139,7 +4139,7 @@
         <v>45441</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4250,7 +4250,7 @@
         <v>44816</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4356,7 +4356,7 @@
         <v>45477</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4471,7 +4471,7 @@
         <v>45894</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4586,7 +4586,7 @@
         <v>45905</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4697,7 +4697,7 @@
         <v>45950</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4808,7 +4808,7 @@
         <v>45644</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4914,7 +4914,7 @@
         <v>44981</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5025,7 +5025,7 @@
         <v>46174</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5136,7 +5136,7 @@
         <v>46181</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5247,7 +5247,7 @@
         <v>46181</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5358,7 +5358,7 @@
         <v>45425</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5464,7 +5464,7 @@
         <v>45235</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5575,7 +5575,7 @@
         <v>45121</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5690,7 +5690,7 @@
         <v>44903</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5800,7 +5800,7 @@
         <v>44683</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5910,7 +5910,7 @@
         <v>44776</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6015,7 +6015,7 @@
         <v>44504</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6125,7 +6125,7 @@
         <v>44529</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6230,7 +6230,7 @@
         <v>45567</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6344,7 +6344,7 @@
         <v>45082</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6454,7 +6454,7 @@
         <v>45149</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6563,7 +6563,7 @@
         <v>44501</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6673,7 +6673,7 @@
         <v>44897</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6787,7 +6787,7 @@
         <v>45744</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6901,7 +6901,7 @@
         <v>45636</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7006,7 +7006,7 @@
         <v>45328</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7115,7 +7115,7 @@
         <v>45229</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7225,7 +7225,7 @@
         <v>44599</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7335,7 +7335,7 @@
         <v>45447</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7445,7 +7445,7 @@
         <v>45555</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7559,7 +7559,7 @@
         <v>46043</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7673,7 +7673,7 @@
         <v>45905</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7783,7 +7783,7 @@
         <v>45883</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7893,7 +7893,7 @@
         <v>45446</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7998,7 +7998,7 @@
         <v>44965</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8112,7 +8112,7 @@
         <v>46155</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8226,7 +8226,7 @@
         <v>45566</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8340,7 +8340,7 @@
         <v>44930</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8450,7 +8450,7 @@
         <v>44915</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8560,7 +8560,7 @@
         <v>45302</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8669,7 +8669,7 @@
         <v>45232</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8779,7 +8779,7 @@
         <v>44622</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8884,7 +8884,7 @@
         <v>46058</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8998,7 +8998,7 @@
         <v>46189</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9103,7 +9103,7 @@
         <v>44817</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9213,7 +9213,7 @@
         <v>46129</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9327,7 +9327,7 @@
         <v>44915</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9437,7 +9437,7 @@
         <v>46181</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9547,7 +9547,7 @@
         <v>45070</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9657,7 +9657,7 @@
         <v>44992</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9767,7 +9767,7 @@
         <v>45615</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9881,7 +9881,7 @@
         <v>46258</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9991,7 +9991,7 @@
         <v>46258</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10105,7 +10105,7 @@
         <v>45845</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10215,7 +10215,7 @@
         <v>45846</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10325,7 +10325,7 @@
         <v>45880</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10435,7 +10435,7 @@
         <v>44711</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10545,7 +10545,7 @@
         <v>45428</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10650,7 +10650,7 @@
         <v>46107</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10760,7 +10760,7 @@
         <v>46188</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10874,7 +10874,7 @@
         <v>44755</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10952,7 +10952,7 @@
         <v>44675</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11025,7 +11025,7 @@
         <v>44676</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11103,7 +11103,7 @@
         <v>44864</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11176,7 +11176,7 @@
         <v>44600</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11249,7 +11249,7 @@
         <v>44824</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11322,7 +11322,7 @@
         <v>44536</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11400,7 +11400,7 @@
         <v>44799</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11473,7 +11473,7 @@
         <v>44795</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11546,7 +11546,7 @@
         <v>44856</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11619,7 +11619,7 @@
         <v>44578</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11697,7 +11697,7 @@
         <v>44675</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11770,7 +11770,7 @@
         <v>44852</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -11848,7 +11848,7 @@
         <v>44601</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -11926,7 +11926,7 @@
         <v>44601</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -11999,7 +11999,7 @@
         <v>44551</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12072,7 +12072,7 @@
         <v>44525</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12145,7 +12145,7 @@
         <v>44574</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12223,7 +12223,7 @@
         <v>44574</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12296,7 +12296,7 @@
         <v>44588</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12374,7 +12374,7 @@
         <v>44889</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12447,7 +12447,7 @@
         <v>44627</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12520,7 +12520,7 @@
         <v>44503</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -12598,7 +12598,7 @@
         <v>44525</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -12676,7 +12676,7 @@
         <v>44503</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -12749,7 +12749,7 @@
         <v>44874</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -12822,7 +12822,7 @@
         <v>44502</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -12900,7 +12900,7 @@
         <v>44551</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -12973,7 +12973,7 @@
         <v>44712</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -13051,7 +13051,7 @@
         <v>44581</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -13124,7 +13124,7 @@
         <v>44833</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -13197,7 +13197,7 @@
         <v>44601</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -13270,7 +13270,7 @@
         <v>44672</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -13343,7 +13343,7 @@
         <v>44859</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -13416,7 +13416,7 @@
         <v>44735</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -13489,7 +13489,7 @@
         <v>44796</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -13562,7 +13562,7 @@
         <v>44782</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -13635,7 +13635,7 @@
         <v>44741</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -13708,7 +13708,7 @@
         <v>44613</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -13786,7 +13786,7 @@
         <v>44859</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -13859,7 +13859,7 @@
         <v>44678</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -13932,7 +13932,7 @@
         <v>44855</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -14010,7 +14010,7 @@
         <v>44887</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -14083,7 +14083,7 @@
         <v>44860</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -14156,7 +14156,7 @@
         <v>44753</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -14229,7 +14229,7 @@
         <v>44802</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -14302,7 +14302,7 @@
         <v>44844</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -14380,7 +14380,7 @@
         <v>44781</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -14453,7 +14453,7 @@
         <v>44541</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -14526,7 +14526,7 @@
         <v>44564</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -14599,7 +14599,7 @@
         <v>44859</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -14672,7 +14672,7 @@
         <v>44595</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -14745,7 +14745,7 @@
         <v>44582</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -14818,7 +14818,7 @@
         <v>44816</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -14891,7 +14891,7 @@
         <v>44508</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -14964,7 +14964,7 @@
         <v>44656</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -15037,7 +15037,7 @@
         <v>44587</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -15110,7 +15110,7 @@
         <v>44627</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -15183,7 +15183,7 @@
         <v>44820</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -15256,7 +15256,7 @@
         <v>44532</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -15329,7 +15329,7 @@
         <v>44552</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -15402,7 +15402,7 @@
         <v>44879</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -15475,7 +15475,7 @@
         <v>44588</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -15553,7 +15553,7 @@
         <v>44581</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -15626,7 +15626,7 @@
         <v>44875</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -15699,7 +15699,7 @@
         <v>44743</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -15772,7 +15772,7 @@
         <v>44831</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -15850,7 +15850,7 @@
         <v>44819</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -15923,7 +15923,7 @@
         <v>44581</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -16001,7 +16001,7 @@
         <v>44630</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -16074,7 +16074,7 @@
         <v>44804</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -16152,7 +16152,7 @@
         <v>44601</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -16225,7 +16225,7 @@
         <v>44742</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -16303,7 +16303,7 @@
         <v>44859</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -16376,7 +16376,7 @@
         <v>44600</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -16449,7 +16449,7 @@
         <v>44635</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -16522,7 +16522,7 @@
         <v>44776</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -16595,7 +16595,7 @@
         <v>44713</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -16673,7 +16673,7 @@
         <v>44697</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -16751,7 +16751,7 @@
         <v>44533</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -16824,7 +16824,7 @@
         <v>44601</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -16897,7 +16897,7 @@
         <v>44678</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -16970,7 +16970,7 @@
         <v>44564</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -17043,7 +17043,7 @@
         <v>44704</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -17116,7 +17116,7 @@
         <v>44642</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -17189,7 +17189,7 @@
         <v>44659</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -17267,7 +17267,7 @@
         <v>44656</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -17345,7 +17345,7 @@
         <v>45447</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -17423,7 +17423,7 @@
         <v>44966</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -17496,7 +17496,7 @@
         <v>45103</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -17569,7 +17569,7 @@
         <v>44866</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -17642,7 +17642,7 @@
         <v>45293</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -17715,7 +17715,7 @@
         <v>45033</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -17793,7 +17793,7 @@
         <v>45258</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -17866,7 +17866,7 @@
         <v>45009</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -17939,7 +17939,7 @@
         <v>44677</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -18012,7 +18012,7 @@
         <v>44802</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -18085,7 +18085,7 @@
         <v>44898</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -18158,7 +18158,7 @@
         <v>44897</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -18236,7 +18236,7 @@
         <v>44918</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -18314,7 +18314,7 @@
         <v>44595</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -18392,7 +18392,7 @@
         <v>45097</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -18465,7 +18465,7 @@
         <v>45086</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -18538,7 +18538,7 @@
         <v>45063</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -18611,7 +18611,7 @@
         <v>44672</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -18684,7 +18684,7 @@
         <v>45260</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -18757,7 +18757,7 @@
         <v>45021</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -18830,7 +18830,7 @@
         <v>45330</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -18903,7 +18903,7 @@
         <v>44973</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -18981,7 +18981,7 @@
         <v>45107</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -19054,7 +19054,7 @@
         <v>44767</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -19127,7 +19127,7 @@
         <v>45293</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -19205,7 +19205,7 @@
         <v>45428</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -19283,7 +19283,7 @@
         <v>45206</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -19356,7 +19356,7 @@
         <v>45705</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -19429,7 +19429,7 @@
         <v>45555</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -19507,7 +19507,7 @@
         <v>45623</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -19580,7 +19580,7 @@
         <v>45642</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -19658,7 +19658,7 @@
         <v>45095</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -19736,7 +19736,7 @@
         <v>44993</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -19809,7 +19809,7 @@
         <v>45749</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -19887,7 +19887,7 @@
         <v>44844</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -19960,7 +19960,7 @@
         <v>44844</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -20033,7 +20033,7 @@
         <v>45554</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -20106,7 +20106,7 @@
         <v>44960</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -20184,7 +20184,7 @@
         <v>44914</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -20257,7 +20257,7 @@
         <v>45728</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -20335,7 +20335,7 @@
         <v>45357</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -20408,7 +20408,7 @@
         <v>45740</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -20486,7 +20486,7 @@
         <v>45688</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -20564,7 +20564,7 @@
         <v>44778</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -20637,7 +20637,7 @@
         <v>45253</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -20715,7 +20715,7 @@
         <v>45149</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -20788,7 +20788,7 @@
         <v>45084</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -20861,7 +20861,7 @@
         <v>45441</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -20934,7 +20934,7 @@
         <v>45233</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -21007,7 +21007,7 @@
         <v>44861</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -21085,7 +21085,7 @@
         <v>45677</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -21163,7 +21163,7 @@
         <v>44942</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -21236,7 +21236,7 @@
         <v>44900</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -21309,7 +21309,7 @@
         <v>45095</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -21387,7 +21387,7 @@
         <v>45095</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -21460,7 +21460,7 @@
         <v>44817</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -21538,7 +21538,7 @@
         <v>45259</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -21611,7 +21611,7 @@
         <v>45103</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -21684,7 +21684,7 @@
         <v>45623</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -21762,7 +21762,7 @@
         <v>44880</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -21840,7 +21840,7 @@
         <v>45264</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -21918,7 +21918,7 @@
         <v>44974</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -21991,7 +21991,7 @@
         <v>45008</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -22064,7 +22064,7 @@
         <v>45720</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -22142,7 +22142,7 @@
         <v>44918</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -22220,7 +22220,7 @@
         <v>45040</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -22298,7 +22298,7 @@
         <v>45710</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -22371,7 +22371,7 @@
         <v>45554</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -22444,7 +22444,7 @@
         <v>45337</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -22517,7 +22517,7 @@
         <v>45593</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -22595,7 +22595,7 @@
         <v>44958</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -22668,7 +22668,7 @@
         <v>44490</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -22741,7 +22741,7 @@
         <v>45274</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -22814,7 +22814,7 @@
         <v>45415</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -22887,7 +22887,7 @@
         <v>45328</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -22960,7 +22960,7 @@
         <v>45095</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -23033,7 +23033,7 @@
         <v>44950</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -23111,7 +23111,7 @@
         <v>44860</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -23184,7 +23184,7 @@
         <v>45456</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -23262,7 +23262,7 @@
         <v>45744</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -23340,7 +23340,7 @@
         <v>45257</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -23418,7 +23418,7 @@
         <v>45257</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -23496,7 +23496,7 @@
         <v>44949</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -23569,7 +23569,7 @@
         <v>45740</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -23647,7 +23647,7 @@
         <v>45103</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -23720,7 +23720,7 @@
         <v>45178</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -23793,7 +23793,7 @@
         <v>45002</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -23871,7 +23871,7 @@
         <v>45421</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -23949,7 +23949,7 @@
         <v>44503</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -24022,7 +24022,7 @@
         <v>44840</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -24095,7 +24095,7 @@
         <v>45541</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -24173,7 +24173,7 @@
         <v>45041</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -24246,7 +24246,7 @@
         <v>45125</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -24324,7 +24324,7 @@
         <v>45257</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -24402,7 +24402,7 @@
         <v>45206</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -24475,7 +24475,7 @@
         <v>45463</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -24548,7 +24548,7 @@
         <v>44516</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -24621,7 +24621,7 @@
         <v>44964</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -24699,7 +24699,7 @@
         <v>44993</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -24772,7 +24772,7 @@
         <v>45020</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -24845,7 +24845,7 @@
         <v>44607</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -24918,7 +24918,7 @@
         <v>45167</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -24996,7 +24996,7 @@
         <v>44767</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -25069,7 +25069,7 @@
         <v>44930</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -25142,7 +25142,7 @@
         <v>44957</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -25215,7 +25215,7 @@
         <v>44662</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -25293,7 +25293,7 @@
         <v>45084</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -25366,7 +25366,7 @@
         <v>44732</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -25444,7 +25444,7 @@
         <v>45601</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -25517,7 +25517,7 @@
         <v>44914</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -25595,7 +25595,7 @@
         <v>44734</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -25668,7 +25668,7 @@
         <v>45463</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -25741,7 +25741,7 @@
         <v>45147</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -25814,7 +25814,7 @@
         <v>45442</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -25887,7 +25887,7 @@
         <v>44536</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -25960,7 +25960,7 @@
         <v>45883</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -26038,7 +26038,7 @@
         <v>45883</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -26116,7 +26116,7 @@
         <v>44887</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -26189,7 +26189,7 @@
         <v>45832</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -26262,7 +26262,7 @@
         <v>45615</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -26340,7 +26340,7 @@
         <v>44614</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -26413,7 +26413,7 @@
         <v>45468</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -26491,7 +26491,7 @@
         <v>45516</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -26564,7 +26564,7 @@
         <v>45915</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -26642,7 +26642,7 @@
         <v>44833</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -26720,7 +26720,7 @@
         <v>45700</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -26798,7 +26798,7 @@
         <v>44508</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -26871,7 +26871,7 @@
         <v>44817</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -26944,7 +26944,7 @@
         <v>44550</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -27017,7 +27017,7 @@
         <v>45621</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -27095,7 +27095,7 @@
         <v>45560</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -27173,7 +27173,7 @@
         <v>45888</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -27251,7 +27251,7 @@
         <v>45891</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -27329,7 +27329,7 @@
         <v>45707</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -27407,7 +27407,7 @@
         <v>44865</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -27485,7 +27485,7 @@
         <v>44980</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -27558,7 +27558,7 @@
         <v>45118</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -27631,7 +27631,7 @@
         <v>45894</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -27709,7 +27709,7 @@
         <v>45895</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -27782,7 +27782,7 @@
         <v>45692</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -27860,7 +27860,7 @@
         <v>45166</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -27938,7 +27938,7 @@
         <v>45467</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -28011,7 +28011,7 @@
         <v>45896</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -28089,7 +28089,7 @@
         <v>44735</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -28162,7 +28162,7 @@
         <v>45898</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -28235,7 +28235,7 @@
         <v>45853</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -28308,7 +28308,7 @@
         <v>45600</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -28381,7 +28381,7 @@
         <v>46064</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -28459,7 +28459,7 @@
         <v>45229</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -28537,7 +28537,7 @@
         <v>44900</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -28610,7 +28610,7 @@
         <v>45903</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -28688,7 +28688,7 @@
         <v>45903</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -28766,7 +28766,7 @@
         <v>45103</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -28839,7 +28839,7 @@
         <v>45903</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -28917,7 +28917,7 @@
         <v>45903</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -28995,7 +28995,7 @@
         <v>45903</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -29073,7 +29073,7 @@
         <v>45343</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -29151,7 +29151,7 @@
         <v>45905</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -29229,7 +29229,7 @@
         <v>45904</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -29307,7 +29307,7 @@
         <v>45082</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -29385,7 +29385,7 @@
         <v>45905</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -29463,7 +29463,7 @@
         <v>45299</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -29536,7 +29536,7 @@
         <v>45006</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -29609,7 +29609,7 @@
         <v>45904</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -29687,7 +29687,7 @@
         <v>45908</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -29760,7 +29760,7 @@
         <v>45379</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -29833,7 +29833,7 @@
         <v>44840</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -29911,7 +29911,7 @@
         <v>45040</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -29984,7 +29984,7 @@
         <v>46141</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -30057,7 +30057,7 @@
         <v>45075</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -30130,7 +30130,7 @@
         <v>45617</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -30208,7 +30208,7 @@
         <v>44725</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -30281,7 +30281,7 @@
         <v>45082</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -30359,7 +30359,7 @@
         <v>45055</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -30432,7 +30432,7 @@
         <v>45688</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -30510,7 +30510,7 @@
         <v>45250</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -30588,7 +30588,7 @@
         <v>45250</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -30661,7 +30661,7 @@
         <v>45133</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -30734,7 +30734,7 @@
         <v>44903</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -30812,7 +30812,7 @@
         <v>45548</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -30885,7 +30885,7 @@
         <v>45267</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -30963,7 +30963,7 @@
         <v>45924</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -31036,7 +31036,7 @@
         <v>45008</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -31114,7 +31114,7 @@
         <v>45344</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -31187,7 +31187,7 @@
         <v>45362</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -31260,7 +31260,7 @@
         <v>44634</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -31338,7 +31338,7 @@
         <v>45252</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -31411,7 +31411,7 @@
         <v>45209</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -31484,7 +31484,7 @@
         <v>45209</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -31557,7 +31557,7 @@
         <v>45931</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -31630,7 +31630,7 @@
         <v>45184</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -31703,7 +31703,7 @@
         <v>45980</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -31776,7 +31776,7 @@
         <v>45846</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -31854,7 +31854,7 @@
         <v>45935</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -31932,7 +31932,7 @@
         <v>45566</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -32010,7 +32010,7 @@
         <v>44664</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -32088,7 +32088,7 @@
         <v>44946</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -32166,7 +32166,7 @@
         <v>44946</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -32244,7 +32244,7 @@
         <v>44944</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -32322,7 +32322,7 @@
         <v>45944</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -32395,7 +32395,7 @@
         <v>45009</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -32473,7 +32473,7 @@
         <v>45247</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -32546,7 +32546,7 @@
         <v>45095</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -32619,7 +32619,7 @@
         <v>45845</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -32697,7 +32697,7 @@
         <v>45523</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -32775,7 +32775,7 @@
         <v>45950</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -32853,7 +32853,7 @@
         <v>44767</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -32926,7 +32926,7 @@
         <v>44964</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -33004,7 +33004,7 @@
         <v>44759</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -33077,7 +33077,7 @@
         <v>45258</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -33150,7 +33150,7 @@
         <v>44617</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -33223,7 +33223,7 @@
         <v>45955</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -33296,7 +33296,7 @@
         <v>45042</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -33374,7 +33374,7 @@
         <v>44937</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -33447,7 +33447,7 @@
         <v>45709</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -33525,7 +33525,7 @@
         <v>44993</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -33598,7 +33598,7 @@
         <v>45095</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -33671,7 +33671,7 @@
         <v>46077</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -33749,7 +33749,7 @@
         <v>44564</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -33822,7 +33822,7 @@
         <v>45607</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -33895,7 +33895,7 @@
         <v>45607</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -33968,7 +33968,7 @@
         <v>45609</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -34046,7 +34046,7 @@
         <v>45665</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -34119,7 +34119,7 @@
         <v>45551</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -34192,7 +34192,7 @@
         <v>44774</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -34270,7 +34270,7 @@
         <v>45969</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -34343,7 +34343,7 @@
         <v>45744</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -34421,7 +34421,7 @@
         <v>45971</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -34494,7 +34494,7 @@
         <v>45013</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -34572,7 +34572,7 @@
         <v>45688</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -34650,7 +34650,7 @@
         <v>45428</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -34723,7 +34723,7 @@
         <v>45744</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -34801,7 +34801,7 @@
         <v>45979</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -34874,7 +34874,7 @@
         <v>45077</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -34952,7 +34952,7 @@
         <v>45002</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -35030,7 +35030,7 @@
         <v>45068</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -35108,7 +35108,7 @@
         <v>44867</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -35181,7 +35181,7 @@
         <v>45983</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -35254,7 +35254,7 @@
         <v>45983</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -35327,7 +35327,7 @@
         <v>45983</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -35400,7 +35400,7 @@
         <v>45985</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -35473,7 +35473,7 @@
         <v>44886</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -35546,7 +35546,7 @@
         <v>45636</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -35619,7 +35619,7 @@
         <v>45986</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -35692,7 +35692,7 @@
         <v>45728</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -35770,7 +35770,7 @@
         <v>45280</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -35848,7 +35848,7 @@
         <v>45986</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -35921,7 +35921,7 @@
         <v>45225</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -35994,7 +35994,7 @@
         <v>44987</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -36067,7 +36067,7 @@
         <v>45082</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -36145,7 +36145,7 @@
         <v>45566</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -36223,7 +36223,7 @@
         <v>45177</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -36296,7 +36296,7 @@
         <v>44995</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -36374,7 +36374,7 @@
         <v>45147</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -36447,7 +36447,7 @@
         <v>44966</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -36520,7 +36520,7 @@
         <v>46000</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -36598,7 +36598,7 @@
         <v>45230</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -36671,7 +36671,7 @@
         <v>45040</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -36744,7 +36744,7 @@
         <v>46002</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -36822,7 +36822,7 @@
         <v>46003</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -36895,7 +36895,7 @@
         <v>46002</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -36973,7 +36973,7 @@
         <v>46174</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -37051,7 +37051,7 @@
         <v>46174</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -37129,7 +37129,7 @@
         <v>46002</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -37207,7 +37207,7 @@
         <v>44876</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -37280,7 +37280,7 @@
         <v>46002</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -37358,7 +37358,7 @@
         <v>45179</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -37431,7 +37431,7 @@
         <v>45179</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -37504,7 +37504,7 @@
         <v>45709</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -37582,7 +37582,7 @@
         <v>46006</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -37655,7 +37655,7 @@
         <v>46006</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -37733,7 +37733,7 @@
         <v>45309</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -37811,7 +37811,7 @@
         <v>45309</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -37884,7 +37884,7 @@
         <v>45309</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -37957,7 +37957,7 @@
         <v>46006</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -38035,7 +38035,7 @@
         <v>44949</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -38108,7 +38108,7 @@
         <v>45323</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -38186,7 +38186,7 @@
         <v>45013</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -38264,7 +38264,7 @@
         <v>44981</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -38342,7 +38342,7 @@
         <v>44930</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -38420,7 +38420,7 @@
         <v>45086</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -38493,7 +38493,7 @@
         <v>45042</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -38566,7 +38566,7 @@
         <v>45042</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -38639,7 +38639,7 @@
         <v>44939</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -38712,7 +38712,7 @@
         <v>45607</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -38785,7 +38785,7 @@
         <v>44732</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -38863,7 +38863,7 @@
         <v>45425</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -38936,7 +38936,7 @@
         <v>45177</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -39009,7 +39009,7 @@
         <v>45302</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -39087,7 +39087,7 @@
         <v>45678</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -39165,7 +39165,7 @@
         <v>45622</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -39238,7 +39238,7 @@
         <v>45853</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -39311,7 +39311,7 @@
         <v>46029</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -39384,7 +39384,7 @@
         <v>46030</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -39462,7 +39462,7 @@
         <v>45237</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -39540,7 +39540,7 @@
         <v>46030</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -39618,7 +39618,7 @@
         <v>46031</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -39696,7 +39696,7 @@
         <v>44642</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -39769,7 +39769,7 @@
         <v>46034</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -39847,7 +39847,7 @@
         <v>46176</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -39920,7 +39920,7 @@
         <v>45770</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -39993,7 +39993,7 @@
         <v>46176</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -40066,7 +40066,7 @@
         <v>46176</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -40139,7 +40139,7 @@
         <v>46034</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -40217,7 +40217,7 @@
         <v>46034</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -40295,7 +40295,7 @@
         <v>46036</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -40373,7 +40373,7 @@
         <v>46036</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -40451,7 +40451,7 @@
         <v>46040</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -40524,7 +40524,7 @@
         <v>46040</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -40597,7 +40597,7 @@
         <v>45456</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -40675,7 +40675,7 @@
         <v>44749</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -40748,7 +40748,7 @@
         <v>45082</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -40826,7 +40826,7 @@
         <v>45082</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -40904,7 +40904,7 @@
         <v>46178</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -40977,7 +40977,7 @@
         <v>46178</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -41050,7 +41050,7 @@
         <v>45167</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -41123,7 +41123,7 @@
         <v>46177</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -41196,7 +41196,7 @@
         <v>44930</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -41269,7 +41269,7 @@
         <v>46178</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -41342,7 +41342,7 @@
         <v>44782</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -41415,7 +41415,7 @@
         <v>46048</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -41493,7 +41493,7 @@
         <v>45646</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -41566,7 +41566,7 @@
         <v>46049</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -41639,7 +41639,7 @@
         <v>46048</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -41717,7 +41717,7 @@
         <v>46048</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -41795,7 +41795,7 @@
         <v>45181</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -41868,7 +41868,7 @@
         <v>45225</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -41941,7 +41941,7 @@
         <v>46050</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -42019,7 +42019,7 @@
         <v>44754</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -42092,7 +42092,7 @@
         <v>46050</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -42170,7 +42170,7 @@
         <v>45421</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -42248,7 +42248,7 @@
         <v>46055</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -42326,7 +42326,7 @@
         <v>46052</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -42399,7 +42399,7 @@
         <v>46181</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -42477,7 +42477,7 @@
         <v>45551</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -42550,7 +42550,7 @@
         <v>45530</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -42623,7 +42623,7 @@
         <v>46058</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -42701,7 +42701,7 @@
         <v>46058</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -42779,7 +42779,7 @@
         <v>46058</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -42857,7 +42857,7 @@
         <v>46058</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -42935,7 +42935,7 @@
         <v>46060</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -43008,7 +43008,7 @@
         <v>44986</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -43081,7 +43081,7 @@
         <v>46063</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -43159,7 +43159,7 @@
         <v>46063</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -43237,7 +43237,7 @@
         <v>44770</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -43310,7 +43310,7 @@
         <v>46064</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -43388,7 +43388,7 @@
         <v>45566</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -43466,7 +43466,7 @@
         <v>46065</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -43544,7 +43544,7 @@
         <v>46065</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -43622,7 +43622,7 @@
         <v>46064</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -43700,7 +43700,7 @@
         <v>46064</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -43778,7 +43778,7 @@
         <v>46064</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -43856,7 +43856,7 @@
         <v>46064</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -43934,7 +43934,7 @@
         <v>46064</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -44012,7 +44012,7 @@
         <v>46069</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -44090,7 +44090,7 @@
         <v>46185</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -44163,7 +44163,7 @@
         <v>46070</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -44241,7 +44241,7 @@
         <v>46070</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -44319,7 +44319,7 @@
         <v>46185</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -44392,7 +44392,7 @@
         <v>45302</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -44470,7 +44470,7 @@
         <v>45601</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -44543,7 +44543,7 @@
         <v>46073</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -44621,7 +44621,7 @@
         <v>46188</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -44694,7 +44694,7 @@
         <v>44678</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -44772,7 +44772,7 @@
         <v>46076</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -44850,7 +44850,7 @@
         <v>46076</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -44928,7 +44928,7 @@
         <v>44637</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -45001,7 +45001,7 @@
         <v>46078</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -45079,7 +45079,7 @@
         <v>46080</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -45157,7 +45157,7 @@
         <v>46080</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -45235,7 +45235,7 @@
         <v>46079</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -45313,7 +45313,7 @@
         <v>46080</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -45391,7 +45391,7 @@
         <v>46080</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -45469,7 +45469,7 @@
         <v>45279</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -45547,7 +45547,7 @@
         <v>45609</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -45625,7 +45625,7 @@
         <v>46085</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -45703,7 +45703,7 @@
         <v>46085</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -45781,7 +45781,7 @@
         <v>46085</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -45859,7 +45859,7 @@
         <v>46085</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -45937,7 +45937,7 @@
         <v>45070</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -46015,7 +46015,7 @@
         <v>44973</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -46093,7 +46093,7 @@
         <v>44891</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -46166,7 +46166,7 @@
         <v>45616</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -46239,7 +46239,7 @@
         <v>46094</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -46317,7 +46317,7 @@
         <v>44949</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -46390,7 +46390,7 @@
         <v>46097</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -46463,7 +46463,7 @@
         <v>44966</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -46536,7 +46536,7 @@
         <v>44953</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -46614,7 +46614,7 @@
         <v>46099</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -46692,7 +46692,7 @@
         <v>46099</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -46765,7 +46765,7 @@
         <v>46099</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -46843,7 +46843,7 @@
         <v>46099</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -46921,7 +46921,7 @@
         <v>44823</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -46994,7 +46994,7 @@
         <v>45202</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -47067,7 +47067,7 @@
         <v>46099</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -47140,7 +47140,7 @@
         <v>46196</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -47218,7 +47218,7 @@
         <v>45379</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -47291,7 +47291,7 @@
         <v>45428</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -47369,7 +47369,7 @@
         <v>46106</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -47447,7 +47447,7 @@
         <v>45174</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -47525,7 +47525,7 @@
         <v>45770</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -47598,7 +47598,7 @@
         <v>46111</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -47676,7 +47676,7 @@
         <v>45236</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -47754,7 +47754,7 @@
         <v>45236</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -47832,7 +47832,7 @@
         <v>46114</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -47910,7 +47910,7 @@
         <v>46114</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -47988,7 +47988,7 @@
         <v>46114</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -48066,7 +48066,7 @@
         <v>46113</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -48144,7 +48144,7 @@
         <v>45357</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -48217,7 +48217,7 @@
         <v>45243</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -48295,7 +48295,7 @@
         <v>46120</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -48373,7 +48373,7 @@
         <v>46121</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -48451,7 +48451,7 @@
         <v>46122</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -48524,7 +48524,7 @@
         <v>45022</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -48602,7 +48602,7 @@
         <v>46199</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -48675,7 +48675,7 @@
         <v>46125</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -48748,7 +48748,7 @@
         <v>45846</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -48826,7 +48826,7 @@
         <v>44816</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -48899,7 +48899,7 @@
         <v>45314</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -48972,7 +48972,7 @@
         <v>46129</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -49050,7 +49050,7 @@
         <v>46128</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -49123,7 +49123,7 @@
         <v>44820</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -49196,7 +49196,7 @@
         <v>45535</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -49274,7 +49274,7 @@
         <v>45706</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -49347,7 +49347,7 @@
         <v>45250</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -49425,7 +49425,7 @@
         <v>45706</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -49498,7 +49498,7 @@
         <v>45197</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -49571,7 +49571,7 @@
         <v>46134</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -49644,7 +49644,7 @@
         <v>45086</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -49717,7 +49717,7 @@
         <v>46204</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -49790,7 +49790,7 @@
         <v>46203</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -49863,7 +49863,7 @@
         <v>44966</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -49936,7 +49936,7 @@
         <v>44806</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -50014,7 +50014,7 @@
         <v>45740</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -50087,7 +50087,7 @@
         <v>45783</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -50165,7 +50165,7 @@
         <v>45113</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -50238,7 +50238,7 @@
         <v>45719</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -50316,7 +50316,7 @@
         <v>44964</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -50394,7 +50394,7 @@
         <v>46209</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -50467,7 +50467,7 @@
         <v>45420</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -50540,7 +50540,7 @@
         <v>44834</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -50618,7 +50618,7 @@
         <v>45616</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -50691,7 +50691,7 @@
         <v>45258</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -50764,7 +50764,7 @@
         <v>44865</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -50837,7 +50837,7 @@
         <v>44953</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -50910,7 +50910,7 @@
         <v>45617</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -50988,7 +50988,7 @@
         <v>44879</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -51061,7 +51061,7 @@
         <v>45713</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -51139,7 +51139,7 @@
         <v>46212</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -51212,7 +51212,7 @@
         <v>45735</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -51290,7 +51290,7 @@
         <v>46211</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -51363,7 +51363,7 @@
         <v>44862</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -51441,7 +51441,7 @@
         <v>44887</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -51514,7 +51514,7 @@
         <v>44887</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -51587,7 +51587,7 @@
         <v>45426</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -51660,7 +51660,7 @@
         <v>44616</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -51738,7 +51738,7 @@
         <v>46218</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -51816,7 +51816,7 @@
         <v>46218</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -51894,7 +51894,7 @@
         <v>44949</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -51967,7 +51967,7 @@
         <v>44995</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -52045,7 +52045,7 @@
         <v>44813</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -52123,7 +52123,7 @@
         <v>46219</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -52196,7 +52196,7 @@
         <v>46225</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -52269,7 +52269,7 @@
         <v>46226</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -52342,7 +52342,7 @@
         <v>46226</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -52415,7 +52415,7 @@
         <v>46225</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -52488,7 +52488,7 @@
         <v>45142</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -52561,7 +52561,7 @@
         <v>45715</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -52634,7 +52634,7 @@
         <v>44653</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -52707,7 +52707,7 @@
         <v>45645</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -52785,7 +52785,7 @@
         <v>45593</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -52863,7 +52863,7 @@
         <v>44987</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -52936,7 +52936,7 @@
         <v>45555</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -53014,7 +53014,7 @@
         <v>45639</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -53092,7 +53092,7 @@
         <v>45314</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -53165,7 +53165,7 @@
         <v>46232</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -53238,7 +53238,7 @@
         <v>45447</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -53316,7 +53316,7 @@
         <v>44729</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -53389,7 +53389,7 @@
         <v>44844</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -53462,7 +53462,7 @@
         <v>44973</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -53540,7 +53540,7 @@
         <v>45076</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -53618,7 +53618,7 @@
         <v>45095</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -53691,7 +53691,7 @@
         <v>46279</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -53764,7 +53764,7 @@
         <v>45639</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -53842,7 +53842,7 @@
         <v>44526</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -53915,7 +53915,7 @@
         <v>44922</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -53993,7 +53993,7 @@
         <v>46233</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -54066,7 +54066,7 @@
         <v>46279</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -54139,7 +54139,7 @@
         <v>46279</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -54212,7 +54212,7 @@
         <v>44795</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -54290,7 +54290,7 @@
         <v>45260</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -54363,7 +54363,7 @@
         <v>44491</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -54436,7 +54436,7 @@
         <v>45041</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -54514,7 +54514,7 @@
         <v>45257</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -54587,7 +54587,7 @@
         <v>44871</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -54660,7 +54660,7 @@
         <v>45391</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -54733,7 +54733,7 @@
         <v>45692</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -54811,7 +54811,7 @@
         <v>45070</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -54889,7 +54889,7 @@
         <v>45202</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -54962,7 +54962,7 @@
         <v>44966</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -55040,7 +55040,7 @@
         <v>46282</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -55118,7 +55118,7 @@
         <v>45323</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -55196,7 +55196,7 @@
         <v>46282</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -55274,7 +55274,7 @@
         <v>46282</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -55352,7 +55352,7 @@
         <v>46282</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -55430,7 +55430,7 @@
         <v>46282</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -55508,7 +55508,7 @@
         <v>45341</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -55586,7 +55586,7 @@
         <v>46281</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -55659,7 +55659,7 @@
         <v>46282</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -55737,7 +55737,7 @@
         <v>44550</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -55810,7 +55810,7 @@
         <v>45566</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -55888,7 +55888,7 @@
         <v>45566</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -55966,7 +55966,7 @@
         <v>46282</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -56044,7 +56044,7 @@
         <v>46282</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -56122,7 +56122,7 @@
         <v>46282</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -56200,7 +56200,7 @@
         <v>45441</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -56273,7 +56273,7 @@
         <v>45374</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -56351,7 +56351,7 @@
         <v>45391</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -56424,7 +56424,7 @@
         <v>44981</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -56502,7 +56502,7 @@
         <v>44679</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -56580,7 +56580,7 @@
         <v>45293</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -56653,7 +56653,7 @@
         <v>45554</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -56726,7 +56726,7 @@
         <v>45214</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -56799,7 +56799,7 @@
         <v>45110</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -56872,7 +56872,7 @@
         <v>45660</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -56950,7 +56950,7 @@
         <v>46286</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -57028,7 +57028,7 @@
         <v>45735</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -57106,7 +57106,7 @@
         <v>45516</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -57184,7 +57184,7 @@
         <v>44966</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -57262,7 +57262,7 @@
         <v>45078</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -57335,7 +57335,7 @@
         <v>45113</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -57408,7 +57408,7 @@
         <v>45191</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -57481,7 +57481,7 @@
         <v>45763</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -57554,7 +57554,7 @@
         <v>44551</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -57627,7 +57627,7 @@
         <v>44833</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -57705,7 +57705,7 @@
         <v>45103</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -57778,7 +57778,7 @@
         <v>45863</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -57851,7 +57851,7 @@
         <v>45618</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -57924,7 +57924,7 @@
         <v>45639</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -58002,7 +58002,7 @@
         <v>45299</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -58075,7 +58075,7 @@
         <v>45301</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -58153,7 +58153,7 @@
         <v>44714</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -58226,7 +58226,7 @@
         <v>45870</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -58299,7 +58299,7 @@
         <v>44622</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -58372,7 +58372,7 @@
         <v>45232</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -58450,7 +58450,7 @@
         <v>44887</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -58523,7 +58523,7 @@
         <v>45422</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -58596,7 +58596,7 @@
         <v>44622</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -58669,7 +58669,7 @@
         <v>45191</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -58742,7 +58742,7 @@
         <v>44595</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -58815,7 +58815,7 @@
         <v>44589</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -58888,7 +58888,7 @@
         <v>45308</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -58961,7 +58961,7 @@
         <v>44922</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -59039,7 +59039,7 @@
         <v>45615</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -59117,7 +59117,7 @@
         <v>46295</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -59195,7 +59195,7 @@
         <v>46295</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -59273,7 +59273,7 @@
         <v>45149</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -59346,7 +59346,7 @@
         <v>45762</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -59419,7 +59419,7 @@
         <v>44817</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -59492,7 +59492,7 @@
         <v>45149</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -59565,7 +59565,7 @@
         <v>45622</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -59638,7 +59638,7 @@
         <v>45554</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -59711,7 +59711,7 @@
         <v>45095</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -59784,7 +59784,7 @@
         <v>45593</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -59862,7 +59862,7 @@
         <v>45275</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -59935,7 +59935,7 @@
         <v>44564</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -60008,7 +60008,7 @@
         <v>45744</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -60086,7 +60086,7 @@
         <v>46255</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -60164,7 +60164,7 @@
         <v>45407</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -60237,7 +60237,7 @@
         <v>45071</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -60315,7 +60315,7 @@
         <v>45257</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -60393,7 +60393,7 @@
         <v>45257</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -60466,7 +60466,7 @@
         <v>45566</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -60544,7 +60544,7 @@
         <v>46300</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -60617,7 +60617,7 @@
         <v>45566</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -60695,7 +60695,7 @@
         <v>45566</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -60773,7 +60773,7 @@
         <v>45735</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -60851,7 +60851,7 @@
         <v>45736</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -60929,7 +60929,7 @@
         <v>45642</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -61002,7 +61002,7 @@
         <v>45530</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -61075,7 +61075,7 @@
         <v>46258</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -61153,7 +61153,7 @@
         <v>45530</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -61226,7 +61226,7 @@
         <v>45371</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -61304,7 +61304,7 @@
         <v>46258</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -61382,7 +61382,7 @@
         <v>46302</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -61455,7 +61455,7 @@
         <v>45727</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -61528,7 +61528,7 @@
         <v>45267</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -61606,7 +61606,7 @@
         <v>46307</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -61679,7 +61679,7 @@
         <v>45797</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -61752,7 +61752,7 @@
         <v>45797</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -61830,7 +61830,7 @@
         <v>45796</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -61908,7 +61908,7 @@
         <v>46304</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -61981,7 +61981,7 @@
         <v>46304</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -62054,7 +62054,7 @@
         <v>46307</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -62127,7 +62127,7 @@
         <v>46304</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -62200,7 +62200,7 @@
         <v>45797</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -62273,7 +62273,7 @@
         <v>45796</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -62351,7 +62351,7 @@
         <v>45702</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -62429,7 +62429,7 @@
         <v>46209</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -62502,7 +62502,7 @@
         <v>46304</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -62575,7 +62575,7 @@
         <v>45316</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -62653,7 +62653,7 @@
         <v>46160</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -62726,7 +62726,7 @@
         <v>46308</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -62799,7 +62799,7 @@
         <v>46308</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -62877,7 +62877,7 @@
         <v>46308</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -62955,7 +62955,7 @@
         <v>46308</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -63028,7 +63028,7 @@
         <v>45800</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -63106,7 +63106,7 @@
         <v>46308</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -63179,7 +63179,7 @@
         <v>45800</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -63257,7 +63257,7 @@
         <v>45800</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -63335,7 +63335,7 @@
         <v>45800</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -63413,7 +63413,7 @@
         <v>46308</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -63491,7 +63491,7 @@
         <v>46308</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -63564,7 +63564,7 @@
         <v>46308</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -63637,7 +63637,7 @@
         <v>46308</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -63710,7 +63710,7 @@
         <v>46308</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -63783,7 +63783,7 @@
         <v>46308</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -63856,7 +63856,7 @@
         <v>46269</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -63929,7 +63929,7 @@
         <v>45812</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -64007,7 +64007,7 @@
         <v>45812</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -64085,7 +64085,7 @@
         <v>46269</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -64158,7 +64158,7 @@
         <v>46269</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
@@ -64231,7 +64231,7 @@
         <v>45639</v>
       </c>
       <c r="E802" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -64309,7 +64309,7 @@
         <v>46269</v>
       </c>
       <c r="E803" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
@@ -64382,7 +64382,7 @@
         <v>45819</v>
       </c>
       <c r="E804" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
@@ -64460,7 +64460,7 @@
         <v>45819</v>
       </c>
       <c r="E805" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>
@@ -64538,7 +64538,7 @@
         <v>45824</v>
       </c>
       <c r="E806" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F806" t="inlineStr">
         <is>
@@ -64616,7 +64616,7 @@
         <v>45824</v>
       </c>
       <c r="E807" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F807" t="inlineStr">
         <is>
@@ -64694,7 +64694,7 @@
         <v>45824</v>
       </c>
       <c r="E808" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F808" t="inlineStr">
         <is>
@@ -64772,7 +64772,7 @@
         <v>46269</v>
       </c>
       <c r="E809" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F809" t="inlineStr">
         <is>
@@ -64845,7 +64845,7 @@
         <v>45824</v>
       </c>
       <c r="E810" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F810" t="inlineStr">
         <is>
@@ -64923,7 +64923,7 @@
         <v>45835</v>
       </c>
       <c r="E811" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F811" t="inlineStr">
         <is>
@@ -65001,7 +65001,7 @@
         <v>45840</v>
       </c>
       <c r="E812" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F812" t="inlineStr">
         <is>
@@ -65079,7 +65079,7 @@
         <v>45845</v>
       </c>
       <c r="E813" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F813" t="inlineStr">
         <is>
@@ -65157,7 +65157,7 @@
         <v>45776</v>
       </c>
       <c r="E814" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F814" t="inlineStr">
         <is>
@@ -65230,7 +65230,7 @@
         <v>45854</v>
       </c>
       <c r="E815" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F815" t="inlineStr">
         <is>
@@ -65303,7 +65303,7 @@
         <v>45854</v>
       </c>
       <c r="E816" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F816" t="inlineStr">
         <is>
@@ -65376,7 +65376,7 @@
         <v>45853</v>
       </c>
       <c r="E817" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F817" t="inlineStr">
         <is>
@@ -65449,7 +65449,7 @@
         <v>45855</v>
       </c>
       <c r="E818" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F818" t="inlineStr">
         <is>
@@ -65522,7 +65522,7 @@
         <v>45523</v>
       </c>
       <c r="E819" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F819" t="inlineStr">
         <is>
@@ -65595,7 +65595,7 @@
         <v>45831</v>
       </c>
       <c r="E820" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F820" t="inlineStr">
         <is>
@@ -65668,7 +65668,7 @@
         <v>45820</v>
       </c>
       <c r="E821" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F821" t="inlineStr">
         <is>
@@ -65746,7 +65746,7 @@
         <v>45870</v>
       </c>
       <c r="E822" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F822" t="inlineStr">
         <is>
@@ -65819,7 +65819,7 @@
         <v>45709</v>
       </c>
       <c r="E823" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F823" t="inlineStr">
         <is>
@@ -65897,7 +65897,7 @@
         <v>45880</v>
       </c>
       <c r="E824" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F824" t="inlineStr">
         <is>
@@ -65975,7 +65975,7 @@
         <v>45880</v>
       </c>
       <c r="E825" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F825" t="inlineStr">
         <is>
@@ -66053,7 +66053,7 @@
         <v>45881</v>
       </c>
       <c r="E826" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F826" t="inlineStr">
         <is>
@@ -66131,7 +66131,7 @@
         <v>45644</v>
       </c>
       <c r="E827" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F827" t="inlineStr">
         <is>
@@ -66204,7 +66204,7 @@
         <v>45428</v>
       </c>
       <c r="E828" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F828" t="inlineStr">
         <is>
@@ -66277,7 +66277,7 @@
         <v>45429</v>
       </c>
       <c r="E829" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F829" t="inlineStr">
         <is>
@@ -66350,7 +66350,7 @@
         <v>45250</v>
       </c>
       <c r="E830" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F830" t="inlineStr">
         <is>
@@ -66428,7 +66428,7 @@
         <v>46188</v>
       </c>
       <c r="E831" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F831" t="inlineStr">
         <is>
@@ -66506,7 +66506,7 @@
         <v>46258</v>
       </c>
       <c r="E832" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F832" t="inlineStr">
         <is>

--- a/Översikt FINSPÅNG.xlsx
+++ b/Översikt FINSPÅNG.xlsx
@@ -601,7 +601,7 @@
         <v>46244</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -727,7 +727,7 @@
         <v>45945</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -858,7 +858,7 @@
         <v>45134</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
         <v>44896</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1121,7 +1121,7 @@
         <v>45210</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1247,7 +1247,7 @@
         <v>44888</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1369,7 +1369,7 @@
         <v>44777</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1488,7 +1488,7 @@
         <v>44897</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1607,7 +1607,7 @@
         <v>44910</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1734,7 +1734,7 @@
         <v>45322</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1855,7 +1855,7 @@
         <v>44624</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1971,7 +1971,7 @@
         <v>44599</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2082,7 +2082,7 @@
         <v>45891</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2198,7 +2198,7 @@
         <v>45421</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2318,7 +2318,7 @@
         <v>45238</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2433,7 +2433,7 @@
         <v>45898</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2548,7 +2548,7 @@
         <v>45267</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2663,7 +2663,7 @@
         <v>45679</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2782,7 +2782,7 @@
         <v>45812</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2896,7 +2896,7 @@
         <v>44791</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3010,7 +3010,7 @@
         <v>44665</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3123,7 +3123,7 @@
         <v>46307</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3235,7 +3235,7 @@
         <v>45681</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3352,7 +3352,7 @@
         <v>45819</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3468,7 +3468,7 @@
         <v>46196</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3580,7 +3580,7 @@
         <v>45602</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3692,7 +3692,7 @@
         <v>45800</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3804,7 +3804,7 @@
         <v>45082</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3916,7 +3916,7 @@
         <v>44774</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4028,7 +4028,7 @@
         <v>44690</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4139,7 +4139,7 @@
         <v>45894</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4254,7 +4254,7 @@
         <v>44816</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4360,7 +4360,7 @@
         <v>45905</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4471,7 +4471,7 @@
         <v>46174</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4582,7 +4582,7 @@
         <v>45425</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4688,7 +4688,7 @@
         <v>45121</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4803,7 +4803,7 @@
         <v>44903</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4913,7 +4913,7 @@
         <v>46181</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5024,7 +5024,7 @@
         <v>46181</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5135,7 +5135,7 @@
         <v>45950</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5246,7 +5246,7 @@
         <v>45477</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5361,7 +5361,7 @@
         <v>44981</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5472,7 +5472,7 @@
         <v>45644</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5578,7 +5578,7 @@
         <v>45441</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5689,7 +5689,7 @@
         <v>45235</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5800,7 +5800,7 @@
         <v>44683</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5910,7 +5910,7 @@
         <v>44776</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6015,7 +6015,7 @@
         <v>44504</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6125,7 +6125,7 @@
         <v>44529</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6230,7 +6230,7 @@
         <v>44930</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6340,7 +6340,7 @@
         <v>45232</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6450,7 +6450,7 @@
         <v>45905</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6560,7 +6560,7 @@
         <v>45883</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6670,7 +6670,7 @@
         <v>45636</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6775,7 +6775,7 @@
         <v>44622</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6880,7 +6880,7 @@
         <v>44915</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6990,7 +6990,7 @@
         <v>45082</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7100,7 +7100,7 @@
         <v>45744</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7214,7 +7214,7 @@
         <v>45446</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7319,7 +7319,7 @@
         <v>46189</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7424,7 +7424,7 @@
         <v>45567</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7538,7 +7538,7 @@
         <v>46181</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7648,7 +7648,7 @@
         <v>46058</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7762,7 +7762,7 @@
         <v>45846</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7872,7 +7872,7 @@
         <v>45845</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7982,7 +7982,7 @@
         <v>46258</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8092,7 +8092,7 @@
         <v>46258</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8206,7 +8206,7 @@
         <v>46129</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8320,7 +8320,7 @@
         <v>45880</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8430,7 +8430,7 @@
         <v>44915</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8540,7 +8540,7 @@
         <v>46043</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8654,7 +8654,7 @@
         <v>45447</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8764,7 +8764,7 @@
         <v>45566</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8878,7 +8878,7 @@
         <v>44599</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8988,7 +8988,7 @@
         <v>44992</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9098,7 +9098,7 @@
         <v>44897</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9212,7 +9212,7 @@
         <v>46318</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9317,7 +9317,7 @@
         <v>46318</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9426,7 +9426,7 @@
         <v>46155</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9540,7 +9540,7 @@
         <v>45328</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9649,7 +9649,7 @@
         <v>45615</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9763,7 +9763,7 @@
         <v>44817</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9873,7 +9873,7 @@
         <v>45070</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9983,7 +9983,7 @@
         <v>44965</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10097,7 +10097,7 @@
         <v>45149</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10206,7 +10206,7 @@
         <v>45229</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10316,7 +10316,7 @@
         <v>45302</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10425,7 +10425,7 @@
         <v>45555</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10539,7 +10539,7 @@
         <v>44501</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10649,7 +10649,7 @@
         <v>44711</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10759,7 +10759,7 @@
         <v>45428</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10864,7 +10864,7 @@
         <v>46107</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10974,7 +10974,7 @@
         <v>46188</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11088,7 +11088,7 @@
         <v>44675</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11161,7 +11161,7 @@
         <v>44676</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11239,7 +11239,7 @@
         <v>44536</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11317,7 +11317,7 @@
         <v>44864</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11390,7 +11390,7 @@
         <v>44600</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11463,7 +11463,7 @@
         <v>44824</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11536,7 +11536,7 @@
         <v>44799</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11609,7 +11609,7 @@
         <v>44795</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11682,7 +11682,7 @@
         <v>44856</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11755,7 +11755,7 @@
         <v>44578</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11833,7 +11833,7 @@
         <v>44675</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -11906,7 +11906,7 @@
         <v>44852</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -11984,7 +11984,7 @@
         <v>44601</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12062,7 +12062,7 @@
         <v>44601</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12135,7 +12135,7 @@
         <v>44551</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12208,7 +12208,7 @@
         <v>44525</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12281,7 +12281,7 @@
         <v>44574</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12359,7 +12359,7 @@
         <v>44588</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12437,7 +12437,7 @@
         <v>44574</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12510,7 +12510,7 @@
         <v>44889</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12583,7 +12583,7 @@
         <v>44627</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -12656,7 +12656,7 @@
         <v>44525</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -12734,7 +12734,7 @@
         <v>44503</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -12812,7 +12812,7 @@
         <v>44503</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -12885,7 +12885,7 @@
         <v>44874</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -12958,7 +12958,7 @@
         <v>44502</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13036,7 +13036,7 @@
         <v>44551</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -13109,7 +13109,7 @@
         <v>44712</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -13187,7 +13187,7 @@
         <v>44581</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -13260,7 +13260,7 @@
         <v>44833</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -13333,7 +13333,7 @@
         <v>44601</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -13406,7 +13406,7 @@
         <v>44859</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -13479,7 +13479,7 @@
         <v>44672</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -13552,7 +13552,7 @@
         <v>44735</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -13625,7 +13625,7 @@
         <v>44796</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -13698,7 +13698,7 @@
         <v>44782</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -13771,7 +13771,7 @@
         <v>44741</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -13844,7 +13844,7 @@
         <v>44859</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -13917,7 +13917,7 @@
         <v>44613</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -13995,7 +13995,7 @@
         <v>44678</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -14068,7 +14068,7 @@
         <v>44855</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -14146,7 +14146,7 @@
         <v>44887</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -14219,7 +14219,7 @@
         <v>44860</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -14292,7 +14292,7 @@
         <v>44753</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -14365,7 +14365,7 @@
         <v>44802</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -14438,7 +14438,7 @@
         <v>44781</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -14511,7 +14511,7 @@
         <v>44541</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -14584,7 +14584,7 @@
         <v>44564</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -14657,7 +14657,7 @@
         <v>44859</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -14730,7 +14730,7 @@
         <v>44595</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -14803,7 +14803,7 @@
         <v>44582</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -14876,7 +14876,7 @@
         <v>44816</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -14949,7 +14949,7 @@
         <v>44508</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -15022,7 +15022,7 @@
         <v>44656</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -15095,7 +15095,7 @@
         <v>44627</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -15168,7 +15168,7 @@
         <v>44587</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -15241,7 +15241,7 @@
         <v>44820</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -15314,7 +15314,7 @@
         <v>44532</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -15387,7 +15387,7 @@
         <v>44552</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -15460,7 +15460,7 @@
         <v>44879</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -15533,7 +15533,7 @@
         <v>44581</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -15606,7 +15606,7 @@
         <v>44588</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -15684,7 +15684,7 @@
         <v>44875</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -15757,7 +15757,7 @@
         <v>44743</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -15830,7 +15830,7 @@
         <v>44831</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -15908,7 +15908,7 @@
         <v>44819</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -15981,7 +15981,7 @@
         <v>44581</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -16059,7 +16059,7 @@
         <v>44630</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -16132,7 +16132,7 @@
         <v>44601</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -16205,7 +16205,7 @@
         <v>44742</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -16283,7 +16283,7 @@
         <v>44859</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -16356,7 +16356,7 @@
         <v>44600</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -16429,7 +16429,7 @@
         <v>44635</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -16502,7 +16502,7 @@
         <v>44776</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -16575,7 +16575,7 @@
         <v>44713</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -16653,7 +16653,7 @@
         <v>44697</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -16731,7 +16731,7 @@
         <v>44533</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -16804,7 +16804,7 @@
         <v>44601</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -16877,7 +16877,7 @@
         <v>44678</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -16950,7 +16950,7 @@
         <v>44704</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -17023,7 +17023,7 @@
         <v>44564</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -17096,7 +17096,7 @@
         <v>44642</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -17169,7 +17169,7 @@
         <v>45883</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -17247,7 +17247,7 @@
         <v>44659</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -17325,7 +17325,7 @@
         <v>45888</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -17403,7 +17403,7 @@
         <v>44508</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -17476,7 +17476,7 @@
         <v>45621</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -17554,7 +17554,7 @@
         <v>44662</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -17632,7 +17632,7 @@
         <v>45617</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -17710,7 +17710,7 @@
         <v>45618</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -17783,7 +17783,7 @@
         <v>44754</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -17856,7 +17856,7 @@
         <v>45555</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -17934,7 +17934,7 @@
         <v>44802</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -18007,7 +18007,7 @@
         <v>45042</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -18080,7 +18080,7 @@
         <v>44918</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -18158,7 +18158,7 @@
         <v>45330</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -18231,7 +18231,7 @@
         <v>44778</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -18304,7 +18304,7 @@
         <v>45891</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -18382,7 +18382,7 @@
         <v>45707</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -18460,7 +18460,7 @@
         <v>45622</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -18533,7 +18533,7 @@
         <v>45894</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -18611,7 +18611,7 @@
         <v>45896</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -18689,7 +18689,7 @@
         <v>45895</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -18762,7 +18762,7 @@
         <v>44930</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -18840,7 +18840,7 @@
         <v>45258</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -18913,7 +18913,7 @@
         <v>45379</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -18986,7 +18986,7 @@
         <v>45898</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -19059,7 +19059,7 @@
         <v>44833</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -19137,7 +19137,7 @@
         <v>45535</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -19215,7 +19215,7 @@
         <v>44770</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -19288,7 +19288,7 @@
         <v>45260</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -19361,7 +19361,7 @@
         <v>45257</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -19439,7 +19439,7 @@
         <v>45257</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -19512,7 +19512,7 @@
         <v>45541</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -19590,7 +19590,7 @@
         <v>45021</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -19663,7 +19663,7 @@
         <v>45362</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -19736,7 +19736,7 @@
         <v>45167</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -19809,7 +19809,7 @@
         <v>45008</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -19882,7 +19882,7 @@
         <v>45374</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -19960,7 +19960,7 @@
         <v>44930</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -20033,7 +20033,7 @@
         <v>44930</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -20106,7 +20106,7 @@
         <v>45903</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -20184,7 +20184,7 @@
         <v>44844</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -20257,7 +20257,7 @@
         <v>44616</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -20335,7 +20335,7 @@
         <v>45903</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -20413,7 +20413,7 @@
         <v>45904</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -20491,7 +20491,7 @@
         <v>45903</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -20569,7 +20569,7 @@
         <v>45903</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -20647,7 +20647,7 @@
         <v>45904</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -20725,7 +20725,7 @@
         <v>45903</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -20803,7 +20803,7 @@
         <v>45908</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -20876,7 +20876,7 @@
         <v>44550</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -20949,7 +20949,7 @@
         <v>45905</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -21027,7 +21027,7 @@
         <v>45230</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -21100,7 +21100,7 @@
         <v>45905</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -21178,7 +21178,7 @@
         <v>46077</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -21256,7 +21256,7 @@
         <v>45554</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -21329,7 +21329,7 @@
         <v>45095</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -21407,7 +21407,7 @@
         <v>45055</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -21480,7 +21480,7 @@
         <v>45095</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -21553,7 +21553,7 @@
         <v>45425</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -21626,7 +21626,7 @@
         <v>44817</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -21699,7 +21699,7 @@
         <v>44898</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -21772,7 +21772,7 @@
         <v>45924</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -21845,7 +21845,7 @@
         <v>45177</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -21918,7 +21918,7 @@
         <v>44806</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -21996,7 +21996,7 @@
         <v>45456</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -22074,7 +22074,7 @@
         <v>44865</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -22152,7 +22152,7 @@
         <v>44980</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -22225,7 +22225,7 @@
         <v>44966</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -22303,7 +22303,7 @@
         <v>45931</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -22376,7 +22376,7 @@
         <v>45357</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -22449,7 +22449,7 @@
         <v>44914</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -22522,7 +22522,7 @@
         <v>45935</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -22600,7 +22600,7 @@
         <v>46176</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -22673,7 +22673,7 @@
         <v>46176</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -22746,7 +22746,7 @@
         <v>44974</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -22819,7 +22819,7 @@
         <v>44816</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -22892,7 +22892,7 @@
         <v>44950</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -22970,7 +22970,7 @@
         <v>45846</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -23048,7 +23048,7 @@
         <v>45744</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -23126,7 +23126,7 @@
         <v>45744</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -23204,7 +23204,7 @@
         <v>45601</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -23277,7 +23277,7 @@
         <v>45323</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -23355,7 +23355,7 @@
         <v>46176</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -23428,7 +23428,7 @@
         <v>45181</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -23501,7 +23501,7 @@
         <v>45042</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -23579,7 +23579,7 @@
         <v>46174</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -23657,7 +23657,7 @@
         <v>45257</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -23735,7 +23735,7 @@
         <v>45225</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -23808,7 +23808,7 @@
         <v>46174</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -23886,7 +23886,7 @@
         <v>45252</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -23959,7 +23959,7 @@
         <v>45944</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -24032,7 +24032,7 @@
         <v>46177</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -24105,7 +24105,7 @@
         <v>45082</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -24183,7 +24183,7 @@
         <v>45149</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -24256,7 +24256,7 @@
         <v>44887</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -24329,7 +24329,7 @@
         <v>44953</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -24402,7 +24402,7 @@
         <v>45447</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -24480,7 +24480,7 @@
         <v>45442</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -24553,7 +24553,7 @@
         <v>44767</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -24626,7 +24626,7 @@
         <v>46181</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -24704,7 +24704,7 @@
         <v>44986</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -24777,7 +24777,7 @@
         <v>44957</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -24850,7 +24850,7 @@
         <v>46178</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -24923,7 +24923,7 @@
         <v>46178</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -24996,7 +24996,7 @@
         <v>46178</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -25069,7 +25069,7 @@
         <v>45950</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -25147,7 +25147,7 @@
         <v>44993</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -25220,7 +25220,7 @@
         <v>44987</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -25293,7 +25293,7 @@
         <v>45247</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -25366,7 +25366,7 @@
         <v>45422</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -25439,7 +25439,7 @@
         <v>45214</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -25512,7 +25512,7 @@
         <v>45421</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -25590,7 +25590,7 @@
         <v>45420</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -25663,7 +25663,7 @@
         <v>45125</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -25741,7 +25741,7 @@
         <v>45033</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -25819,7 +25819,7 @@
         <v>45103</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -25892,7 +25892,7 @@
         <v>45688</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -25970,7 +25970,7 @@
         <v>45955</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -26043,7 +26043,7 @@
         <v>46185</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -26116,7 +26116,7 @@
         <v>45022</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -26194,7 +26194,7 @@
         <v>45744</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -26272,7 +26272,7 @@
         <v>45267</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -26350,7 +26350,7 @@
         <v>45202</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -26423,7 +26423,7 @@
         <v>45118</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -26496,7 +26496,7 @@
         <v>46185</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -26569,7 +26569,7 @@
         <v>45258</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -26642,7 +26642,7 @@
         <v>45225</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -26715,7 +26715,7 @@
         <v>44900</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -26788,7 +26788,7 @@
         <v>46188</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -26861,7 +26861,7 @@
         <v>45258</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -26934,7 +26934,7 @@
         <v>45260</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -27007,7 +27007,7 @@
         <v>45191</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -27080,7 +27080,7 @@
         <v>45178</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -27153,7 +27153,7 @@
         <v>45177</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -27226,7 +27226,7 @@
         <v>45623</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -27304,7 +27304,7 @@
         <v>45639</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -27382,7 +27382,7 @@
         <v>45197</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -27455,7 +27455,7 @@
         <v>45264</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -27533,7 +27533,7 @@
         <v>45969</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -27606,7 +27606,7 @@
         <v>45971</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -27679,7 +27679,7 @@
         <v>45110</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -27752,7 +27752,7 @@
         <v>45250</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -27825,7 +27825,7 @@
         <v>45593</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -27903,7 +27903,7 @@
         <v>46196</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -27981,7 +27981,7 @@
         <v>44942</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -28054,7 +28054,7 @@
         <v>45846</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -28132,7 +28132,7 @@
         <v>46199</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -28205,7 +28205,7 @@
         <v>44617</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -28278,7 +28278,7 @@
         <v>45979</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -28351,7 +28351,7 @@
         <v>46203</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -28424,7 +28424,7 @@
         <v>44939</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -28497,7 +28497,7 @@
         <v>45202</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -28570,7 +28570,7 @@
         <v>45082</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -28648,7 +28648,7 @@
         <v>45323</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -28726,7 +28726,7 @@
         <v>45299</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -28799,7 +28799,7 @@
         <v>45983</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -28872,7 +28872,7 @@
         <v>45983</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -28945,7 +28945,7 @@
         <v>46204</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -29018,7 +29018,7 @@
         <v>45250</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -29096,7 +29096,7 @@
         <v>45206</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -29169,7 +29169,7 @@
         <v>45986</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -29242,7 +29242,7 @@
         <v>44891</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -29315,7 +29315,7 @@
         <v>45983</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -29388,7 +29388,7 @@
         <v>45986</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -29461,7 +29461,7 @@
         <v>45985</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -29534,7 +29534,7 @@
         <v>44964</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -29612,7 +29612,7 @@
         <v>46209</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -29685,7 +29685,7 @@
         <v>45607</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -29758,7 +29758,7 @@
         <v>45607</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -29831,7 +29831,7 @@
         <v>46211</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -29904,7 +29904,7 @@
         <v>46212</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -29977,7 +29977,7 @@
         <v>45770</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -30050,7 +30050,7 @@
         <v>45749</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -30128,7 +30128,7 @@
         <v>45551</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -30201,7 +30201,7 @@
         <v>45639</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -30279,7 +30279,7 @@
         <v>45709</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -30357,7 +30357,7 @@
         <v>45097</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -30430,7 +30430,7 @@
         <v>45095</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -30503,7 +30503,7 @@
         <v>45566</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -30581,7 +30581,7 @@
         <v>45566</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -30659,7 +30659,7 @@
         <v>45463</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -30732,7 +30732,7 @@
         <v>45740</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -30810,7 +30810,7 @@
         <v>46218</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -30888,7 +30888,7 @@
         <v>46000</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -30966,7 +30966,7 @@
         <v>45103</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -31039,7 +31039,7 @@
         <v>45232</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -31117,7 +31117,7 @@
         <v>46218</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -31195,7 +31195,7 @@
         <v>46219</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -31268,7 +31268,7 @@
         <v>45609</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -31346,7 +31346,7 @@
         <v>46002</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -31424,7 +31424,7 @@
         <v>46002</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -31502,7 +31502,7 @@
         <v>45566</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -31580,7 +31580,7 @@
         <v>45566</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -31658,7 +31658,7 @@
         <v>45566</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -31736,7 +31736,7 @@
         <v>46002</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -31814,7 +31814,7 @@
         <v>45735</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -31892,7 +31892,7 @@
         <v>46002</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -31970,7 +31970,7 @@
         <v>45736</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -32048,7 +32048,7 @@
         <v>46006</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -32126,7 +32126,7 @@
         <v>46006</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -32204,7 +32204,7 @@
         <v>46226</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -32277,7 +32277,7 @@
         <v>46003</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -32350,7 +32350,7 @@
         <v>46226</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -32423,7 +32423,7 @@
         <v>46225</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -32496,7 +32496,7 @@
         <v>46225</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -32569,7 +32569,7 @@
         <v>46006</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -32642,7 +32642,7 @@
         <v>45530</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -32715,7 +32715,7 @@
         <v>46232</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -32788,7 +32788,7 @@
         <v>46233</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -32861,7 +32861,7 @@
         <v>46279</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -32934,7 +32934,7 @@
         <v>46279</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -33007,7 +33007,7 @@
         <v>45642</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -33080,7 +33080,7 @@
         <v>46279</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -33153,7 +33153,7 @@
         <v>45267</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -33231,7 +33231,7 @@
         <v>45530</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -33304,7 +33304,7 @@
         <v>45727</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -33377,7 +33377,7 @@
         <v>45371</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -33455,7 +33455,7 @@
         <v>46282</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -33533,7 +33533,7 @@
         <v>46282</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -33611,7 +33611,7 @@
         <v>46282</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -33689,7 +33689,7 @@
         <v>46282</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -33767,7 +33767,7 @@
         <v>46282</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -33845,7 +33845,7 @@
         <v>46282</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -33923,7 +33923,7 @@
         <v>45853</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -33996,7 +33996,7 @@
         <v>46282</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -34074,7 +34074,7 @@
         <v>46030</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -34152,7 +34152,7 @@
         <v>46282</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -34230,7 +34230,7 @@
         <v>46030</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -34308,7 +34308,7 @@
         <v>46282</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -34386,7 +34386,7 @@
         <v>46029</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -34459,7 +34459,7 @@
         <v>46031</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -34537,7 +34537,7 @@
         <v>46281</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -34610,7 +34610,7 @@
         <v>46034</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -34688,7 +34688,7 @@
         <v>46034</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -34766,7 +34766,7 @@
         <v>46034</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -34844,7 +34844,7 @@
         <v>46036</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -34922,7 +34922,7 @@
         <v>46036</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -35000,7 +35000,7 @@
         <v>45796</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -35078,7 +35078,7 @@
         <v>46286</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -35156,7 +35156,7 @@
         <v>45796</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -35234,7 +35234,7 @@
         <v>46040</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -35307,7 +35307,7 @@
         <v>45863</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -35380,7 +35380,7 @@
         <v>46040</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -35453,7 +35453,7 @@
         <v>45316</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -35531,7 +35531,7 @@
         <v>45797</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -35604,7 +35604,7 @@
         <v>45797</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -35677,7 +35677,7 @@
         <v>45797</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -35755,7 +35755,7 @@
         <v>45702</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -35833,7 +35833,7 @@
         <v>46048</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -35911,7 +35911,7 @@
         <v>46048</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -35989,7 +35989,7 @@
         <v>45800</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -36067,7 +36067,7 @@
         <v>46048</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -36145,7 +36145,7 @@
         <v>45800</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -36223,7 +36223,7 @@
         <v>46050</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -36301,7 +36301,7 @@
         <v>45800</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -36379,7 +36379,7 @@
         <v>45800</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -36457,7 +36457,7 @@
         <v>46050</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -36535,7 +36535,7 @@
         <v>46049</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -36608,7 +36608,7 @@
         <v>46052</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -36681,7 +36681,7 @@
         <v>45293</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -36759,7 +36759,7 @@
         <v>46055</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -36837,7 +36837,7 @@
         <v>44860</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -36910,7 +36910,7 @@
         <v>46058</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -36988,7 +36988,7 @@
         <v>45328</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -37061,7 +37061,7 @@
         <v>46058</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -37139,7 +37139,7 @@
         <v>46058</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -37217,7 +37217,7 @@
         <v>46060</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -37290,7 +37290,7 @@
         <v>46058</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -37368,7 +37368,7 @@
         <v>46064</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -37446,7 +37446,7 @@
         <v>45812</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -37524,7 +37524,7 @@
         <v>46064</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -37602,7 +37602,7 @@
         <v>46064</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -37680,7 +37680,7 @@
         <v>45812</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -37758,7 +37758,7 @@
         <v>46063</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -37836,7 +37836,7 @@
         <v>46064</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -37914,7 +37914,7 @@
         <v>46063</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -37992,7 +37992,7 @@
         <v>46064</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -38070,7 +38070,7 @@
         <v>46064</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -38148,7 +38148,7 @@
         <v>45870</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -38221,7 +38221,7 @@
         <v>46065</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -38299,7 +38299,7 @@
         <v>45639</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -38377,7 +38377,7 @@
         <v>46065</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -38455,7 +38455,7 @@
         <v>46069</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -38533,7 +38533,7 @@
         <v>46070</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -38611,7 +38611,7 @@
         <v>46070</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -38689,7 +38689,7 @@
         <v>45819</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -38767,7 +38767,7 @@
         <v>45819</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -38845,7 +38845,7 @@
         <v>45467</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -38918,7 +38918,7 @@
         <v>45824</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -38996,7 +38996,7 @@
         <v>46073</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -39074,7 +39074,7 @@
         <v>45824</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -39152,7 +39152,7 @@
         <v>46076</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -39230,7 +39230,7 @@
         <v>46076</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -39308,7 +39308,7 @@
         <v>45824</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -39386,7 +39386,7 @@
         <v>45824</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -39464,7 +39464,7 @@
         <v>46078</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -39542,7 +39542,7 @@
         <v>46079</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -39620,7 +39620,7 @@
         <v>46080</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -39698,7 +39698,7 @@
         <v>46295</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -39776,7 +39776,7 @@
         <v>46295</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -39854,7 +39854,7 @@
         <v>46080</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -39932,7 +39932,7 @@
         <v>46080</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -40010,7 +40010,7 @@
         <v>46080</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -40088,7 +40088,7 @@
         <v>46085</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -40166,7 +40166,7 @@
         <v>46085</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -40244,7 +40244,7 @@
         <v>46085</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -40322,7 +40322,7 @@
         <v>46085</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -40400,7 +40400,7 @@
         <v>45835</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -40478,7 +40478,7 @@
         <v>45840</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -40556,7 +40556,7 @@
         <v>46094</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -40634,7 +40634,7 @@
         <v>46097</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -40707,7 +40707,7 @@
         <v>46099</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -40780,7 +40780,7 @@
         <v>46099</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -40853,7 +40853,7 @@
         <v>46255</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -40931,7 +40931,7 @@
         <v>46099</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -41009,7 +41009,7 @@
         <v>46099</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -41087,7 +41087,7 @@
         <v>46099</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -41165,7 +41165,7 @@
         <v>45845</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -41243,7 +41243,7 @@
         <v>46302</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -41316,7 +41316,7 @@
         <v>45776</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -41389,7 +41389,7 @@
         <v>46106</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -41467,7 +41467,7 @@
         <v>45853</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -41540,7 +41540,7 @@
         <v>46258</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -41618,7 +41618,7 @@
         <v>46258</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -41696,7 +41696,7 @@
         <v>45337</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -41769,7 +41769,7 @@
         <v>45854</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -41842,7 +41842,7 @@
         <v>45855</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -41915,7 +41915,7 @@
         <v>45854</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -41988,7 +41988,7 @@
         <v>45523</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -42061,7 +42061,7 @@
         <v>46300</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -42134,7 +42134,7 @@
         <v>46111</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -42212,7 +42212,7 @@
         <v>45831</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -42285,7 +42285,7 @@
         <v>46304</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -42358,7 +42358,7 @@
         <v>45428</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -42436,7 +42436,7 @@
         <v>45428</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -42514,7 +42514,7 @@
         <v>46113</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -42592,7 +42592,7 @@
         <v>45280</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -42670,7 +42670,7 @@
         <v>46114</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -42748,7 +42748,7 @@
         <v>46114</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -42826,7 +42826,7 @@
         <v>44844</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -42899,7 +42899,7 @@
         <v>44844</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -42972,7 +42972,7 @@
         <v>44866</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -43045,7 +43045,7 @@
         <v>44840</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -43123,7 +43123,7 @@
         <v>46114</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -43201,7 +43201,7 @@
         <v>45870</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -43274,7 +43274,7 @@
         <v>46304</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -43347,7 +43347,7 @@
         <v>45820</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -43425,7 +43425,7 @@
         <v>46304</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -43498,7 +43498,7 @@
         <v>46120</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -43576,7 +43576,7 @@
         <v>46121</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -43654,7 +43654,7 @@
         <v>45607</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -43727,7 +43727,7 @@
         <v>46125</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -43800,7 +43800,7 @@
         <v>46122</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -43873,7 +43873,7 @@
         <v>44656</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -43951,7 +43951,7 @@
         <v>46304</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -44024,7 +44024,7 @@
         <v>45709</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -44102,7 +44102,7 @@
         <v>46129</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -44180,7 +44180,7 @@
         <v>45880</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -44258,7 +44258,7 @@
         <v>45880</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -44336,7 +44336,7 @@
         <v>46308</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -44414,7 +44414,7 @@
         <v>46308</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -44487,7 +44487,7 @@
         <v>46209</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -44560,7 +44560,7 @@
         <v>46128</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -44633,7 +44633,7 @@
         <v>46307</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -44706,7 +44706,7 @@
         <v>46308</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -44779,7 +44779,7 @@
         <v>45881</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -44857,7 +44857,7 @@
         <v>44865</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -44930,7 +44930,7 @@
         <v>44887</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -45003,7 +45003,7 @@
         <v>44887</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -45076,7 +45076,7 @@
         <v>45740</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -45154,7 +45154,7 @@
         <v>44637</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -45227,7 +45227,7 @@
         <v>46308</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -45305,7 +45305,7 @@
         <v>46308</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -45383,7 +45383,7 @@
         <v>45883</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -45461,7 +45461,7 @@
         <v>44550</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -45534,7 +45534,7 @@
         <v>45642</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -45612,7 +45612,7 @@
         <v>45086</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -45685,7 +45685,7 @@
         <v>45706</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -45758,7 +45758,7 @@
         <v>46160</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -45831,7 +45831,7 @@
         <v>45692</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -45909,7 +45909,7 @@
         <v>46308</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -45982,7 +45982,7 @@
         <v>46308</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -46055,7 +46055,7 @@
         <v>45740</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -46128,7 +46128,7 @@
         <v>46308</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -46201,7 +46201,7 @@
         <v>45622</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -46274,7 +46274,7 @@
         <v>46308</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -46347,7 +46347,7 @@
         <v>46307</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -46420,7 +46420,7 @@
         <v>46308</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -46493,7 +46493,7 @@
         <v>46308</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -46566,7 +46566,7 @@
         <v>44966</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -46639,7 +46639,7 @@
         <v>45915</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -46717,7 +46717,7 @@
         <v>45706</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -46790,7 +46790,7 @@
         <v>45853</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -46863,7 +46863,7 @@
         <v>45783</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -46941,7 +46941,7 @@
         <v>46134</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -47014,7 +47014,7 @@
         <v>44964</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -47092,7 +47092,7 @@
         <v>44897</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -47170,7 +47170,7 @@
         <v>46269</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -47243,7 +47243,7 @@
         <v>45700</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -47321,7 +47321,7 @@
         <v>46269</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -47394,7 +47394,7 @@
         <v>44966</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -47467,7 +47467,7 @@
         <v>46269</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -47540,7 +47540,7 @@
         <v>45554</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -47613,7 +47613,7 @@
         <v>45516</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -47686,7 +47686,7 @@
         <v>46269</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -47759,7 +47759,7 @@
         <v>46269</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -47832,7 +47832,7 @@
         <v>44677</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -47905,7 +47905,7 @@
         <v>46314</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -47983,7 +47983,7 @@
         <v>46314</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -48061,7 +48061,7 @@
         <v>46316</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -48139,7 +48139,7 @@
         <v>44813</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -48217,7 +48217,7 @@
         <v>44817</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -48295,7 +48295,7 @@
         <v>45002</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -48373,7 +48373,7 @@
         <v>44981</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -48451,7 +48451,7 @@
         <v>44981</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -48529,7 +48529,7 @@
         <v>44995</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -48607,7 +48607,7 @@
         <v>45560</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -48685,7 +48685,7 @@
         <v>45719</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -48763,7 +48763,7 @@
         <v>45013</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -48841,7 +48841,7 @@
         <v>44973</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -48919,7 +48919,7 @@
         <v>44844</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -48997,7 +48997,7 @@
         <v>44922</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -49075,7 +49075,7 @@
         <v>44946</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -49153,7 +49153,7 @@
         <v>46316</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -49231,7 +49231,7 @@
         <v>45554</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -49304,7 +49304,7 @@
         <v>46316</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -49382,7 +49382,7 @@
         <v>46316</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -49460,7 +49460,7 @@
         <v>45832</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -49533,7 +49533,7 @@
         <v>46315</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -49606,7 +49606,7 @@
         <v>46315</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -49679,7 +49679,7 @@
         <v>44755</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -49757,7 +49757,7 @@
         <v>44966</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -49835,7 +49835,7 @@
         <v>44995</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -49913,7 +49913,7 @@
         <v>45013</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -49991,7 +49991,7 @@
         <v>46315</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -50064,7 +50064,7 @@
         <v>44922</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -50142,7 +50142,7 @@
         <v>46315</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -50215,7 +50215,7 @@
         <v>46315</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -50288,7 +50288,7 @@
         <v>45076</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -50366,7 +50366,7 @@
         <v>44946</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -50444,7 +50444,7 @@
         <v>45071</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -50522,7 +50522,7 @@
         <v>44804</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -50600,7 +50600,7 @@
         <v>45008</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -50678,7 +50678,7 @@
         <v>45566</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -50756,7 +50756,7 @@
         <v>45555</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -50834,7 +50834,7 @@
         <v>45678</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -50912,7 +50912,7 @@
         <v>44903</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -50990,7 +50990,7 @@
         <v>45428</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -51063,7 +51063,7 @@
         <v>45229</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -51141,7 +51141,7 @@
         <v>46064</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -51219,7 +51219,7 @@
         <v>45343</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -51297,7 +51297,7 @@
         <v>45441</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -51370,7 +51370,7 @@
         <v>45441</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -51443,7 +51443,7 @@
         <v>44964</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -51521,7 +51521,7 @@
         <v>45179</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -51594,7 +51594,7 @@
         <v>45179</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -51667,7 +51667,7 @@
         <v>46141</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -51740,7 +51740,7 @@
         <v>44734</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -51813,7 +51813,7 @@
         <v>44732</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -51891,7 +51891,7 @@
         <v>44918</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -51969,7 +51969,7 @@
         <v>45705</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -52042,7 +52042,7 @@
         <v>45006</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -52115,7 +52115,7 @@
         <v>44614</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -52188,7 +52188,7 @@
         <v>45426</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -52261,7 +52261,7 @@
         <v>44679</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -52339,7 +52339,7 @@
         <v>44725</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -52412,7 +52412,7 @@
         <v>44653</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -52485,7 +52485,7 @@
         <v>45980</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -52558,7 +52558,7 @@
         <v>45107</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -52631,7 +52631,7 @@
         <v>45415</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -52704,7 +52704,7 @@
         <v>45184</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -52777,7 +52777,7 @@
         <v>45070</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -52855,7 +52855,7 @@
         <v>45600</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -52928,7 +52928,7 @@
         <v>45279</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -53006,7 +53006,7 @@
         <v>45421</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -53084,7 +53084,7 @@
         <v>45845</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -53162,7 +53162,7 @@
         <v>45344</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -53235,7 +53235,7 @@
         <v>45257</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -53313,7 +53313,7 @@
         <v>45301</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -53391,7 +53391,7 @@
         <v>45095</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -53464,7 +53464,7 @@
         <v>45086</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -53537,7 +53537,7 @@
         <v>45166</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -53615,7 +53615,7 @@
         <v>45075</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -53688,7 +53688,7 @@
         <v>45639</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -53766,7 +53766,7 @@
         <v>45665</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -53839,7 +53839,7 @@
         <v>45009</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -53917,7 +53917,7 @@
         <v>45516</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -53995,7 +53995,7 @@
         <v>45142</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -54068,7 +54068,7 @@
         <v>45616</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -54141,7 +54141,7 @@
         <v>45616</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -54214,7 +54214,7 @@
         <v>45593</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -54292,7 +54292,7 @@
         <v>45646</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -54365,7 +54365,7 @@
         <v>44774</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -54443,7 +54443,7 @@
         <v>45095</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -54521,7 +54521,7 @@
         <v>45095</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -54594,7 +54594,7 @@
         <v>45709</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -54672,7 +54672,7 @@
         <v>45728</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -54750,7 +54750,7 @@
         <v>45615</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -54828,7 +54828,7 @@
         <v>45530</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -54901,7 +54901,7 @@
         <v>45713</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -54979,7 +54979,7 @@
         <v>45744</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -55057,7 +55057,7 @@
         <v>45147</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -55130,7 +55130,7 @@
         <v>44759</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -55203,7 +55203,7 @@
         <v>44840</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -55276,7 +55276,7 @@
         <v>45692</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -55354,7 +55354,7 @@
         <v>45688</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -55432,7 +55432,7 @@
         <v>44820</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -55505,7 +55505,7 @@
         <v>45041</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -55583,7 +55583,7 @@
         <v>45082</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -55661,7 +55661,7 @@
         <v>45688</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -55739,7 +55739,7 @@
         <v>44834</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -55817,7 +55817,7 @@
         <v>44862</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -55895,7 +55895,7 @@
         <v>44973</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -55973,7 +55973,7 @@
         <v>44880</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -56051,7 +56051,7 @@
         <v>45710</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -56124,7 +56124,7 @@
         <v>45191</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -56197,7 +56197,7 @@
         <v>45770</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -56270,7 +56270,7 @@
         <v>45236</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -56348,7 +56348,7 @@
         <v>45236</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -56426,7 +56426,7 @@
         <v>44886</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -56499,7 +56499,7 @@
         <v>45070</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -56577,7 +56577,7 @@
         <v>45566</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -56655,7 +56655,7 @@
         <v>45042</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -56728,7 +56728,7 @@
         <v>45728</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -56806,7 +56806,7 @@
         <v>44876</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -56879,7 +56879,7 @@
         <v>44642</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -56952,7 +56952,7 @@
         <v>44536</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -57025,7 +57025,7 @@
         <v>45735</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -57103,7 +57103,7 @@
         <v>45237</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -57181,7 +57181,7 @@
         <v>45735</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -57259,7 +57259,7 @@
         <v>44944</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -57337,7 +57337,7 @@
         <v>44595</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -57415,7 +57415,7 @@
         <v>45233</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -57488,7 +57488,7 @@
         <v>44564</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -57561,7 +57561,7 @@
         <v>45566</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -57639,7 +57639,7 @@
         <v>45095</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -57712,7 +57712,7 @@
         <v>45082</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -57790,7 +57790,7 @@
         <v>45082</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -57868,7 +57868,7 @@
         <v>45086</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -57941,7 +57941,7 @@
         <v>44589</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -58014,7 +58014,7 @@
         <v>45407</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -58087,7 +58087,7 @@
         <v>44900</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -58160,7 +58160,7 @@
         <v>45357</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -58233,7 +58233,7 @@
         <v>44887</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -58306,7 +58306,7 @@
         <v>45259</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -58379,7 +58379,7 @@
         <v>45275</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -58452,7 +58452,7 @@
         <v>45463</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -58525,7 +58525,7 @@
         <v>45677</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -58603,7 +58603,7 @@
         <v>45103</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -58676,7 +58676,7 @@
         <v>45113</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -58749,7 +58749,7 @@
         <v>44993</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -58822,7 +58822,7 @@
         <v>45293</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -58895,7 +58895,7 @@
         <v>45391</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -58968,7 +58968,7 @@
         <v>45250</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -59046,7 +59046,7 @@
         <v>44949</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -59119,7 +59119,7 @@
         <v>44973</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -59197,7 +59197,7 @@
         <v>45103</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -59270,7 +59270,7 @@
         <v>45341</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -59348,7 +59348,7 @@
         <v>45293</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -59421,7 +59421,7 @@
         <v>45391</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -59494,7 +59494,7 @@
         <v>44678</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -59572,7 +59572,7 @@
         <v>45002</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -59650,7 +59650,7 @@
         <v>45078</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -59723,7 +59723,7 @@
         <v>44993</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -59796,7 +59796,7 @@
         <v>45133</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -59869,7 +59869,7 @@
         <v>44551</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -59942,7 +59942,7 @@
         <v>45447</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -60020,7 +60020,7 @@
         <v>45167</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -60098,7 +60098,7 @@
         <v>44937</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -60171,7 +60171,7 @@
         <v>45314</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -60244,7 +60244,7 @@
         <v>45041</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -60317,7 +60317,7 @@
         <v>45063</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -60390,7 +60390,7 @@
         <v>45113</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -60463,7 +60463,7 @@
         <v>45601</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -60536,7 +60536,7 @@
         <v>45040</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -60609,7 +60609,7 @@
         <v>45020</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -60682,7 +60682,7 @@
         <v>45593</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -60760,7 +60760,7 @@
         <v>45068</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -60838,7 +60838,7 @@
         <v>45149</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -60911,7 +60911,7 @@
         <v>45617</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -60989,7 +60989,7 @@
         <v>45302</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -61067,7 +61067,7 @@
         <v>44622</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -61140,7 +61140,7 @@
         <v>44564</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -61213,7 +61213,7 @@
         <v>44958</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -61286,7 +61286,7 @@
         <v>45095</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -61359,7 +61359,7 @@
         <v>44516</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -61432,7 +61432,7 @@
         <v>45040</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -61510,7 +61510,7 @@
         <v>45615</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -61588,7 +61588,7 @@
         <v>45609</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -61666,7 +61666,7 @@
         <v>45554</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -61739,7 +61739,7 @@
         <v>45551</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -61812,7 +61812,7 @@
         <v>44622</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -61885,7 +61885,7 @@
         <v>45077</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -61963,7 +61963,7 @@
         <v>45206</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -62036,7 +62036,7 @@
         <v>45084</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -62109,7 +62109,7 @@
         <v>45456</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -62187,7 +62187,7 @@
         <v>45174</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -62265,7 +62265,7 @@
         <v>45645</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -62343,7 +62343,7 @@
         <v>44795</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -62421,7 +62421,7 @@
         <v>45715</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -62494,7 +62494,7 @@
         <v>44634</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -62572,7 +62572,7 @@
         <v>45762</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -62645,7 +62645,7 @@
         <v>45147</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -62718,7 +62718,7 @@
         <v>45209</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -62791,7 +62791,7 @@
         <v>45209</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -62864,7 +62864,7 @@
         <v>45243</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -62942,7 +62942,7 @@
         <v>45660</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -63020,7 +63020,7 @@
         <v>45103</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -63093,7 +63093,7 @@
         <v>45253</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -63171,7 +63171,7 @@
         <v>44664</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -63249,7 +63249,7 @@
         <v>45274</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -63322,7 +63322,7 @@
         <v>44767</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -63395,7 +63395,7 @@
         <v>45720</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -63473,7 +63473,7 @@
         <v>44735</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -63546,7 +63546,7 @@
         <v>44729</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -63619,7 +63619,7 @@
         <v>45149</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -63692,7 +63692,7 @@
         <v>45257</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -63770,7 +63770,7 @@
         <v>45314</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -63843,7 +63843,7 @@
         <v>44672</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -63916,7 +63916,7 @@
         <v>45308</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -63989,7 +63989,7 @@
         <v>44823</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -64062,7 +64062,7 @@
         <v>45623</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -64135,7 +64135,7 @@
         <v>44833</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -64213,7 +64213,7 @@
         <v>45468</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -64291,7 +64291,7 @@
         <v>45379</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
@@ -64364,7 +64364,7 @@
         <v>45309</v>
       </c>
       <c r="E802" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -64442,7 +64442,7 @@
         <v>45309</v>
       </c>
       <c r="E803" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
@@ -64515,7 +64515,7 @@
         <v>45309</v>
       </c>
       <c r="E804" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
@@ -64588,7 +64588,7 @@
         <v>45257</v>
       </c>
       <c r="E805" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>
@@ -64661,7 +64661,7 @@
         <v>45302</v>
       </c>
       <c r="E806" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F806" t="inlineStr">
         <is>
@@ -64739,7 +64739,7 @@
         <v>44966</v>
       </c>
       <c r="E807" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F807" t="inlineStr">
         <is>
@@ -64812,7 +64812,7 @@
         <v>44767</v>
       </c>
       <c r="E808" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F808" t="inlineStr">
         <is>
@@ -64885,7 +64885,7 @@
         <v>45040</v>
       </c>
       <c r="E809" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F809" t="inlineStr">
         <is>
@@ -64958,7 +64958,7 @@
         <v>44595</v>
       </c>
       <c r="E810" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F810" t="inlineStr">
         <is>
@@ -65031,7 +65031,7 @@
         <v>45009</v>
       </c>
       <c r="E811" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F811" t="inlineStr">
         <is>
@@ -65104,7 +65104,7 @@
         <v>45084</v>
       </c>
       <c r="E812" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F812" t="inlineStr">
         <is>
@@ -65177,7 +65177,7 @@
         <v>44782</v>
       </c>
       <c r="E813" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F813" t="inlineStr">
         <is>
@@ -65250,7 +65250,7 @@
         <v>44714</v>
       </c>
       <c r="E814" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F814" t="inlineStr">
         <is>
@@ -65323,7 +65323,7 @@
         <v>45299</v>
       </c>
       <c r="E815" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F815" t="inlineStr">
         <is>
@@ -65396,7 +65396,7 @@
         <v>44749</v>
       </c>
       <c r="E816" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F816" t="inlineStr">
         <is>
@@ -65469,7 +65469,7 @@
         <v>44861</v>
       </c>
       <c r="E817" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F817" t="inlineStr">
         <is>
@@ -65547,7 +65547,7 @@
         <v>44987</v>
       </c>
       <c r="E818" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F818" t="inlineStr">
         <is>
@@ -65620,7 +65620,7 @@
         <v>44879</v>
       </c>
       <c r="E819" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F819" t="inlineStr">
         <is>
@@ -65693,7 +65693,7 @@
         <v>44871</v>
       </c>
       <c r="E820" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F820" t="inlineStr">
         <is>
@@ -65766,7 +65766,7 @@
         <v>44526</v>
       </c>
       <c r="E821" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F821" t="inlineStr">
         <is>
@@ -65839,7 +65839,7 @@
         <v>44914</v>
       </c>
       <c r="E822" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F822" t="inlineStr">
         <is>
@@ -65917,7 +65917,7 @@
         <v>45548</v>
       </c>
       <c r="E823" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F823" t="inlineStr">
         <is>
@@ -65990,7 +65990,7 @@
         <v>45763</v>
       </c>
       <c r="E824" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F824" t="inlineStr">
         <is>
@@ -66063,7 +66063,7 @@
         <v>44503</v>
       </c>
       <c r="E825" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F825" t="inlineStr">
         <is>
@@ -66136,7 +66136,7 @@
         <v>45636</v>
       </c>
       <c r="E826" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F826" t="inlineStr">
         <is>
@@ -66209,7 +66209,7 @@
         <v>44607</v>
       </c>
       <c r="E827" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F827" t="inlineStr">
         <is>
@@ -66282,7 +66282,7 @@
         <v>44953</v>
       </c>
       <c r="E828" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F828" t="inlineStr">
         <is>
@@ -66360,7 +66360,7 @@
         <v>44817</v>
       </c>
       <c r="E829" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F829" t="inlineStr">
         <is>
@@ -66433,7 +66433,7 @@
         <v>45523</v>
       </c>
       <c r="E830" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F830" t="inlineStr">
         <is>
@@ -66511,7 +66511,7 @@
         <v>44867</v>
       </c>
       <c r="E831" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F831" t="inlineStr">
         <is>
@@ -66584,7 +66584,7 @@
         <v>44732</v>
       </c>
       <c r="E832" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F832" t="inlineStr">
         <is>
@@ -66662,7 +66662,7 @@
         <v>44949</v>
       </c>
       <c r="E833" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F833" t="inlineStr">
         <is>
@@ -66735,7 +66735,7 @@
         <v>44949</v>
       </c>
       <c r="E834" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F834" t="inlineStr">
         <is>
@@ -66808,7 +66808,7 @@
         <v>44949</v>
       </c>
       <c r="E835" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F835" t="inlineStr">
         <is>
@@ -66881,7 +66881,7 @@
         <v>44960</v>
       </c>
       <c r="E836" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F836" t="inlineStr">
         <is>
@@ -66959,7 +66959,7 @@
         <v>44966</v>
       </c>
       <c r="E837" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F837" t="inlineStr">
         <is>
@@ -67032,7 +67032,7 @@
         <v>45644</v>
       </c>
       <c r="E838" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F838" t="inlineStr">
         <is>
@@ -67105,7 +67105,7 @@
         <v>45428</v>
       </c>
       <c r="E839" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F839" t="inlineStr">
         <is>
@@ -67178,7 +67178,7 @@
         <v>45429</v>
       </c>
       <c r="E840" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F840" t="inlineStr">
         <is>
@@ -67251,7 +67251,7 @@
         <v>45250</v>
       </c>
       <c r="E841" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F841" t="inlineStr">
         <is>
@@ -67329,7 +67329,7 @@
         <v>46188</v>
       </c>
       <c r="E842" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F842" t="inlineStr">
         <is>
@@ -67407,7 +67407,7 @@
         <v>46258</v>
       </c>
       <c r="E843" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F843" t="inlineStr">
         <is>

--- a/Översikt FINSPÅNG.xlsx
+++ b/Översikt FINSPÅNG.xlsx
@@ -601,7 +601,7 @@
         <v>46244</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -727,7 +727,7 @@
         <v>45945</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -858,7 +858,7 @@
         <v>45134</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
         <v>44896</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1121,7 +1121,7 @@
         <v>45210</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1247,7 +1247,7 @@
         <v>44888</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1369,7 +1369,7 @@
         <v>44777</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1488,7 +1488,7 @@
         <v>44897</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1607,7 +1607,7 @@
         <v>44910</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1734,7 +1734,7 @@
         <v>45322</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1855,7 +1855,7 @@
         <v>44624</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1971,7 +1971,7 @@
         <v>44599</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2082,7 +2082,7 @@
         <v>45891</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2198,7 +2198,7 @@
         <v>45421</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2318,7 +2318,7 @@
         <v>45238</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2433,7 +2433,7 @@
         <v>45898</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2548,7 +2548,7 @@
         <v>45267</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2663,7 +2663,7 @@
         <v>45679</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2782,7 +2782,7 @@
         <v>45812</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2896,7 +2896,7 @@
         <v>44791</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3010,7 +3010,7 @@
         <v>44665</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3123,7 +3123,7 @@
         <v>46307</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3235,7 +3235,7 @@
         <v>45681</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3352,7 +3352,7 @@
         <v>45819</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3468,7 +3468,7 @@
         <v>46196</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3580,7 +3580,7 @@
         <v>45602</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3692,7 +3692,7 @@
         <v>45800</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3804,7 +3804,7 @@
         <v>45082</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3916,7 +3916,7 @@
         <v>44774</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4028,7 +4028,7 @@
         <v>44690</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4139,7 +4139,7 @@
         <v>45894</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4254,7 +4254,7 @@
         <v>44816</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4360,7 +4360,7 @@
         <v>45905</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4471,7 +4471,7 @@
         <v>46174</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4582,7 +4582,7 @@
         <v>45425</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4688,7 +4688,7 @@
         <v>45121</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4803,7 +4803,7 @@
         <v>44903</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4913,7 +4913,7 @@
         <v>46181</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5024,7 +5024,7 @@
         <v>46181</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5135,7 +5135,7 @@
         <v>45950</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5246,7 +5246,7 @@
         <v>45477</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5361,7 +5361,7 @@
         <v>44981</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5472,7 +5472,7 @@
         <v>45644</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5578,7 +5578,7 @@
         <v>45441</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5689,7 +5689,7 @@
         <v>45235</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5800,7 +5800,7 @@
         <v>44683</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5910,7 +5910,7 @@
         <v>44776</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6015,7 +6015,7 @@
         <v>44504</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6125,7 +6125,7 @@
         <v>44529</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6230,7 +6230,7 @@
         <v>44930</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6340,7 +6340,7 @@
         <v>45232</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6450,7 +6450,7 @@
         <v>45905</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6560,7 +6560,7 @@
         <v>45883</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6670,7 +6670,7 @@
         <v>45636</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6775,7 +6775,7 @@
         <v>44622</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6880,7 +6880,7 @@
         <v>44915</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6990,7 +6990,7 @@
         <v>45082</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7100,7 +7100,7 @@
         <v>45744</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7214,7 +7214,7 @@
         <v>45446</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7319,7 +7319,7 @@
         <v>46189</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7424,7 +7424,7 @@
         <v>45567</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7538,7 +7538,7 @@
         <v>46181</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7648,7 +7648,7 @@
         <v>46058</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7762,7 +7762,7 @@
         <v>45846</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7872,7 +7872,7 @@
         <v>45845</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7982,7 +7982,7 @@
         <v>46258</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8092,7 +8092,7 @@
         <v>46258</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8206,7 +8206,7 @@
         <v>46129</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8320,7 +8320,7 @@
         <v>45880</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8430,7 +8430,7 @@
         <v>44915</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8540,7 +8540,7 @@
         <v>46043</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8654,7 +8654,7 @@
         <v>45447</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8764,7 +8764,7 @@
         <v>45566</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8878,7 +8878,7 @@
         <v>44599</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8988,7 +8988,7 @@
         <v>44992</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9098,7 +9098,7 @@
         <v>44897</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9212,7 +9212,7 @@
         <v>46318</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9317,7 +9317,7 @@
         <v>46318</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9426,7 +9426,7 @@
         <v>46155</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9540,7 +9540,7 @@
         <v>45328</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9649,7 +9649,7 @@
         <v>45615</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9763,7 +9763,7 @@
         <v>44817</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9873,7 +9873,7 @@
         <v>45070</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9983,7 +9983,7 @@
         <v>44965</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10097,7 +10097,7 @@
         <v>45149</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10206,7 +10206,7 @@
         <v>45229</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10316,7 +10316,7 @@
         <v>45302</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10425,7 +10425,7 @@
         <v>45555</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10539,7 +10539,7 @@
         <v>44501</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10649,7 +10649,7 @@
         <v>44711</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10759,7 +10759,7 @@
         <v>45428</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10864,7 +10864,7 @@
         <v>46107</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10974,7 +10974,7 @@
         <v>46188</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11088,7 +11088,7 @@
         <v>44675</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11161,7 +11161,7 @@
         <v>44676</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11239,7 +11239,7 @@
         <v>44536</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11317,7 +11317,7 @@
         <v>44864</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11390,7 +11390,7 @@
         <v>44600</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11463,7 +11463,7 @@
         <v>44824</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11536,7 +11536,7 @@
         <v>44799</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11609,7 +11609,7 @@
         <v>44795</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11682,7 +11682,7 @@
         <v>44856</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11755,7 +11755,7 @@
         <v>44578</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11833,7 +11833,7 @@
         <v>44675</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -11906,7 +11906,7 @@
         <v>44852</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -11984,7 +11984,7 @@
         <v>44601</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12062,7 +12062,7 @@
         <v>44601</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12135,7 +12135,7 @@
         <v>44551</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12208,7 +12208,7 @@
         <v>44525</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12281,7 +12281,7 @@
         <v>44574</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12359,7 +12359,7 @@
         <v>44588</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12437,7 +12437,7 @@
         <v>44574</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12510,7 +12510,7 @@
         <v>44889</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12583,7 +12583,7 @@
         <v>44627</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -12656,7 +12656,7 @@
         <v>44525</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -12734,7 +12734,7 @@
         <v>44503</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -12812,7 +12812,7 @@
         <v>44503</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -12885,7 +12885,7 @@
         <v>44874</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -12958,7 +12958,7 @@
         <v>44502</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13036,7 +13036,7 @@
         <v>44551</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -13109,7 +13109,7 @@
         <v>44712</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -13187,7 +13187,7 @@
         <v>44581</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -13260,7 +13260,7 @@
         <v>44833</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -13333,7 +13333,7 @@
         <v>44601</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -13406,7 +13406,7 @@
         <v>44859</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -13479,7 +13479,7 @@
         <v>44672</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -13552,7 +13552,7 @@
         <v>44735</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -13625,7 +13625,7 @@
         <v>44796</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -13698,7 +13698,7 @@
         <v>44782</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -13771,7 +13771,7 @@
         <v>44741</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -13844,7 +13844,7 @@
         <v>44859</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -13917,7 +13917,7 @@
         <v>44613</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -13995,7 +13995,7 @@
         <v>44678</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -14068,7 +14068,7 @@
         <v>44855</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -14146,7 +14146,7 @@
         <v>44887</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -14219,7 +14219,7 @@
         <v>44860</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -14292,7 +14292,7 @@
         <v>44753</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -14365,7 +14365,7 @@
         <v>44802</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -14438,7 +14438,7 @@
         <v>44781</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -14511,7 +14511,7 @@
         <v>44541</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -14584,7 +14584,7 @@
         <v>44564</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -14657,7 +14657,7 @@
         <v>44859</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -14730,7 +14730,7 @@
         <v>44595</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -14803,7 +14803,7 @@
         <v>44582</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -14876,7 +14876,7 @@
         <v>44816</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -14949,7 +14949,7 @@
         <v>44508</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -15022,7 +15022,7 @@
         <v>44656</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -15095,7 +15095,7 @@
         <v>44627</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -15168,7 +15168,7 @@
         <v>44587</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -15241,7 +15241,7 @@
         <v>44820</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -15314,7 +15314,7 @@
         <v>44532</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -15387,7 +15387,7 @@
         <v>44552</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -15460,7 +15460,7 @@
         <v>44879</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -15533,7 +15533,7 @@
         <v>44581</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -15606,7 +15606,7 @@
         <v>44588</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -15684,7 +15684,7 @@
         <v>44875</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -15757,7 +15757,7 @@
         <v>44743</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -15830,7 +15830,7 @@
         <v>44831</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -15908,7 +15908,7 @@
         <v>44819</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -15981,7 +15981,7 @@
         <v>44581</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -16059,7 +16059,7 @@
         <v>44630</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -16132,7 +16132,7 @@
         <v>44601</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -16205,7 +16205,7 @@
         <v>44742</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -16283,7 +16283,7 @@
         <v>44859</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -16356,7 +16356,7 @@
         <v>44600</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -16429,7 +16429,7 @@
         <v>44635</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -16502,7 +16502,7 @@
         <v>44776</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -16575,7 +16575,7 @@
         <v>44713</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -16653,7 +16653,7 @@
         <v>44697</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -16731,7 +16731,7 @@
         <v>44533</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -16804,7 +16804,7 @@
         <v>44601</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -16877,7 +16877,7 @@
         <v>44678</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -16950,7 +16950,7 @@
         <v>44704</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -17023,7 +17023,7 @@
         <v>44564</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -17096,7 +17096,7 @@
         <v>44642</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -17169,7 +17169,7 @@
         <v>45883</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -17247,7 +17247,7 @@
         <v>44659</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -17325,7 +17325,7 @@
         <v>45888</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -17403,7 +17403,7 @@
         <v>44508</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -17476,7 +17476,7 @@
         <v>45621</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -17554,7 +17554,7 @@
         <v>44662</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -17632,7 +17632,7 @@
         <v>45617</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -17710,7 +17710,7 @@
         <v>45618</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -17783,7 +17783,7 @@
         <v>44754</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -17856,7 +17856,7 @@
         <v>45555</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -17934,7 +17934,7 @@
         <v>44802</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -18007,7 +18007,7 @@
         <v>45042</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -18080,7 +18080,7 @@
         <v>44918</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -18158,7 +18158,7 @@
         <v>45330</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -18231,7 +18231,7 @@
         <v>44778</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -18304,7 +18304,7 @@
         <v>45891</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -18382,7 +18382,7 @@
         <v>45707</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -18460,7 +18460,7 @@
         <v>45622</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -18533,7 +18533,7 @@
         <v>45894</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -18611,7 +18611,7 @@
         <v>45896</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -18689,7 +18689,7 @@
         <v>45895</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -18762,7 +18762,7 @@
         <v>44930</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -18840,7 +18840,7 @@
         <v>45258</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -18913,7 +18913,7 @@
         <v>45379</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -18986,7 +18986,7 @@
         <v>45898</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -19059,7 +19059,7 @@
         <v>44833</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -19137,7 +19137,7 @@
         <v>45535</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -19215,7 +19215,7 @@
         <v>44770</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -19288,7 +19288,7 @@
         <v>45260</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -19361,7 +19361,7 @@
         <v>45257</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -19439,7 +19439,7 @@
         <v>45257</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -19512,7 +19512,7 @@
         <v>45541</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -19590,7 +19590,7 @@
         <v>45021</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -19663,7 +19663,7 @@
         <v>45362</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -19736,7 +19736,7 @@
         <v>45167</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -19809,7 +19809,7 @@
         <v>45008</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -19882,7 +19882,7 @@
         <v>45374</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -19960,7 +19960,7 @@
         <v>44930</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -20033,7 +20033,7 @@
         <v>44930</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -20106,7 +20106,7 @@
         <v>45903</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -20184,7 +20184,7 @@
         <v>44844</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -20257,7 +20257,7 @@
         <v>44616</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -20335,7 +20335,7 @@
         <v>45903</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -20413,7 +20413,7 @@
         <v>45904</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -20491,7 +20491,7 @@
         <v>45903</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -20569,7 +20569,7 @@
         <v>45903</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -20647,7 +20647,7 @@
         <v>45904</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -20725,7 +20725,7 @@
         <v>45903</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -20803,7 +20803,7 @@
         <v>45908</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -20876,7 +20876,7 @@
         <v>44550</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -20949,7 +20949,7 @@
         <v>45905</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -21027,7 +21027,7 @@
         <v>45230</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -21100,7 +21100,7 @@
         <v>45905</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -21178,7 +21178,7 @@
         <v>46077</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -21256,7 +21256,7 @@
         <v>45554</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -21329,7 +21329,7 @@
         <v>45095</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -21407,7 +21407,7 @@
         <v>45055</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -21480,7 +21480,7 @@
         <v>45095</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -21553,7 +21553,7 @@
         <v>45425</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -21626,7 +21626,7 @@
         <v>44817</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -21699,7 +21699,7 @@
         <v>44898</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -21772,7 +21772,7 @@
         <v>45924</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -21845,7 +21845,7 @@
         <v>45177</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -21918,7 +21918,7 @@
         <v>44806</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -21996,7 +21996,7 @@
         <v>45456</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -22074,7 +22074,7 @@
         <v>44865</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -22152,7 +22152,7 @@
         <v>44980</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -22225,7 +22225,7 @@
         <v>44966</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -22303,7 +22303,7 @@
         <v>45931</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -22376,7 +22376,7 @@
         <v>45357</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -22449,7 +22449,7 @@
         <v>44914</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -22522,7 +22522,7 @@
         <v>45935</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -22600,7 +22600,7 @@
         <v>46176</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -22673,7 +22673,7 @@
         <v>46176</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -22746,7 +22746,7 @@
         <v>44974</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -22819,7 +22819,7 @@
         <v>44816</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -22892,7 +22892,7 @@
         <v>44950</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -22970,7 +22970,7 @@
         <v>45846</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -23048,7 +23048,7 @@
         <v>45744</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -23126,7 +23126,7 @@
         <v>45744</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -23204,7 +23204,7 @@
         <v>45601</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -23277,7 +23277,7 @@
         <v>45323</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -23355,7 +23355,7 @@
         <v>46176</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -23428,7 +23428,7 @@
         <v>45181</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -23501,7 +23501,7 @@
         <v>45042</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -23579,7 +23579,7 @@
         <v>46174</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -23657,7 +23657,7 @@
         <v>45257</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -23735,7 +23735,7 @@
         <v>45225</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -23808,7 +23808,7 @@
         <v>46174</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -23886,7 +23886,7 @@
         <v>45252</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -23959,7 +23959,7 @@
         <v>45944</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -24032,7 +24032,7 @@
         <v>46177</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -24105,7 +24105,7 @@
         <v>45082</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -24183,7 +24183,7 @@
         <v>45149</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -24256,7 +24256,7 @@
         <v>44887</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -24329,7 +24329,7 @@
         <v>44953</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -24402,7 +24402,7 @@
         <v>45447</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -24480,7 +24480,7 @@
         <v>45442</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -24553,7 +24553,7 @@
         <v>44767</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -24626,7 +24626,7 @@
         <v>46181</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -24704,7 +24704,7 @@
         <v>44986</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -24777,7 +24777,7 @@
         <v>44957</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -24850,7 +24850,7 @@
         <v>46178</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -24923,7 +24923,7 @@
         <v>46178</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -24996,7 +24996,7 @@
         <v>46178</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -25069,7 +25069,7 @@
         <v>45950</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -25147,7 +25147,7 @@
         <v>44993</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -25220,7 +25220,7 @@
         <v>44987</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -25293,7 +25293,7 @@
         <v>45247</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -25366,7 +25366,7 @@
         <v>45422</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -25439,7 +25439,7 @@
         <v>45214</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -25512,7 +25512,7 @@
         <v>45421</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -25590,7 +25590,7 @@
         <v>45420</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -25663,7 +25663,7 @@
         <v>45125</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -25741,7 +25741,7 @@
         <v>45033</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -25819,7 +25819,7 @@
         <v>45103</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -25892,7 +25892,7 @@
         <v>45688</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -25970,7 +25970,7 @@
         <v>45955</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -26043,7 +26043,7 @@
         <v>46185</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -26116,7 +26116,7 @@
         <v>45022</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -26194,7 +26194,7 @@
         <v>45744</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -26272,7 +26272,7 @@
         <v>45267</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -26350,7 +26350,7 @@
         <v>45202</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -26423,7 +26423,7 @@
         <v>45118</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -26496,7 +26496,7 @@
         <v>46185</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -26569,7 +26569,7 @@
         <v>45258</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -26642,7 +26642,7 @@
         <v>45225</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -26715,7 +26715,7 @@
         <v>44900</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -26788,7 +26788,7 @@
         <v>46188</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -26861,7 +26861,7 @@
         <v>45258</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -26934,7 +26934,7 @@
         <v>45260</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -27007,7 +27007,7 @@
         <v>45191</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -27080,7 +27080,7 @@
         <v>45178</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -27153,7 +27153,7 @@
         <v>45177</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -27226,7 +27226,7 @@
         <v>45623</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -27304,7 +27304,7 @@
         <v>45639</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -27382,7 +27382,7 @@
         <v>45197</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -27455,7 +27455,7 @@
         <v>45264</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -27533,7 +27533,7 @@
         <v>45969</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -27606,7 +27606,7 @@
         <v>45971</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -27679,7 +27679,7 @@
         <v>45110</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -27752,7 +27752,7 @@
         <v>45250</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -27825,7 +27825,7 @@
         <v>45593</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -27903,7 +27903,7 @@
         <v>46196</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -27981,7 +27981,7 @@
         <v>44942</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -28054,7 +28054,7 @@
         <v>45846</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -28132,7 +28132,7 @@
         <v>46199</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -28205,7 +28205,7 @@
         <v>44617</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -28278,7 +28278,7 @@
         <v>45979</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -28351,7 +28351,7 @@
         <v>46203</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -28424,7 +28424,7 @@
         <v>44939</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -28497,7 +28497,7 @@
         <v>45202</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -28570,7 +28570,7 @@
         <v>45082</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -28648,7 +28648,7 @@
         <v>45323</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -28726,7 +28726,7 @@
         <v>45299</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -28799,7 +28799,7 @@
         <v>45983</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -28872,7 +28872,7 @@
         <v>45983</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -28945,7 +28945,7 @@
         <v>46204</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -29018,7 +29018,7 @@
         <v>45250</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -29096,7 +29096,7 @@
         <v>45206</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -29169,7 +29169,7 @@
         <v>45986</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -29242,7 +29242,7 @@
         <v>44891</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -29315,7 +29315,7 @@
         <v>45983</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -29388,7 +29388,7 @@
         <v>45986</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -29461,7 +29461,7 @@
         <v>45985</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -29534,7 +29534,7 @@
         <v>44964</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -29612,7 +29612,7 @@
         <v>46209</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -29685,7 +29685,7 @@
         <v>45607</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -29758,7 +29758,7 @@
         <v>45607</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -29831,7 +29831,7 @@
         <v>46211</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -29904,7 +29904,7 @@
         <v>46212</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -29977,7 +29977,7 @@
         <v>45770</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -30050,7 +30050,7 @@
         <v>45749</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -30128,7 +30128,7 @@
         <v>45551</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -30201,7 +30201,7 @@
         <v>45639</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -30279,7 +30279,7 @@
         <v>45709</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -30357,7 +30357,7 @@
         <v>45097</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -30430,7 +30430,7 @@
         <v>45095</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -30503,7 +30503,7 @@
         <v>45566</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -30581,7 +30581,7 @@
         <v>45566</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -30659,7 +30659,7 @@
         <v>45463</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -30732,7 +30732,7 @@
         <v>45740</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -30810,7 +30810,7 @@
         <v>46218</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -30888,7 +30888,7 @@
         <v>46000</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -30966,7 +30966,7 @@
         <v>45103</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -31039,7 +31039,7 @@
         <v>45232</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -31117,7 +31117,7 @@
         <v>46218</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -31195,7 +31195,7 @@
         <v>46219</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -31268,7 +31268,7 @@
         <v>45609</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -31346,7 +31346,7 @@
         <v>46002</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -31424,7 +31424,7 @@
         <v>46002</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -31502,7 +31502,7 @@
         <v>45566</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -31580,7 +31580,7 @@
         <v>45566</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -31658,7 +31658,7 @@
         <v>45566</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -31736,7 +31736,7 @@
         <v>46002</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -31814,7 +31814,7 @@
         <v>45735</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -31892,7 +31892,7 @@
         <v>46002</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -31970,7 +31970,7 @@
         <v>45736</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -32048,7 +32048,7 @@
         <v>46006</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -32126,7 +32126,7 @@
         <v>46006</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -32204,7 +32204,7 @@
         <v>46226</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -32277,7 +32277,7 @@
         <v>46003</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -32350,7 +32350,7 @@
         <v>46226</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -32423,7 +32423,7 @@
         <v>46225</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -32496,7 +32496,7 @@
         <v>46225</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -32569,7 +32569,7 @@
         <v>46006</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -32642,7 +32642,7 @@
         <v>45530</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -32715,7 +32715,7 @@
         <v>46232</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -32788,7 +32788,7 @@
         <v>46233</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -32861,7 +32861,7 @@
         <v>46279</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -32934,7 +32934,7 @@
         <v>46279</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -33007,7 +33007,7 @@
         <v>45642</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -33080,7 +33080,7 @@
         <v>46279</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -33153,7 +33153,7 @@
         <v>45267</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -33231,7 +33231,7 @@
         <v>45530</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -33304,7 +33304,7 @@
         <v>45727</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -33377,7 +33377,7 @@
         <v>45371</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -33455,7 +33455,7 @@
         <v>46282</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -33533,7 +33533,7 @@
         <v>46282</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -33611,7 +33611,7 @@
         <v>46282</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -33689,7 +33689,7 @@
         <v>46282</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -33767,7 +33767,7 @@
         <v>46282</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -33845,7 +33845,7 @@
         <v>46282</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -33923,7 +33923,7 @@
         <v>45853</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -33996,7 +33996,7 @@
         <v>46282</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -34074,7 +34074,7 @@
         <v>46030</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -34152,7 +34152,7 @@
         <v>46282</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -34230,7 +34230,7 @@
         <v>46030</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -34308,7 +34308,7 @@
         <v>46282</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -34386,7 +34386,7 @@
         <v>46029</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -34459,7 +34459,7 @@
         <v>46031</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -34537,7 +34537,7 @@
         <v>46281</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -34610,7 +34610,7 @@
         <v>46034</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -34688,7 +34688,7 @@
         <v>46034</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -34766,7 +34766,7 @@
         <v>46034</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -34844,7 +34844,7 @@
         <v>46036</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -34922,7 +34922,7 @@
         <v>46036</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -35000,7 +35000,7 @@
         <v>45796</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -35078,7 +35078,7 @@
         <v>46286</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -35156,7 +35156,7 @@
         <v>45796</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -35234,7 +35234,7 @@
         <v>46040</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -35307,7 +35307,7 @@
         <v>45863</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -35380,7 +35380,7 @@
         <v>46040</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -35453,7 +35453,7 @@
         <v>45316</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -35531,7 +35531,7 @@
         <v>45797</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -35604,7 +35604,7 @@
         <v>45797</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -35677,7 +35677,7 @@
         <v>45797</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -35755,7 +35755,7 @@
         <v>45702</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -35833,7 +35833,7 @@
         <v>46048</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -35911,7 +35911,7 @@
         <v>46048</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -35989,7 +35989,7 @@
         <v>45800</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -36067,7 +36067,7 @@
         <v>46048</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -36145,7 +36145,7 @@
         <v>45800</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -36223,7 +36223,7 @@
         <v>46050</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -36301,7 +36301,7 @@
         <v>45800</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -36379,7 +36379,7 @@
         <v>45800</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -36457,7 +36457,7 @@
         <v>46050</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -36535,7 +36535,7 @@
         <v>46049</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -36608,7 +36608,7 @@
         <v>46052</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -36681,7 +36681,7 @@
         <v>45293</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -36759,7 +36759,7 @@
         <v>46055</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -36837,7 +36837,7 @@
         <v>44860</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -36910,7 +36910,7 @@
         <v>46058</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -36988,7 +36988,7 @@
         <v>45328</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -37061,7 +37061,7 @@
         <v>46058</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -37139,7 +37139,7 @@
         <v>46058</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -37217,7 +37217,7 @@
         <v>46060</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -37290,7 +37290,7 @@
         <v>46058</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -37368,7 +37368,7 @@
         <v>46064</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -37446,7 +37446,7 @@
         <v>45812</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -37524,7 +37524,7 @@
         <v>46064</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -37602,7 +37602,7 @@
         <v>46064</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -37680,7 +37680,7 @@
         <v>45812</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -37758,7 +37758,7 @@
         <v>46063</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -37836,7 +37836,7 @@
         <v>46064</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -37914,7 +37914,7 @@
         <v>46063</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -37992,7 +37992,7 @@
         <v>46064</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -38070,7 +38070,7 @@
         <v>46064</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -38148,7 +38148,7 @@
         <v>45870</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -38221,7 +38221,7 @@
         <v>46065</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -38299,7 +38299,7 @@
         <v>45639</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -38377,7 +38377,7 @@
         <v>46065</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -38455,7 +38455,7 @@
         <v>46069</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -38533,7 +38533,7 @@
         <v>46070</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -38611,7 +38611,7 @@
         <v>46070</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -38689,7 +38689,7 @@
         <v>45819</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -38767,7 +38767,7 @@
         <v>45819</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -38845,7 +38845,7 @@
         <v>45467</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -38918,7 +38918,7 @@
         <v>45824</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -38996,7 +38996,7 @@
         <v>46073</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -39074,7 +39074,7 @@
         <v>45824</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -39152,7 +39152,7 @@
         <v>46076</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -39230,7 +39230,7 @@
         <v>46076</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -39308,7 +39308,7 @@
         <v>45824</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -39386,7 +39386,7 @@
         <v>45824</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -39464,7 +39464,7 @@
         <v>46078</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -39542,7 +39542,7 @@
         <v>46079</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -39620,7 +39620,7 @@
         <v>46080</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -39698,7 +39698,7 @@
         <v>46295</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -39776,7 +39776,7 @@
         <v>46295</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -39854,7 +39854,7 @@
         <v>46080</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -39932,7 +39932,7 @@
         <v>46080</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -40010,7 +40010,7 @@
         <v>46080</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -40088,7 +40088,7 @@
         <v>46085</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -40166,7 +40166,7 @@
         <v>46085</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -40244,7 +40244,7 @@
         <v>46085</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -40322,7 +40322,7 @@
         <v>46085</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -40400,7 +40400,7 @@
         <v>45835</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -40478,7 +40478,7 @@
         <v>45840</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -40556,7 +40556,7 @@
         <v>46094</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -40634,7 +40634,7 @@
         <v>46097</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -40707,7 +40707,7 @@
         <v>46099</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -40780,7 +40780,7 @@
         <v>46099</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -40853,7 +40853,7 @@
         <v>46255</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -40931,7 +40931,7 @@
         <v>46099</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -41009,7 +41009,7 @@
         <v>46099</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -41087,7 +41087,7 @@
         <v>46099</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -41165,7 +41165,7 @@
         <v>45845</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -41243,7 +41243,7 @@
         <v>46302</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -41316,7 +41316,7 @@
         <v>45776</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -41389,7 +41389,7 @@
         <v>46106</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -41467,7 +41467,7 @@
         <v>45853</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -41540,7 +41540,7 @@
         <v>46258</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -41618,7 +41618,7 @@
         <v>46258</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -41696,7 +41696,7 @@
         <v>45337</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -41769,7 +41769,7 @@
         <v>45854</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -41842,7 +41842,7 @@
         <v>45855</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -41915,7 +41915,7 @@
         <v>45854</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -41988,7 +41988,7 @@
         <v>45523</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -42061,7 +42061,7 @@
         <v>46300</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -42134,7 +42134,7 @@
         <v>46111</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -42212,7 +42212,7 @@
         <v>45831</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -42285,7 +42285,7 @@
         <v>46304</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -42358,7 +42358,7 @@
         <v>45428</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -42436,7 +42436,7 @@
         <v>45428</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -42514,7 +42514,7 @@
         <v>46113</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -42592,7 +42592,7 @@
         <v>45280</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -42670,7 +42670,7 @@
         <v>46114</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -42748,7 +42748,7 @@
         <v>46114</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -42826,7 +42826,7 @@
         <v>44844</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -42899,7 +42899,7 @@
         <v>44844</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -42972,7 +42972,7 @@
         <v>44866</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -43045,7 +43045,7 @@
         <v>44840</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -43123,7 +43123,7 @@
         <v>46114</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -43201,7 +43201,7 @@
         <v>45870</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -43274,7 +43274,7 @@
         <v>46304</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -43347,7 +43347,7 @@
         <v>45820</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -43425,7 +43425,7 @@
         <v>46304</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -43498,7 +43498,7 @@
         <v>46120</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -43576,7 +43576,7 @@
         <v>46121</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -43654,7 +43654,7 @@
         <v>45607</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -43727,7 +43727,7 @@
         <v>46125</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -43800,7 +43800,7 @@
         <v>46122</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -43873,7 +43873,7 @@
         <v>44656</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -43951,7 +43951,7 @@
         <v>46304</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -44024,7 +44024,7 @@
         <v>45709</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -44102,7 +44102,7 @@
         <v>46129</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -44180,7 +44180,7 @@
         <v>45880</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -44258,7 +44258,7 @@
         <v>45880</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -44336,7 +44336,7 @@
         <v>46308</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -44414,7 +44414,7 @@
         <v>46308</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -44487,7 +44487,7 @@
         <v>46209</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -44560,7 +44560,7 @@
         <v>46128</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -44633,7 +44633,7 @@
         <v>46307</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -44706,7 +44706,7 @@
         <v>46308</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -44779,7 +44779,7 @@
         <v>45881</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -44857,7 +44857,7 @@
         <v>44865</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -44930,7 +44930,7 @@
         <v>44887</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -45003,7 +45003,7 @@
         <v>44887</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -45076,7 +45076,7 @@
         <v>45740</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -45154,7 +45154,7 @@
         <v>44637</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -45227,7 +45227,7 @@
         <v>46308</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -45305,7 +45305,7 @@
         <v>46308</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -45383,7 +45383,7 @@
         <v>45883</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -45461,7 +45461,7 @@
         <v>44550</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -45534,7 +45534,7 @@
         <v>45642</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -45612,7 +45612,7 @@
         <v>45086</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -45685,7 +45685,7 @@
         <v>45706</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -45758,7 +45758,7 @@
         <v>46160</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -45831,7 +45831,7 @@
         <v>45692</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -45909,7 +45909,7 @@
         <v>46308</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -45982,7 +45982,7 @@
         <v>46308</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -46055,7 +46055,7 @@
         <v>45740</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -46128,7 +46128,7 @@
         <v>46308</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -46201,7 +46201,7 @@
         <v>45622</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -46274,7 +46274,7 @@
         <v>46308</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -46347,7 +46347,7 @@
         <v>46307</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -46420,7 +46420,7 @@
         <v>46308</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -46493,7 +46493,7 @@
         <v>46308</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -46566,7 +46566,7 @@
         <v>44966</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -46639,7 +46639,7 @@
         <v>45915</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -46717,7 +46717,7 @@
         <v>45706</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -46790,7 +46790,7 @@
         <v>45853</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -46863,7 +46863,7 @@
         <v>45783</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -46941,7 +46941,7 @@
         <v>46134</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -47014,7 +47014,7 @@
         <v>44964</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -47092,7 +47092,7 @@
         <v>44897</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -47170,7 +47170,7 @@
         <v>46269</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -47243,7 +47243,7 @@
         <v>45700</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -47321,7 +47321,7 @@
         <v>46269</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -47394,7 +47394,7 @@
         <v>44966</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -47467,7 +47467,7 @@
         <v>46269</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -47540,7 +47540,7 @@
         <v>45554</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -47613,7 +47613,7 @@
         <v>45516</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -47686,7 +47686,7 @@
         <v>46269</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -47759,7 +47759,7 @@
         <v>46269</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -47832,7 +47832,7 @@
         <v>44677</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -47905,7 +47905,7 @@
         <v>46314</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -47983,7 +47983,7 @@
         <v>46314</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -48061,7 +48061,7 @@
         <v>46316</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -48139,7 +48139,7 @@
         <v>44813</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -48217,7 +48217,7 @@
         <v>44817</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -48295,7 +48295,7 @@
         <v>45002</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -48373,7 +48373,7 @@
         <v>44981</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -48451,7 +48451,7 @@
         <v>44981</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -48529,7 +48529,7 @@
         <v>44995</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -48607,7 +48607,7 @@
         <v>45560</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -48685,7 +48685,7 @@
         <v>45719</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -48763,7 +48763,7 @@
         <v>45013</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -48841,7 +48841,7 @@
         <v>44973</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -48919,7 +48919,7 @@
         <v>44844</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -48997,7 +48997,7 @@
         <v>44922</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -49075,7 +49075,7 @@
         <v>44946</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -49153,7 +49153,7 @@
         <v>46316</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -49231,7 +49231,7 @@
         <v>45554</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -49304,7 +49304,7 @@
         <v>46316</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -49382,7 +49382,7 @@
         <v>46316</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -49460,7 +49460,7 @@
         <v>45832</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -49533,7 +49533,7 @@
         <v>46315</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -49606,7 +49606,7 @@
         <v>46315</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -49679,7 +49679,7 @@
         <v>44755</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -49757,7 +49757,7 @@
         <v>44966</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -49835,7 +49835,7 @@
         <v>44995</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -49913,7 +49913,7 @@
         <v>45013</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -49991,7 +49991,7 @@
         <v>46315</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -50064,7 +50064,7 @@
         <v>44922</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -50142,7 +50142,7 @@
         <v>46315</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -50215,7 +50215,7 @@
         <v>46315</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -50288,7 +50288,7 @@
         <v>45076</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -50366,7 +50366,7 @@
         <v>44946</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -50444,7 +50444,7 @@
         <v>45071</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -50522,7 +50522,7 @@
         <v>44804</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -50600,7 +50600,7 @@
         <v>45008</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -50678,7 +50678,7 @@
         <v>45566</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -50756,7 +50756,7 @@
         <v>45555</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -50834,7 +50834,7 @@
         <v>45678</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -50912,7 +50912,7 @@
         <v>44903</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -50990,7 +50990,7 @@
         <v>45428</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -51063,7 +51063,7 @@
         <v>45229</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -51141,7 +51141,7 @@
         <v>46064</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -51219,7 +51219,7 @@
         <v>45343</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -51297,7 +51297,7 @@
         <v>45441</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -51370,7 +51370,7 @@
         <v>45441</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -51443,7 +51443,7 @@
         <v>44964</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -51521,7 +51521,7 @@
         <v>45179</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -51594,7 +51594,7 @@
         <v>45179</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -51667,7 +51667,7 @@
         <v>46141</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -51740,7 +51740,7 @@
         <v>44734</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -51813,7 +51813,7 @@
         <v>44732</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -51891,7 +51891,7 @@
         <v>44918</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -51969,7 +51969,7 @@
         <v>45705</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -52042,7 +52042,7 @@
         <v>45006</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -52115,7 +52115,7 @@
         <v>44614</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -52188,7 +52188,7 @@
         <v>45426</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -52261,7 +52261,7 @@
         <v>44679</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -52339,7 +52339,7 @@
         <v>44725</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -52412,7 +52412,7 @@
         <v>44653</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -52485,7 +52485,7 @@
         <v>45980</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -52558,7 +52558,7 @@
         <v>45107</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -52631,7 +52631,7 @@
         <v>45415</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -52704,7 +52704,7 @@
         <v>45184</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -52777,7 +52777,7 @@
         <v>45070</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -52855,7 +52855,7 @@
         <v>45600</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -52928,7 +52928,7 @@
         <v>45279</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -53006,7 +53006,7 @@
         <v>45421</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -53084,7 +53084,7 @@
         <v>45845</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -53162,7 +53162,7 @@
         <v>45344</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -53235,7 +53235,7 @@
         <v>45257</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -53313,7 +53313,7 @@
         <v>45301</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -53391,7 +53391,7 @@
         <v>45095</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -53464,7 +53464,7 @@
         <v>45086</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -53537,7 +53537,7 @@
         <v>45166</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -53615,7 +53615,7 @@
         <v>45075</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -53688,7 +53688,7 @@
         <v>45639</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -53766,7 +53766,7 @@
         <v>45665</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -53839,7 +53839,7 @@
         <v>45009</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -53917,7 +53917,7 @@
         <v>45516</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -53995,7 +53995,7 @@
         <v>45142</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -54068,7 +54068,7 @@
         <v>45616</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -54141,7 +54141,7 @@
         <v>45616</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -54214,7 +54214,7 @@
         <v>45593</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -54292,7 +54292,7 @@
         <v>45646</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -54365,7 +54365,7 @@
         <v>44774</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -54443,7 +54443,7 @@
         <v>45095</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -54521,7 +54521,7 @@
         <v>45095</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -54594,7 +54594,7 @@
         <v>45709</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -54672,7 +54672,7 @@
         <v>45728</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -54750,7 +54750,7 @@
         <v>45615</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -54828,7 +54828,7 @@
         <v>45530</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -54901,7 +54901,7 @@
         <v>45713</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -54979,7 +54979,7 @@
         <v>45744</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -55057,7 +55057,7 @@
         <v>45147</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -55130,7 +55130,7 @@
         <v>44759</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -55203,7 +55203,7 @@
         <v>44840</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -55276,7 +55276,7 @@
         <v>45692</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -55354,7 +55354,7 @@
         <v>45688</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -55432,7 +55432,7 @@
         <v>44820</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -55505,7 +55505,7 @@
         <v>45041</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -55583,7 +55583,7 @@
         <v>45082</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -55661,7 +55661,7 @@
         <v>45688</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -55739,7 +55739,7 @@
         <v>44834</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -55817,7 +55817,7 @@
         <v>44862</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -55895,7 +55895,7 @@
         <v>44973</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -55973,7 +55973,7 @@
         <v>44880</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -56051,7 +56051,7 @@
         <v>45710</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -56124,7 +56124,7 @@
         <v>45191</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -56197,7 +56197,7 @@
         <v>45770</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -56270,7 +56270,7 @@
         <v>45236</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -56348,7 +56348,7 @@
         <v>45236</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -56426,7 +56426,7 @@
         <v>44886</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -56499,7 +56499,7 @@
         <v>45070</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -56577,7 +56577,7 @@
         <v>45566</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -56655,7 +56655,7 @@
         <v>45042</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -56728,7 +56728,7 @@
         <v>45728</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -56806,7 +56806,7 @@
         <v>44876</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -56879,7 +56879,7 @@
         <v>44642</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -56952,7 +56952,7 @@
         <v>44536</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -57025,7 +57025,7 @@
         <v>45735</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -57103,7 +57103,7 @@
         <v>45237</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -57181,7 +57181,7 @@
         <v>45735</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -57259,7 +57259,7 @@
         <v>44944</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -57337,7 +57337,7 @@
         <v>44595</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -57415,7 +57415,7 @@
         <v>45233</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -57488,7 +57488,7 @@
         <v>44564</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -57561,7 +57561,7 @@
         <v>45566</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -57639,7 +57639,7 @@
         <v>45095</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -57712,7 +57712,7 @@
         <v>45082</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -57790,7 +57790,7 @@
         <v>45082</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -57868,7 +57868,7 @@
         <v>45086</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -57941,7 +57941,7 @@
         <v>44589</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -58014,7 +58014,7 @@
         <v>45407</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -58087,7 +58087,7 @@
         <v>44900</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -58160,7 +58160,7 @@
         <v>45357</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -58233,7 +58233,7 @@
         <v>44887</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -58306,7 +58306,7 @@
         <v>45259</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -58379,7 +58379,7 @@
         <v>45275</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -58452,7 +58452,7 @@
         <v>45463</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -58525,7 +58525,7 @@
         <v>45677</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -58603,7 +58603,7 @@
         <v>45103</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -58676,7 +58676,7 @@
         <v>45113</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -58749,7 +58749,7 @@
         <v>44993</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -58822,7 +58822,7 @@
         <v>45293</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -58895,7 +58895,7 @@
         <v>45391</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -58968,7 +58968,7 @@
         <v>45250</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -59046,7 +59046,7 @@
         <v>44949</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -59119,7 +59119,7 @@
         <v>44973</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -59197,7 +59197,7 @@
         <v>45103</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -59270,7 +59270,7 @@
         <v>45341</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -59348,7 +59348,7 @@
         <v>45293</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -59421,7 +59421,7 @@
         <v>45391</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -59494,7 +59494,7 @@
         <v>44678</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -59572,7 +59572,7 @@
         <v>45002</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -59650,7 +59650,7 @@
         <v>45078</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -59723,7 +59723,7 @@
         <v>44993</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -59796,7 +59796,7 @@
         <v>45133</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -59869,7 +59869,7 @@
         <v>44551</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -59942,7 +59942,7 @@
         <v>45447</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -60020,7 +60020,7 @@
         <v>45167</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -60098,7 +60098,7 @@
         <v>44937</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -60171,7 +60171,7 @@
         <v>45314</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -60244,7 +60244,7 @@
         <v>45041</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -60317,7 +60317,7 @@
         <v>45063</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -60390,7 +60390,7 @@
         <v>45113</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -60463,7 +60463,7 @@
         <v>45601</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -60536,7 +60536,7 @@
         <v>45040</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -60609,7 +60609,7 @@
         <v>45020</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -60682,7 +60682,7 @@
         <v>45593</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -60760,7 +60760,7 @@
         <v>45068</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -60838,7 +60838,7 @@
         <v>45149</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -60911,7 +60911,7 @@
         <v>45617</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -60989,7 +60989,7 @@
         <v>45302</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -61067,7 +61067,7 @@
         <v>44622</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -61140,7 +61140,7 @@
         <v>44564</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -61213,7 +61213,7 @@
         <v>44958</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -61286,7 +61286,7 @@
         <v>45095</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -61359,7 +61359,7 @@
         <v>44516</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -61432,7 +61432,7 @@
         <v>45040</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -61510,7 +61510,7 @@
         <v>45615</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -61588,7 +61588,7 @@
         <v>45609</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -61666,7 +61666,7 @@
         <v>45554</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -61739,7 +61739,7 @@
         <v>45551</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -61812,7 +61812,7 @@
         <v>44622</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -61885,7 +61885,7 @@
         <v>45077</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -61963,7 +61963,7 @@
         <v>45206</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -62036,7 +62036,7 @@
         <v>45084</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -62109,7 +62109,7 @@
         <v>45456</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -62187,7 +62187,7 @@
         <v>45174</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -62265,7 +62265,7 @@
         <v>45645</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -62343,7 +62343,7 @@
         <v>44795</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -62421,7 +62421,7 @@
         <v>45715</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -62494,7 +62494,7 @@
         <v>44634</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -62572,7 +62572,7 @@
         <v>45762</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -62645,7 +62645,7 @@
         <v>45147</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -62718,7 +62718,7 @@
         <v>45209</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -62791,7 +62791,7 @@
         <v>45209</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -62864,7 +62864,7 @@
         <v>45243</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -62942,7 +62942,7 @@
         <v>45660</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -63020,7 +63020,7 @@
         <v>45103</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -63093,7 +63093,7 @@
         <v>45253</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -63171,7 +63171,7 @@
         <v>44664</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -63249,7 +63249,7 @@
         <v>45274</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -63322,7 +63322,7 @@
         <v>44767</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -63395,7 +63395,7 @@
         <v>45720</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -63473,7 +63473,7 @@
         <v>44735</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -63546,7 +63546,7 @@
         <v>44729</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -63619,7 +63619,7 @@
         <v>45149</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -63692,7 +63692,7 @@
         <v>45257</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -63770,7 +63770,7 @@
         <v>45314</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -63843,7 +63843,7 @@
         <v>44672</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -63916,7 +63916,7 @@
         <v>45308</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -63989,7 +63989,7 @@
         <v>44823</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -64062,7 +64062,7 @@
         <v>45623</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -64135,7 +64135,7 @@
         <v>44833</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -64213,7 +64213,7 @@
         <v>45468</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -64291,7 +64291,7 @@
         <v>45379</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
@@ -64364,7 +64364,7 @@
         <v>45309</v>
       </c>
       <c r="E802" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -64442,7 +64442,7 @@
         <v>45309</v>
       </c>
       <c r="E803" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
@@ -64515,7 +64515,7 @@
         <v>45309</v>
       </c>
       <c r="E804" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
@@ -64588,7 +64588,7 @@
         <v>45257</v>
       </c>
       <c r="E805" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>
@@ -64661,7 +64661,7 @@
         <v>45302</v>
       </c>
       <c r="E806" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F806" t="inlineStr">
         <is>
@@ -64739,7 +64739,7 @@
         <v>44966</v>
       </c>
       <c r="E807" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F807" t="inlineStr">
         <is>
@@ -64812,7 +64812,7 @@
         <v>44767</v>
       </c>
       <c r="E808" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F808" t="inlineStr">
         <is>
@@ -64885,7 +64885,7 @@
         <v>45040</v>
       </c>
       <c r="E809" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F809" t="inlineStr">
         <is>
@@ -64958,7 +64958,7 @@
         <v>44595</v>
       </c>
       <c r="E810" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F810" t="inlineStr">
         <is>
@@ -65031,7 +65031,7 @@
         <v>45009</v>
       </c>
       <c r="E811" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F811" t="inlineStr">
         <is>
@@ -65104,7 +65104,7 @@
         <v>45084</v>
       </c>
       <c r="E812" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F812" t="inlineStr">
         <is>
@@ -65177,7 +65177,7 @@
         <v>44782</v>
       </c>
       <c r="E813" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F813" t="inlineStr">
         <is>
@@ -65250,7 +65250,7 @@
         <v>44714</v>
       </c>
       <c r="E814" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F814" t="inlineStr">
         <is>
@@ -65323,7 +65323,7 @@
         <v>45299</v>
       </c>
       <c r="E815" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F815" t="inlineStr">
         <is>
@@ -65396,7 +65396,7 @@
         <v>44749</v>
       </c>
       <c r="E816" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F816" t="inlineStr">
         <is>
@@ -65469,7 +65469,7 @@
         <v>44861</v>
       </c>
       <c r="E817" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F817" t="inlineStr">
         <is>
@@ -65547,7 +65547,7 @@
         <v>44987</v>
       </c>
       <c r="E818" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F818" t="inlineStr">
         <is>
@@ -65620,7 +65620,7 @@
         <v>44879</v>
       </c>
       <c r="E819" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F819" t="inlineStr">
         <is>
@@ -65693,7 +65693,7 @@
         <v>44871</v>
       </c>
       <c r="E820" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F820" t="inlineStr">
         <is>
@@ -65766,7 +65766,7 @@
         <v>44526</v>
       </c>
       <c r="E821" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F821" t="inlineStr">
         <is>
@@ -65839,7 +65839,7 @@
         <v>44914</v>
       </c>
       <c r="E822" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F822" t="inlineStr">
         <is>
@@ -65917,7 +65917,7 @@
         <v>45548</v>
       </c>
       <c r="E823" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F823" t="inlineStr">
         <is>
@@ -65990,7 +65990,7 @@
         <v>45763</v>
       </c>
       <c r="E824" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F824" t="inlineStr">
         <is>
@@ -66063,7 +66063,7 @@
         <v>44503</v>
       </c>
       <c r="E825" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F825" t="inlineStr">
         <is>
@@ -66136,7 +66136,7 @@
         <v>45636</v>
       </c>
       <c r="E826" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F826" t="inlineStr">
         <is>
@@ -66209,7 +66209,7 @@
         <v>44607</v>
       </c>
       <c r="E827" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F827" t="inlineStr">
         <is>
@@ -66282,7 +66282,7 @@
         <v>44953</v>
       </c>
       <c r="E828" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F828" t="inlineStr">
         <is>
@@ -66360,7 +66360,7 @@
         <v>44817</v>
       </c>
       <c r="E829" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F829" t="inlineStr">
         <is>
@@ -66433,7 +66433,7 @@
         <v>45523</v>
       </c>
       <c r="E830" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F830" t="inlineStr">
         <is>
@@ -66511,7 +66511,7 @@
         <v>44867</v>
       </c>
       <c r="E831" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F831" t="inlineStr">
         <is>
@@ -66584,7 +66584,7 @@
         <v>44732</v>
       </c>
       <c r="E832" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F832" t="inlineStr">
         <is>
@@ -66662,7 +66662,7 @@
         <v>44949</v>
       </c>
       <c r="E833" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F833" t="inlineStr">
         <is>
@@ -66735,7 +66735,7 @@
         <v>44949</v>
       </c>
       <c r="E834" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F834" t="inlineStr">
         <is>
@@ -66808,7 +66808,7 @@
         <v>44949</v>
       </c>
       <c r="E835" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F835" t="inlineStr">
         <is>
@@ -66881,7 +66881,7 @@
         <v>44960</v>
       </c>
       <c r="E836" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F836" t="inlineStr">
         <is>
@@ -66959,7 +66959,7 @@
         <v>44966</v>
       </c>
       <c r="E837" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F837" t="inlineStr">
         <is>
@@ -67032,7 +67032,7 @@
         <v>45644</v>
       </c>
       <c r="E838" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F838" t="inlineStr">
         <is>
@@ -67105,7 +67105,7 @@
         <v>45428</v>
       </c>
       <c r="E839" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F839" t="inlineStr">
         <is>
@@ -67178,7 +67178,7 @@
         <v>45429</v>
       </c>
       <c r="E840" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F840" t="inlineStr">
         <is>
@@ -67251,7 +67251,7 @@
         <v>45250</v>
       </c>
       <c r="E841" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F841" t="inlineStr">
         <is>
@@ -67329,7 +67329,7 @@
         <v>46188</v>
       </c>
       <c r="E842" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F842" t="inlineStr">
         <is>
@@ -67407,7 +67407,7 @@
         <v>46258</v>
       </c>
       <c r="E843" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F843" t="inlineStr">
         <is>
